--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -49506,10 +49506,10 @@
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.510675727847615</v>
+        <v>-4.5104996601223</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.691073257259139</v>
+        <v>2.691143684349265</v>
       </c>
       <c r="F2085" t="n">
         <v>1.204475799584464</v>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.6%</t>
+          <t>45.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.68</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.2%</t>
+          <t>87.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.4%</t>
+          <t>-76.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.1%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.2%</t>
+          <t>-73.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>420.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-612.6%</t>
+          <t>-625.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.62</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.6%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-107.1%</t>
+          <t>-112.3%</t>
         </is>
       </c>
     </row>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.1%</t>
+          <t>-324.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.5%</t>
+          <t>-103.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>112.9%</t>
+          <t>113.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>103.1%</t>
+          <t>104.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.1%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>75.8%</t>
+          <t>76.1%</t>
         </is>
       </c>
     </row>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.26580459461942</v>
+        <v>-5.3908391606028</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7592765892357378</v>
+        <v>0.7092627628423855</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.089912502151988</v>
+        <v>-5.214947068135368</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8332325497433595</v>
+        <v>0.7832187233500072</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.918466039129524</v>
+        <v>-5.043500605112905</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9151386410068985</v>
+        <v>0.8651248146135462</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838443752020403</v>
+        <v>-4.963478318003784</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9461680334668439</v>
+        <v>0.8961542070734918</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774808009786469</v>
+        <v>-4.899842575769849</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.976317131414735</v>
+        <v>0.9263033050213827</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.681110691570074</v>
+        <v>-4.806145257553454</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9949903174850887</v>
+        <v>0.9449764910917364</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.691613314635362</v>
+        <v>-4.816647880618743</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9925323448838506</v>
+        <v>0.9425185184904983</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.579127053966488</v>
+        <v>-4.704161619949868</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145616298622</v>
+        <v>0.9914423365928684</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.561413367088623</v>
+        <v>-4.686447933072003</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.049220221654707</v>
+        <v>0.9992063952613544</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437939095775604</v>
+        <v>-4.562973661758985</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.095608001399907</v>
+        <v>1.045594175006555</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217918297738594</v>
+        <v>-4.342952863721974</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.185195357625326</v>
+        <v>1.135181531231974</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085050608675316</v>
+        <v>-4.210085174658697</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.25423661605246</v>
+        <v>1.204222789659108</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964877525310817</v>
+        <v>-4.089912091294198</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.303451693838561</v>
+        <v>1.253437867445209</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.82962416398084</v>
+        <v>-3.954658729964221</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.367641140931992</v>
+        <v>1.31762731453864</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889498991338533</v>
+        <v>-4.014533557321913</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.329728701390341</v>
+        <v>1.279714874996989</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769678760427695</v>
+        <v>-3.894713326411076</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.392945962988885</v>
+        <v>1.342932136595532</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772148466889501</v>
+        <v>-3.897183032872882</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.299602279726604</v>
+        <v>1.249588453333252</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
@@ -46079,10 +46079,10 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840518653213511</v>
+        <v>-3.965553219196892</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191516066682301</v>
+        <v>1.141502240288949</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
@@ -46102,10 +46102,10 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.952390932839662</v>
+        <v>-4.077425498823042</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.137203863463732</v>
+        <v>1.08719003707038</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
@@ -46125,10 +46125,10 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.007911008732251</v>
+        <v>-4.132945574715632</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.252026669798899</v>
+        <v>1.202012843405547</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
@@ -46148,10 +46148,10 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.832436748939782</v>
+        <v>-3.957471314923163</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.326783605707674</v>
+        <v>1.276769779314322</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
@@ -46171,10 +46171,10 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.824512374354868</v>
+        <v>-3.949546940338248</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.305695384302847</v>
+        <v>1.255681557909495</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.818234171785019</v>
+        <v>-3.943268737768399</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.236744978732236</v>
+        <v>1.186731152338884</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
@@ -46217,10 +46217,10 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.758381552581296</v>
+        <v>-3.883416118564676</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.270858412845858</v>
+        <v>1.220844586452506</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.672138089554918</v>
+        <v>-3.797172655538299</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.300302068630269</v>
+        <v>1.250288242236917</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.717444908953898</v>
+        <v>-3.842479474937279</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.273955116315203</v>
+        <v>1.223941289921851</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7464780136562</v>
+        <v>-3.87151257963958</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.262893747467384</v>
+        <v>1.212879921074032</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.653667532205341</v>
+        <v>-3.778702098188721</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.229290631939093</v>
+        <v>1.179276805545741</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.698057001534768</v>
+        <v>-3.823091567518149</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.213408320131923</v>
+        <v>1.163394493738571</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.677553307649271</v>
+        <v>-3.802587873632651</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.216685506197845</v>
+        <v>1.166671679804493</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.717477402231843</v>
+        <v>-3.842511968215224</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.206207164195483</v>
+        <v>1.156193337802131</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.749639770635983</v>
+        <v>-3.870292366116577</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.204839418602366</v>
+        <v>1.156578380410129</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7661187175398151</v>
+        <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.164722981694396</v>
+        <v>3.167352163996068</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.868020443366121</v>
+        <v>-3.988673038846715</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9958428695109642</v>
+        <v>0.9475818313187268</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.962747990404464</v>
+        <v>2.965377172706136</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.976634521809452</v>
+        <v>-4.097287117290046</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.072546898852837</v>
+        <v>1.0242858606606</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.082897651123669</v>
+        <v>3.085526833425341</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.941225483561309</v>
+        <v>-4.061878079041903</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.101223540254418</v>
+        <v>1.05296250206218</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.097410677225992</v>
+        <v>3.100039859527664</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.902841821003158</v>
+        <v>-4.023494416483752</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.113996446620047</v>
+        <v>1.065735408427809</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7372845279469901</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.117860316103251</v>
+        <v>3.120489498404924</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.725725490967992</v>
+        <v>-3.846378086448586</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.181572007479415</v>
+        <v>1.133310969287178</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7372845279469901</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.114589344948554</v>
+        <v>3.117218527250226</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.770817735801538</v>
+        <v>-3.891470331282131</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.16421850130791</v>
+        <v>1.115957463115673</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6753884847776003</v>
+        <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.078135110808833</v>
+        <v>3.080764293110505</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.59144231456277</v>
+        <v>-3.712094910043364</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.229755645109831</v>
+        <v>1.181494606917594</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.832165242948319</v>
+        <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.165988141017678</v>
+        <v>3.16861732331935</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.636456528083376</v>
+        <v>-3.75710912356397</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.192557415033179</v>
+        <v>1.144296376840941</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8018163476337143</v>
+        <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.128586259160505</v>
+        <v>3.131215441462177</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.903461038355812</v>
+        <v>-4.024113633836405</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.09144717326315</v>
+        <v>1.043186135070913</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6074533095907657</v>
+        <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.017659998673682</v>
+        <v>3.020289180975354</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.004658819792985</v>
+        <v>-4.125311415273578</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.050171982584783</v>
+        <v>1.001910944392545</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5390444960454466</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.975818632442992</v>
+        <v>2.978447814744664</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.998147853178672</v>
+        <v>-4.118800448659266</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.050376330784824</v>
+        <v>1.002115292592587</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5390444960454466</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.973418593997309</v>
+        <v>2.976047776298981</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.979109725471375</v>
+        <v>-4.099762320951968</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.054516301075988</v>
+        <v>1.006255262883751</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.480860884714252</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.935033146406837</v>
+        <v>2.937662328708509</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.031625527746195</v>
+        <v>-4.152278123226789</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.15280438180025</v>
+        <v>1.104543343608013</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.480860884714252</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.054327548041027</v>
+        <v>3.056956730342699</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.035033839180775</v>
+        <v>-4.155686434661368</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.152274386212552</v>
+        <v>1.104013348020314</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5133774537236294</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.074670818432787</v>
+        <v>3.077300000734459</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.99455084725843</v>
+        <v>-4.115203442739023</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.174476113378416</v>
+        <v>1.126215075186179</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5133774537236294</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.080679348829713</v>
+        <v>3.083308531131385</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.846807877023428</v>
+        <v>-3.967460472504021</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.131523522749616</v>
+        <v>1.083262484557379</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6811848109585126</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.079313984447842</v>
+        <v>3.081943166749515</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.930629098298126</v>
+        <v>-4.051281693778719</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.100788655771218</v>
+        <v>1.052527617578981</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6811848109585126</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.082107605979323</v>
+        <v>3.084736788280996</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.924476392245342</v>
+        <v>-4.045128987725935</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.10391208658399</v>
+        <v>1.055651048391753</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6873375170112969</v>
+        <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.086461578002652</v>
+        <v>3.089090760304325</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.941285690395843</v>
+        <v>-4.061938285876437</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.0962688440639</v>
+        <v>1.048007805871662</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6705282188607953</v>
+        <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.075456475852462</v>
+        <v>3.078085658154134</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.878987691619721</v>
+        <v>-3.999640287100315</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.187523597371169</v>
+        <v>1.139262559178932</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7158224831352373</v>
+        <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.168968588213948</v>
+        <v>3.17159777051562</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.677197493954564</v>
+        <v>-3.797850089435157</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.070531678151359</v>
+        <v>1.022270639959122</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9138406753043917</v>
+        <v>0.9182226458071785</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.090071505229568</v>
+        <v>3.09270068753124</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.728084206640758</v>
+        <v>-3.848736802121352</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.120467225399057</v>
+        <v>1.072206187206819</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8629539626181972</v>
+        <v>0.867335933120984</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.129829709940026</v>
+        <v>3.132458892241698</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.641473463990951</v>
+        <v>-3.762126059471544</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.169739258575023</v>
+        <v>1.121478220382786</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9415796938233555</v>
+        <v>0.9459616643261423</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.191632884779165</v>
+        <v>3.194262067080837</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.701682761996235</v>
+        <v>-3.822335357476829</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.144191520197581</v>
+        <v>1.095930482005344</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.881370395818071</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.154043286800666</v>
+        <v>3.156672469102338</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.652496113311884</v>
+        <v>-3.773148708792478</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.16235779771125</v>
+        <v>1.114096759519013</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.881370395818071</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.152534904840594</v>
+        <v>3.155164087142266</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.608122981673315</v>
+        <v>-3.728775577153909</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.179969917802114</v>
+        <v>1.131708879609877</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9257435274566396</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.179021651259172</v>
+        <v>3.181650833560844</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.6306033325322</v>
+        <v>-3.751255928012794</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.165371571597151</v>
+        <v>1.117110533404913</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9257435274566396</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.173415445397762</v>
+        <v>3.176044627699434</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.582947601971145</v>
+        <v>-3.703600197451738</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.190815620849377</v>
+        <v>1.14255458265714</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9733992580176952</v>
+        <v>0.977781228520482</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.2083906407622</v>
+        <v>3.211019823063872</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.48242944347239</v>
+        <v>-3.603082038952984</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.235915257623604</v>
+        <v>1.187654219431367</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.07391741651645</v>
+        <v>1.078299387019237</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.273593909236177</v>
+        <v>3.27622309153785</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.466524114040038</v>
+        <v>-3.587176709520631</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.229032061872417</v>
+        <v>1.18077102368018</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9948047558072108</v>
+        <v>0.9991867263099976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.212880985286506</v>
+        <v>3.215510167588179</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.42168571243164</v>
+        <v>-3.542338307912233</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.251065125126405</v>
+        <v>1.202804086934168</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9993481887520803</v>
+        <v>1.003730159254867</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.219704747664057</v>
+        <v>3.222333929965729</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.441184168673648</v>
+        <v>-3.561836764154241</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.24742668226068</v>
+        <v>1.199165644068442</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.951263547472176</v>
+        <v>0.9556455179749628</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.195014902527192</v>
+        <v>3.197644084828864</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.396981331587747</v>
+        <v>-3.517633927068341</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.270987419622877</v>
+        <v>1.22272638143064</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9954663845580765</v>
+        <v>0.9998483550608632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.22741620730657</v>
+        <v>3.230045389608242</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.404540997424794</v>
+        <v>-3.525193592905388</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.266373553757306</v>
+        <v>1.218112515565068</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.050269788567896</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.258708250181709</v>
+        <v>3.261337432483381</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.246249579885522</v>
+        <v>-3.366902175366115</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.380937885956055</v>
+        <v>1.332676847763817</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.050269788567896</v>
+        <v>1.054651759070683</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.309956015364748</v>
+        <v>3.31258519766642</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.038607576251046</v>
+        <v>-3.159260171731639</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.462435392004098</v>
+        <v>1.414174353811861</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.257911792202372</v>
+        <v>1.262293762705159</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.432981922139687</v>
+        <v>3.435611104441359</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.987575483528518</v>
+        <v>-3.108228079009111</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.477796457331379</v>
+        <v>1.429535419139142</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.3089438849249</v>
+        <v>1.313325855427687</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.458549406011474</v>
+        <v>3.461178588313146</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.922351302401312</v>
+        <v>-3.043003897881905</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.521073533874967</v>
+        <v>1.472812495682729</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.374168066052105</v>
+        <v>1.378550036554892</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.514871318780502</v>
+        <v>3.517500501082174</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.884924282330178</v>
+        <v>-3.005576877810772</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.532005314202701</v>
+        <v>1.483744276010463</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.379419604081287</v>
+        <v>1.383801574584074</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.513983213897292</v>
+        <v>3.516612396198964</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.905035938364886</v>
+        <v>-3.02568853384548</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.525217444120057</v>
+        <v>1.47695640592782</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.390446949078706</v>
+        <v>1.394828919581493</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.521856413226983</v>
+        <v>3.524485595528656</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.876622675265003</v>
+        <v>-2.997275270745596</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.697140520381222</v>
+        <v>1.648879482188984</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.331471386332278</v>
+        <v>1.335853356835065</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.647028846600337</v>
+        <v>3.649658028902009</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.80184041423999</v>
+        <v>-2.922493009720584</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.847166334009044</v>
+        <v>1.798905295816807</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.40625364735729</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.812011112433161</v>
+        <v>3.814640294734834</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.775756329976182</v>
+        <v>-2.896408925456776</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.849307943728426</v>
+        <v>1.801046905536189</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.40625364735729</v>
+        <v>1.410635617860077</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80371908844702</v>
+        <v>3.806348270748693</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.687878416867062</v>
+        <v>-2.808531012347655</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.882652304555854</v>
+        <v>1.834391266363616</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.522179289780641</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.871467669484811</v>
+        <v>3.874096851786483</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.678985955473778</v>
+        <v>-2.799638550954372</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.903763694839959</v>
+        <v>1.855502656647721</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.522179289780641</v>
+        <v>1.526561260283428</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.889022075211602</v>
+        <v>3.891651257513274</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.847462072443656</v>
+        <v>-2.96811466792425</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.828228295456591</v>
+        <v>1.779967257264354</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.49423145406406</v>
+        <v>1.498613424566847</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.864108421186238</v>
+        <v>3.86673760348791</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.401205879814216</v>
+        <v>-2.52185847529481</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.988000469696229</v>
+        <v>1.939739431503992</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.399512784394428</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.78854691657232</v>
+        <v>3.791176098873992</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.378484776131064</v>
+        <v>-2.499137371611657</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.987752933666395</v>
+        <v>1.939491895474157</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.399512784394428</v>
+        <v>1.403894754897215</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.779210939069224</v>
+        <v>3.781840121370896</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.507686589425106</v>
+        <v>-2.6283391849057</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.094978334199947</v>
+        <v>2.046717296007709</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.270310971100385</v>
+        <v>1.274692941603172</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.860595976943968</v>
+        <v>3.86322515924564</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.533560987899132</v>
+        <v>-2.654213583379725</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.121706397303983</v>
+        <v>2.073445359111746</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.315222579812127</v>
+        <v>1.319604550314914</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.92462076466466</v>
+        <v>3.927249946966332</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.526506297683958</v>
+        <v>-2.647158893164552</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.121203629379598</v>
+        <v>2.07294259118736</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.3222772700273</v>
+        <v>1.326659240530087</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.925528934783308</v>
+        <v>3.928158117084981</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.49955507335747</v>
+        <v>-2.620207668838064</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.141990272754934</v>
+        <v>2.093729234562697</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.33715761605502</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.944463296044682</v>
+        <v>3.947092478346354</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.521099301188257</v>
+        <v>-2.641751896668851</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.317475713767579</v>
+        <v>2.269214675575342</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.33715761605502</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.128566428189641</v>
+        <v>4.131195610491313</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.543507418993129</v>
+        <v>-2.664160014473723</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.300629161548624</v>
+        <v>2.252368123356386</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.33715761605502</v>
+        <v>1.341539586557807</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.120683123092634</v>
+        <v>4.123312305394307</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.57173165457073</v>
+        <v>-2.692384250051323</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.291393466867221</v>
+        <v>2.243132428674984</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.355134368506328</v>
+        <v>1.359516339009115</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.133523174113058</v>
+        <v>4.13615235641473</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.58117258045926</v>
+        <v>-2.701825175939853</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.343870814233656</v>
+        <v>2.295609776041418</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.47756148604972</v>
+        <v>1.481943456552507</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.263233162360939</v>
+        <v>4.265862344662612</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.670049211627734</v>
+        <v>-2.790701807108327</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.311211256311568</v>
+        <v>2.26295021811933</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.388684854881246</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.212798278205156</v>
+        <v>4.215427460506828</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.74637918922864</v>
+        <v>-2.867031784709233</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.27879107816498</v>
+        <v>2.230530039972743</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.388684854881246</v>
+        <v>1.393066825384033</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.210910091098931</v>
+        <v>4.213539273400603</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.840043133906181</v>
+        <v>-2.960695729386774</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.236145729896826</v>
+        <v>2.187884691704589</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.295020910203704</v>
+        <v>1.299402880706491</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.149531953895268</v>
+        <v>4.15216113619694</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.001611559433436</v>
+        <v>-3.12226415491403</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.169952369896076</v>
+        <v>2.121691331703839</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.168237986405825</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.071896209826694</v>
+        <v>4.074525392128366</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.109912221303555</v>
+        <v>-3.230564816784149</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.139705512013947</v>
+        <v>2.09144447382171</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.168237986405825</v>
+        <v>1.172619956908612</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.084969616692612</v>
+        <v>4.087598798994284</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.1277161930243</v>
+        <v>-3.248368788504893</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.124589120108589</v>
+        <v>2.076328081916352</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.097703363500624</v>
+        <v>1.102085334003411</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.034654039732431</v>
+        <v>4.037283222034104</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.155616980133773</v>
+        <v>-3.276269575614366</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.111952846391802</v>
+        <v>2.063691808199565</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.063106439357689</v>
+        <v>1.067488409860476</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.012419926373672</v>
+        <v>4.015049108675345</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.278143082836666</v>
+        <v>-3.39879567831726</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.059706849287843</v>
+        <v>2.011445811095606</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9405803366547953</v>
+        <v>0.9449623071575823</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.935668708729135</v>
+        <v>3.938297891030807</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.508657579022255</v>
+        <v>-3.629310174502849</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.034207010404112</v>
+        <v>1.985945972211874</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7100658404692066</v>
+        <v>0.7144478109719936</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.864065970608285</v>
+        <v>3.866695152909958</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.857402664246699</v>
+        <v>-3.978055259727292</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.035020695316181</v>
+        <v>1.986759657123944</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6013178865503088</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.939128917258794</v>
+        <v>3.941758099560466</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.01138908202284</v>
+        <v>-4.132041677503433</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.042406397351365</v>
+        <v>1.994145359159127</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6013178865503088</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.008109186404433</v>
+        <v>4.010738368706106</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.960867178195174</v>
+        <v>-4.081519773675767</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.048666361002552</v>
+        <v>2.000405322810315</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6013178865503088</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.994160388524555</v>
+        <v>3.996789570826227</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.213342332202898</v>
+        <v>-4.333994927683491</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.959546788454876</v>
+        <v>1.911285750262639</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6013178865503088</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.006030877579969</v>
+        <v>4.008660059881641</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.50623808868231</v>
+        <v>-4.626890684162904</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.843599020382055</v>
+        <v>1.795337982189818</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6013178865503088</v>
+        <v>0.6056998570530958</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.007241412098912</v>
+        <v>4.009870594400584</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.692902216817118</v>
+        <v>-4.813554812297712</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.773055111355453</v>
+        <v>1.724794073163216</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5745789157257489</v>
+        <v>0.5789608862285359</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.995319771831498</v>
+        <v>3.99794895413317</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.83892290373108</v>
+        <v>-4.959575499211674</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.709724689326058</v>
+        <v>1.661463651133821</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5654958239318919</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.984947769491373</v>
+        <v>3.987576951793045</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.930636912840665</v>
+        <v>-5.051289508321259</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.835243142381268</v>
+        <v>1.78698210418903</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5654958239318919</v>
+        <v>0.5698777944346789</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.147151826190417</v>
+        <v>4.149781008492089</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.962288571900634</v>
+        <v>-5.082941167381229</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.817429116721095</v>
+        <v>1.769168078528857</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5603273666874518</v>
+        <v>0.5647093371902387</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.138897389807567</v>
+        <v>4.141526572109239</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.044223390169518</v>
+        <v>-5.164875985650112</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.794884606982032</v>
+        <v>1.746623568789794</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5503926211003716</v>
+        <v>0.5547745916031586</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.14316596002381</v>
+        <v>4.145795142325482</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.146199512417925</v>
+        <v>-5.26685210789852</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.763019796538572</v>
+        <v>1.714758758346334</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.448416498851964</v>
+        <v>0.452798469354751</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.090905925130667</v>
+        <v>4.09353510743234</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.036193228940704</v>
+        <v>-5.156845824421298</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.799175197173636</v>
+        <v>1.750914158981398</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4716210707692392</v>
+        <v>0.4760030412720262</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.096981555525208</v>
+        <v>4.099610737826881</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.893133653199778</v>
+        <v>-5.013786248680372</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.86064903819198</v>
+        <v>1.812387999999743</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4796344973592185</v>
+        <v>0.4840164678620055</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.10603962220117</v>
+        <v>4.108668804502843</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.59168692772794</v>
+        <v>-4.712339523208534</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.988488611263252</v>
+        <v>1.940227573071014</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7810812228310557</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.294168540366808</v>
+        <v>4.29679772266848</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.616277171963124</v>
+        <v>-4.736929767443718</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.979623691321889</v>
+        <v>1.931362653129651</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7810812228310557</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.295139718119519</v>
+        <v>4.297768900421191</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.565238795956604</v>
+        <v>-4.685891391437198</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.000881946104252</v>
+        <v>1.952620907912014</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7810812228310557</v>
+        <v>0.7854631933338427</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.295982622499275</v>
+        <v>4.298611804800947</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.524099501089973</v>
+        <v>-4.644752096570567</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.03637576292505</v>
+        <v>1.988114724732812</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8222205176976866</v>
+        <v>0.8266024882004736</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.339704298293398</v>
+        <v>4.34233348059507</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.427464589071333</v>
+        <v>-4.548117184551927</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.891213723856441</v>
+        <v>1.842952685664203</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9188554297163265</v>
+        <v>0.9232374002191135</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.213869241628517</v>
+        <v>4.216498423930189</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.558045323602175</v>
+        <v>-4.67869791908277</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.842483474118068</v>
+        <v>1.79422243592583</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.788274695185484</v>
+        <v>0.792656665688271</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.139022844983976</v>
+        <v>4.141652027285648</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.393548989411213</v>
+        <v>-4.514201584891808</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.892708826870535</v>
+        <v>1.844447788678297</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9527710293764459</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.222147464574635</v>
+        <v>4.224776646876307</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.316450387869341</v>
+        <v>-4.437102983349935</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.922735977923714</v>
+        <v>1.874474939731476</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9527710293764459</v>
+        <v>0.9571529998792329</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.221335175011065</v>
+        <v>4.223964357312737</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.32683558275923</v>
+        <v>-4.447488178239825</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.928450679092831</v>
+        <v>1.880189640900593</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9423858344865566</v>
+        <v>0.9467678049893435</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.224972837202204</v>
+        <v>4.227602019503876</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.345423741481455</v>
+        <v>-4.46607633696205</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.991852421380366</v>
+        <v>1.943591383188128</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9237976757643311</v>
+        <v>0.9281796462671181</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.284656947745294</v>
+        <v>4.287286130046966</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.345722288177491</v>
+        <v>-4.466374883658085</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.98860201352025</v>
+        <v>1.940340975328012</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9234991290682952</v>
+        <v>0.9278810995710822</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.281346830545971</v>
+        <v>4.283976012847643</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.244899154487063</v>
+        <v>-4.365551749967658</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.033462161935812</v>
+        <v>1.985201123743574</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9359633445526491</v>
+        <v>0.9403453150554361</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.293356254775975</v>
+        <v>4.295985437077647</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.054117793734656</v>
+        <v>-4.174770389215251</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.109903959715318</v>
+        <v>2.06164292152308</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.126744705305057</v>
+        <v>1.131126675807844</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.407954324705963</v>
+        <v>4.410583507007635</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.947154435885235</v>
+        <v>-4.067807031365829</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.132526148592683</v>
+        <v>2.084265110400445</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.185209313264858</v>
+        <v>1.189591283767645</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.42286993521944</v>
+        <v>4.425499117521112</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.891823847983473</v>
+        <v>-4.012476443464067</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.189625320365447</v>
+        <v>2.141364282173209</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.24053990116662</v>
+        <v>1.244921871669407</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.491035224572555</v>
+        <v>4.493664406874228</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.87976972107051</v>
+        <v>-4.000422316551104</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.188133539032069</v>
+        <v>2.139872500839832</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.252594028079583</v>
+        <v>1.25697599858237</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.491954268621771</v>
+        <v>4.494583450923443</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.920924840638731</v>
+        <v>-4.041577436119325</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.173552121388917</v>
+        <v>2.12529108319668</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.211438908511362</v>
+        <v>1.215820879014149</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.469141827064974</v>
+        <v>4.471771009366647</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.852876277947201</v>
+        <v>-3.973528873427795</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.213622572343412</v>
+        <v>2.165361534151174</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.279487471202892</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.522821990557775</v>
+        <v>4.525451172859447</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.084476671116702</v>
+        <v>-4.205129266597296</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.141185085249205</v>
+        <v>2.092924047056968</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.279487471202892</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.543024660731369</v>
+        <v>4.545653843033041</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.134528216645922</v>
+        <v>-4.255180812126515</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.104770703104399</v>
+        <v>2.056509664912162</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.279487471202892</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.526630896798251</v>
+        <v>4.529260079099923</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.309635049222367</v>
+        <v>-4.430287644702959</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.994979883667288</v>
+        <v>1.946718845475051</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.279487471202892</v>
+        <v>1.283869441705679</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.486882810391718</v>
+        <v>4.48951199269339</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.113534895791844</v>
+        <v>-4.234187491272436</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.080442564036437</v>
+        <v>2.0321815258442</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.475587624633415</v>
+        <v>1.479969595136202</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.611565521446972</v>
+        <v>4.614194703748644</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.96050950367856</v>
+        <v>-4.081162099159152</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.240823720454655</v>
+        <v>2.192562682262419</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.628613016746699</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.802551756287846</v>
+        <v>4.805180938589518</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.98881681755183</v>
+        <v>-4.109469413032422</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.41696701981364</v>
+        <v>2.368705981621403</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.628613016746699</v>
+        <v>1.632994987249486</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.990017981196138</v>
+        <v>4.992647163497811</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.155410042665352</v>
+        <v>-4.276062638145945</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.319732681122313</v>
+        <v>2.271471642930076</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.462019791633176</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.859464997482108</v>
+        <v>4.86209417978378</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.132374249303786</v>
+        <v>-4.253026844784379</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.332623401128657</v>
+        <v>2.28436236293642</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.462019791633176</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.863141400143825</v>
+        <v>4.865770582445498</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.103128268848089</v>
+        <v>-4.223780864328682</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.341939848434431</v>
+        <v>2.293678810242194</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.462019791633176</v>
+        <v>1.466401762135963</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.860759455267321</v>
+        <v>4.863388637568993</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.21005381672594</v>
+        <v>-4.330706412206533</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.296462868440926</v>
+        <v>2.248201830248689</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.355094243755325</v>
+        <v>1.359476214258112</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.793897365698244</v>
+        <v>4.796526547999917</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.355072375233189</v>
+        <v>-4.475724970713782</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.23988424718126</v>
+        <v>2.191623208989023</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.210075685248077</v>
+        <v>1.214457655750864</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.708315032737129</v>
+        <v>4.710944215038802</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.473414141017907</v>
+        <v>-4.594066736498499</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.292478780125126</v>
+        <v>2.244217741932889</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.220761723810967</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.814657895132616</v>
+        <v>4.817287077434289</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.524824563338615</v>
+        <v>-4.645477158819207</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.269700308322782</v>
+        <v>2.221439270130545</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.220761723810967</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.812443592258555</v>
+        <v>4.815072774560227</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.604244014546366</v>
+        <v>-4.724896610026959</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.237835655913971</v>
+        <v>2.189574617721734</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.220761723810967</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.812346720332845</v>
+        <v>4.814975902634517</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.699707012463584</v>
+        <v>-4.820359607944177</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.199644350305127</v>
+        <v>2.15138331211289</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.220761723810967</v>
+        <v>1.225143694313754</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.812340613890888</v>
+        <v>4.81496979619256</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.635331101612869</v>
+        <v>-4.755983697093462</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.223491111208024</v>
+        <v>2.175230073015787</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.285137634661682</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.849062556963928</v>
+        <v>4.8516917392656</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.690700263745063</v>
+        <v>-4.811352859225655</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.207077264102873</v>
+        <v>2.158816225910636</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.285137634661682</v>
+        <v>1.289519605164469</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.854796374711655</v>
+        <v>4.857425557013327</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.73613804357589</v>
+        <v>-4.856790639056483</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.188440515513475</v>
+        <v>2.140179477321237</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.242292643983522</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.828627743647691</v>
+        <v>4.831256925949363</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.647931209428312</v>
+        <v>-4.768583804908904</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.243597642022825</v>
+        <v>2.195336603830587</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.242292643983522</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.84850213649801</v>
+        <v>4.851131318799682</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.541896214223002</v>
+        <v>-4.662548809703595</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.269712340629676</v>
+        <v>2.221451302437439</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.242292643983522</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.832202837022738</v>
+        <v>4.83483201932441</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.358684551089907</v>
+        <v>-4.4793371465705</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.34542795534696</v>
+        <v>2.297166917154723</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.242292643983522</v>
+        <v>1.246674614486309</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.834633786486783</v>
+        <v>4.837262968788456</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.286963104076056</v>
+        <v>-4.407615699556649</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.339907720000389</v>
+        <v>2.291646681808152</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.314014090997373</v>
+        <v>1.31839606150016</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.843457840542984</v>
+        <v>4.846087022844656</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.26459007846835</v>
+        <v>-4.385242673948943</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.295772676164644</v>
+        <v>2.247511637972407</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.325269842110274</v>
+        <v>1.329651812613061</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.797127037131895</v>
+        <v>4.799756219433569</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.297606374379095</v>
+        <v>-4.418258969859687</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.467764362685701</v>
+        <v>2.419503324493464</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.255832465443523</v>
+        <v>1.26021443594631</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.9406628160172</v>
+        <v>4.943291998318872</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.286078738729486</v>
+        <v>-4.406731334210079</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.464296642773794</v>
+        <v>2.416035604581557</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.314833123644885</v>
+        <v>1.319215094147672</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.967984436766267</v>
+        <v>4.970613619067939</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.383420240071855</v>
+        <v>-4.504072835552448</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.429028154758635</v>
+        <v>2.380767116566398</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.270412941479397</v>
+        <v>1.274794911982184</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.945000439988762</v>
+        <v>4.947629622290435</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.469276269411822</v>
+        <v>-4.589928864892414</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.395936825215486</v>
+        <v>2.347675787023249</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.228036872253262</v>
+        <v>1.232418842756049</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.92082588064592</v>
+        <v>4.923455062947592</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.478113066827941</v>
+        <v>-4.598765662308534</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.37482130806954</v>
+        <v>2.326560269877303</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.220594699611911</v>
+        <v>1.224976670114698</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.898779778881611</v>
+        <v>4.901408961183283</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.569495629393399</v>
+        <v>-4.690148224873992</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.348432794088406</v>
+        <v>2.300171755896169</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.129212137046453</v>
+        <v>1.13359410754924</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.854114752387385</v>
+        <v>4.856743934689058</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.557788911406393</v>
+        <v>-4.678441506886986</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.455243739107477</v>
+        <v>2.40698270091524</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.140918855033459</v>
+        <v>1.145300825536246</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.963267041003857</v>
+        <v>4.965896223305529</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.458125407322731</v>
+        <v>-4.578778002803324</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.498141479472347</v>
+        <v>2.44988044128011</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.204105938237146</v>
+        <v>1.208487908739933</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.004211629657474</v>
+        <v>5.006840811959147</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.468441505489083</v>
+        <v>-4.589094100969676</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.706919873483864</v>
+        <v>2.658658835291627</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.204105938237146</v>
+        <v>1.208487908739933</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.217116462935532</v>
+        <v>5.219745645237205</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.46834753747171</v>
+        <v>-4.589000132952303</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.706136127602903</v>
+        <v>2.657875089410666</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.216517046656013</v>
+        <v>5.219146228957685</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.475566361671555</v>
+        <v>-4.596218957152147</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.697480583867319</v>
+        <v>2.649219545675082</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.210749032600367</v>
+        <v>5.213378214902039</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.474617938553516</v>
+        <v>-4.595270534034109</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.697859953114534</v>
+        <v>2.649598914922297</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.210749032600367</v>
+        <v>5.213378214902039</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.63168639680914</v>
+        <v>-4.752338992289733</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.647760177793377</v>
+        <v>2.59949913960114</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.223476640581459</v>
+        <v>5.226105822883131</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.625694150020329</v>
+        <v>-4.746346745500921</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.652103074933289</v>
+        <v>2.603842036741052</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.225422639005846</v>
+        <v>5.228051821307519</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.537136188889561</v>
+        <v>-4.657788784370154</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.681180395403365</v>
+        <v>2.632919357211128</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.219076775023615</v>
+        <v>5.221705957325288</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.876150205856855</v>
+        <v>3.457966651694101</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.5104996601223</v>
+        <v>-4.64002970686708</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.691143684349265</v>
+        <v>2.639331665651353</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.204475799584464</v>
+        <v>1.208857770087251</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.218385452462611</v>
+        <v>5.221014634764283</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.69157173394072</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615284</v>
+        <v>3.685161381615285</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812104</v>
+        <v>3.684843823812105</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646218</v>
+        <v>3.710935533646219</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232416</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097247</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017774</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839726</v>
+        <v>3.833252747839728</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388731</v>
+        <v>3.839374447388733</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626477</v>
+        <v>3.856161751626479</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291813</v>
+        <v>3.787330429291814</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785788</v>
+        <v>3.80163712278579</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390429</v>
+        <v>3.76318224839043</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105954</v>
+        <v>3.784718794105956</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960988</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607645</v>
+        <v>3.692931855607647</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.770422583987905</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710815</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409207</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098112</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493423</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.82855148672282</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792049</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919908</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057527</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279184</v>
+        <v>3.826354974279186</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011497</v>
+        <v>3.835957987011499</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392986</v>
+        <v>3.780933911392988</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242296</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367685</v>
+        <v>3.821593509367687</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502338</v>
+        <v>3.84861662650234</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.81866895167594</v>
+        <v>3.818668951675942</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539951</v>
+        <v>3.843274527539953</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496259</v>
+        <v>3.845047386496261</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576996</v>
+        <v>3.791273551576998</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942104</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674513</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
@@ -46050,7 +46050,7 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430691</v>
+        <v>3.729146398430693</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
@@ -46073,7 +46073,7 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003601</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225444</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264163</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316046</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803191</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809499</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472736</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798536</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.689597840498863</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,7 +46418,7 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705324</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
@@ -46441,7 +46441,7 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729269</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
@@ -46464,7 +46464,7 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190766</v>
+        <v>3.733012441190768</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
@@ -46487,7 +46487,7 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913424</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
@@ -46510,7 +46510,7 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532485</v>
+        <v>3.751147197532487</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
@@ -46533,7 +46533,7 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793904</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
@@ -46556,7 +46556,7 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011235</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
@@ -46579,7 +46579,7 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
@@ -46602,7 +46602,7 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.73702660850954</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
@@ -46625,7 +46625,7 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760811</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
@@ -46648,7 +46648,7 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815455</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
@@ -46671,7 +46671,7 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.7095104433781</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
@@ -46694,7 +46694,7 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131248</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
@@ -46717,7 +46717,7 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067864</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
@@ -46740,7 +46740,7 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.787425580789122</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
@@ -46763,7 +46763,7 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519907</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
@@ -46786,7 +46786,7 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
@@ -46809,7 +46809,7 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394732</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
@@ -46832,7 +46832,7 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
@@ -46855,7 +46855,7 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798426</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
@@ -46878,7 +46878,7 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.848729139992193</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
@@ -46901,7 +46901,7 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852423</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
@@ -46924,7 +46924,7 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319546</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
@@ -46947,7 +46947,7 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489387</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
@@ -46970,7 +46970,7 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397796</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
@@ -46993,7 +46993,7 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316251</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
@@ -47016,7 +47016,7 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105964</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
@@ -47039,7 +47039,7 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190323</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
@@ -47062,7 +47062,7 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569616</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
@@ -47085,7 +47085,7 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557293</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
@@ -47108,7 +47108,7 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
@@ -47131,7 +47131,7 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917049</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
@@ -47154,7 +47154,7 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405959</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
@@ -47177,7 +47177,7 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265643</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
@@ -47982,7 +47982,7 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609755</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
@@ -49500,7 +49500,7 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.457966651694101</v>
+        <v>3.457966651694102</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -605,7 +605,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,12 +628,12 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.5%</t>
         </is>
       </c>
     </row>
@@ -758,26 +758,26 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.9%</t>
+          <t>98.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>41.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.47</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>40.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>87.3%</t>
+          <t>82.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.6</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>137.9%</t>
+          <t>127.9%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.9%</t>
+          <t>-76.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>107.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.7%</t>
+          <t>123.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.2%</t>
+          <t>-72.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.2%</t>
+          <t>89.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.5%</t>
+          <t>420.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-625.6%</t>
+          <t>-610.3%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.1%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.8%</t>
+          <t>47.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.3%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.2%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-112.3%</t>
+          <t>-106.2%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,16 +1242,16 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-324.7%</t>
+          <t>-325.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-103.1%</t>
+          <t>-94.6%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>113.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-09-12</t>
+          <t>2024-09-13</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>82.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.7%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.9%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.0%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>104.4%</t>
+          <t>40.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.2%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.3</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-15.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.3%</t>
+          <t>36.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>76.1%</t>
+          <t>-7.1%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2085"/>
+  <dimension ref="A1:G2086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.251475576074622</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191737</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108639</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094117</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199284</v>
+        <v>3.405960511199285</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923085</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297748</v>
+        <v>3.458100091297749</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317617</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341316</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539465</v>
+        <v>3.501052558539466</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937499</v>
+        <v>3.4924487119375</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141702</v>
+        <v>3.502790399141703</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729891</v>
+        <v>3.496851904729892</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440635</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608601</v>
+        <v>3.490059241608602</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410274</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764398</v>
+        <v>3.480692492764399</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297399</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322543</v>
+        <v>3.573674025322544</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158923</v>
+        <v>3.600038265158924</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.67684154977058</v>
+        <v>3.676841549770581</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646219</v>
+        <v>3.71093553364622</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955331</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232416</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45688,10 +45688,10 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.3908391606028</v>
+        <v>-5.406160668420325</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7092627628423855</v>
+        <v>0.7031341597153755</v>
       </c>
       <c r="F1919" t="n">
         <v>0.112527687200088</v>
@@ -45711,10 +45711,10 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.214947068135368</v>
+        <v>-5.230268575952893</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7832187233500072</v>
+        <v>0.7770901202229972</v>
       </c>
       <c r="F1920" t="n">
         <v>0.112527687200088</v>
@@ -45734,10 +45734,10 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.043500605112905</v>
+        <v>-5.05882211293043</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8651248146135462</v>
+        <v>0.8589962114865362</v>
       </c>
       <c r="F1921" t="n">
         <v>0.2839741502225512</v>
@@ -45757,10 +45757,10 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.963478318003784</v>
+        <v>-4.978799825821309</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8961542070734918</v>
+        <v>0.8900256039464818</v>
       </c>
       <c r="F1922" t="n">
         <v>0.3639964373316721</v>
@@ -45780,10 +45780,10 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.899842575769849</v>
+        <v>-4.915164083587374</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9263033050213827</v>
+        <v>0.9201747018943727</v>
       </c>
       <c r="F1923" t="n">
         <v>0.4276321795656067</v>
@@ -45803,10 +45803,10 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.806145257553454</v>
+        <v>-4.821466765370979</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9449764910917364</v>
+        <v>0.9388478879647264</v>
       </c>
       <c r="F1924" t="n">
         <v>0.4276321795656067</v>
@@ -45826,10 +45826,10 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.816647880618743</v>
+        <v>-4.831969388436268</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9425185184904983</v>
+        <v>0.9363899153634883</v>
       </c>
       <c r="F1925" t="n">
         <v>0.4171295565003178</v>
@@ -45849,10 +45849,10 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.704161619949868</v>
+        <v>-4.719483127767393</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9914423365928684</v>
+        <v>0.9853137334658584</v>
       </c>
       <c r="F1926" t="n">
         <v>0.4171295565003178</v>
@@ -45872,10 +45872,10 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.686447933072003</v>
+        <v>-4.701769440889528</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9992063952613544</v>
+        <v>0.9930777921343443</v>
       </c>
       <c r="F1927" t="n">
         <v>0.4203108853972346</v>
@@ -45895,10 +45895,10 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.562973661758985</v>
+        <v>-4.57829516957651</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.045594175006555</v>
+        <v>1.039465571879545</v>
       </c>
       <c r="F1928" t="n">
         <v>0.4203108853972346</v>
@@ -45918,10 +45918,10 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.342952863721974</v>
+        <v>-4.358274371539499</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.135181531231974</v>
+        <v>1.129052928104963</v>
       </c>
       <c r="F1929" t="n">
         <v>0.5615307304652148</v>
@@ -45941,10 +45941,10 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.210085174658697</v>
+        <v>-4.225406682476222</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.204222789659108</v>
+        <v>1.198094186532098</v>
       </c>
       <c r="F1930" t="n">
         <v>0.5615307304652148</v>
@@ -45964,10 +45964,10 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.089912091294198</v>
+        <v>-4.105233599111723</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.253437867445209</v>
+        <v>1.247309264318199</v>
       </c>
       <c r="F1931" t="n">
         <v>0.6817038138297138</v>
@@ -45987,10 +45987,10 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.954658729964221</v>
+        <v>-3.969980237781746</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.31762731453864</v>
+        <v>1.31149871141163</v>
       </c>
       <c r="F1932" t="n">
         <v>0.8169571751596909</v>
@@ -46010,10 +46010,10 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.014533557321913</v>
+        <v>-4.029855065139438</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.279714874996989</v>
+        <v>1.273586271869979</v>
       </c>
       <c r="F1933" t="n">
         <v>0.7570823478019988</v>
@@ -46033,10 +46033,10 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.894713326411076</v>
+        <v>-3.910034834228601</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.342932136595532</v>
+        <v>1.336803533468522</v>
       </c>
       <c r="F1934" t="n">
         <v>0.7570823478019988</v>
@@ -46056,10 +46056,10 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.897183032872882</v>
+        <v>-3.912504540690407</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.249588453333252</v>
+        <v>1.243459850206242</v>
       </c>
       <c r="F1935" t="n">
         <v>0.7546126413401926</v>
@@ -46073,16 +46073,16 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003601</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.965553219196892</v>
+        <v>-3.980874727014417</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.141502240288949</v>
+        <v>1.135373637161939</v>
       </c>
       <c r="F1936" t="n">
         <v>0.7638883403764075</v>
@@ -46096,16 +46096,16 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.71417913950837</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.077425498823042</v>
+        <v>-4.092747006640567</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.08719003707038</v>
+        <v>1.08106143394337</v>
       </c>
       <c r="F1937" t="n">
         <v>0.7638883403764075</v>
@@ -46119,16 +46119,16 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417706</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.132945574715632</v>
+        <v>-4.148267082533157</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.202012843405547</v>
+        <v>1.195884240278537</v>
       </c>
       <c r="F1938" t="n">
         <v>0.7638883403764075</v>
@@ -46142,16 +46142,16 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205899</v>
+        <v>3.7460425262059</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.957471314923163</v>
+        <v>-3.972792822740688</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.276769779314322</v>
+        <v>1.270641176187312</v>
       </c>
       <c r="F1939" t="n">
         <v>0.7638883403764075</v>
@@ -46165,16 +46165,16 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225444</v>
+        <v>3.765024323225445</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.949546940338248</v>
+        <v>-3.964868448155773</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.255681557909495</v>
+        <v>1.249552954782485</v>
       </c>
       <c r="F1940" t="n">
         <v>0.7638883403764075</v>
@@ -46194,10 +46194,10 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.943268737768399</v>
+        <v>-3.958590245585925</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.186731152338884</v>
+        <v>1.180602549211874</v>
       </c>
       <c r="F1941" t="n">
         <v>0.7701665429462565</v>
@@ -46211,16 +46211,16 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264163</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.883416118564676</v>
+        <v>-3.898737626382201</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.220844586452506</v>
+        <v>1.214715983325496</v>
       </c>
       <c r="F1942" t="n">
         <v>0.7701665429462565</v>
@@ -46240,10 +46240,10 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.797172655538299</v>
+        <v>-3.812494163355824</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.250288242236917</v>
+        <v>1.244159639109907</v>
       </c>
       <c r="F1943" t="n">
         <v>0.7701665429462565</v>
@@ -46263,10 +46263,10 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.842479474937279</v>
+        <v>-3.857800982754804</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.223941289921851</v>
+        <v>1.217812686794841</v>
       </c>
       <c r="F1944" t="n">
         <v>0.7293563799370257</v>
@@ -46286,10 +46286,10 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.87151257963958</v>
+        <v>-3.886834087457105</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.212879921074032</v>
+        <v>1.206751317947022</v>
       </c>
       <c r="F1945" t="n">
         <v>0.7293563799370257</v>
@@ -46309,10 +46309,10 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.778702098188721</v>
+        <v>-3.794023606006246</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.179276805545741</v>
+        <v>1.173148202418731</v>
       </c>
       <c r="F1946" t="n">
         <v>0.8221668613878851</v>
@@ -46332,10 +46332,10 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.823091567518149</v>
+        <v>-3.838413075335674</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.163394493738571</v>
+        <v>1.157265890611561</v>
       </c>
       <c r="F1947" t="n">
         <v>0.7777773920584574</v>
@@ -46355,10 +46355,10 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.802587873632651</v>
+        <v>-3.817909381450177</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.166671679804493</v>
+        <v>1.160543076677483</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7982810859439547</v>
@@ -46378,10 +46378,10 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.842511968215224</v>
+        <v>-3.857833476032749</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.156193337802131</v>
+        <v>1.150064734675121</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7982810859439547</v>
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.870292366116577</v>
+        <v>-3.889995844436888</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.156578380410129</v>
+        <v>1.148696989082004</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7661187175398151</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.164722981694396</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.988673038846715</v>
+        <v>-4.008376517167027</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9475818313187268</v>
+        <v>0.9397004399906022</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.6989008653888389</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>2.962747990404464</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.097287117290046</v>
+        <v>-4.116990595610358</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.0242858606606</v>
+        <v>1.016404469332475</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.6989008653888389</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.082897651123669</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.061878079041903</v>
+        <v>-4.081581557362215</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.05296250206218</v>
+        <v>1.045081110734055</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.6989008653888389</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.097410677225992</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.023494416483752</v>
+        <v>-4.043197894804064</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.065735408427809</v>
+        <v>1.057854017099685</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7372845279469901</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.117860316103251</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.846378086448586</v>
+        <v>-3.866081564768898</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.133310969287178</v>
+        <v>1.125429577959053</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.7372845279469901</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.114589344948554</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.891470331282131</v>
+        <v>-3.911173809602444</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.115957463115673</v>
+        <v>1.108076071787548</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.6753884847776003</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.078135110808833</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.712094910043364</v>
+        <v>-3.731798388363676</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.181494606917594</v>
+        <v>1.173613215589469</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.832165242948319</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.165988141017678</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.75710912356397</v>
+        <v>-3.776812601884282</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.144296376840941</v>
+        <v>1.136414985512817</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.8018163476337143</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.128586259160505</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.024113633836405</v>
+        <v>-4.043817112156717</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.043186135070913</v>
+        <v>1.035304743742788</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.6074533095907657</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>3.017659998673682</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.125311415273578</v>
+        <v>-4.14501489359389</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.001910944392545</v>
+        <v>0.9940295530644203</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5390444960454466</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>2.975818632442992</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.118800448659266</v>
+        <v>-4.138503926979578</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.002115292592587</v>
+        <v>0.9942339012644621</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.5390444960454466</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>2.973418593997309</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.099762320951968</v>
+        <v>-4.11946579927228</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.006255262883751</v>
+        <v>0.9983738715556258</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.480860884714252</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.935033146406837</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.152278123226789</v>
+        <v>-4.171981601547101</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.104543343608013</v>
+        <v>1.096661952279888</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.480860884714252</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.054327548041027</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.155686434661368</v>
+        <v>-4.17538991298168</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.104013348020314</v>
+        <v>1.09613195669219</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5133774537236294</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.074670818432787</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.115203442739023</v>
+        <v>-4.134906921059335</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.126215075186179</v>
+        <v>1.118333683858054</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5133774537236294</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.080679348829713</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.967460472504021</v>
+        <v>-3.987163950824333</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.083262484557379</v>
+        <v>1.075381093229254</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.6811848109585126</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>3.079313984447842</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.051281693778719</v>
+        <v>-4.070985172099031</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.052527617578981</v>
+        <v>1.044646226250856</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.6811848109585126</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>3.082107605979323</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.045128987725935</v>
+        <v>-4.064832466046247</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.055651048391753</v>
+        <v>1.047769657063628</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.6873375170112969</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>3.086461578002652</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.061938285876437</v>
+        <v>-4.081641764196749</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.048007805871662</v>
+        <v>1.040126414543537</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.6705282188607953</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>3.075456475852462</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.999640287100315</v>
+        <v>-4.019343765420627</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.139262559178932</v>
+        <v>1.131381167850807</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.7158224831352373</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.168968588213948</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.797850089435157</v>
+        <v>-3.817553567755469</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.022270639959122</v>
+        <v>1.014389248630998</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9182226458071785</v>
+        <v>0.9138406753043917</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.09270068753124</v>
+        <v>3.090071505229568</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.848736802121352</v>
+        <v>-3.868440280441663</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.072206187206819</v>
+        <v>1.064324795878695</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.867335933120984</v>
+        <v>0.8629539626181972</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132458892241698</v>
+        <v>3.129829709940026</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.762126059471544</v>
+        <v>-3.781829537791856</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.121478220382786</v>
+        <v>1.113596829054661</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9459616643261423</v>
+        <v>0.9415796938233555</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194262067080837</v>
+        <v>3.191632884779165</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.822335357476829</v>
+        <v>-3.84203883579714</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.095930482005344</v>
+        <v>1.088049090677219</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.881370395818071</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156672469102338</v>
+        <v>3.154043286800666</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.773148708792478</v>
+        <v>-3.792852187112789</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.114096759519013</v>
+        <v>1.106215368190888</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.881370395818071</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155164087142266</v>
+        <v>3.152534904840594</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.728775577153909</v>
+        <v>-3.74847905547422</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.131708879609877</v>
+        <v>1.123827488281752</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9257435274566396</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181650833560844</v>
+        <v>3.179021651259172</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.751255928012794</v>
+        <v>-3.770959406333105</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.117110533404913</v>
+        <v>1.109229142076789</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9301254979594263</v>
+        <v>0.9257435274566396</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176044627699434</v>
+        <v>3.173415445397762</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.703600197451738</v>
+        <v>-3.723303675772049</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.14255458265714</v>
+        <v>1.134673191329016</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.977781228520482</v>
+        <v>0.9733992580176952</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.211019823063872</v>
+        <v>3.2083906407622</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.603082038952984</v>
+        <v>-3.622785517273295</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.187654219431367</v>
+        <v>1.179772828103242</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.078299387019237</v>
+        <v>1.07391741651645</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.27622309153785</v>
+        <v>3.273593909236177</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.587176709520631</v>
+        <v>-3.606880187840942</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.18077102368018</v>
+        <v>1.172889632352055</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9991867263099976</v>
+        <v>0.9948047558072108</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.215510167588179</v>
+        <v>3.212880985286506</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.542338307912233</v>
+        <v>-3.562041786232544</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.202804086934168</v>
+        <v>1.194922695606043</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.003730159254867</v>
+        <v>0.9993481887520803</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.222333929965729</v>
+        <v>3.219704747664057</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.561836764154241</v>
+        <v>-3.581540242474552</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.199165644068442</v>
+        <v>1.191284252740318</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9556455179749628</v>
+        <v>0.951263547472176</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.197644084828864</v>
+        <v>3.195014902527192</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.517633927068341</v>
+        <v>-3.537337405388652</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.22272638143064</v>
+        <v>1.214844990102515</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9998483550608632</v>
+        <v>0.9954663845580765</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.230045389608242</v>
+        <v>3.22741620730657</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.525193592905388</v>
+        <v>-3.544897071225699</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.218112515565068</v>
+        <v>1.210231124236944</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.054651759070683</v>
+        <v>1.050269788567896</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.261337432483381</v>
+        <v>3.258708250181709</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.86389508028488</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.366902175366115</v>
+        <v>-3.386605653686427</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.332676847763817</v>
+        <v>1.324795456435693</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.054651759070683</v>
+        <v>1.050269788567896</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.31258519766642</v>
+        <v>3.309956015364748</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321024</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.159260171731639</v>
+        <v>-3.17896365005195</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.414174353811861</v>
+        <v>1.406292962483736</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.262293762705159</v>
+        <v>1.257911792202372</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.435611104441359</v>
+        <v>3.432981922139687</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475141</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.108228079009111</v>
+        <v>-3.127931557329422</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.429535419139142</v>
+        <v>1.421654027811017</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.313325855427687</v>
+        <v>1.3089438849249</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.461178588313146</v>
+        <v>3.458549406011474</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404855</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.043003897881905</v>
+        <v>-3.062707376202217</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.472812495682729</v>
+        <v>1.464931104354605</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.378550036554892</v>
+        <v>1.374168066052105</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.517500501082174</v>
+        <v>3.514871318780502</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882559</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.005576877810772</v>
+        <v>-3.025280356131083</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.483744276010463</v>
+        <v>1.475862884682339</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.383801574584074</v>
+        <v>1.379419604081287</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.516612396198964</v>
+        <v>3.513983213897292</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992663</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.02568853384548</v>
+        <v>-3.045392012165791</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.47695640592782</v>
+        <v>1.469075014599696</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.394828919581493</v>
+        <v>1.390446949078706</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.524485595528656</v>
+        <v>3.521856413226983</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.82866144563629</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.997275270745596</v>
+        <v>-3.016978749065907</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.648879482188984</v>
+        <v>1.64099809086086</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.335853356835065</v>
+        <v>1.331471386332278</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.649658028902009</v>
+        <v>3.647028846600337</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957629</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.922493009720584</v>
+        <v>-2.942196488040895</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.798905295816807</v>
+        <v>1.791023904488682</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.410635617860077</v>
+        <v>1.40625364735729</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.814640294734834</v>
+        <v>3.812011112433161</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.896408925456776</v>
+        <v>-2.916112403777087</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.801046905536189</v>
+        <v>1.793165514208064</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.410635617860077</v>
+        <v>1.40625364735729</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.806348270748693</v>
+        <v>3.80371908844702</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896928</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.808531012347655</v>
+        <v>-2.828234490667966</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.834391266363616</v>
+        <v>1.826509875035492</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.526561260283428</v>
+        <v>1.522179289780641</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.874096851786483</v>
+        <v>3.871467669484811</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959857</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.799638550954372</v>
+        <v>-2.819342029274683</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.855502656647721</v>
+        <v>1.847621265319597</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.526561260283428</v>
+        <v>1.522179289780641</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.891651257513274</v>
+        <v>3.889022075211602</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.96811466792425</v>
+        <v>-2.826439103752724</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.779967257264354</v>
+        <v>1.836637482932964</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.498613424566847</v>
+        <v>1.583269099227561</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.86673760348791</v>
+        <v>3.917531008284338</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.795574066782709</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.52185847529481</v>
+        <v>-2.380182911123285</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.939739431503992</v>
+        <v>1.996409657172602</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.403894754897215</v>
+        <v>1.488550429557928</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.791176098873992</v>
+        <v>3.84196950367042</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.499137371611657</v>
+        <v>-2.357461807440132</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.939491895474157</v>
+        <v>1.996162121142767</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.403894754897215</v>
+        <v>1.488550429557928</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.781840121370896</v>
+        <v>3.832633526167325</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.6283391849057</v>
+        <v>-2.486663620734175</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.046717296007709</v>
+        <v>2.10338752167632</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.274692941603172</v>
+        <v>1.359348616263886</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.86322515924564</v>
+        <v>3.914018564042069</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.654213583379725</v>
+        <v>-2.512538019208201</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.073445359111746</v>
+        <v>2.130115584780356</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.319604550314914</v>
+        <v>1.404260224975627</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.927249946966332</v>
+        <v>3.97804335176276</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.647158893164552</v>
+        <v>-2.505483328993027</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.07294259118736</v>
+        <v>2.12961281685597</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.326659240530087</v>
+        <v>1.411314915190801</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.928158117084981</v>
+        <v>3.97895152188141</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331114</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.620207668838064</v>
+        <v>-2.478532104666539</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.093729234562697</v>
+        <v>2.150399460231307</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.341539586557807</v>
+        <v>1.42619526121852</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.947092478346354</v>
+        <v>3.997885883142782</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.76805206778411</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.641751896668851</v>
+        <v>-2.500076332497326</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.269214675575342</v>
+        <v>2.325884901243952</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.341539586557807</v>
+        <v>1.42619526121852</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.131195610491313</v>
+        <v>4.181989015287742</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.664160014473723</v>
+        <v>-2.522484450302198</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.252368123356386</v>
+        <v>2.309038349024996</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.341539586557807</v>
+        <v>1.42619526121852</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.123312305394307</v>
+        <v>4.174105710190736</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.692384250051323</v>
+        <v>-2.550708685879798</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.243132428674984</v>
+        <v>2.299802654343593</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.359516339009115</v>
+        <v>1.444172013669829</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.13615235641473</v>
+        <v>4.186945761211158</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.701825175939853</v>
+        <v>-2.560149611768328</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.295609776041418</v>
+        <v>2.352280001710029</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.481943456552507</v>
+        <v>1.56659913121322</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.265862344662612</v>
+        <v>4.31665574945904</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.790701807108327</v>
+        <v>-2.649026242936802</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.26295021811933</v>
+        <v>2.31962044378794</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.393066825384033</v>
+        <v>1.477722500044746</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.215427460506828</v>
+        <v>4.266220865303256</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.867031784709233</v>
+        <v>-2.725356220537708</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.230530039972743</v>
+        <v>2.287200265641353</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.393066825384033</v>
+        <v>1.477722500044746</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.213539273400603</v>
+        <v>4.264332678197031</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.960695729386774</v>
+        <v>-2.81902016521525</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.187884691704589</v>
+        <v>2.244554917373199</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.299402880706491</v>
+        <v>1.384058555367205</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.15216113619694</v>
+        <v>4.202954540993369</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.12226415491403</v>
+        <v>-2.980588590742505</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.121691331703839</v>
+        <v>2.178361557372449</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.172619956908612</v>
+        <v>1.257275631569326</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.074525392128366</v>
+        <v>4.125318796924794</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.230564816784149</v>
+        <v>-3.088889252612624</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.09144447382171</v>
+        <v>2.14811469949032</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.172619956908612</v>
+        <v>1.257275631569326</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.087598798994284</v>
+        <v>4.138392203790712</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.248368788504893</v>
+        <v>-3.106693224333368</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.076328081916352</v>
+        <v>2.132998307584962</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.102085334003411</v>
+        <v>1.186741008664125</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.037283222034104</v>
+        <v>4.088076626830532</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.276269575614366</v>
+        <v>-3.134594011442841</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.063691808199565</v>
+        <v>2.120362033868175</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.067488409860476</v>
+        <v>1.15214408452119</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.015049108675345</v>
+        <v>4.065842513471773</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.39879567831726</v>
+        <v>-3.257120114145735</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.011445811095606</v>
+        <v>2.068116036764216</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9449623071575823</v>
+        <v>1.029617981818296</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.938297891030807</v>
+        <v>3.989091295827235</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.629310174502849</v>
+        <v>-3.487634610331324</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.985945972211874</v>
+        <v>2.042616197880484</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7144478109719936</v>
+        <v>0.7991034856327073</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.866695152909958</v>
+        <v>3.917488557706386</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.978055259727292</v>
+        <v>-3.836379695555768</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.986759657123944</v>
+        <v>2.043429882792553</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6903555317138095</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.941758099560466</v>
+        <v>3.992551504356894</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.132041677503433</v>
+        <v>-3.990366113331908</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.994145359159127</v>
+        <v>2.050815584827737</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6903555317138095</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.010738368706106</v>
+        <v>4.061531773502534</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.61992301642339</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.081519773675767</v>
+        <v>-3.939844209504242</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.000405322810315</v>
+        <v>2.057075548478925</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6903555317138095</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.996789570826227</v>
+        <v>4.047582975622655</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609755</v>
+        <v>3.656332733609756</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.333994927683491</v>
+        <v>-4.192319363511967</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.911285750262639</v>
+        <v>1.967955975931249</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6903555317138095</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.008660059881641</v>
+        <v>4.059453464678069</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973161</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.626890684162904</v>
+        <v>-4.485215119991379</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.795337982189818</v>
+        <v>1.852008207858428</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6056998570530958</v>
+        <v>0.6903555317138095</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.009870594400584</v>
+        <v>4.060663999197012</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.813554812297712</v>
+        <v>-4.671879248126187</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.724794073163216</v>
+        <v>1.781464298831826</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5789608862285359</v>
+        <v>0.6636165608892496</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.99794895413317</v>
+        <v>4.048742358929598</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.959575499211674</v>
+        <v>-4.817899935040149</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.661463651133821</v>
+        <v>1.71813387680243</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.6545334690953926</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.987576951793045</v>
+        <v>4.038370356589473</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.051289508321259</v>
+        <v>-4.909613944149735</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.78698210418903</v>
+        <v>1.84365232985764</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5698777944346789</v>
+        <v>0.6545334690953926</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.149781008492089</v>
+        <v>4.200574413288518</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.082941167381229</v>
+        <v>-4.941265603209704</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.769168078528857</v>
+        <v>1.825838304197467</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5647093371902387</v>
+        <v>0.6493650118509524</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.141526572109239</v>
+        <v>4.192319976905667</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.164875985650112</v>
+        <v>-5.023200421478587</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.746623568789794</v>
+        <v>1.803293794458404</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5547745916031586</v>
+        <v>0.6394302662638722</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.145795142325482</v>
+        <v>4.196588547121911</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.26685210789852</v>
+        <v>-5.125176543726995</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.714758758346334</v>
+        <v>1.771428984014944</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.452798469354751</v>
+        <v>0.5374541440154647</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.09353510743234</v>
+        <v>4.144328512228769</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.156845824421298</v>
+        <v>-5.015170260249773</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.750914158981398</v>
+        <v>1.807584384650008</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4760030412720262</v>
+        <v>0.5606587159327399</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.099610737826881</v>
+        <v>4.150404142623309</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.013786248680372</v>
+        <v>-4.872110684508847</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.812387999999743</v>
+        <v>1.869058225668353</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4840164678620055</v>
+        <v>0.5686721425227191</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.108668804502843</v>
+        <v>4.159462209299271</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.712339523208534</v>
+        <v>-4.57066395903701</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.940227573071014</v>
+        <v>1.996897798739623</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8701188679945564</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.29679772266848</v>
+        <v>4.347591127464909</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.736929767443718</v>
+        <v>-4.595254203272193</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.931362653129651</v>
+        <v>1.988032878798261</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8701188679945564</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.297768900421191</v>
+        <v>4.348562305217619</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474161</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.685891391437198</v>
+        <v>-4.544215827265673</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.952620907912014</v>
+        <v>2.009291133580624</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7854631933338427</v>
+        <v>0.8701188679945564</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.298611804800947</v>
+        <v>4.349405209597375</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969545</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.644752096570567</v>
+        <v>-4.503076532399042</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.988114724732812</v>
+        <v>2.044784950401422</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8266024882004736</v>
+        <v>0.9112581628611872</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.34233348059507</v>
+        <v>4.393126885391499</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.548117184551927</v>
+        <v>-4.406441620380402</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.842952685664203</v>
+        <v>1.899622911332813</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9232374002191135</v>
+        <v>1.007893074879827</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.216498423930189</v>
+        <v>4.267291828726617</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.67869791908277</v>
+        <v>-4.537022354911245</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.79422243592583</v>
+        <v>1.85089266159444</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.792656665688271</v>
+        <v>0.8773123403489846</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.141652027285648</v>
+        <v>4.192445432082076</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.514201584891808</v>
+        <v>-4.372526020720283</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.844447788678297</v>
+        <v>1.901118014346907</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9571529998792329</v>
+        <v>1.041808674539947</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.224776646876307</v>
+        <v>4.275570051672736</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.437102983349935</v>
+        <v>-4.29542741917841</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.874474939731476</v>
+        <v>1.931145165400086</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9571529998792329</v>
+        <v>1.041808674539947</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.223964357312737</v>
+        <v>4.274757762109165</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147911</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.447488178239825</v>
+        <v>-4.3058126140683</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.880189640900593</v>
+        <v>1.936859866569203</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9467678049893435</v>
+        <v>1.031423479650057</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.227602019503876</v>
+        <v>4.278395424300305</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.46607633696205</v>
+        <v>-4.324400772790525</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.943591383188128</v>
+        <v>2.000261608856738</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9281796462671181</v>
+        <v>1.012835320927832</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.287286130046966</v>
+        <v>4.338079534843394</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496555</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.466374883658085</v>
+        <v>-4.324699319486561</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.940340975328012</v>
+        <v>1.997011200996622</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9278810995710822</v>
+        <v>1.012536774231796</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.283976012847643</v>
+        <v>4.334769417644071</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.81564321210886</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.365551749967658</v>
+        <v>-4.223876185796133</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.985201123743574</v>
+        <v>2.041871349412185</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9403453150554361</v>
+        <v>1.02500098971615</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.295985437077647</v>
+        <v>4.346778841874075</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121471</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.174770389215251</v>
+        <v>-4.033094825043726</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.06164292152308</v>
+        <v>2.118313147191691</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.131126675807844</v>
+        <v>1.215782350468557</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.410583507007635</v>
+        <v>4.461376911804063</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906084</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.067807031365829</v>
+        <v>-3.926131467194304</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.084265110400445</v>
+        <v>2.140935336069056</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.189591283767645</v>
+        <v>1.274246958428359</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.425499117521112</v>
+        <v>4.47629252231754</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.012476443464067</v>
+        <v>-3.870800879292542</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.141364282173209</v>
+        <v>2.198034507841819</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.244921871669407</v>
+        <v>1.329577546330121</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.493664406874228</v>
+        <v>4.544457811670656</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539898</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.000422316551104</v>
+        <v>-3.85874675237958</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.139872500839832</v>
+        <v>2.196542726508442</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.25697599858237</v>
+        <v>1.341631673243084</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.494583450923443</v>
+        <v>4.545376855719871</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811013</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.041577436119325</v>
+        <v>-3.8999018719478</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.12529108319668</v>
+        <v>2.181961308865289</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.215820879014149</v>
+        <v>1.300476553674863</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.471771009366647</v>
+        <v>4.522564414163075</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382924</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.973528873427795</v>
+        <v>-3.831853309256271</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.165361534151174</v>
+        <v>2.222031759819783</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.283869441705679</v>
+        <v>1.368525116366393</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.525451172859447</v>
+        <v>4.576244577655875</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013431</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.205129266597296</v>
+        <v>-4.063453702425772</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.092924047056968</v>
+        <v>2.149594272725578</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.283869441705679</v>
+        <v>1.368525116366393</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.545653843033041</v>
+        <v>4.596447247829469</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.666747201498969</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.255180812126515</v>
+        <v>-4.113505247954992</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.056509664912162</v>
+        <v>2.113179890580771</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.283869441705679</v>
+        <v>1.368525116366393</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.529260079099923</v>
+        <v>4.580053483896351</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.430287644702959</v>
+        <v>-4.288612080531436</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.946718845475051</v>
+        <v>2.00338907114366</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.283869441705679</v>
+        <v>1.368525116366393</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.48951199269339</v>
+        <v>4.540305397489818</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660851</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.234187491272436</v>
+        <v>-4.092511927100913</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.0321815258442</v>
+        <v>2.088851751512809</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.479969595136202</v>
+        <v>1.564625269796915</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.614194703748644</v>
+        <v>4.664988108545072</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395088</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.081162099159152</v>
+        <v>-3.939486534987629</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.192562682262419</v>
+        <v>2.249232907931027</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.632994987249486</v>
+        <v>1.717650661910199</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.805180938589518</v>
+        <v>4.855974343385946</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.74127833279115</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.109469413032422</v>
+        <v>-3.967793848860899</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.368705981621403</v>
+        <v>2.425376207290012</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.632994987249486</v>
+        <v>1.717650661910199</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.992647163497811</v>
+        <v>5.043440568294239</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620435</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.276062638145945</v>
+        <v>-4.134387073974422</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.271471642930076</v>
+        <v>2.328141868598685</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.466401762135963</v>
+        <v>1.551057436796677</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.86209417978378</v>
+        <v>4.912887584580208</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285648</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.253026844784379</v>
+        <v>-4.111351280612856</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.28436236293642</v>
+        <v>2.34103258860503</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.466401762135963</v>
+        <v>1.551057436796677</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.865770582445498</v>
+        <v>4.916563987241926</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399471</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.223780864328682</v>
+        <v>-4.082105300157159</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.293678810242194</v>
+        <v>2.350349035910804</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.466401762135963</v>
+        <v>1.551057436796677</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.863388637568993</v>
+        <v>4.914182042365421</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256374</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.330706412206533</v>
+        <v>-4.18903084803501</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.248201830248689</v>
+        <v>2.304872055917298</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.359476214258112</v>
+        <v>1.444131888918826</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.796526547999917</v>
+        <v>4.847319952796345</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701004</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.475724970713782</v>
+        <v>-4.334049406542259</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.191623208989023</v>
+        <v>2.248293434657633</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.214457655750864</v>
+        <v>1.299113330411577</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.710944215038802</v>
+        <v>4.76173761983523</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687017</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.594066736498499</v>
+        <v>-4.452391172326976</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.244217741932889</v>
+        <v>2.300887967601499</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.225143694313754</v>
+        <v>1.309799368974467</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.817287077434289</v>
+        <v>4.868080482230718</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790807</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.645477158819207</v>
+        <v>-4.503801594647684</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.221439270130545</v>
+        <v>2.278109495799154</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.225143694313754</v>
+        <v>1.309799368974467</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.815072774560227</v>
+        <v>4.865866179356656</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437335</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.724896610026959</v>
+        <v>-4.583221045855436</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.189574617721734</v>
+        <v>2.246244843390343</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.225143694313754</v>
+        <v>1.309799368974467</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.814975902634517</v>
+        <v>4.865769307430946</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.7368049522984</v>
+        <v>3.736804952298402</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.820359607944177</v>
+        <v>-4.678684043772654</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.15138331211289</v>
+        <v>2.2080535377815</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.225143694313754</v>
+        <v>1.309799368974467</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.81496979619256</v>
+        <v>4.865763200988989</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218005</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.755983697093462</v>
+        <v>-4.614308132921939</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.175230073015787</v>
+        <v>2.231900298684396</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.289519605164469</v>
+        <v>1.374175279825183</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.8516917392656</v>
+        <v>4.902485144062029</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.811352859225655</v>
+        <v>-4.669677295054132</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.158816225910636</v>
+        <v>2.215486451579245</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.289519605164469</v>
+        <v>1.374175279825183</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.857425557013327</v>
+        <v>4.908218961809755</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113284</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.856790639056483</v>
+        <v>-4.71511507488496</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.140179477321237</v>
+        <v>2.196849702989846</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.246674614486309</v>
+        <v>1.331330289147023</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.831256925949363</v>
+        <v>4.882050330745791</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113691</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.768583804908904</v>
+        <v>-4.626908240737381</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.195336603830587</v>
+        <v>2.252006829499197</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.246674614486309</v>
+        <v>1.331330289147023</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.851131318799682</v>
+        <v>4.90192472359611</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.79448684401644</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.662548809703595</v>
+        <v>-4.520873245532072</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.221451302437439</v>
+        <v>2.278121528106048</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.246674614486309</v>
+        <v>1.331330289147023</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.83483201932441</v>
+        <v>4.885625424120838</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307671</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.4793371465705</v>
+        <v>-4.337661582398977</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.297166917154723</v>
+        <v>2.353837142823332</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.246674614486309</v>
+        <v>1.331330289147023</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.837262968788456</v>
+        <v>4.888056373584884</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.407615699556649</v>
+        <v>-4.265940135385126</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.291646681808152</v>
+        <v>2.348316907476762</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.31839606150016</v>
+        <v>1.403051736160874</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.846087022844656</v>
+        <v>4.896880427641084</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.385242673948943</v>
+        <v>-4.24356710977742</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.247511637972407</v>
+        <v>2.304181863641016</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.329651812613061</v>
+        <v>1.414307487273775</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.799756219433569</v>
+        <v>4.850549624229997</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456734</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.418258969859687</v>
+        <v>-4.276583405688164</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.419503324493464</v>
+        <v>2.476173550162073</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.26021443594631</v>
+        <v>1.344870110607024</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.943291998318872</v>
+        <v>4.994085403115301</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883681</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.406731334210079</v>
+        <v>-4.265055770038556</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.416035604581557</v>
+        <v>2.472705830250166</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.319215094147672</v>
+        <v>1.403870768808386</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.970613619067939</v>
+        <v>5.021407023864367</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.504072835552448</v>
+        <v>-4.362397271380924</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.380767116566398</v>
+        <v>2.437437342235007</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.274794911982184</v>
+        <v>1.359450586642898</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.947629622290435</v>
+        <v>4.998423027086863</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.589928864892414</v>
+        <v>-4.448253300720891</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.347675787023249</v>
+        <v>2.404346012691859</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.232418842756049</v>
+        <v>1.317074517416763</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.923455062947592</v>
+        <v>4.974248467744021</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.69183549961038</v>
+        <v>3.691835499610382</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.598765662308534</v>
+        <v>-4.457090098137011</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.326560269877303</v>
+        <v>2.383230495545913</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.224976670114698</v>
+        <v>1.309632344775412</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.901408961183283</v>
+        <v>4.952202365979711</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.690148224873992</v>
+        <v>-4.548472660702469</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.300171755896169</v>
+        <v>2.356841981564779</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.13359410754924</v>
+        <v>1.218249782209954</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.856743934689058</v>
+        <v>4.907537339485486</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.678441506886986</v>
+        <v>-4.536765942715463</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.40698270091524</v>
+        <v>2.463652926583849</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.145300825536246</v>
+        <v>1.22995650019696</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.965896223305529</v>
+        <v>5.016689628101958</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.578778002803324</v>
+        <v>-4.437102438631801</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.44988044128011</v>
+        <v>2.506550666948719</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.208487908739933</v>
+        <v>1.293143583400646</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.006840811959147</v>
+        <v>5.057634216755575</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452574</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.589094100969676</v>
+        <v>-4.447418536798152</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.658658835291627</v>
+        <v>2.715329060960237</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.208487908739933</v>
+        <v>1.293143583400646</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.219745645237205</v>
+        <v>5.270539050033633</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.589000132952303</v>
+        <v>-4.44732456878078</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.657875089410666</v>
+        <v>2.714545315079275</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.219146228957685</v>
+        <v>5.269939633754113</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.633213467988024</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.596218957152147</v>
+        <v>-4.454543392980624</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.649219545675082</v>
+        <v>2.705889771343691</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.213378214902039</v>
+        <v>5.264171619698467</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.595270534034109</v>
+        <v>-4.453594969862586</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.649598914922297</v>
+        <v>2.706269140590907</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.213378214902039</v>
+        <v>5.264171619698467</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.752338992289733</v>
+        <v>-4.61066342811821</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.59949913960114</v>
+        <v>2.656169365269749</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.226105822883131</v>
+        <v>5.276899227679559</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.746346745500921</v>
+        <v>-4.604671181329398</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.603842036741052</v>
+        <v>2.660512262409661</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.228051821307519</v>
+        <v>5.278845226103947</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.657788784370154</v>
+        <v>-4.516113220198631</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.632919357211128</v>
+        <v>2.689589582879737</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.221705957325288</v>
+        <v>5.272499362121716</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,45 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.457966651694102</v>
+        <v>3.735300721383091</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.64002970686708</v>
+        <v>-4.48757888264767</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.639331665651353</v>
+        <v>2.700311995339117</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.208857770087251</v>
+        <v>1.293513444747964</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.221014634764283</v>
+        <v>5.271808039560711</v>
+      </c>
+    </row>
+    <row r="2086">
+      <c r="A2086" s="2" t="n">
+        <v>45548</v>
+      </c>
+      <c r="B2086" t="n">
+        <v>3.456112387260593</v>
+      </c>
+      <c r="C2086" t="n">
+        <v>4.395711017120513</v>
+      </c>
+      <c r="D2086" t="n">
+        <v>-4.48757888264767</v>
+      </c>
+      <c r="E2086" t="n">
+        <v>2.700311995339117</v>
+      </c>
+      <c r="F2086" t="n">
+        <v>1.293513444747964</v>
+      </c>
+      <c r="G2086" t="n">
+        <v>4.388774814106881</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>45.4%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.68</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.2%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>17.5%</t>
+          <t>43.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>98.1%</t>
+          <t>101.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.4%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>40.1%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.7%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.3%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>127.9%</t>
+          <t>135.8%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.1%</t>
+          <t>-77.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.4%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.2%</t>
+          <t>124.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-616.8%</t>
+          <t>-631.0%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.1%</t>
+          <t>-46.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.4%</t>
+          <t>-73.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.0%</t>
+          <t>89.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.9%</t>
+          <t>418.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-6.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.3%</t>
+          <t>-639.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.1%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-247.1%</t>
+          <t>-252.8%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-33.7%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,32 +1165,32 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>29.2%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>47.9%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>1.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-106.2%</t>
+          <t>-118.0%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.0%</t>
+          <t>-6.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>63.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-228.8%</t>
+          <t>-243.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>125.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-325.1%</t>
+          <t>-97.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-94.6%</t>
+          <t>-117.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>72.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>1.17</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.9%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>82.5%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.0%</t>
+          <t>92.7%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-137.6%</t>
+          <t>-146.2%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>40.4%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-15.1%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.2%</t>
+          <t>35.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-7.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.455994000230163</v>
+        <v>-1.598332969419539</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.534166243036052</v>
+        <v>2.477230655360302</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.253873330619843</v>
+        <v>1.111534361430468</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.86924426581377</v>
+        <v>3.783840884300145</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.822062727374816</v>
+        <v>-1.964401696564191</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.38082305148464</v>
+        <v>2.32388746380889</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.88780460347519</v>
+        <v>0.7454656342858149</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.642687328833428</v>
+        <v>3.557283947319803</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.0305535088265</v>
+        <v>-2.172892478015876</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.317765028642734</v>
+        <v>2.260829440966984</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.6793138220235055</v>
+        <v>0.5369748528341305</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.537931149701186</v>
+        <v>3.452527768187561</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.277754693591722</v>
+        <v>-2.420093662781097</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.226983305145214</v>
+        <v>2.170047717469465</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.699467175522318</v>
+        <v>0.5571282063329429</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.558121912209042</v>
+        <v>3.472718530695416</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.770139721615819</v>
+        <v>-2.912478690805194</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.031135685979308</v>
+        <v>1.974200098303558</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.06474317830884618</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.263797287438316</v>
+        <v>3.178393905924691</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.155320112545891</v>
+        <v>-3.297659081735266</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.875606068420142</v>
+        <v>1.818670480744392</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.2070821474982212</v>
+        <v>0.06474317830884618</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.262339826251179</v>
+        <v>3.176936444737554</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.405190792560473</v>
+        <v>-3.547529761749848</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.777426919868925</v>
+        <v>1.720491332193176</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.2433448673286845</v>
+        <v>0.1010058981393094</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.285866581604073</v>
+        <v>3.200463200090448</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.611702569447494</v>
+        <v>-3.754041538636869</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.690928267770375</v>
+        <v>1.633992680094625</v>
       </c>
       <c r="F1857" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1055058787477121</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.158065574128118</v>
+        <v>3.072662192614493</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-3.931046644527996</v>
+        <v>-4.073385613717371</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.564963564438434</v>
+        <v>1.508027976762684</v>
       </c>
       <c r="F1858" t="n">
-        <v>0.036833090441663</v>
+        <v>-0.1055058787477121</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.159838500828378</v>
+        <v>3.074435119314753</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.31725647580377</v>
+        <v>-4.459595444993147</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.396812519395528</v>
+        <v>1.339876931719778</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.05393984927578033</v>
+        <v>-0.1962788184651554</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.091707624465316</v>
+        <v>3.006304242951691</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.551950469936322</v>
+        <v>-4.694289439125699</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.291219696744598</v>
+        <v>1.234284109068848</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.04760358204652515</v>
+        <v>-0.1899425512359002</v>
       </c>
       <c r="G1860" t="n">
-        <v>3.08379415980496</v>
+        <v>2.998390778291335</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-4.887613117166775</v>
+        <v>-5.029952086356151</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.155535229508382</v>
+        <v>1.098599641832632</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.11553456753543</v>
+        <v>-0.257873536724805</v>
       </c>
       <c r="G1861" t="n">
-        <v>3.041616160167582</v>
+        <v>2.956212778653957</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-4.964057447369647</v>
+        <v>-5.106396416559023</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.131445057661475</v>
+        <v>1.074509469985725</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.03508905844176807</v>
+        <v>-0.1774280276311431</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.096371025858021</v>
+        <v>3.010967644344396</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.329184830008393</v>
+        <v>-5.47152379919777</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9846486196118076</v>
+        <v>0.9277130319360576</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.3313998427407806</v>
+        <v>-0.4737388119301557</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.917839070284444</v>
+        <v>2.832435688770819</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.737773607189072</v>
+        <v>-5.880112576378448</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.8199746527542953</v>
+        <v>0.7630390650785452</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.671447347990797</v>
+        <v>2.586043966477171</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.851534019211937</v>
+        <v>-5.993872988401312</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7696559204166098</v>
+        <v>0.7127203327408602</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.666632780462257</v>
+        <v>2.581229398948632</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.267925893498934</v>
+        <v>-6.41026486268831</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.6010932213106881</v>
+        <v>0.5441576336349385</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.664626831071135</v>
+        <v>2.579223449557509</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.629099523315922</v>
+        <v>-6.771438492505298</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.4668824600525721</v>
+        <v>0.409946872376822</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.674885521739814</v>
+        <v>2.589482140226188</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-6.972358042958941</v>
+        <v>-7.114697012148317</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.3256786173410595</v>
+        <v>0.2687430296653099</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.670985086885509</v>
+        <v>2.585581705371884</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.020560860201285</v>
+        <v>-7.16289982939066</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.3048024104991232</v>
+        <v>0.2478668228233731</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.739988619921459</v>
+        <v>-0.8823275891108341</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.669390006940509</v>
+        <v>2.583986625426885</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.187369520175647</v>
+        <v>-7.329708489365022</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.2418579224385864</v>
+        <v>0.1849223347628368</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.9246109128239706</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.647798988641836</v>
+        <v>2.562395607128211</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.37408922848495</v>
+        <v>-7.516428197674325</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1631437345804621</v>
+        <v>0.1062081469047125</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.9246109128239706</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.643772684107433</v>
+        <v>2.558369302593808</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.757090617227581</v>
+        <v>-7.899429586416956</v>
       </c>
       <c r="E1872" t="n">
-        <v>0.009841077761825634</v>
+        <v>-0.04709450991392394</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.7822719436345955</v>
+        <v>-0.9246109128239706</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.643670582785849</v>
+        <v>2.558267201272224</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.761577062428969</v>
+        <v>-7.903916031618345</v>
       </c>
       <c r="E1873" t="n">
-        <v>0.01061801565270049</v>
+        <v>-0.04631757202304954</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.9290973580253592</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.643550231636446</v>
+        <v>2.558146850122821</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.121107384932973</v>
+        <v>-8.263446354122348</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1278438100508503</v>
+        <v>-0.1847793977266003</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.7867583888359841</v>
+        <v>-0.9290973580253592</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.648900534934496</v>
+        <v>2.563497153420871</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.171456448387195</v>
+        <v>-8.31379541757657</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1400674154753618</v>
+        <v>-0.1970030031511114</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.8371074522902062</v>
+        <v>-0.9794464214795813</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.62660711681914</v>
+        <v>2.541203735305515</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.269075725808591</v>
+        <v>-8.411414694997966</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.1760733758221513</v>
+        <v>-0.2330089634979013</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.9347267297116029</v>
+        <v>-1.077065698900978</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.571077300988071</v>
+        <v>2.485673919474446</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.32314722531695</v>
+        <v>-8.465486194506324</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.1948084193039228</v>
+        <v>-0.2517440069796724</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.9887982292199623</v>
+        <v>-1.131137198409337</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.541527957604627</v>
+        <v>2.456124576091002</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.326723011408697</v>
+        <v>-8.469061980598072</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.1907255366219793</v>
+        <v>-0.2476611242977294</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.014327151136455</v>
+        <v>-1.15666612032583</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.531723801573374</v>
+        <v>2.446320420059749</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.360375849917171</v>
+        <v>-8.502714819106545</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.1997041175409326</v>
+        <v>-0.2566397052166827</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.114740519053492</v>
+        <v>-1.257079488242867</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.475958335307588</v>
+        <v>2.390554953793963</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.499461964536028</v>
+        <v>-8.641800933725403</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2399668618950543</v>
+        <v>-0.2969024495708044</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.253826633672349</v>
+        <v>-1.396165602861724</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.407878368029695</v>
+        <v>2.32247498651607</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.674586381922571</v>
+        <v>-8.816925351111946</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.2954614081021552</v>
+        <v>-0.3523969957779047</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.571290020248268</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.317358938345286</v>
+        <v>2.23195555683166</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.909038475937061</v>
+        <v>-9.051377445126436</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.3964614106095468</v>
+        <v>-0.4533969982852968</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.428951051058893</v>
+        <v>-1.571290020248268</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.310139773443689</v>
+        <v>2.224736391930064</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.013413206963508</v>
+        <v>-9.155752176152882</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4448834937941015</v>
+        <v>-0.5018190814698515</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.533325782085339</v>
+        <v>-1.675664751274714</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.240842744053846</v>
+        <v>2.155439362540221</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.175926672662092</v>
+        <v>-9.318265641851466</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5087730902349792</v>
+        <v>-0.5657086779107288</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.630959212504025</v>
+        <v>-1.7732981816934</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.18337847564119</v>
+        <v>2.097975094127565</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.301963466030381</v>
+        <v>-9.444302435219756</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5564940789531803</v>
+        <v>-0.6134296666289298</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.748046558883658</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.20122317795615</v>
+        <v>2.115819796442525</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.24489169413445</v>
+        <v>-9.387230663323825</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5296750345084069</v>
+        <v>-0.5866106221841569</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.748046558883658</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.205213513642551</v>
+        <v>2.119810132128926</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.386563535858571</v>
+        <v>-9.528902505047945</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5878189980967967</v>
+        <v>-0.6447545857725467</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.605707589694283</v>
+        <v>-1.748046558883658</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.20373828674381</v>
+        <v>2.118334905230184</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.336972691433736</v>
+        <v>-9.479311660623111</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5529292501619909</v>
+        <v>-0.6098648378377405</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.556116745269449</v>
+        <v>-1.698455714458824</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.248546203563582</v>
+        <v>2.163142822049957</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.18805435696188</v>
+        <v>-9.330393326151254</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5064130500199311</v>
+        <v>-0.5633486376956811</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.524867154534276</v>
+        <v>-1.667206123723651</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.254244824358003</v>
+        <v>2.168841442844378</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-9.104548173431844</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.4634315035717083</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.625279448136487</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.203576521232885</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-8.979969517094252</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.4124608964806127</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.625279448136487</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.204715665788944</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-8.954932835525742</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.3998124496911011</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.599950360585752</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.222546892481493</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.882799660237861</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.3652254753373119</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.599950360585752</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.228280596720129</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.811433267628214</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.3464161806873181</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.528583967976104</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.261363169892053</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.717974233642989</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.3189160484061362</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.528583967976104</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.251479688579145</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.707321052089558</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.3164893362841372</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.528583967976104</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.249645128079771</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.609414013413067</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.2776268357870015</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.460598218115547</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.290136263022645</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.585460472437109</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.267376913251125</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.43664467713959</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.305176893753713</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.321400534114312</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.1750132540837583</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.172584738816794</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.450352540585638</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.614320910609474</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.1050315616578761</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.172584738816794</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.447565506925337</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.574136612243284</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.1214489048921936</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-1.132400440450603</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.472019709832893</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.410736741303921</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.1861756744886955</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.9690005695112403</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.569426453617268</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-7.177255519074323</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.2874925922183875</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.7355193472816417</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.717439615792879</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-7.027589128066808</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.3444669383084342</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.6426158560391058</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.770289500225442</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.895313654435921</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.2986379137679434</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.5103403824082191</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.750915570411128</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581113469681644</v>
+        <v>-6.723452438871019</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.427133048357291</v>
+        <v>0.370197460681541</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.3384791668433162</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.856847360437706</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.496148802952325</v>
+        <v>-6.638487772141699</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4740252562726774</v>
+        <v>0.4170896685969274</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.2535145001139967</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>2.920732501698957</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.601738792725429</v>
+        <v>-6.744077761914804</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3038133307642168</v>
+        <v>0.2468777430884672</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.359104489887101</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.729402578235876</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.533504208100002</v>
+        <v>-6.675843177289376</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3796515064914745</v>
+        <v>0.3227159188157245</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.340689167014565</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.788996113836484</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.385564166692403</v>
+        <v>-6.527903135881777</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3222067144161072</v>
+        <v>0.2652711267403571</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.3203682511060075</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.684567854743211</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.332594644438414</v>
+        <v>-6.474933613627789</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3346805370642243</v>
+        <v>0.2777449493884743</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.2673987288520186</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.707635581842126</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.166806448478123</v>
+        <v>-6.309145417667498</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3940352033532473</v>
+        <v>0.3370996156774977</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.2673987288520186</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.700674969747033</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.133443241999355</v>
+        <v>-6.275782211188729</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.421842840325898</v>
+        <v>0.364907252650148</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.2673987288520186</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.715137324128176</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.025184104876833</v>
+        <v>-6.167523074066207</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4596786156341017</v>
+        <v>0.4027430279583517</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.2673987288520186</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.709669444587371</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.901892970059702</v>
+        <v>-6.044231939249077</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5064931635715308</v>
+        <v>0.4495575758957808</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>-0.1441075940348881</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.781142219488226</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849196102928411</v>
+        <v>-5.991535072117785</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5352728886613725</v>
+        <v>0.4783373009856229</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>-0.09141072690359692</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.820461318004326</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605430660944966</v>
+        <v>-5.747769630134341</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6285597738018009</v>
+        <v>0.5716241861260514</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>-0.09141072690359692</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.816242026351377</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.515654988568494</v>
+        <v>-5.657993957757869</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6665943566724057</v>
+        <v>0.6096587689966562</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>-0.0298112819892869</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.855326007219979</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.406160668420325</v>
+        <v>-5.533178129792175</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7031341597153755</v>
+        <v>0.652327175166636</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>-0.0298112819892869</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.848068082203681</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.230268575952893</v>
+        <v>-5.357286037324743</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7770901202229972</v>
+        <v>0.7262831356742576</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>-0.0298112819892869</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.85166720572433</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.05882211293043</v>
+        <v>-5.185839574302279</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8589962114865362</v>
+        <v>0.8081892269377966</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.1416351810331762</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>2.967862589592361</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.978799825821309</v>
+        <v>-5.105817287193158</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8900256039464818</v>
+        <v>0.8392186193977418</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.2216574681422972</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.014896439474131</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.915164083587374</v>
+        <v>-5.042181544959224</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.9201747018943727</v>
+        <v>0.8693677173456331</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.2852932103762317</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.057772685868809</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.821466765370979</v>
+        <v>-4.948484226742829</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9388478879647264</v>
+        <v>0.8880409034159866</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.2852932103762317</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.038966944652604</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.831969388436268</v>
+        <v>-4.958986849808118</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9363899153634883</v>
+        <v>0.8855829308147485</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.2747905873109429</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.034408447438309</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.719483127767393</v>
+        <v>-4.846500589139243</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9853137334658584</v>
+        <v>0.9345067489171184</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.2747905873109429</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.038337761273129</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.701769440889528</v>
+        <v>-4.828786902261378</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9930777921343443</v>
+        <v>0.9422708075856046</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.2779719162078597</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.040925142528619</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.57829516957651</v>
+        <v>-4.705312630948359</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.039465571879545</v>
+        <v>0.9886585873308054</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.2779719162078597</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.037923213748612</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.358274371539499</v>
+        <v>-4.485291832911349</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.129052928104963</v>
+        <v>1.078245943556224</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.4191917612758399</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.124234157800015</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.225406682476222</v>
+        <v>-4.352424143848071</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.198094186532098</v>
+        <v>1.147287201983358</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.4191917612758399</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.140128340601838</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.105233599111723</v>
+        <v>-4.232251060483573</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.247309264318199</v>
+        <v>1.196502279769459</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.5393648446403388</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.213378035060839</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.969980237781746</v>
+        <v>-4.096997699153595</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.31149871141163</v>
+        <v>1.26069172686289</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.674618205970316</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.304618154420266</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.029855065139438</v>
+        <v>-4.156872526511288</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.273586271869979</v>
+        <v>1.222779287321239</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.6147433786126238</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.254730749407076</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.910034834228601</v>
+        <v>-4.037052295600451</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.336803533468522</v>
+        <v>1.285996548919782</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.6147433786126238</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.270019918641284</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.912504540690407</v>
+        <v>-4.039522002062257</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.243459850206242</v>
+        <v>1.192652865657502</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.6122736721508177</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.176182294086642</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.980874727014417</v>
+        <v>-4.107892188386267</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.135373637161939</v>
+        <v>1.084566652613199</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.6215493711870327</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.101009574993673</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.092747006640567</v>
+        <v>-4.219764468012418</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.08106143394337</v>
+        <v>1.03025444939463</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.6215493711870327</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.091446283625564</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.148267082533157</v>
+        <v>-4.275284543905007</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.195884240278537</v>
+        <v>1.145077255729796</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.6215493711870327</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.228477120317766</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.972792822740688</v>
+        <v>-4.099810284112538</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.270641176187312</v>
+        <v>1.219834191638572</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.6215493711870327</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.233044352309554</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.964868448155773</v>
+        <v>-4.091885909527623</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.249552954782485</v>
+        <v>1.198745970233745</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.6215493711870327</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.208786381070762</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.958590245585925</v>
+        <v>-4.085607706957775</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.180602549211874</v>
+        <v>1.129795564663134</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.6278275737568817</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.14109161601412</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.898737626382201</v>
+        <v>-4.025755087754051</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.214715983325496</v>
+        <v>1.163908998776756</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.6278275737568817</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.151264002446253</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.812494163355824</v>
+        <v>-3.939511624727674</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.244159639109907</v>
+        <v>1.193352654561167</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.6278275737568817</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.146210273020113</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.857800982754804</v>
+        <v>-3.984818444126653</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.217812686794841</v>
+        <v>1.167005702246101</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.5870174107476509</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.1134999506591</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.886834087457105</v>
+        <v>-4.013851548828955</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.206751317947022</v>
+        <v>1.155944333398282</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.5870174107476509</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.114051823692202</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.794023606006246</v>
+        <v>-3.921041067378095</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.173148202418731</v>
+        <v>1.122341217869991</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.6798278921985103</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.099010804454083</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.838413075335674</v>
+        <v>-3.965430536707523</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.157265890611561</v>
+        <v>1.106458906062821</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.6354384228690826</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.074250598781027</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.817909381450177</v>
+        <v>-3.944926842822026</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.160543076677483</v>
+        <v>1.109736092128743</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.6559421167545799</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.081628523624049</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.857833476032749</v>
+        <v>-3.984850937404597</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.150064734675121</v>
+        <v>1.099257750126382</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.6559421167545799</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.087119819454716</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.889995844436888</v>
+        <v>-4.01263133530595</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.148696989082004</v>
+        <v>1.099642792734379</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7661187175398151</v>
+        <v>0.6281617188532269</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.164722981694396</v>
+        <v>3.081948782482443</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.008376517167027</v>
+        <v>-4.131012008036088</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9397004399906022</v>
+        <v>0.8906462436429774</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.5609438667022507</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.962747990404464</v>
+        <v>2.879973791192511</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.116990595610358</v>
+        <v>-4.23962608647942</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.016404469332475</v>
+        <v>0.9673502729848507</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.5609438667022507</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.082897651123669</v>
+        <v>3.000123451911716</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.081581557362215</v>
+        <v>-4.204217048231277</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.045081110734055</v>
+        <v>0.9960269143864307</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6989008653888389</v>
+        <v>0.5609438667022507</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.097410677225992</v>
+        <v>3.014636478014039</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.043197894804064</v>
+        <v>-4.165833385673126</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.057854017099685</v>
+        <v>1.00879982075206</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7372845279469901</v>
+        <v>0.5993275292604019</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.117860316103251</v>
+        <v>3.035086116891299</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.866081564768898</v>
+        <v>-3.988717055637959</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.125429577959053</v>
+        <v>1.076375381611428</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7372845279469901</v>
+        <v>0.5993275292604019</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.114589344948554</v>
+        <v>3.0318151457366</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.911173809602444</v>
+        <v>-4.033809300471505</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.108076071787548</v>
+        <v>1.059021875439923</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6753884847776003</v>
+        <v>0.5374314860910121</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.078135110808833</v>
+        <v>2.99536091159688</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.731798388363676</v>
+        <v>-3.854433879232738</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.173613215589469</v>
+        <v>1.124559019241844</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.832165242948319</v>
+        <v>0.6942082442617308</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.165988141017678</v>
+        <v>3.083213941805726</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.776812601884282</v>
+        <v>-3.899448092753344</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.136414985512817</v>
+        <v>1.087360789165192</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8018163476337143</v>
+        <v>0.6638593489471262</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.128586259160505</v>
+        <v>3.045812059948553</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.043817112156717</v>
+        <v>-4.166452603025779</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.035304743742788</v>
+        <v>0.9862505473951633</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6074533095907657</v>
+        <v>0.4694963109041776</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.017659998673682</v>
+        <v>2.934885799461729</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.14501489359389</v>
+        <v>-4.267650384462952</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9940295530644203</v>
+        <v>0.9449753567167956</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5390444960454466</v>
+        <v>0.4010874973588584</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.975818632442992</v>
+        <v>2.893044433231039</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.138503926979578</v>
+        <v>-4.261139417848639</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9942339012644621</v>
+        <v>0.9451797049168373</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5390444960454466</v>
+        <v>0.4010874973588584</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.973418593997309</v>
+        <v>2.890644394785356</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.11946579927228</v>
+        <v>-4.242101290141342</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9983738715556258</v>
+        <v>0.9493196752080013</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.480860884714252</v>
+        <v>0.3429038860276639</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.935033146406837</v>
+        <v>2.852258947194884</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.171981601547101</v>
+        <v>-4.294617092416162</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.096661952279888</v>
+        <v>1.047607755932263</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.480860884714252</v>
+        <v>0.3429038860276639</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.054327548041027</v>
+        <v>2.971553348829074</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.17538991298168</v>
+        <v>-4.298025403850742</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.09613195669219</v>
+        <v>1.047077760344565</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5133774537236294</v>
+        <v>0.3754204550370412</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.074670818432787</v>
+        <v>2.991896619220834</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.134906921059335</v>
+        <v>-4.257542411928397</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.118333683858054</v>
+        <v>1.069279487510429</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5133774537236294</v>
+        <v>0.3754204550370412</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.080679348829713</v>
+        <v>2.99790514961776</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.987163950824333</v>
+        <v>-4.109799441693395</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.075381093229254</v>
+        <v>1.026326896881629</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6811848109585126</v>
+        <v>0.5432278122719244</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.079313984447842</v>
+        <v>2.996539785235889</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.070985172099031</v>
+        <v>-4.193620662968093</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.044646226250856</v>
+        <v>0.9955920299032313</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6811848109585126</v>
+        <v>0.5432278122719244</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.082107605979323</v>
+        <v>2.99933340676737</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.064832466046247</v>
+        <v>-4.187467956915309</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.047769657063628</v>
+        <v>0.9987154607160034</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6873375170112969</v>
+        <v>0.5493805183247087</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.086461578002652</v>
+        <v>3.003687378790699</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.081641764196749</v>
+        <v>-4.204277255065811</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.040126414543537</v>
+        <v>0.9910722181959128</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.6705282188607953</v>
+        <v>0.532571220174207</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.075456475852462</v>
+        <v>2.992682276640509</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.019343765420627</v>
+        <v>-4.141979256289688</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.131381167850807</v>
+        <v>1.082326971503182</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7158224831352373</v>
+        <v>0.577865484448649</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.168968588213948</v>
+        <v>3.086194389001995</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.817553567755469</v>
+        <v>-3.94018905862453</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.014389248630998</v>
+        <v>0.9653350522833728</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9138406753043917</v>
+        <v>0.7758836766178034</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.090071505229568</v>
+        <v>3.007297306017614</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.868440280441663</v>
+        <v>-3.991075771310725</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.064324795878695</v>
+        <v>1.01527059953107</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8629539626181972</v>
+        <v>0.724996963931609</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.129829709940026</v>
+        <v>3.047055510728073</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.781829537791856</v>
+        <v>-3.904465028660918</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.113596829054661</v>
+        <v>1.064542632707037</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9415796938233555</v>
+        <v>0.8036226951367672</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.191632884779165</v>
+        <v>3.108858685567212</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.84203883579714</v>
+        <v>-3.964674326666202</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.088049090677219</v>
+        <v>1.038994894329595</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.881370395818071</v>
+        <v>0.7434133971314827</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.154043286800666</v>
+        <v>3.071269087588712</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.792852187112789</v>
+        <v>-3.915487677981851</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.106215368190888</v>
+        <v>1.057161171843264</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.881370395818071</v>
+        <v>0.7434133971314827</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.152534904840594</v>
+        <v>3.069760705628641</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.74847905547422</v>
+        <v>-3.871114546343282</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.123827488281752</v>
+        <v>1.074773291934127</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9257435274566396</v>
+        <v>0.7877865287700513</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.179021651259172</v>
+        <v>3.096247452047218</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.770959406333105</v>
+        <v>-3.893594897202167</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.109229142076789</v>
+        <v>1.060174945729164</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9257435274566396</v>
+        <v>0.7877865287700513</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.173415445397762</v>
+        <v>3.090641246185809</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.723303675772049</v>
+        <v>-3.845939166641111</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.134673191329016</v>
+        <v>1.085618994981391</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.9733992580176952</v>
+        <v>0.8354422593311069</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.2083906407622</v>
+        <v>3.125616441550247</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.622785517273295</v>
+        <v>-3.745421008142356</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.179772828103242</v>
+        <v>1.130718631755617</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.07391741651645</v>
+        <v>0.9359604178298615</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.273593909236177</v>
+        <v>3.190819710024225</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.606880187840942</v>
+        <v>-3.729515678710004</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.172889632352055</v>
+        <v>1.123835436004431</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9948047558072108</v>
+        <v>0.8568477571206226</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.212880985286506</v>
+        <v>3.130106786074554</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.562041786232544</v>
+        <v>-3.684677277101606</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.194922695606043</v>
+        <v>1.145868499258419</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.9993481887520803</v>
+        <v>0.861391190065492</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.219704747664057</v>
+        <v>3.136930548452104</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.581540242474552</v>
+        <v>-3.704175733343614</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.191284252740318</v>
+        <v>1.142230056392693</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.951263547472176</v>
+        <v>0.8133065487855877</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.195014902527192</v>
+        <v>3.112240703315239</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.537337405388652</v>
+        <v>-3.659972896257714</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.214844990102515</v>
+        <v>1.165790793754891</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9954663845580765</v>
+        <v>0.8575093858714882</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.22741620730657</v>
+        <v>3.144642008094617</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.544897071225699</v>
+        <v>-3.667532562094761</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.210231124236944</v>
+        <v>1.161176927889319</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.050269788567896</v>
+        <v>0.9123127898813075</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.258708250181709</v>
+        <v>3.175934050969756</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.386605653686427</v>
+        <v>-3.509241144555488</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.324795456435693</v>
+        <v>1.275741260088068</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.050269788567896</v>
+        <v>0.9123127898813075</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.309956015364748</v>
+        <v>3.227181816152795</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.17896365005195</v>
+        <v>-3.301599140921012</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.406292962483736</v>
+        <v>1.357238766136112</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.257911792202372</v>
+        <v>1.119954793515784</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.432981922139687</v>
+        <v>3.350207722927734</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.127931557329422</v>
+        <v>-3.250567048198484</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.421654027811017</v>
+        <v>1.372599831463393</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.3089438849249</v>
+        <v>1.170986886238312</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.458549406011474</v>
+        <v>3.375775206799521</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.062707376202217</v>
+        <v>-3.185342867071278</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.464931104354605</v>
+        <v>1.41587690800698</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.374168066052105</v>
+        <v>1.236211067365517</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.514871318780502</v>
+        <v>3.432097119568549</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.025280356131083</v>
+        <v>-3.147915847000144</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.475862884682339</v>
+        <v>1.426808688334714</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.379419604081287</v>
+        <v>1.241462605394699</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.513983213897292</v>
+        <v>3.431209014685339</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.045392012165791</v>
+        <v>-3.168027503034853</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.469075014599696</v>
+        <v>1.420020818252071</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.390446949078706</v>
+        <v>1.252489950392118</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.521856413226983</v>
+        <v>3.439082214015031</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.016978749065907</v>
+        <v>-3.139614239934969</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.64099809086086</v>
+        <v>1.591943894513235</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.331471386332278</v>
+        <v>1.19351438764569</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.647028846600337</v>
+        <v>3.564254647388384</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.942196488040895</v>
+        <v>-3.064831978909957</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.791023904488682</v>
+        <v>1.741969708141057</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.40625364735729</v>
+        <v>1.268296648670702</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.812011112433161</v>
+        <v>3.729236913221209</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.916112403777087</v>
+        <v>-3.038747894646149</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.793165514208064</v>
+        <v>1.744111317860439</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.40625364735729</v>
+        <v>1.268296648670702</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.80371908844702</v>
+        <v>3.720944889235068</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.828234490667966</v>
+        <v>-2.950869981537028</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.826509875035492</v>
+        <v>1.777455678687867</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.522179289780641</v>
+        <v>1.384222291094053</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.871467669484811</v>
+        <v>3.788693470272858</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.819342029274683</v>
+        <v>-2.941977520143745</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.847621265319597</v>
+        <v>1.798567068971972</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.522179289780641</v>
+        <v>1.384222291094053</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.889022075211602</v>
+        <v>3.806247875999649</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.826439103752724</v>
+        <v>-3.110453637113622</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.836637482932964</v>
+        <v>1.723031669588605</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.583269099227561</v>
+        <v>1.356274455377472</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.917531008284338</v>
+        <v>3.781334221974285</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.380182911123285</v>
+        <v>-2.664197444484182</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.996409657172602</v>
+        <v>1.882803843828243</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.488550429557928</v>
+        <v>1.26155578570784</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.84196950367042</v>
+        <v>3.705772717360367</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.357461807440132</v>
+        <v>-2.64147634080103</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.996162121142767</v>
+        <v>1.882556307798408</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.488550429557928</v>
+        <v>1.26155578570784</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.832633526167325</v>
+        <v>3.696436739857272</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.486663620734175</v>
+        <v>-2.770678154095072</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.10338752167632</v>
+        <v>1.98978170833196</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.359348616263886</v>
+        <v>1.132353972413797</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.914018564042069</v>
+        <v>3.777821777732015</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.512538019208201</v>
+        <v>-2.796552552569098</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.130115584780356</v>
+        <v>2.016509771435997</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.404260224975627</v>
+        <v>1.177265581125539</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.97804335176276</v>
+        <v>3.841846565452706</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.505483328993027</v>
+        <v>-2.789497862353925</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.12961281685597</v>
+        <v>2.016007003511611</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.411314915190801</v>
+        <v>1.184320271340712</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.97895152188141</v>
+        <v>3.842754735571356</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.478532104666539</v>
+        <v>-2.762546638027437</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.150399460231307</v>
+        <v>2.036793646886948</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.42619526121852</v>
+        <v>1.199200617368432</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.997885883142782</v>
+        <v>3.861689096832729</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.500076332497326</v>
+        <v>-2.784090865858224</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.325884901243952</v>
+        <v>2.212279087899593</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.42619526121852</v>
+        <v>1.199200617368432</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.181989015287742</v>
+        <v>4.045792228977689</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.522484450302198</v>
+        <v>-2.806498983663096</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.309038349024996</v>
+        <v>2.195432535680637</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.42619526121852</v>
+        <v>1.199200617368432</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.174105710190736</v>
+        <v>4.037908923880682</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.550708685879798</v>
+        <v>-2.834723219240696</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.299802654343593</v>
+        <v>2.186196840999235</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.444172013669829</v>
+        <v>1.21717736981974</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.186945761211158</v>
+        <v>4.050748974901104</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.560149611768328</v>
+        <v>-2.844164145129226</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.352280001710029</v>
+        <v>2.238674188365669</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.56659913121322</v>
+        <v>1.339604487363132</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.31665574945904</v>
+        <v>4.180458963148986</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.649026242936802</v>
+        <v>-2.9330407762977</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.31962044378794</v>
+        <v>2.206014630443581</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.477722500044746</v>
+        <v>1.250727856194658</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.266220865303256</v>
+        <v>4.130024078993203</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.725356220537708</v>
+        <v>-3.009370753898606</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.287200265641353</v>
+        <v>2.173594452296994</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.477722500044746</v>
+        <v>1.250727856194658</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.264332678197031</v>
+        <v>4.128135891886978</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.81902016521525</v>
+        <v>-3.103034698576147</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.244554917373199</v>
+        <v>2.13094910402884</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.384058555367205</v>
+        <v>1.157063911517116</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.202954540993369</v>
+        <v>4.066757754683316</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.980588590742505</v>
+        <v>-3.264603124103402</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.178361557372449</v>
+        <v>2.06475574402809</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.257275631569326</v>
+        <v>1.030280987719237</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.125318796924794</v>
+        <v>3.98912201061474</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.088889252612624</v>
+        <v>-3.372903785973522</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.14811469949032</v>
+        <v>2.034508886145961</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.257275631569326</v>
+        <v>1.030280987719237</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.138392203790712</v>
+        <v>4.002195417480659</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.106693224333368</v>
+        <v>-3.390707757694266</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.132998307584962</v>
+        <v>2.019392494240603</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.186741008664125</v>
+        <v>0.9597463648140359</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.088076626830532</v>
+        <v>3.951879840520478</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.134594011442841</v>
+        <v>-3.418608544803739</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.120362033868175</v>
+        <v>2.006756220523815</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.15214408452119</v>
+        <v>0.9251494406711011</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.065842513471773</v>
+        <v>3.929645727161719</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.257120114145735</v>
+        <v>-3.541134647506633</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.068116036764216</v>
+        <v>1.954510223419857</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.029617981818296</v>
+        <v>0.8026233379682072</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.989091295827235</v>
+        <v>3.852894509517182</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.487634610331324</v>
+        <v>-3.771649143692222</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.042616197880484</v>
+        <v>1.929010384536125</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7991034856327073</v>
+        <v>0.5721088417826184</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.917488557706386</v>
+        <v>3.781291771396332</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.836379695555768</v>
+        <v>-4.120394228916665</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.043429882792553</v>
+        <v>1.929824069448195</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6903555317138095</v>
+        <v>0.4633608878637206</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.992551504356894</v>
+        <v>3.856354718046841</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.990366113331908</v>
+        <v>-4.274380646692806</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.050815584827737</v>
+        <v>1.937209771483378</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6903555317138095</v>
+        <v>0.4633608878637206</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.061531773502534</v>
+        <v>3.92533498719248</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.939844209504242</v>
+        <v>-4.22385874286514</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.057075548478925</v>
+        <v>1.943469735134566</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6903555317138095</v>
+        <v>0.4633608878637206</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.047582975622655</v>
+        <v>3.911386189312601</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.192319363511967</v>
+        <v>-4.476333896872864</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.967955975931249</v>
+        <v>1.85435016258689</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6903555317138095</v>
+        <v>0.4633608878637206</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.059453464678069</v>
+        <v>3.923256678368015</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.485215119991379</v>
+        <v>-4.769229653352276</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.852008207858428</v>
+        <v>1.738402394514069</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6903555317138095</v>
+        <v>0.4633608878637206</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.060663999197012</v>
+        <v>3.924467212886959</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.671879248126187</v>
+        <v>-4.955893781487084</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.781464298831826</v>
+        <v>1.667858485487467</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6636165608892496</v>
+        <v>0.4366219170391608</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.048742358929598</v>
+        <v>3.912545572619544</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.817899935040149</v>
+        <v>-5.101914468401047</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.71813387680243</v>
+        <v>1.604528063458071</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6545334690953926</v>
+        <v>0.4275388252453038</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.038370356589473</v>
+        <v>3.90217357027942</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.909613944149735</v>
+        <v>-5.193628477510632</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.84365232985764</v>
+        <v>1.730046516513281</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6545334690953926</v>
+        <v>0.4275388252453038</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.200574413288518</v>
+        <v>4.064377626978464</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.941265603209704</v>
+        <v>-5.225280136570602</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.825838304197467</v>
+        <v>1.712232490853108</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6493650118509524</v>
+        <v>0.4223703680008636</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.192319976905667</v>
+        <v>4.056123190595614</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.023200421478587</v>
+        <v>-5.307214954839485</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.803293794458404</v>
+        <v>1.689687981114045</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6394302662638722</v>
+        <v>0.4124356224137834</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.196588547121911</v>
+        <v>4.060391760811857</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.125176543726995</v>
+        <v>-5.409191077087892</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.771428984014944</v>
+        <v>1.657823170670585</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5374541440154647</v>
+        <v>0.3104595001653758</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.144328512228769</v>
+        <v>4.008131725918715</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.015170260249773</v>
+        <v>-5.299184793610671</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.807584384650008</v>
+        <v>1.693978571305649</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5606587159327399</v>
+        <v>0.333664072082651</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.150404142623309</v>
+        <v>4.014207356313255</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.872110684508847</v>
+        <v>-5.156125217869745</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.869058225668353</v>
+        <v>1.755452412323994</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5686721425227191</v>
+        <v>0.3416774986726303</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.159462209299271</v>
+        <v>4.023265422989217</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.57066395903701</v>
+        <v>-4.854678492397907</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.996897798739623</v>
+        <v>1.883291985395265</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8701188679945564</v>
+        <v>0.6431242241444676</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.347591127464909</v>
+        <v>4.211394341154856</v>
       </c>
     </row>
     <row r="2030">
@@ -48241,16 +48241,16 @@
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.595254203272193</v>
+        <v>-4.879268736633091</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.988032878798261</v>
+        <v>1.874427065453902</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8701188679945564</v>
+        <v>0.6431242241444676</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.348562305217619</v>
+        <v>4.212365518907566</v>
       </c>
     </row>
     <row r="2031">
@@ -48264,16 +48264,16 @@
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.544215827265673</v>
+        <v>-4.828230360626571</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.009291133580624</v>
+        <v>1.895685320236265</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8701188679945564</v>
+        <v>0.6431242241444676</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.349405209597375</v>
+        <v>4.213208423287321</v>
       </c>
     </row>
     <row r="2032">
@@ -48287,16 +48287,16 @@
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.503076532399042</v>
+        <v>-4.78709106575994</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.044784950401422</v>
+        <v>1.931179137057063</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9112581628611872</v>
+        <v>0.6842635190110984</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.393126885391499</v>
+        <v>4.256930099081446</v>
       </c>
     </row>
     <row r="2033">
@@ -48310,16 +48310,16 @@
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.406441620380402</v>
+        <v>-4.6904561537413</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.899622911332813</v>
+        <v>1.786017097988454</v>
       </c>
       <c r="F2033" t="n">
-        <v>1.007893074879827</v>
+        <v>0.7808984310297383</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.267291828726617</v>
+        <v>4.131095042416564</v>
       </c>
     </row>
     <row r="2034">
@@ -48333,16 +48333,16 @@
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.537022354911245</v>
+        <v>-4.821036888272142</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.85089266159444</v>
+        <v>1.737286848250081</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8773123403489846</v>
+        <v>0.6503176964988958</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.192445432082076</v>
+        <v>4.056248645772023</v>
       </c>
     </row>
     <row r="2035">
@@ -48356,16 +48356,16 @@
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.372526020720283</v>
+        <v>-4.656540554081181</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.901118014346907</v>
+        <v>1.787512201002548</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.041808674539947</v>
+        <v>0.8148140306898577</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.275570051672736</v>
+        <v>4.139373265362682</v>
       </c>
     </row>
     <row r="2036">
@@ -48379,16 +48379,16 @@
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.29542741917841</v>
+        <v>-4.579441952539308</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.931145165400086</v>
+        <v>1.817539352055727</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.041808674539947</v>
+        <v>0.8148140306898577</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.274757762109165</v>
+        <v>4.138560975799113</v>
       </c>
     </row>
     <row r="2037">
@@ -48402,16 +48402,16 @@
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.3058126140683</v>
+        <v>-4.589827147429197</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.936859866569203</v>
+        <v>1.823254053224844</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.031423479650057</v>
+        <v>0.8044288357999684</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.278395424300305</v>
+        <v>4.142198637990251</v>
       </c>
     </row>
     <row r="2038">
@@ -48425,16 +48425,16 @@
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.324400772790525</v>
+        <v>-4.608415306151422</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.000261608856738</v>
+        <v>1.886655795512379</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.012835320927832</v>
+        <v>0.7858406770777431</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.338079534843394</v>
+        <v>4.201882748533341</v>
       </c>
     </row>
     <row r="2039">
@@ -48448,16 +48448,16 @@
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.324699319486561</v>
+        <v>-4.608713852847458</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.997011200996622</v>
+        <v>1.883405387652263</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.012536774231796</v>
+        <v>0.7855421303817072</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.334769417644071</v>
+        <v>4.198572631334018</v>
       </c>
     </row>
     <row r="2040">
@@ -48471,16 +48471,16 @@
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.223876185796133</v>
+        <v>-4.507890719157031</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.041871349412185</v>
+        <v>1.928265536067825</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.02500098971615</v>
+        <v>0.798006345866061</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.346778841874075</v>
+        <v>4.210582055564021</v>
       </c>
     </row>
     <row r="2041">
@@ -48494,16 +48494,16 @@
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.033094825043726</v>
+        <v>-4.317109358404624</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.118313147191691</v>
+        <v>2.004707333847331</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.215782350468557</v>
+        <v>0.9887877066184685</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.461376911804063</v>
+        <v>4.325180125494009</v>
       </c>
     </row>
     <row r="2042">
@@ -48517,16 +48517,16 @@
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.926131467194304</v>
+        <v>-4.210146000555202</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.140935336069056</v>
+        <v>2.027329522724696</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.274246958428359</v>
+        <v>1.04725231457827</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.47629252231754</v>
+        <v>4.340095736007487</v>
       </c>
     </row>
     <row r="2043">
@@ -48540,16 +48540,16 @@
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.870800879292542</v>
+        <v>-4.15481541265344</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.198034507841819</v>
+        <v>2.08442869449746</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.329577546330121</v>
+        <v>1.102582902480032</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.544457811670656</v>
+        <v>4.408261025360603</v>
       </c>
     </row>
     <row r="2044">
@@ -48563,16 +48563,16 @@
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.85874675237958</v>
+        <v>-4.142761285740477</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.196542726508442</v>
+        <v>2.082936913164083</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.341631673243084</v>
+        <v>1.114637029392995</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.545376855719871</v>
+        <v>4.409180069409818</v>
       </c>
     </row>
     <row r="2045">
@@ -48586,16 +48586,16 @@
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.8999018719478</v>
+        <v>-4.183916405308698</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.181961308865289</v>
+        <v>2.06835549552093</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.300476553674863</v>
+        <v>1.073481909824774</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.522564414163075</v>
+        <v>4.386367627853021</v>
       </c>
     </row>
     <row r="2046">
@@ -48609,16 +48609,16 @@
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.831853309256271</v>
+        <v>-4.115867842617168</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.222031759819783</v>
+        <v>2.108425946475425</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.368525116366393</v>
+        <v>1.141530472516304</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.576244577655875</v>
+        <v>4.440047791345822</v>
       </c>
     </row>
     <row r="2047">
@@ -48632,16 +48632,16 @@
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.063453702425772</v>
+        <v>-4.347468235786669</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.149594272725578</v>
+        <v>2.035988459381219</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.368525116366393</v>
+        <v>1.141530472516304</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.596447247829469</v>
+        <v>4.460250461519416</v>
       </c>
     </row>
     <row r="2048">
@@ -48655,16 +48655,16 @@
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.113505247954992</v>
+        <v>-4.397519781315887</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.113179890580771</v>
+        <v>1.999574077236413</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.368525116366393</v>
+        <v>1.141530472516304</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.580053483896351</v>
+        <v>4.443856697586298</v>
       </c>
     </row>
     <row r="2049">
@@ -48678,16 +48678,16 @@
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.288612080531436</v>
+        <v>-4.572626613892332</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.00338907114366</v>
+        <v>1.889783257799302</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.368525116366393</v>
+        <v>1.141530472516304</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.540305397489818</v>
+        <v>4.404108611179764</v>
       </c>
     </row>
     <row r="2050">
@@ -48701,16 +48701,16 @@
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.092511927100913</v>
+        <v>-4.376526460461809</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.088851751512809</v>
+        <v>1.975245938168451</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.564625269796915</v>
+        <v>1.337630625946827</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.664988108545072</v>
+        <v>4.528791322235018</v>
       </c>
     </row>
     <row r="2051">
@@ -48724,16 +48724,16 @@
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.939486534987629</v>
+        <v>-4.223501068348525</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.249232907931027</v>
+        <v>2.13562709458667</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.717650661910199</v>
+        <v>1.490656018060111</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.855974343385946</v>
+        <v>4.719777557075894</v>
       </c>
     </row>
     <row r="2052">
@@ -48747,16 +48747,16 @@
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.967793848860899</v>
+        <v>-4.251808382221795</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.425376207290012</v>
+        <v>2.311770393945654</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.717650661910199</v>
+        <v>1.490656018060111</v>
       </c>
       <c r="G2052" t="n">
-        <v>5.043440568294239</v>
+        <v>4.907243781984185</v>
       </c>
     </row>
     <row r="2053">
@@ -48770,16 +48770,16 @@
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.134387073974422</v>
+        <v>-4.418401607335317</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.328141868598685</v>
+        <v>2.214536055254327</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.551057436796677</v>
+        <v>1.324062792946588</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.912887584580208</v>
+        <v>4.776690798270154</v>
       </c>
     </row>
     <row r="2054">
@@ -48793,16 +48793,16 @@
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.111351280612856</v>
+        <v>-4.395365813973751</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.34103258860503</v>
+        <v>2.227426775260671</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.551057436796677</v>
+        <v>1.324062792946588</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.916563987241926</v>
+        <v>4.780367200931872</v>
       </c>
     </row>
     <row r="2055">
@@ -48816,16 +48816,16 @@
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.082105300157159</v>
+        <v>-4.366119833518055</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.350349035910804</v>
+        <v>2.236743222566445</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.551057436796677</v>
+        <v>1.324062792946588</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.914182042365421</v>
+        <v>4.777985256055367</v>
       </c>
     </row>
     <row r="2056">
@@ -48839,16 +48839,16 @@
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.18903084803501</v>
+        <v>-4.473045381395906</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.304872055917298</v>
+        <v>2.19126624257294</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.444131888918826</v>
+        <v>1.217137245068737</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.847319952796345</v>
+        <v>4.711123166486292</v>
       </c>
     </row>
     <row r="2057">
@@ -48862,16 +48862,16 @@
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.334049406542259</v>
+        <v>-4.618063939903155</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.248293434657633</v>
+        <v>2.134687621313274</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.299113330411577</v>
+        <v>1.072118686561488</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.76173761983523</v>
+        <v>4.625540833525177</v>
       </c>
     </row>
     <row r="2058">
@@ -48885,16 +48885,16 @@
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.452391172326976</v>
+        <v>-4.736405705687872</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.300887967601499</v>
+        <v>2.18728215425714</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.309799368974467</v>
+        <v>1.082804725124379</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.868080482230718</v>
+        <v>4.731883695920664</v>
       </c>
     </row>
     <row r="2059">
@@ -48908,16 +48908,16 @@
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.503801594647684</v>
+        <v>-4.78781612800858</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.278109495799154</v>
+        <v>2.164503682454796</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.309799368974467</v>
+        <v>1.082804725124379</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.865866179356656</v>
+        <v>4.729669393046603</v>
       </c>
     </row>
     <row r="2060">
@@ -48931,16 +48931,16 @@
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.583221045855436</v>
+        <v>-4.867235579216332</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.246244843390343</v>
+        <v>2.132639030045985</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.309799368974467</v>
+        <v>1.082804725124379</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.865769307430946</v>
+        <v>4.729572521120892</v>
       </c>
     </row>
     <row r="2061">
@@ -48954,16 +48954,16 @@
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.678684043772654</v>
+        <v>-4.962698577133549</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.2080535377815</v>
+        <v>2.094447724437141</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.309799368974467</v>
+        <v>1.082804725124379</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.865763200988989</v>
+        <v>4.729566414678936</v>
       </c>
     </row>
     <row r="2062">
@@ -48977,16 +48977,16 @@
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.614308132921939</v>
+        <v>-4.898322666282835</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.231900298684396</v>
+        <v>2.118294485340038</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.374175279825183</v>
+        <v>1.147180635975094</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.902485144062029</v>
+        <v>4.766288357751975</v>
       </c>
     </row>
     <row r="2063">
@@ -49000,16 +49000,16 @@
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.669677295054132</v>
+        <v>-4.953691828415028</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.215486451579245</v>
+        <v>2.101880638234887</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.374175279825183</v>
+        <v>1.147180635975094</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.908218961809755</v>
+        <v>4.772022175499702</v>
       </c>
     </row>
     <row r="2064">
@@ -49023,16 +49023,16 @@
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.71511507488496</v>
+        <v>-4.999129608245855</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.196849702989846</v>
+        <v>2.083243889645488</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.331330289147023</v>
+        <v>1.104335645296934</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.882050330745791</v>
+        <v>4.745853544435739</v>
       </c>
     </row>
     <row r="2065">
@@ -49046,16 +49046,16 @@
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.626908240737381</v>
+        <v>-4.910922774098277</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.252006829499197</v>
+        <v>2.138401016154838</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.331330289147023</v>
+        <v>1.104335645296934</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.90192472359611</v>
+        <v>4.765727937286058</v>
       </c>
     </row>
     <row r="2066">
@@ -49069,16 +49069,16 @@
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.520873245532072</v>
+        <v>-4.804887778892968</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.278121528106048</v>
+        <v>2.16451571476169</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.331330289147023</v>
+        <v>1.104335645296934</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.885625424120838</v>
+        <v>4.749428637810786</v>
       </c>
     </row>
     <row r="2067">
@@ -49092,16 +49092,16 @@
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.337661582398977</v>
+        <v>-4.621676115759873</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.353837142823332</v>
+        <v>2.240231329478974</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.331330289147023</v>
+        <v>1.104335645296934</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.888056373584884</v>
+        <v>4.751859587274831</v>
       </c>
     </row>
     <row r="2068">
@@ -49115,16 +49115,16 @@
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.265940135385126</v>
+        <v>-4.549954668746022</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.348316907476762</v>
+        <v>2.234711094132403</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.403051736160874</v>
+        <v>1.176057092310785</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.896880427641084</v>
+        <v>4.76068364133103</v>
       </c>
     </row>
     <row r="2069">
@@ -49138,16 +49138,16 @@
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.24356710977742</v>
+        <v>-4.527581643138316</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.304181863641016</v>
+        <v>2.190576050296658</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.414307487273775</v>
+        <v>1.187312843423686</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.850549624229997</v>
+        <v>4.714352837919943</v>
       </c>
     </row>
     <row r="2070">
@@ -49161,16 +49161,16 @@
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.276583405688164</v>
+        <v>-4.56059793904906</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.476173550162073</v>
+        <v>2.362567736817715</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.344870110607024</v>
+        <v>1.117875466756935</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.994085403115301</v>
+        <v>4.857888616805248</v>
       </c>
     </row>
     <row r="2071">
@@ -49184,16 +49184,16 @@
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.265055770038556</v>
+        <v>-4.549070303399452</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.472705830250166</v>
+        <v>2.359100016905808</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.403870768808386</v>
+        <v>1.176876124958297</v>
       </c>
       <c r="G2071" t="n">
-        <v>5.021407023864367</v>
+        <v>4.885210237554314</v>
       </c>
     </row>
     <row r="2072">
@@ -49207,16 +49207,16 @@
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.362397271380924</v>
+        <v>-4.64641180474182</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.437437342235007</v>
+        <v>2.323831528890649</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.359450586642898</v>
+        <v>1.132455942792809</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.998423027086863</v>
+        <v>4.86222624077681</v>
       </c>
     </row>
     <row r="2073">
@@ -49230,16 +49230,16 @@
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.448253300720891</v>
+        <v>-4.732267834081787</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.404346012691859</v>
+        <v>2.2907401993475</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.317074517416763</v>
+        <v>1.090079873566674</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.974248467744021</v>
+        <v>4.838051681433967</v>
       </c>
     </row>
     <row r="2074">
@@ -49253,16 +49253,16 @@
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.457090098137011</v>
+        <v>-4.741104631497906</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.383230495545913</v>
+        <v>2.269624682201554</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.309632344775412</v>
+        <v>1.082637700925323</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.952202365979711</v>
+        <v>4.816005579669659</v>
       </c>
     </row>
     <row r="2075">
@@ -49276,16 +49276,16 @@
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.548472660702469</v>
+        <v>-4.832487194063365</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.356841981564779</v>
+        <v>2.24323616822042</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.218249782209954</v>
+        <v>0.9912551383598649</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.907537339485486</v>
+        <v>4.771340553175433</v>
       </c>
     </row>
     <row r="2076">
@@ -49299,16 +49299,16 @@
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.536765942715463</v>
+        <v>-4.820780476076359</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.463652926583849</v>
+        <v>2.350047113239491</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.22995650019696</v>
+        <v>1.002961856346871</v>
       </c>
       <c r="G2076" t="n">
-        <v>5.016689628101958</v>
+        <v>4.880492841791905</v>
       </c>
     </row>
     <row r="2077">
@@ -49322,16 +49322,16 @@
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.437102438631801</v>
+        <v>-4.721116971992696</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.506550666948719</v>
+        <v>2.39294485360436</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.293143583400646</v>
+        <v>1.066148939550558</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.057634216755575</v>
+        <v>4.921437430445521</v>
       </c>
     </row>
     <row r="2078">
@@ -49345,16 +49345,16 @@
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.447418536798152</v>
+        <v>-4.731433070159048</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.715329060960237</v>
+        <v>2.601723247615878</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.293143583400646</v>
+        <v>1.066148939550558</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.270539050033633</v>
+        <v>5.134342263723579</v>
       </c>
     </row>
     <row r="2079">
@@ -49368,16 +49368,16 @@
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.44732456878078</v>
+        <v>-4.731339102141676</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.714545315079275</v>
+        <v>2.600939501734917</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.269939633754113</v>
+        <v>5.13374284744406</v>
       </c>
     </row>
     <row r="2080">
@@ -49391,16 +49391,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.454543392980624</v>
+        <v>-4.73855792634152</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.705889771343691</v>
+        <v>2.592283957999333</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.264171619698467</v>
+        <v>5.127974833388413</v>
       </c>
     </row>
     <row r="2081">
@@ -49414,16 +49414,16 @@
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.453594969862586</v>
+        <v>-4.737609503223482</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.706269140590907</v>
+        <v>2.592663327246548</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.264171619698467</v>
+        <v>5.127974833388413</v>
       </c>
     </row>
     <row r="2082">
@@ -49437,16 +49437,16 @@
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.61066342811821</v>
+        <v>-4.894677961479106</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.656169365269749</v>
+        <v>2.542563551925391</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.276899227679559</v>
+        <v>5.140702441369505</v>
       </c>
     </row>
     <row r="2083">
@@ -49460,16 +49460,16 @@
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.604671181329398</v>
+        <v>-4.888685714690294</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.660512262409661</v>
+        <v>2.546906449065303</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.278845226103947</v>
+        <v>5.142648439793893</v>
       </c>
     </row>
     <row r="2084">
@@ -49483,16 +49483,16 @@
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.516113220198631</v>
+        <v>-4.800127753559527</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.689589582879737</v>
+        <v>2.575983769535379</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.272499362121716</v>
+        <v>5.136302575811662</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383091</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.48757888264767</v>
+        <v>-4.782368676056453</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.700311995339117</v>
+        <v>2.582396077975604</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.271808039560711</v>
+        <v>5.135611253250658</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.456112387260593</v>
+        <v>3.71425897897649</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.395711017120513</v>
+        <v>4.474483822994813</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.48757888264767</v>
+        <v>-4.782368676056453</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.700311995339117</v>
+        <v>2.582396077975604</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.293513444747964</v>
+        <v>1.066518800897876</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.388774814106881</v>
+        <v>4.467547619981181</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.7%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>43.3%</t>
+          <t>50.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>103.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.6%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.7%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>86.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.3%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>135.8%</t>
+          <t>142.4%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-77.5%</t>
+          <t>-76.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.72</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>124.2%</t>
+          <t>123.6%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>91.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -977,7 +977,7 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-631.0%</t>
+          <t>-616.8%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>22.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.6%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-73.6%</t>
+          <t>-72.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>418.0%</t>
+          <t>423.0%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.8%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-639.8%</t>
+          <t>-607.8%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>35.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1135,7 +1135,7 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-252.8%</t>
+          <t>-247.1%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.7%</t>
+          <t>-35.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>29.2%</t>
+          <t>32.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1175,7 +1175,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>0.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>1.7%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-118.0%</t>
+          <t>-105.2%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-6.2%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>67.0%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-0.05</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.2%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.8%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-243.0%</t>
+          <t>-228.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>3.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>125.8%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-97.3%</t>
+          <t>-323.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-117.3%</t>
+          <t>-102.1%</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>62.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>92.7%</t>
+          <t>92.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-146.2%</t>
+          <t>-137.6%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.0%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.7%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.7%</t>
+          <t>7.3%</t>
         </is>
       </c>
     </row>
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074622</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.598332969419539</v>
+        <v>-1.455994000230163</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.477230655360302</v>
+        <v>2.534166243036052</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.111534361430468</v>
+        <v>1.253873330619843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.783840884300145</v>
+        <v>3.86924426581377</v>
       </c>
     </row>
     <row r="1851">
@@ -44118,22 +44118,22 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.964401696564191</v>
+        <v>-1.822062727374816</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.32388746380889</v>
+        <v>2.38082305148464</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7454656342858149</v>
+        <v>0.88780460347519</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.557283947319803</v>
+        <v>3.642687328833428</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.172892478015876</v>
+        <v>-2.0305535088265</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.260829440966984</v>
+        <v>2.317765028642734</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.5369748528341305</v>
+        <v>0.6793138220235055</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.452527768187561</v>
+        <v>3.537931149701186</v>
       </c>
     </row>
     <row r="1853">
@@ -44164,22 +44164,22 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.420093662781097</v>
+        <v>-2.277754693591722</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.170047717469465</v>
+        <v>2.226983305145214</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.5571282063329429</v>
+        <v>0.699467175522318</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.472718530695416</v>
+        <v>3.558121912209042</v>
       </c>
     </row>
     <row r="1854">
@@ -44187,22 +44187,22 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382327</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.912478690805194</v>
+        <v>-2.770139721615819</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.974200098303558</v>
+        <v>2.031135685979308</v>
       </c>
       <c r="F1854" t="n">
-        <v>0.06474317830884618</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.178393905924691</v>
+        <v>3.263797287438316</v>
       </c>
     </row>
     <row r="1855">
@@ -44210,22 +44210,22 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495498</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.297659081735266</v>
+        <v>-3.155320112545891</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.818670480744392</v>
+        <v>1.875606068420142</v>
       </c>
       <c r="F1855" t="n">
-        <v>0.06474317830884618</v>
+        <v>0.2070821474982212</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.176936444737554</v>
+        <v>3.262339826251179</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.547529761749848</v>
+        <v>-3.405190792560473</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.720491332193176</v>
+        <v>1.777426919868925</v>
       </c>
       <c r="F1856" t="n">
-        <v>0.1010058981393094</v>
+        <v>0.2433448673286845</v>
       </c>
       <c r="G1856" t="n">
-        <v>3.200463200090448</v>
+        <v>3.285866581604073</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.754041538636869</v>
+        <v>-3.611702569447494</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.633992680094625</v>
+        <v>1.690928267770375</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.1055058787477121</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1857" t="n">
-        <v>3.072662192614493</v>
+        <v>3.158065574128118</v>
       </c>
     </row>
     <row r="1858">
@@ -44279,22 +44279,22 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.073385613717371</v>
+        <v>-3.931046644527996</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.508027976762684</v>
+        <v>1.564963564438434</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.1055058787477121</v>
+        <v>0.036833090441663</v>
       </c>
       <c r="G1858" t="n">
-        <v>3.074435119314753</v>
+        <v>3.159838500828378</v>
       </c>
     </row>
     <row r="1859">
@@ -44302,22 +44302,22 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207813</v>
+        <v>3.305316798207811</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.459595444993147</v>
+        <v>-4.31725647580377</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.339876931719778</v>
+        <v>1.396812519395528</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.1962788184651554</v>
+        <v>-0.05393984927578033</v>
       </c>
       <c r="G1859" t="n">
-        <v>3.006304242951691</v>
+        <v>3.091707624465316</v>
       </c>
     </row>
     <row r="1860">
@@ -44325,22 +44325,22 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.694289439125699</v>
+        <v>-4.551950469936322</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.234284109068848</v>
+        <v>1.291219696744598</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.1899425512359002</v>
+        <v>-0.04760358204652515</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.998390778291335</v>
+        <v>3.08379415980496</v>
       </c>
     </row>
     <row r="1861">
@@ -44348,22 +44348,22 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006533</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.029952086356151</v>
+        <v>-4.887613117166775</v>
       </c>
       <c r="E1861" t="n">
-        <v>1.098599641832632</v>
+        <v>1.155535229508382</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.257873536724805</v>
+        <v>-0.11553456753543</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.956212778653957</v>
+        <v>3.041616160167582</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.106396416559023</v>
+        <v>-4.964057447369647</v>
       </c>
       <c r="E1862" t="n">
-        <v>1.074509469985725</v>
+        <v>1.131445057661475</v>
       </c>
       <c r="F1862" t="n">
-        <v>-0.1774280276311431</v>
+        <v>-0.03508905844176807</v>
       </c>
       <c r="G1862" t="n">
-        <v>3.010967644344396</v>
+        <v>3.096371025858021</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970904</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-5.47152379919777</v>
+        <v>-5.329184830008393</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.9277130319360576</v>
+        <v>0.9846486196118076</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.4737388119301557</v>
+        <v>-0.3313998427407806</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.832435688770819</v>
+        <v>2.917839070284444</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330522</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-5.880112576378448</v>
+        <v>-5.737773607189072</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.7630390650785452</v>
+        <v>0.8199746527542953</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.586043966477171</v>
+        <v>2.671447347990797</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-5.993872988401312</v>
+        <v>-5.851534019211937</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.7127203327408602</v>
+        <v>0.7696559204166098</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.581229398948632</v>
+        <v>2.666632780462257</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-6.41026486268831</v>
+        <v>-6.267925893498934</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.5441576336349385</v>
+        <v>0.6010932213106881</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.579223449557509</v>
+        <v>2.664626831071135</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-6.771438492505298</v>
+        <v>-6.629099523315922</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.409946872376822</v>
+        <v>0.4668824600525721</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.589482140226188</v>
+        <v>2.674885521739814</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094117</v>
+        <v>3.374439043094115</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-7.114697012148317</v>
+        <v>-6.972358042958941</v>
       </c>
       <c r="E1868" t="n">
-        <v>0.2687430296653099</v>
+        <v>0.3256786173410595</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.585581705371884</v>
+        <v>2.670985086885509</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199283</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-7.16289982939066</v>
+        <v>-7.020560860201285</v>
       </c>
       <c r="E1869" t="n">
-        <v>0.2478668228233731</v>
+        <v>0.3048024104991232</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.8823275891108341</v>
+        <v>-0.739988619921459</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.583986625426885</v>
+        <v>2.669390006940509</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969591</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-7.329708489365022</v>
+        <v>-7.187369520175647</v>
       </c>
       <c r="E1870" t="n">
-        <v>0.1849223347628368</v>
+        <v>0.2418579224385864</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.9246109128239706</v>
+        <v>-0.7822719436345955</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.562395607128211</v>
+        <v>2.647798988641836</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923084</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-7.516428197674325</v>
+        <v>-7.37408922848495</v>
       </c>
       <c r="E1871" t="n">
-        <v>0.1062081469047125</v>
+        <v>0.1631437345804621</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.9246109128239706</v>
+        <v>-0.7822719436345955</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.558369302593808</v>
+        <v>2.643772684107433</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.458100091297747</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-7.899429586416956</v>
+        <v>-7.757090617227581</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.04709450991392394</v>
+        <v>0.009841077761825634</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.9246109128239706</v>
+        <v>-0.7822719436345955</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.558267201272224</v>
+        <v>2.643670582785849</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-7.903916031618345</v>
+        <v>-7.761577062428969</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.04631757202304954</v>
+        <v>0.01061801565270049</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.9290973580253592</v>
+        <v>-0.7867583888359841</v>
       </c>
       <c r="G1873" t="n">
-        <v>2.558146850122821</v>
+        <v>2.643550231636446</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-8.263446354122348</v>
+        <v>-8.121107384932973</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.1847793977266003</v>
+        <v>-0.1278438100508503</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.9290973580253592</v>
+        <v>-0.7867583888359841</v>
       </c>
       <c r="G1874" t="n">
-        <v>2.563497153420871</v>
+        <v>2.648900534934496</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341316</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-8.31379541757657</v>
+        <v>-8.171456448387195</v>
       </c>
       <c r="E1875" t="n">
-        <v>-0.1970030031511114</v>
+        <v>-0.1400674154753618</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.9794464214795813</v>
+        <v>-0.8371074522902062</v>
       </c>
       <c r="G1875" t="n">
-        <v>2.541203735305515</v>
+        <v>2.62660711681914</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539466</v>
+        <v>3.501052558539464</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-8.411414694997966</v>
+        <v>-8.269075725808591</v>
       </c>
       <c r="E1876" t="n">
-        <v>-0.2330089634979013</v>
+        <v>-0.1760733758221513</v>
       </c>
       <c r="F1876" t="n">
-        <v>-1.077065698900978</v>
+        <v>-0.9347267297116029</v>
       </c>
       <c r="G1876" t="n">
-        <v>2.485673919474446</v>
+        <v>2.571077300988071</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.4924487119375</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
       </c>
       <c r="D1877" t="n">
-        <v>-8.465486194506324</v>
+        <v>-8.32314722531695</v>
       </c>
       <c r="E1877" t="n">
-        <v>-0.2517440069796724</v>
+        <v>-0.1948084193039228</v>
       </c>
       <c r="F1877" t="n">
-        <v>-1.131137198409337</v>
+        <v>-0.9887982292199623</v>
       </c>
       <c r="G1877" t="n">
-        <v>2.456124576091002</v>
+        <v>2.541527957604627</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141703</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.469061980598072</v>
+        <v>-8.326723011408697</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.2476611242977294</v>
+        <v>-0.1907255366219793</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.15666612032583</v>
+        <v>-1.014327151136455</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.446320420059749</v>
+        <v>2.531723801573374</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729892</v>
+        <v>3.49685190472989</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.502714819106545</v>
+        <v>-8.360375849917171</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.2566397052166827</v>
+        <v>-0.1997041175409326</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.257079488242867</v>
+        <v>-1.114740519053492</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.390554953793963</v>
+        <v>2.475958335307588</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440635</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.641800933725403</v>
+        <v>-8.499461964536028</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2969024495708044</v>
+        <v>-0.2399668618950543</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.396165602861724</v>
+        <v>-1.253826633672349</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.32247498651607</v>
+        <v>2.407878368029695</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608602</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.816925351111946</v>
+        <v>-8.674586381922571</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3523969957779047</v>
+        <v>-0.2954614081021552</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.571290020248268</v>
+        <v>-1.428951051058893</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.23195555683166</v>
+        <v>2.317358938345286</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410274</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.051377445126436</v>
+        <v>-8.909038475937061</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4533969982852968</v>
+        <v>-0.3964614106095468</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.571290020248268</v>
+        <v>-1.428951051058893</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.224736391930064</v>
+        <v>2.310139773443689</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764399</v>
+        <v>3.480692492764397</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.155752176152882</v>
+        <v>-9.013413206963508</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5018190814698515</v>
+        <v>-0.4448834937941015</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.675664751274714</v>
+        <v>-1.533325782085339</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.155439362540221</v>
+        <v>2.240842744053846</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390587</v>
+        <v>3.493716014390586</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.318265641851466</v>
+        <v>-9.175926672662092</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5657086779107288</v>
+        <v>-0.5087730902349792</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.7732981816934</v>
+        <v>-1.630959212504025</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.097975094127565</v>
+        <v>2.18337847564119</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297399</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.444302435219756</v>
+        <v>-9.301963466030381</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6134296666289298</v>
+        <v>-0.5564940789531803</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.748046558883658</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.115819796442525</v>
+        <v>2.20122317795615</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322544</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.387230663323825</v>
+        <v>-9.24489169413445</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5866106221841569</v>
+        <v>-0.5296750345084069</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.748046558883658</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.119810132128926</v>
+        <v>2.205213513642551</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158924</v>
+        <v>3.600038265158922</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.528902505047945</v>
+        <v>-9.386563535858571</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6447545857725467</v>
+        <v>-0.5878189980967967</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.748046558883658</v>
+        <v>-1.605707589694283</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.118334905230184</v>
+        <v>2.20373828674381</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.69157173394072</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.479311660623111</v>
+        <v>-9.336972691433736</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6098648378377405</v>
+        <v>-0.5529292501619909</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.698455714458824</v>
+        <v>-1.556116745269449</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.163142822049957</v>
+        <v>2.248546203563582</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770581</v>
+        <v>3.676841549770579</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.330393326151254</v>
+        <v>-9.18805435696188</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5633486376956811</v>
+        <v>-0.5064130500199311</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.667206123723651</v>
+        <v>-1.524867154534276</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.168841442844378</v>
+        <v>2.254244824358003</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615285</v>
+        <v>3.685161381615283</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.104548173431844</v>
+        <v>-8.96220920424247</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4634315035717083</v>
+        <v>-0.4064959158959582</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.625279448136487</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.203576521232885</v>
+        <v>2.28897990274651</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812105</v>
+        <v>3.684843823812103</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.979969517094252</v>
+        <v>-8.837630547904878</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4124608964806127</v>
+        <v>-0.3555253088048627</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.625279448136487</v>
+        <v>-1.482940478947112</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.204715665788944</v>
+        <v>2.290119047302569</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.71093553364622</v>
+        <v>3.710935533646218</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.954932835525742</v>
+        <v>-8.812593866336368</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3998124496911011</v>
+        <v>-0.3428768620153511</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.599950360585752</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.222546892481493</v>
+        <v>2.307950273995118</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.882799660237861</v>
+        <v>-8.740460691048487</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3652254753373119</v>
+        <v>-0.3082898876615623</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.599950360585752</v>
+        <v>-1.457611391396377</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.228280596720129</v>
+        <v>2.313683978233754</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955331</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.811433267628214</v>
+        <v>-8.669094298438839</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3464161806873181</v>
+        <v>-0.2894805930115685</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.528583967976104</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.261363169892053</v>
+        <v>2.346766551405678</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.717974233642989</v>
+        <v>-8.575635264453615</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3189160484061362</v>
+        <v>-0.2619804607303862</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.528583967976104</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.251479688579145</v>
+        <v>2.33688307009277</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.707321052089558</v>
+        <v>-8.564982082900183</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3164893362841372</v>
+        <v>-0.2595537486083872</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.528583967976104</v>
+        <v>-1.386244998786729</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.249645128079771</v>
+        <v>2.335048509593396</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.609414013413067</v>
+        <v>-8.467075044223693</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2776268357870015</v>
+        <v>-0.220691248111252</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.460598218115547</v>
+        <v>-1.318259248926172</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.290136263022645</v>
+        <v>2.37553964453627</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097247</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.585460472437109</v>
+        <v>-8.443121503247735</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.267376913251125</v>
+        <v>-0.210441325575375</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.43664467713959</v>
+        <v>-1.294305707950215</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.305176893753713</v>
+        <v>2.390580275267338</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017774</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.321400534114312</v>
+        <v>-8.179061564924938</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1750132540837583</v>
+        <v>-0.1180776664080083</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.172584738816794</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.450352540585638</v>
+        <v>2.535755922099263</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839728</v>
+        <v>3.833252747839726</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.614320910609474</v>
+        <v>-7.4719819414201</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1050315616578761</v>
+        <v>0.1619671493336261</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.172584738816794</v>
+        <v>-1.030245769627419</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.447565506925337</v>
+        <v>2.532968888438962</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388733</v>
+        <v>3.839374447388731</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.574136612243284</v>
+        <v>-7.431797643053909</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1214489048921936</v>
+        <v>0.1783844925679436</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.132400440450603</v>
+        <v>-0.9900614712612278</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.472019709832893</v>
+        <v>2.557423091346518</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626479</v>
+        <v>3.856161751626477</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.410736741303921</v>
+        <v>-7.268397772114547</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1861756744886955</v>
+        <v>0.2431112621644456</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.9690005695112403</v>
+        <v>-0.8266616003218653</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.569426453617268</v>
+        <v>2.654829835130893</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291814</v>
+        <v>3.787330429291813</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.177255519074323</v>
+        <v>-7.034916549884948</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2874925922183875</v>
+        <v>0.3444281798941371</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.7355193472816417</v>
+        <v>-0.5931803780922668</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.717439615792879</v>
+        <v>2.802842997306504</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.80163712278579</v>
+        <v>3.801637122785788</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.027589128066808</v>
+        <v>-6.885250158877433</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3444669383084342</v>
+        <v>0.4014025259841842</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.6426158560391058</v>
+        <v>-0.5002768868497308</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.770289500225442</v>
+        <v>2.855692881739067</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.76318224839043</v>
+        <v>3.763182248390429</v>
       </c>
       <c r="C1905" t="n">
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.895313654435921</v>
+        <v>-6.752974685246547</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2986379137679434</v>
+        <v>0.3555735014436934</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.5103403824082191</v>
+        <v>-0.3680014132188442</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.750915570411128</v>
+        <v>2.836318951924753</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105956</v>
+        <v>3.784718794105954</v>
       </c>
       <c r="C1906" t="n">
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.723452438871019</v>
+        <v>-6.581113469681644</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.370197460681541</v>
+        <v>0.427133048357291</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.3384791668433162</v>
+        <v>-0.1961401976539413</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856847360437706</v>
+        <v>2.942250741951332</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960988</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.638487772141699</v>
+        <v>-6.496148802952325</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4170896685969274</v>
+        <v>0.4740252562726774</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.2535145001139967</v>
+        <v>-0.1111755309246217</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.920732501698957</v>
+        <v>3.006135883212582</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607647</v>
+        <v>3.692931855607645</v>
       </c>
       <c r="C1908" t="n">
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.744077761914804</v>
+        <v>-6.601738792725429</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2468777430884672</v>
+        <v>0.3038133307642168</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.359104489887101</v>
+        <v>-0.2167655206977261</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.729402578235876</v>
+        <v>2.814805959749501</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987905</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.675843177289376</v>
+        <v>-6.533504208100002</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3227159188157245</v>
+        <v>0.3796515064914745</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.340689167014565</v>
+        <v>-0.1983501978251901</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.788996113836484</v>
+        <v>2.874399495350109</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710815</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.527903135881777</v>
+        <v>-6.385564166692403</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2652711267403571</v>
+        <v>0.3222067144161072</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.3203682511060075</v>
+        <v>-0.1780292819166325</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.684567854743211</v>
+        <v>2.769971236256836</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409207</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.474933613627789</v>
+        <v>-6.332594644438414</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2777449493884743</v>
+        <v>0.3346805370642243</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.2673987288520186</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.707635581842126</v>
+        <v>2.793038963355751</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098112</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.309145417667498</v>
+        <v>-6.166806448478123</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3370996156774977</v>
+        <v>0.3940352033532473</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.2673987288520186</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.700674969747033</v>
+        <v>2.786078351260658</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493423</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.275782211188729</v>
+        <v>-6.133443241999355</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.364907252650148</v>
+        <v>0.421842840325898</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.2673987288520186</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.715137324128176</v>
+        <v>2.800540705641801</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82855148672282</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.167523074066207</v>
+        <v>-6.025184104876833</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4027430279583517</v>
+        <v>0.4596786156341017</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.2673987288520186</v>
+        <v>-0.1250597596626437</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.709669444587371</v>
+        <v>2.795072826100996</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792049</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.044231939249077</v>
+        <v>-5.901892970059702</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4495575758957808</v>
+        <v>0.5064931635715308</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.1441075940348881</v>
+        <v>-0.001768624845513156</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.781142219488226</v>
+        <v>2.866545601001851</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919908</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.991535072117785</v>
+        <v>-5.849196102928411</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4783373009856229</v>
+        <v>0.5352728886613725</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.09141072690359692</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.820461318004326</v>
+        <v>2.905864699517951</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.747769630134341</v>
+        <v>-5.605430660944966</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5716241861260514</v>
+        <v>0.6285597738018009</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.09141072690359692</v>
+        <v>0.05092824228577802</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.816242026351377</v>
+        <v>2.901645407865002</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057527</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.657993957757869</v>
+        <v>-5.515654988568494</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6096587689966562</v>
+        <v>0.6665943566724057</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.0298112819892869</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.855326007219979</v>
+        <v>2.940729388733604</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279186</v>
+        <v>3.826354974279184</v>
       </c>
       <c r="C1919" t="n">
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.533178129792175</v>
+        <v>-5.26580459461942</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.652327175166636</v>
+        <v>0.7592765892357378</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.0298112819892869</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.848068082203681</v>
+        <v>2.933471463717306</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011499</v>
+        <v>3.835957987011497</v>
       </c>
       <c r="C1920" t="n">
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.357286037324743</v>
+        <v>-5.089912502151988</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7262831356742576</v>
+        <v>0.8332325497433595</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.0298112819892869</v>
+        <v>0.112527687200088</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.85166720572433</v>
+        <v>2.937070587237955</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392988</v>
+        <v>3.780933911392986</v>
       </c>
       <c r="C1921" t="n">
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.185839574302279</v>
+        <v>-4.918466039129524</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8081892269377966</v>
+        <v>0.9151386410068985</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.1416351810331762</v>
+        <v>0.2839741502225512</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.967862589592361</v>
+        <v>3.053265971105986</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.105817287193158</v>
+        <v>-4.838443752020403</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8392186193977418</v>
+        <v>0.9461680334668439</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.2216574681422972</v>
+        <v>0.3639964373316721</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.014896439474131</v>
+        <v>3.100299820987756</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.042181544959224</v>
+        <v>-4.774808009786469</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8693677173456331</v>
+        <v>0.976317131414735</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.2852932103762317</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.057772685868809</v>
+        <v>3.143176067382434</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.948484226742829</v>
+        <v>-4.681110691570074</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8880409034159866</v>
+        <v>0.9949903174850887</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.2852932103762317</v>
+        <v>0.4276321795656067</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.038966944652604</v>
+        <v>3.124370326166229</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242296</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.958986849808118</v>
+        <v>-4.691613314635362</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8855829308147485</v>
+        <v>0.9925323448838506</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.2747905873109429</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.034408447438309</v>
+        <v>3.119811828951934</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367687</v>
+        <v>3.821593509367685</v>
       </c>
       <c r="C1926" t="n">
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.846500589139243</v>
+        <v>-4.579127053966488</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9345067489171184</v>
+        <v>1.04145616298622</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.2747905873109429</v>
+        <v>0.4171295565003178</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.038337761273129</v>
+        <v>3.123741142786754</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.828786902261378</v>
+        <v>-4.561413367088623</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9422708075856046</v>
+        <v>1.049220221654707</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2779719162078597</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.040925142528619</v>
+        <v>3.126328524042244</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.84861662650234</v>
+        <v>3.848616626502338</v>
       </c>
       <c r="C1928" t="n">
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.705312630948359</v>
+        <v>-4.437939095775604</v>
       </c>
       <c r="E1928" t="n">
-        <v>0.9886585873308054</v>
+        <v>1.095608001399907</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2779719162078597</v>
+        <v>0.4203108853972346</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.037923213748612</v>
+        <v>3.123326595262237</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675942</v>
+        <v>3.81866895167594</v>
       </c>
       <c r="C1929" t="n">
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.485291832911349</v>
+        <v>-4.217918297738594</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.078245943556224</v>
+        <v>1.185195357625326</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.4191917612758399</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.124234157800015</v>
+        <v>3.20963753931364</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539953</v>
+        <v>3.843274527539951</v>
       </c>
       <c r="C1930" t="n">
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.352424143848071</v>
+        <v>-4.085050608675316</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.147287201983358</v>
+        <v>1.25423661605246</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.4191917612758399</v>
+        <v>0.5615307304652148</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.140128340601838</v>
+        <v>3.225531722115463</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496261</v>
+        <v>3.845047386496259</v>
       </c>
       <c r="C1931" t="n">
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.232251060483573</v>
+        <v>-3.964877525310817</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.196502279769459</v>
+        <v>1.303451693838561</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.5393648446403388</v>
+        <v>0.6817038138297138</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.213378035060839</v>
+        <v>3.298781416574464</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576998</v>
+        <v>3.791273551576996</v>
       </c>
       <c r="C1932" t="n">
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.096997699153595</v>
+        <v>-3.82962416398084</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.26069172686289</v>
+        <v>1.367641140931992</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.674618205970316</v>
+        <v>0.8169571751596909</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.304618154420266</v>
+        <v>3.390021535933891</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942104</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.156872526511288</v>
+        <v>-3.889498991338533</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.222779287321239</v>
+        <v>1.329728701390341</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.6147433786126238</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.254730749407076</v>
+        <v>3.340134130920701</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674513</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.037052295600451</v>
+        <v>-3.769678760427695</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.285996548919782</v>
+        <v>1.392945962988885</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.6147433786126238</v>
+        <v>0.7570823478019988</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.270019918641284</v>
+        <v>3.355423300154909</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430693</v>
+        <v>3.729146398430691</v>
       </c>
       <c r="C1935" t="n">
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.039522002062257</v>
+        <v>-3.772148466889501</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.192652865657502</v>
+        <v>1.299602279726604</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.6122736721508177</v>
+        <v>0.7546126413401926</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.176182294086642</v>
+        <v>3.261585675600267</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.107892188386267</v>
+        <v>-3.840518653213511</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.084566652613199</v>
+        <v>1.191516066682301</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.6215493711870327</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.101009574993673</v>
+        <v>3.186412956507298</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.71417913950837</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.219764468012418</v>
+        <v>-3.952390932839662</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.03025444939463</v>
+        <v>1.137203863463732</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.6215493711870327</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.091446283625564</v>
+        <v>3.176849665139189</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417706</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.275284543905007</v>
+        <v>-4.007911008732251</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.145077255729796</v>
+        <v>1.252026669798899</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.6215493711870327</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.228477120317766</v>
+        <v>3.313880501831391</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.7460425262059</v>
+        <v>3.746042526205899</v>
       </c>
       <c r="C1939" t="n">
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.099810284112538</v>
+        <v>-3.832436748939782</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.219834191638572</v>
+        <v>1.326783605707674</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.6215493711870327</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.233044352309554</v>
+        <v>3.318447733823179</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225445</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.091885909527623</v>
+        <v>-3.824512374354868</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.198745970233745</v>
+        <v>1.305695384302847</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.6215493711870327</v>
+        <v>0.7638883403764075</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.208786381070762</v>
+        <v>3.294189762584386</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.085607706957775</v>
+        <v>-3.818234171785019</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.129795564663134</v>
+        <v>1.236744978732236</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6278275737568817</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.14109161601412</v>
+        <v>3.226494997527745</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-4.025755087754051</v>
+        <v>-3.758381552581296</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.163908998776756</v>
+        <v>1.270858412845858</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6278275737568817</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.151264002446253</v>
+        <v>3.236667383959878</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.939511624727674</v>
+        <v>-3.672138089554918</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.193352654561167</v>
+        <v>1.300302068630269</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6278275737568817</v>
+        <v>0.7701665429462565</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.146210273020113</v>
+        <v>3.231613654533738</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316046</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.984818444126653</v>
+        <v>-3.717444908953898</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.167005702246101</v>
+        <v>1.273955116315203</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5870174107476509</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.1134999506591</v>
+        <v>3.198903332172725</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803191</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-4.013851548828955</v>
+        <v>-3.7464780136562</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.155944333398282</v>
+        <v>1.262893747467384</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5870174107476509</v>
+        <v>0.7293563799370257</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.114051823692202</v>
+        <v>3.199455205205827</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809499</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.921041067378095</v>
+        <v>-3.653667532205341</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.122341217869991</v>
+        <v>1.229290631939093</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6798278921985103</v>
+        <v>0.8221668613878851</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.099010804454083</v>
+        <v>3.184414185967708</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.965430536707523</v>
+        <v>-3.698057001534768</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.106458906062821</v>
+        <v>1.213408320131923</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6354384228690826</v>
+        <v>0.7777773920584574</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.074250598781027</v>
+        <v>3.159653980294652</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472736</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.944926842822026</v>
+        <v>-3.677553307649271</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.109736092128743</v>
+        <v>1.216685506197845</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6559421167545799</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.081628523624049</v>
+        <v>3.167031905137673</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798536</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.984850937404597</v>
+        <v>-3.717477402231843</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.099257750126382</v>
+        <v>1.206207164195483</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6559421167545799</v>
+        <v>0.7982810859439547</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.087119819454716</v>
+        <v>3.172523200968341</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498863</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-4.01263133530595</v>
+        <v>-3.745257800133196</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.099642792734379</v>
+        <v>1.206592206803481</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6281617188532269</v>
+        <v>0.7705006880426017</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.081948782482443</v>
+        <v>3.167352163996068</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705324</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-4.131012008036088</v>
+        <v>-3.863638472863335</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.8906462436429774</v>
+        <v>0.997595657712079</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.5609438667022507</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.879973791192511</v>
+        <v>2.965377172706136</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729269</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.23962608647942</v>
+        <v>-3.972252551306666</v>
       </c>
       <c r="E1952" t="n">
-        <v>0.9673502729848507</v>
+        <v>1.074299687053952</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.5609438667022507</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.000123451911716</v>
+        <v>3.085526833425341</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190768</v>
+        <v>3.733012441190766</v>
       </c>
       <c r="C1953" t="n">
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.204217048231277</v>
+        <v>-3.936843513058523</v>
       </c>
       <c r="E1953" t="n">
-        <v>0.9960269143864307</v>
+        <v>1.102976328455532</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.5609438667022507</v>
+        <v>0.7032828358916255</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.014636478014039</v>
+        <v>3.100039859527664</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913424</v>
       </c>
       <c r="C1954" t="n">
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.165833385673126</v>
+        <v>-3.898459850500372</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.00879982075206</v>
+        <v>1.115749234821161</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.5993275292604019</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.035086116891299</v>
+        <v>3.120489498404924</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532487</v>
+        <v>3.751147197532485</v>
       </c>
       <c r="C1955" t="n">
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.988717055637959</v>
+        <v>-3.721343520465206</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.076375381611428</v>
+        <v>1.18332479568053</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.5993275292604019</v>
+        <v>0.7416664984497767</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.0318151457366</v>
+        <v>3.117218527250226</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793904</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-4.033809300471505</v>
+        <v>-3.766435765298751</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.059021875439923</v>
+        <v>1.165971289509025</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5374314860910121</v>
+        <v>0.6797704552803869</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.99536091159688</v>
+        <v>3.080764293110505</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011235</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.854433879232738</v>
+        <v>-3.587060344059983</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.124559019241844</v>
+        <v>1.231508433310946</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.6942082442617308</v>
+        <v>0.8365472134511056</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.083213941805726</v>
+        <v>3.16861732331935</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.899448092753344</v>
+        <v>-3.63207455758059</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.087360789165192</v>
+        <v>1.194310203234293</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.6638593489471262</v>
+        <v>0.806198318136501</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.045812059948553</v>
+        <v>3.131215441462177</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.73702660850954</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.166452603025779</v>
+        <v>-3.899079067853025</v>
       </c>
       <c r="E1959" t="n">
-        <v>0.9862505473951633</v>
+        <v>1.093199961464265</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.4694963109041776</v>
+        <v>0.6118352800935525</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.934885799461729</v>
+        <v>3.020289180975354</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760811</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.267650384462952</v>
+        <v>-4.000276849290198</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9449753567167956</v>
+        <v>1.051924770785897</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4010874973588584</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.893044433231039</v>
+        <v>2.978447814744664</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815455</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.261139417848639</v>
+        <v>-3.993765882675885</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9451797049168373</v>
+        <v>1.052129118985939</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4010874973588584</v>
+        <v>0.5434264665482333</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.890644394785356</v>
+        <v>2.976047776298981</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.7095104433781</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.242101290141342</v>
+        <v>-3.974727754968588</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9493196752080013</v>
+        <v>1.056269089277103</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3429038860276639</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.852258947194884</v>
+        <v>2.937662328708509</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131248</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.294617092416162</v>
+        <v>-4.027243557243408</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.047607755932263</v>
+        <v>1.154557170001365</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3429038860276639</v>
+        <v>0.4852428552170388</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.971553348829074</v>
+        <v>3.056956730342699</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067864</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.298025403850742</v>
+        <v>-4.030651868677988</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.047077760344565</v>
+        <v>1.154027174413667</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3754204550370412</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.991896619220834</v>
+        <v>3.077300000734459</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789122</v>
+        <v>3.787425580789121</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.257542411928397</v>
+        <v>-3.990168876755643</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.069279487510429</v>
+        <v>1.176228901579531</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3754204550370412</v>
+        <v>0.5177594242264162</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.99790514961776</v>
+        <v>3.083308531131385</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519907</v>
       </c>
       <c r="C1966" t="n">
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-4.109799441693395</v>
+        <v>-3.842425906520641</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.026326896881629</v>
+        <v>1.133276310950731</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5432278122719244</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.996539785235889</v>
+        <v>3.081943166749515</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181169</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.193620662968093</v>
+        <v>-3.926247127795339</v>
       </c>
       <c r="E1967" t="n">
-        <v>0.9955920299032313</v>
+        <v>1.102541443972333</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5432278122719244</v>
+        <v>0.6855667814612993</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.99933340676737</v>
+        <v>3.084736788280996</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394732</v>
+        <v>3.805608985394731</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.187467956915309</v>
+        <v>-3.920094421742555</v>
       </c>
       <c r="E1968" t="n">
-        <v>0.9987154607160034</v>
+        <v>1.105664874785105</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5493805183247087</v>
+        <v>0.6917194875140836</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.003687378790699</v>
+        <v>3.089090760304325</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890609</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.204277255065811</v>
+        <v>-3.936903719893056</v>
       </c>
       <c r="E1969" t="n">
-        <v>0.9910722181959128</v>
+        <v>1.098021632265014</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.532571220174207</v>
+        <v>0.674910189363582</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.992682276640509</v>
+        <v>3.078085658154134</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798426</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-4.141979256289688</v>
+        <v>-3.874605721116934</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.082326971503182</v>
+        <v>1.189276385572284</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.577865484448649</v>
+        <v>0.7202044536380241</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.086194389001995</v>
+        <v>3.17159777051562</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992193</v>
+        <v>3.848729139992191</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.94018905862453</v>
+        <v>-3.672815523451777</v>
       </c>
       <c r="E1971" t="n">
-        <v>0.9653350522833728</v>
+        <v>1.072284466352474</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7758836766178034</v>
+        <v>0.9182226458071785</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.007297306017614</v>
+        <v>3.09270068753124</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852423</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.991075771310725</v>
+        <v>-3.723702236137971</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.01527059953107</v>
+        <v>1.122220013600172</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.724996963931609</v>
+        <v>0.867335933120984</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.047055510728073</v>
+        <v>3.132458892241698</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319546</v>
+        <v>3.819063300319544</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.904465028660918</v>
+        <v>-3.637091493488164</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.064542632707037</v>
+        <v>1.171492046776138</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8036226951367672</v>
+        <v>0.9459616643261423</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.108858685567212</v>
+        <v>3.194262067080837</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489387</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.964674326666202</v>
+        <v>-3.697300791493448</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.038994894329595</v>
+        <v>1.145944308398696</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7434133971314827</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.071269087588712</v>
+        <v>3.156672469102338</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397796</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.915487677981851</v>
+        <v>-3.648114142809097</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.057161171843264</v>
+        <v>1.164110585912365</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7434133971314827</v>
+        <v>0.8857523663208577</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.069760705628641</v>
+        <v>3.155164087142266</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316251</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.871114546343282</v>
+        <v>-3.603741011170528</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.074773291934127</v>
+        <v>1.181722706003229</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7877865287700513</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.096247452047218</v>
+        <v>3.181650833560844</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105964</v>
+        <v>3.821562117105962</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.893594897202167</v>
+        <v>-3.626221362029413</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.060174945729164</v>
+        <v>1.167124359798265</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7877865287700513</v>
+        <v>0.9301254979594263</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.090641246185809</v>
+        <v>3.176044627699434</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190323</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.845939166641111</v>
+        <v>-3.578565631468358</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.085618994981391</v>
+        <v>1.192568409050492</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8354422593311069</v>
+        <v>0.977781228520482</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.125616441550247</v>
+        <v>3.211019823063872</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569616</v>
+        <v>3.822678210569614</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.745421008142356</v>
+        <v>-3.478047472969603</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.130718631755617</v>
+        <v>1.237668045824719</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9359604178298615</v>
+        <v>1.078299387019237</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.190819710024225</v>
+        <v>3.27622309153785</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557293</v>
+        <v>3.828808877557291</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.729515678710004</v>
+        <v>-3.462142143537251</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.123835436004431</v>
+        <v>1.230784850073532</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8568477571206226</v>
+        <v>0.9991867263099976</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.130106786074554</v>
+        <v>3.215510167588179</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932766</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.684677277101606</v>
+        <v>-3.417303741928853</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.145868499258419</v>
+        <v>1.25281791332752</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.861391190065492</v>
+        <v>1.003730159254867</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.136930548452104</v>
+        <v>3.222333929965729</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917049</v>
+        <v>3.817932354917048</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.704175733343614</v>
+        <v>-3.436802198170861</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.142230056392693</v>
+        <v>1.249179470461795</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.8133065487855877</v>
+        <v>0.9556455179749628</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.112240703315239</v>
+        <v>3.197644084828864</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405959</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.659972896257714</v>
+        <v>-3.39259936108496</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.165790793754891</v>
+        <v>1.272740207823992</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8575093858714882</v>
+        <v>0.9998483550608632</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.144642008094617</v>
+        <v>3.230045389608242</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.667532562094761</v>
+        <v>-3.374491763903783</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.161176927889319</v>
+        <v>1.27839324716571</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.9123127898813075</v>
+        <v>1.06432310015072</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.175934050969756</v>
+        <v>3.267140237131403</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.86389508028488</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.509241144555488</v>
+        <v>-3.216200346364511</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.275741260088068</v>
+        <v>1.392957579364459</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.9123127898813075</v>
+        <v>1.06432310015072</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.227181816152795</v>
+        <v>3.318388002314443</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321024</v>
+        <v>3.865338681321022</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.301599140921012</v>
+        <v>-3.008558342730035</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.357238766136112</v>
+        <v>1.474455085412502</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.119954793515784</v>
+        <v>1.271965103785196</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.350207722927734</v>
+        <v>3.441413909089382</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475141</v>
+        <v>3.864489842475139</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.250567048198484</v>
+        <v>-2.957526250007507</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.372599831463393</v>
+        <v>1.489816150739784</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.170986886238312</v>
+        <v>1.322997196507724</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.375775206799521</v>
+        <v>3.466981392961169</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404855</v>
+        <v>3.842547360404853</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.185342867071278</v>
+        <v>-2.892302068880301</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.41587690800698</v>
+        <v>1.533093227283371</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.236211067365517</v>
+        <v>1.38822137763493</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.432097119568549</v>
+        <v>3.523303305730197</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882559</v>
+        <v>3.840061186882557</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-3.147915847000144</v>
+        <v>-2.854875048809168</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.426808688334714</v>
+        <v>1.544025007611105</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.241462605394699</v>
+        <v>1.393472915664112</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.431209014685339</v>
+        <v>3.522415200846986</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992663</v>
+        <v>3.845169808992662</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.168027503034853</v>
+        <v>-2.874986704843876</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.420020818252071</v>
+        <v>1.537237137528462</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.252489950392118</v>
+        <v>1.404500260661531</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.439082214015031</v>
+        <v>3.530288400176678</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563629</v>
+        <v>3.828661445636288</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-3.139614239934969</v>
+        <v>-2.846573441743992</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.591943894513235</v>
+        <v>1.709160213789626</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.19351438764569</v>
+        <v>1.345524697915102</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.564254647388384</v>
+        <v>3.655460833550031</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957629</v>
+        <v>3.813222820957627</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-3.064831978909957</v>
+        <v>-2.77179118071898</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.741969708141057</v>
+        <v>1.859186027417448</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.268296648670702</v>
+        <v>1.420306958940115</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.729236913221209</v>
+        <v>3.820443099382857</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998751</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-3.038747894646149</v>
+        <v>-2.745707096455172</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.744111317860439</v>
+        <v>1.86132763713683</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.268296648670702</v>
+        <v>1.420306958940115</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.720944889235068</v>
+        <v>3.812151075396716</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896928</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.950869981537028</v>
+        <v>-2.657829183346051</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.777455678687867</v>
+        <v>1.894671997964258</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.384222291094053</v>
+        <v>1.536232601363466</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.788693470272858</v>
+        <v>3.879899656434505</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959857</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.941977520143745</v>
+        <v>-2.648936721952768</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.798567068971972</v>
+        <v>1.915783388248363</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.384222291094053</v>
+        <v>1.536232601363466</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.806247875999649</v>
+        <v>3.897454062161297</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945365</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-3.110453637113622</v>
+        <v>-2.817412838922646</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.723031669588605</v>
+        <v>1.840247988864996</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.356274455377472</v>
+        <v>1.508284765646885</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.781334221974285</v>
+        <v>3.872540408135932</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782709</v>
+        <v>3.795574066782708</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.664197444484182</v>
+        <v>-2.371156646293206</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.882803843828243</v>
+        <v>2.000020163104633</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.26155578570784</v>
+        <v>1.413566095977252</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.705772717360367</v>
+        <v>3.796978903522015</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632636</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.64147634080103</v>
+        <v>-2.348435542610053</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.882556307798408</v>
+        <v>1.999772627074799</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.26155578570784</v>
+        <v>1.413566095977252</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.696436739857272</v>
+        <v>3.787642926018919</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777673</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.770678154095072</v>
+        <v>-2.477637355904096</v>
       </c>
       <c r="E1999" t="n">
-        <v>1.98978170833196</v>
+        <v>2.106998027608351</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.132353972413797</v>
+        <v>1.28436428268321</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.777821777732015</v>
+        <v>3.869027963893663</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644414</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.796552552569098</v>
+        <v>-2.503511754378121</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.016509771435997</v>
+        <v>2.133726090712387</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.177265581125539</v>
+        <v>1.329275891394951</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.841846565452706</v>
+        <v>3.933052751614354</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799961</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.789497862353925</v>
+        <v>-2.496457064162948</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.016007003511611</v>
+        <v>2.133223322788002</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.184320271340712</v>
+        <v>1.336330581610125</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.842754735571356</v>
+        <v>3.933960921733004</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.766673496331115</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.762546638027437</v>
+        <v>-2.46950583983646</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.036793646886948</v>
+        <v>2.154009966163339</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.199200617368432</v>
+        <v>1.351210927637844</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.861689096832729</v>
+        <v>3.952895282994376</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.76805206778411</v>
+        <v>3.768052067784108</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.784090865858224</v>
+        <v>-2.491050067667247</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.212279087899593</v>
+        <v>2.329495407175984</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.199200617368432</v>
+        <v>1.351210927637844</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.045792228977689</v>
+        <v>4.136998415139336</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714422</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.806498983663096</v>
+        <v>-2.513458185472119</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.195432535680637</v>
+        <v>2.312648854957028</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.199200617368432</v>
+        <v>1.351210927637844</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.037908923880682</v>
+        <v>4.12911511004233</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155034</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.834723219240696</v>
+        <v>-2.541682421049719</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.186196840999235</v>
+        <v>2.303413160275625</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.21717736981974</v>
+        <v>1.369187680089153</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.050748974901104</v>
+        <v>4.141955161062752</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.72945228516198</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.844164145129226</v>
+        <v>-2.551123346938249</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.238674188365669</v>
+        <v>2.35589050764206</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.339604487363132</v>
+        <v>1.491614797632544</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.180458963148986</v>
+        <v>4.271665149310634</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321637</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.9330407762977</v>
+        <v>-2.639999978106723</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.206014630443581</v>
+        <v>2.323230949719972</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.250727856194658</v>
+        <v>1.40273816646407</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.130024078993203</v>
+        <v>4.22123026515485</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347706</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-3.009370753898606</v>
+        <v>-2.716329955707629</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.173594452296994</v>
+        <v>2.290810771573384</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.250727856194658</v>
+        <v>1.40273816646407</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.128135891886978</v>
+        <v>4.219342078048625</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.710654104887752</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-3.103034698576147</v>
+        <v>-2.80999390038517</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.13094910402884</v>
+        <v>2.24816542330523</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.157063911517116</v>
+        <v>1.309074221786529</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.066757754683316</v>
+        <v>4.157963940844963</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343069</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.264603124103402</v>
+        <v>-2.971562325912426</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.06475574402809</v>
+        <v>2.181972063304481</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.030280987719237</v>
+        <v>1.18229129798865</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.98912201061474</v>
+        <v>4.080328196776388</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389352</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.372903785973522</v>
+        <v>-3.079862987782545</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.034508886145961</v>
+        <v>2.151725205422351</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.030280987719237</v>
+        <v>1.18229129798865</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.002195417480659</v>
+        <v>4.093401603642307</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.74988269137839</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.390707757694266</v>
+        <v>-3.097666959503289</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.019392494240603</v>
+        <v>2.136608813516994</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.9597463648140359</v>
+        <v>1.111756675083448</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.951879840520478</v>
+        <v>4.043086026682126</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006973</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.418608544803739</v>
+        <v>-3.125567746612762</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.006756220523815</v>
+        <v>2.123972539800207</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.9251494406711011</v>
+        <v>1.077159750940514</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.929645727161719</v>
+        <v>4.020851913323367</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787386</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.541134647506633</v>
+        <v>-3.248093849315656</v>
       </c>
       <c r="E2014" t="n">
-        <v>1.954510223419857</v>
+        <v>2.071726542696248</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.8026233379682072</v>
+        <v>0.9546336482376199</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.852894509517182</v>
+        <v>3.94410069567883</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585936</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.771649143692222</v>
+        <v>-3.478608345501245</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.929010384536125</v>
+        <v>2.046226703812516</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.5721088417826184</v>
+        <v>0.7241191520520311</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.781291771396332</v>
+        <v>3.87249795755798</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814665</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-4.120394228916665</v>
+        <v>-3.827353430725688</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.929824069448195</v>
+        <v>2.047040388724585</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.4633608878637206</v>
+        <v>0.6153711981331333</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.856354718046841</v>
+        <v>3.947560904208489</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237095</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.274380646692806</v>
+        <v>-3.953957559222451</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.937209771483378</v>
+        <v>2.06537900647152</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.4633608878637206</v>
+        <v>0.6153711981331333</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.92533498719248</v>
+        <v>4.016541173354129</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.61992301642339</v>
+        <v>3.619923016423388</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.22385874286514</v>
+        <v>-3.903435655394785</v>
       </c>
       <c r="E2018" t="n">
-        <v>1.943469735134566</v>
+        <v>2.071638970122708</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.4633608878637206</v>
+        <v>0.6153711981331333</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.911386189312601</v>
+        <v>4.002592375474249</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609756</v>
+        <v>3.656332733609754</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.476333896872864</v>
+        <v>-4.15591080940251</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.85435016258689</v>
+        <v>1.982519397575031</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.4633608878637206</v>
+        <v>0.6153711981331333</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.923256678368015</v>
+        <v>4.014462864529663</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973161</v>
+        <v>3.674028535973159</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.769229653352276</v>
+        <v>-4.448806565881922</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.738402394514069</v>
+        <v>1.86657162950221</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.4633608878637206</v>
+        <v>0.6153711981331333</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.924467212886959</v>
+        <v>4.015673399048607</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251948</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.955893781487084</v>
+        <v>-4.63547069401673</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.667858485487467</v>
+        <v>1.796027720475609</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.4366219170391608</v>
+        <v>0.5886322273085735</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.912545572619544</v>
+        <v>4.003751758781192</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916204</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-5.101914468401047</v>
+        <v>-4.781491380930692</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.604528063458071</v>
+        <v>1.732697298446213</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4275388252453038</v>
+        <v>0.5795491355147164</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.90217357027942</v>
+        <v>3.993379756441067</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830331</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.193628477510632</v>
+        <v>-4.873205390040278</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.730046516513281</v>
+        <v>1.858215751501423</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4275388252453038</v>
+        <v>0.5795491355147164</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.064377626978464</v>
+        <v>4.155583813140112</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071554</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.225280136570602</v>
+        <v>-4.904857049100247</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.712232490853108</v>
+        <v>1.840401725841249</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4223703680008636</v>
+        <v>0.5743806782702763</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.056123190595614</v>
+        <v>4.147329376757262</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868149</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.307214954839485</v>
+        <v>-4.98679186736913</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.689687981114045</v>
+        <v>1.817857216102187</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.4124356224137834</v>
+        <v>0.5644459326831961</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.060391760811857</v>
+        <v>4.151597946973505</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332694</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.409191077087892</v>
+        <v>-5.088767989617538</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.657823170670585</v>
+        <v>1.785992405658727</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.3104595001653758</v>
+        <v>0.4624698104347885</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.008131725918715</v>
+        <v>4.099337912080363</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231811</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.299184793610671</v>
+        <v>-4.978761706140316</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.693978571305649</v>
+        <v>1.822147806293791</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.333664072082651</v>
+        <v>0.4856743823520637</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.014207356313255</v>
+        <v>4.105413542474903</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818519</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.156125217869745</v>
+        <v>-4.83570213039939</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.755452412323994</v>
+        <v>1.883621647312135</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.3416774986726303</v>
+        <v>0.493687808942043</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.023265422989217</v>
+        <v>4.114471609150865</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051786</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.854678492397907</v>
+        <v>-4.534255404927553</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.883291985395265</v>
+        <v>2.011461220383406</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.6431242241444676</v>
+        <v>0.7951345344138803</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.211394341154856</v>
+        <v>4.302600527316503</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679623</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.879268736633091</v>
+        <v>-4.558845649162737</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.874427065453902</v>
+        <v>2.002596300442043</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.6431242241444676</v>
+        <v>0.7951345344138803</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.212365518907566</v>
+        <v>4.303571705069213</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474161</v>
+        <v>3.821184182474159</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.828230360626571</v>
+        <v>-4.507807273156216</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.895685320236265</v>
+        <v>2.023854555224407</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.6431242241444676</v>
+        <v>0.7951345344138803</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.213208423287321</v>
+        <v>4.304414609448969</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969545</v>
+        <v>3.831734516969544</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.78709106575994</v>
+        <v>-4.466667978289586</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.931179137057063</v>
+        <v>2.059348372045205</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.6842635190110984</v>
+        <v>0.8362738292805111</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.256930099081446</v>
+        <v>4.348136285243093</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.82575293270048</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.6904561537413</v>
+        <v>-4.370033066270945</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.786017097988454</v>
+        <v>1.914186332976596</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.7808984310297383</v>
+        <v>0.932908741299151</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.131095042416564</v>
+        <v>4.222301228578212</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077641</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.821036888272142</v>
+        <v>-4.500613800801788</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.737286848250081</v>
+        <v>1.865456083238223</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.6503176964988958</v>
+        <v>0.8023280067683085</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.056248645772023</v>
+        <v>4.14745483193367</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833459</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.656540554081181</v>
+        <v>-4.336117466610826</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.787512201002548</v>
+        <v>1.91568143599069</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.8148140306898577</v>
+        <v>0.9668243409592704</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.139373265362682</v>
+        <v>4.23057945152433</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077626</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.579441952539308</v>
+        <v>-4.259018865068954</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.817539352055727</v>
+        <v>1.945708587043868</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.8148140306898577</v>
+        <v>0.9668243409592704</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.138560975799113</v>
+        <v>4.22976716196076</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147911</v>
+        <v>3.83230702414791</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.589827147429197</v>
+        <v>-4.269404059958843</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.823254053224844</v>
+        <v>1.951423288212985</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.8044288357999684</v>
+        <v>0.9564391460693811</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.142198637990251</v>
+        <v>4.233404824151899</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735283</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.608415306151422</v>
+        <v>-4.287992218681068</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.886655795512379</v>
+        <v>2.01482503050052</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.7858406770777431</v>
+        <v>0.9378509873471557</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.201882748533341</v>
+        <v>4.293088934694989</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496555</v>
+        <v>3.855120535496553</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.608713852847458</v>
+        <v>-4.288290765377104</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.883405387652263</v>
+        <v>2.011574622640405</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.7855421303817072</v>
+        <v>0.9375524406511198</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.198572631334018</v>
+        <v>4.289778817495666</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.81564321210886</v>
+        <v>3.815643212108858</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.507890719157031</v>
+        <v>-4.187467631686676</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.928265536067825</v>
+        <v>2.056434771055967</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.798006345866061</v>
+        <v>0.9500166561354736</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.210582055564021</v>
+        <v>4.301788241725669</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121471</v>
+        <v>3.807356168121469</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.317109358404624</v>
+        <v>-3.996686270934269</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.004707333847331</v>
+        <v>2.132876568835473</v>
       </c>
       <c r="F2041" t="n">
-        <v>0.9887877066184685</v>
+        <v>1.140798016887881</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.325180125494009</v>
+        <v>4.416386311655657</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906084</v>
+        <v>3.775233033906082</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.210146000555202</v>
+        <v>-3.889722913084847</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.027329522724696</v>
+        <v>2.155498757712839</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.04725231457827</v>
+        <v>1.199262624847683</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.340095736007487</v>
+        <v>4.431301922169134</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912987</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.15481541265344</v>
+        <v>-3.834392325183085</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.08442869449746</v>
+        <v>2.212597929485602</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.102582902480032</v>
+        <v>1.254593212749445</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.408261025360603</v>
+        <v>4.49946721152225</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539898</v>
+        <v>3.743767956539896</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-4.142761285740477</v>
+        <v>-3.822338198270122</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.082936913164083</v>
+        <v>2.211106148152225</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.114637029392995</v>
+        <v>1.266647339662407</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.409180069409818</v>
+        <v>4.500386255571465</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811013</v>
+        <v>3.725010844811012</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.183916405308698</v>
+        <v>-3.863493317838343</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.06835549552093</v>
+        <v>2.196524730509072</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.073481909824774</v>
+        <v>1.225492220094186</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.386367627853021</v>
+        <v>4.477573814014669</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382924</v>
+        <v>3.612322444382922</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-4.115867842617168</v>
+        <v>-3.795444755146813</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.108425946475425</v>
+        <v>2.236595181463567</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.141530472516304</v>
+        <v>1.293540782785716</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.440047791345822</v>
+        <v>4.531253977507469</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013431</v>
+        <v>3.64525678001343</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.347468235786669</v>
+        <v>-4.027045148316314</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.035988459381219</v>
+        <v>2.164157694369361</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.141530472516304</v>
+        <v>1.293540782785716</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.460250461519416</v>
+        <v>4.551456647681063</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498969</v>
+        <v>3.666747201498968</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.397519781315887</v>
+        <v>-4.077096693845533</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.999574077236413</v>
+        <v>2.127743312224555</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.141530472516304</v>
+        <v>1.293540782785716</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.443856697586298</v>
+        <v>4.535062883747946</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800097</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.572626613892332</v>
+        <v>-4.252203526421978</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.889783257799302</v>
+        <v>2.017952492787444</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.141530472516304</v>
+        <v>1.293540782785716</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.404108611179764</v>
+        <v>4.495314797341412</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660851</v>
+        <v>3.745573148660849</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.376526460461809</v>
+        <v>-4.056103372991455</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.975245938168451</v>
+        <v>2.103415173156593</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.337630625946827</v>
+        <v>1.489640936216239</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.528791322235018</v>
+        <v>4.619997508396666</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395088</v>
+        <v>3.730570473395086</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.223501068348525</v>
+        <v>-3.903077980878171</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.13562709458667</v>
+        <v>2.263796329574811</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.490656018060111</v>
+        <v>1.642666328329523</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.719777557075894</v>
+        <v>4.810983743237541</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.74127833279115</v>
+        <v>3.741278332791148</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.251808382221795</v>
+        <v>-3.931385294751441</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.311770393945654</v>
+        <v>2.439939628933796</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.490656018060111</v>
+        <v>1.642666328329523</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.907243781984185</v>
+        <v>4.998449968145833</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620435</v>
+        <v>3.699115615620434</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.418401607335317</v>
+        <v>-4.097978519864963</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.214536055254327</v>
+        <v>2.342705290242469</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.324062792946588</v>
+        <v>1.476073103216001</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.776690798270154</v>
+        <v>4.867896984431802</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285648</v>
+        <v>3.708182519285646</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.395365813973751</v>
+        <v>-4.074942726503397</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.227426775260671</v>
+        <v>2.355596010248813</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.324062792946588</v>
+        <v>1.476073103216001</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.780367200931872</v>
+        <v>4.87157338709352</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399471</v>
+        <v>3.740581401399469</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.366119833518055</v>
+        <v>-4.0456967460477</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.236743222566445</v>
+        <v>2.364912457554587</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.324062792946588</v>
+        <v>1.476073103216001</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.777985256055367</v>
+        <v>4.869191442217015</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256374</v>
+        <v>3.699404642256372</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.473045381395906</v>
+        <v>-4.152622293925551</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.19126624257294</v>
+        <v>2.319435477561082</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.217137245068737</v>
+        <v>1.36914755533815</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.711123166486292</v>
+        <v>4.80232935264794</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701004</v>
+        <v>3.689942600701003</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.618063939903155</v>
+        <v>-4.2976408524328</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.134687621313274</v>
+        <v>2.262856856301416</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.072118686561488</v>
+        <v>1.224128996830901</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.625540833525177</v>
+        <v>4.716747019686824</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687017</v>
+        <v>3.711852429687015</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.736405705687872</v>
+        <v>-4.415982618217518</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.18728215425714</v>
+        <v>2.315451389245282</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.082804725124379</v>
+        <v>1.234815035393791</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.731883695920664</v>
+        <v>4.823089882082312</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790807</v>
+        <v>3.714879051790805</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.78781612800858</v>
+        <v>-4.467393040538226</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.164503682454796</v>
+        <v>2.292672917442938</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.082804725124379</v>
+        <v>1.234815035393791</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.729669393046603</v>
+        <v>4.82087557920825</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437335</v>
+        <v>3.704757949437333</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.867235579216332</v>
+        <v>-4.546812491745977</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.132639030045985</v>
+        <v>2.260808265034127</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.082804725124379</v>
+        <v>1.234815035393791</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.729572521120892</v>
+        <v>4.82077870728254</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298402</v>
+        <v>3.7368049522984</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.962698577133549</v>
+        <v>-4.642275489663195</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.094447724437141</v>
+        <v>2.222616959425283</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.082804725124379</v>
+        <v>1.234815035393791</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.729566414678936</v>
+        <v>4.820772600840583</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218005</v>
+        <v>3.715372960218003</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.898322666282835</v>
+        <v>-4.57789957881248</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.118294485340038</v>
+        <v>2.24646372032818</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.147180635975094</v>
+        <v>1.299190946244506</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.766288357751975</v>
+        <v>4.857494543913623</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353539</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.953691828415028</v>
+        <v>-4.633268740944674</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.101880638234887</v>
+        <v>2.230049873223029</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.147180635975094</v>
+        <v>1.299190946244506</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.772022175499702</v>
+        <v>4.863228361661349</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113284</v>
+        <v>3.736822870113282</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.999129608245855</v>
+        <v>-4.678706520775501</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.083243889645488</v>
+        <v>2.21141312463363</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.104335645296934</v>
+        <v>1.256345955566347</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.745853544435739</v>
+        <v>4.837059730597386</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113691</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.910922774098277</v>
+        <v>-4.590499686627923</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.138401016154838</v>
+        <v>2.26657025114298</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.104335645296934</v>
+        <v>1.256345955566347</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.765727937286058</v>
+        <v>4.856934123447705</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.79448684401644</v>
+        <v>3.794486844016438</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.804887778892968</v>
+        <v>-4.484464691422613</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.16451571476169</v>
+        <v>2.292684949749832</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.104335645296934</v>
+        <v>1.256345955566347</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.749428637810786</v>
+        <v>4.840634823972433</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307671</v>
+        <v>3.79470509330767</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.621676115759873</v>
+        <v>-4.301253028289518</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.240231329478974</v>
+        <v>2.368400564467115</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.104335645296934</v>
+        <v>1.256345955566347</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.751859587274831</v>
+        <v>4.843065773436479</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863551</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.549954668746022</v>
+        <v>-4.229531581275667</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.234711094132403</v>
+        <v>2.362880329120545</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.176057092310785</v>
+        <v>1.328067402580198</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.76068364133103</v>
+        <v>4.851889827492678</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394114</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.527581643138316</v>
+        <v>-4.207158555667961</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.190576050296658</v>
+        <v>2.318745285284799</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.187312843423686</v>
+        <v>1.339323153693099</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.714352837919943</v>
+        <v>4.805559024081591</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456734</v>
+        <v>3.715607446456732</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.56059793904906</v>
+        <v>-4.240174851578706</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.362567736817715</v>
+        <v>2.490736971805857</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.117875466756935</v>
+        <v>1.269885777026347</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.857888616805248</v>
+        <v>4.949094802966895</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883681</v>
+        <v>3.713762536883679</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.549070303399452</v>
+        <v>-4.228647215929097</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.359100016905808</v>
+        <v>2.48726925189395</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.176876124958297</v>
+        <v>1.32888643522771</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.885210237554314</v>
+        <v>4.976416423715961</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236301</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.64641180474182</v>
+        <v>-4.325988717271466</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.323831528890649</v>
+        <v>2.45200076387879</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.132455942792809</v>
+        <v>1.284466253062222</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.86222624077681</v>
+        <v>4.953432426938457</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427689</v>
+        <v>3.705201079427687</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.732267834081787</v>
+        <v>-4.411844746611433</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.2907401993475</v>
+        <v>2.418909434335642</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.090079873566674</v>
+        <v>1.242090183836086</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.838051681433967</v>
+        <v>4.929257867595615</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610382</v>
+        <v>3.691835499610381</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.741104631497906</v>
+        <v>-4.420681544027552</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.269624682201554</v>
+        <v>2.397793917189696</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.082637700925323</v>
+        <v>1.234648011194736</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.816005579669659</v>
+        <v>4.907211765831306</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667458</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.832487194063365</v>
+        <v>-4.51206410659301</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.24323616822042</v>
+        <v>2.371405403208562</v>
       </c>
       <c r="F2075" t="n">
-        <v>0.9912551383598649</v>
+        <v>1.143265448629277</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.771340553175433</v>
+        <v>4.86254673933708</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.673978374889194</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.820780476076359</v>
+        <v>-4.500357388606004</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.350047113239491</v>
+        <v>2.478216348227633</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.002961856346871</v>
+        <v>1.154972166616284</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.880492841791905</v>
+        <v>4.971699027953552</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.68247609940957</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.721116971992696</v>
+        <v>-4.400693884522342</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.39294485360436</v>
+        <v>2.521114088592503</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.066148939550558</v>
+        <v>1.21815924981997</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.921437430445521</v>
+        <v>5.012643616607169</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452574</v>
+        <v>3.672895177452573</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.731433070159048</v>
+        <v>-4.411009982688694</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.601723247615878</v>
+        <v>2.72989248260402</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.066148939550558</v>
+        <v>1.21815924981997</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.134342263723579</v>
+        <v>5.225548449885227</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762291</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.731339102141676</v>
+        <v>-4.410916014671321</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.600939501734917</v>
+        <v>2.729108736723059</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.13374284744406</v>
+        <v>5.224949033605707</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988024</v>
+        <v>3.633213467988022</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.73855792634152</v>
+        <v>-4.418134838871166</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.592283957999333</v>
+        <v>2.720453192987475</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.127974833388413</v>
+        <v>5.219181019550061</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740921</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.737609503223482</v>
+        <v>-4.417186415753127</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.592663327246548</v>
+        <v>2.72083256223469</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.127974833388413</v>
+        <v>5.219181019550061</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663623</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.894677961479106</v>
+        <v>-4.574254874008751</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.542563551925391</v>
+        <v>2.670732786913533</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.140702441369505</v>
+        <v>5.231908627531153</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424767</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.888685714690294</v>
+        <v>-4.56826262721994</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.546906449065303</v>
+        <v>2.675075684053445</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.142648439793893</v>
+        <v>5.233854625955541</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149216</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.800127753559527</v>
+        <v>-4.479704666089172</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.575983769535379</v>
+        <v>2.704153004523521</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.136302575811662</v>
+        <v>5.22750876197331</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383089</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.782368676056453</v>
+        <v>-4.461945588586098</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.582396077975604</v>
+        <v>2.710565312963746</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.135611253250658</v>
+        <v>5.226817439412305</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.71425897897649</v>
+        <v>3.788503044725581</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.474483822994813</v>
+        <v>4.540426601521109</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.782368676056453</v>
+        <v>-4.461945588586098</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.582396077975604</v>
+        <v>2.710565312963746</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.066518800897876</v>
+        <v>1.218529111167288</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.467547619981181</v>
+        <v>4.533490398507476</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>57.9%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.2%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>60.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>103.4%</t>
+          <t>108.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>42.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>43.9%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>86.8%</t>
+          <t>89.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>33.7%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -874,7 +874,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.4%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>142.4%</t>
+          <t>157.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.2%</t>
+          <t>-75.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.70</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.6%</t>
+          <t>123.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-36.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.2%</t>
+          <t>22.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-46.0%</t>
+          <t>-45.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-70.8%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>89.5%</t>
+          <t>89.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>423.0%</t>
+          <t>422.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-607.8%</t>
+          <t>-590.7%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.9%</t>
+          <t>37.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>62.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>52.9%</t>
+          <t>53.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.8%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>32.1%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.9%</t>
+          <t>47.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.2%</t>
+          <t>0.3%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-105.2%</t>
+          <t>-98.4%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.05</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.4%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.8%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-323.7%</t>
+          <t>-322.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.1%</t>
+          <t>-81.2%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>62.5%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.17</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>72.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,37 +1466,37 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-23.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>76.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.5%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>22.3%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382327</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495498</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207811</v>
+        <v>3.305316798207814</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006532</v>
+        <v>3.305849539006535</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970904</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330522</v>
+        <v>3.300815818330525</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097821</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094115</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199283</v>
+        <v>3.405960511199284</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969591</v>
+        <v>3.424633354969592</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923084</v>
+        <v>3.419979433923085</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737171</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539464</v>
+        <v>3.501052558539463</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.49685190472989</v>
+        <v>3.496851904729889</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410273</v>
+        <v>3.485878594410272</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764397</v>
+        <v>3.480692492764396</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390586</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158922</v>
+        <v>3.600038265158921</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940719</v>
+        <v>3.691571733940718</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.76895167461157</v>
+        <v>3.768951674611571</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955329</v>
+        <v>3.72857792995533</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232415</v>
+        <v>3.747702660232417</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436231</v>
+        <v>3.766317079436233</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.78468452131195</v>
+        <v>3.784684521311952</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097245</v>
+        <v>3.800829354097247</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017772</v>
+        <v>3.789311112017773</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722819</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792047</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632782</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883074</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074783</v>
+        <v>3.798814771074785</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242294</v>
+        <v>3.797694884242295</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.822326997879966</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
@@ -46096,7 +46096,7 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508368</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
@@ -46119,7 +46119,7 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417704</v>
+        <v>3.710906731417705</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
@@ -46165,7 +46165,7 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225443</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
@@ -46188,7 +46188,7 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111293</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
@@ -46211,7 +46211,7 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
@@ -46234,7 +46234,7 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742298</v>
+        <v>3.786949957742296</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
@@ -46257,7 +46257,7 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
@@ -46280,7 +46280,7 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
@@ -46303,7 +46303,7 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809497</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
@@ -46326,7 +46326,7 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560424</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
@@ -46349,7 +46349,7 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472732</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
@@ -46372,7 +46372,7 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798535</v>
+        <v>3.743047603798533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
@@ -46395,7 +46395,7 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498862</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705321</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.863638472863335</v>
+        <v>-3.782416487291561</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.997595657712079</v>
+        <v>1.030084451940788</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7798857394768036</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.965377172706136</v>
+        <v>3.011338914857243</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.972252551306666</v>
+        <v>-3.891030565734892</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.074299687053952</v>
+        <v>1.106788481282661</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7798857394768036</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.085526833425341</v>
+        <v>3.131488575576448</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.936843513058523</v>
+        <v>-3.85562152748675</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.102976328455532</v>
+        <v>1.135465122684242</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7032828358916255</v>
+        <v>0.7798857394768036</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.100039859527664</v>
+        <v>3.146001601678771</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.898459850500372</v>
+        <v>-3.817237864928599</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.115749234821161</v>
+        <v>1.148238029049871</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.8182694020349548</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.120489498404924</v>
+        <v>3.166451240556031</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.721343520465206</v>
+        <v>-3.640121534893432</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.18332479568053</v>
+        <v>1.215813589909239</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7416664984497767</v>
+        <v>0.8182694020349548</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.117218527250226</v>
+        <v>3.163180269401332</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793902</v>
+        <v>3.741328448793901</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.766435765298751</v>
+        <v>-3.685213779726978</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.165971289509025</v>
+        <v>1.198460083737734</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6797704552803869</v>
+        <v>0.756373358865565</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.080764293110505</v>
+        <v>3.126726035261612</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011233</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.587060344059983</v>
+        <v>-3.50583835848821</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.231508433310946</v>
+        <v>1.263997227539655</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8365472134511056</v>
+        <v>0.9131501170362837</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.16861732331935</v>
+        <v>3.214579065470457</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982228</v>
+        <v>3.716991718982227</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.63207455758059</v>
+        <v>-3.550852572008817</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.194310203234293</v>
+        <v>1.226798997463002</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.806198318136501</v>
+        <v>0.8828012217216791</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.131215441462177</v>
+        <v>3.177177183613284</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509538</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.899079067853025</v>
+        <v>-3.817857082281252</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.093199961464265</v>
+        <v>1.125688755692974</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6118352800935525</v>
+        <v>0.6884381836787306</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.020289180975354</v>
+        <v>3.066250923126461</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760809</v>
+        <v>3.702309454760807</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.000276849290198</v>
+        <v>-3.919054863718425</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.051924770785897</v>
+        <v>1.084413565014607</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.6200293701334114</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.978447814744664</v>
+        <v>3.024409556895771</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815451</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.993765882675885</v>
+        <v>-3.912543897104112</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.052129118985939</v>
+        <v>1.084617913214648</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5434264665482333</v>
+        <v>0.6200293701334114</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.976047776298981</v>
+        <v>3.022009518450087</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378099</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.974727754968588</v>
+        <v>-3.893505769396815</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.056269089277103</v>
+        <v>1.088757883505812</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5618457588022169</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.937662328708509</v>
+        <v>2.983624070859616</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131244</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.027243557243408</v>
+        <v>-3.946021571671635</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.154557170001365</v>
+        <v>1.187045964230074</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4852428552170388</v>
+        <v>0.5618457588022169</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.056956730342699</v>
+        <v>3.102918472493806</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067861</v>
       </c>
       <c r="C1964" t="n">
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.030651868677988</v>
+        <v>-3.949429883106215</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.154027174413667</v>
+        <v>1.186515968642376</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5943623278115943</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.077300000734459</v>
+        <v>3.123261742885566</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789121</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.990168876755643</v>
+        <v>-3.90894689118387</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.176228901579531</v>
+        <v>1.20871769580824</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5177594242264162</v>
+        <v>0.5943623278115943</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.083308531131385</v>
+        <v>3.129270273282492</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.842425906520641</v>
+        <v>-3.761203920948868</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.133276310950731</v>
+        <v>1.16576510517944</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7621696850464774</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.081943166749515</v>
+        <v>3.127904908900621</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181169</v>
+        <v>3.802245929181168</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.926247127795339</v>
+        <v>-3.845025142223566</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.102541443972333</v>
+        <v>1.135030238201042</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6855667814612993</v>
+        <v>0.7621696850464774</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.084736788280996</v>
+        <v>3.130698530432102</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394731</v>
+        <v>3.805608985394729</v>
       </c>
       <c r="C1968" t="n">
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.920094421742555</v>
+        <v>-3.838872436170782</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.105664874785105</v>
+        <v>1.138153669013814</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6917194875140836</v>
+        <v>0.7683223910992617</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.089090760304325</v>
+        <v>3.135052502455431</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890609</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.936903719893056</v>
+        <v>-3.855681734321283</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.098021632265014</v>
+        <v>1.130510426493724</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.674910189363582</v>
+        <v>0.7515130929487601</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.078085658154134</v>
+        <v>3.124047400305241</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.874605721116934</v>
+        <v>-3.793383735545161</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.189276385572284</v>
+        <v>1.221765179800993</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7202044536380241</v>
+        <v>0.7968073572232022</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.17159777051562</v>
+        <v>3.217559512666726</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992191</v>
+        <v>3.84872913999219</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.672815523451777</v>
+        <v>-3.591593537880003</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.072284466352474</v>
+        <v>1.104773260581184</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9182226458071785</v>
+        <v>0.9948255493923566</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.09270068753124</v>
+        <v>3.138662429682346</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.841444817852419</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.723702236137971</v>
+        <v>-3.642480250566198</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.122220013600172</v>
+        <v>1.154708807828881</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.867335933120984</v>
+        <v>0.9439388367061621</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.132458892241698</v>
+        <v>3.178420634392805</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319544</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.637091493488164</v>
+        <v>-3.555869507916391</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.171492046776138</v>
+        <v>1.203980841004848</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9459616643261423</v>
+        <v>1.02256456791132</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.194262067080837</v>
+        <v>3.240223809231944</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489382</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.697300791493448</v>
+        <v>-3.616078805921675</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.145944308398696</v>
+        <v>1.178433102627405</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9623552699060357</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.156672469102338</v>
+        <v>3.202634211253444</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397793</v>
       </c>
       <c r="C1975" t="n">
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.648114142809097</v>
+        <v>-3.566892157237324</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.164110585912365</v>
+        <v>1.196599380141075</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.8857523663208577</v>
+        <v>0.9623552699060357</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.155164087142266</v>
+        <v>3.201125829293373</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316247</v>
       </c>
       <c r="C1976" t="n">
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.603741011170528</v>
+        <v>-3.522519025598755</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.181722706003229</v>
+        <v>1.214211500231938</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9301254979594263</v>
+        <v>1.006728401544604</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.181650833560844</v>
+        <v>3.22761257571195</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105962</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.626221362029413</v>
+        <v>-3.54499937645764</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.167124359798265</v>
+        <v>1.199613154026975</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9301254979594263</v>
+        <v>1.006728401544604</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.176044627699434</v>
+        <v>3.222006369850541</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.83301114819032</v>
       </c>
       <c r="C1978" t="n">
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.578565631468358</v>
+        <v>-3.497343645896584</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.192568409050492</v>
+        <v>1.225057203279202</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.977781228520482</v>
+        <v>1.05438413210566</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.211019823063872</v>
+        <v>3.256981565214979</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569614</v>
+        <v>3.822678210569612</v>
       </c>
       <c r="C1979" t="n">
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.478047472969603</v>
+        <v>-3.396825487397829</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.237668045824719</v>
+        <v>1.270156840053428</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.078299387019237</v>
+        <v>1.154902290604415</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.27622309153785</v>
+        <v>3.322184833688957</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557291</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.462142143537251</v>
+        <v>-3.380920157965477</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.230784850073532</v>
+        <v>1.263273644302242</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.9991867263099976</v>
+        <v>1.075789629895176</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.215510167588179</v>
+        <v>3.261471909739285</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932766</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.417303741928853</v>
+        <v>-3.336081756357079</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.25281791332752</v>
+        <v>1.285306707556229</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.003730159254867</v>
+        <v>1.080333062840045</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.222333929965729</v>
+        <v>3.268295672116836</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917048</v>
+        <v>3.817932354917046</v>
       </c>
       <c r="C1982" t="n">
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.436802198170861</v>
+        <v>-3.355580212599087</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.249179470461795</v>
+        <v>1.281668264690504</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9556455179749628</v>
+        <v>1.032248421560141</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.197644084828864</v>
+        <v>3.243605826979971</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405956</v>
       </c>
       <c r="C1983" t="n">
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.39259936108496</v>
+        <v>-3.311377375513187</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.272740207823992</v>
+        <v>1.305229002052702</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.9998483550608632</v>
+        <v>1.076451258646041</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.230045389608242</v>
+        <v>3.276007131759348</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265642</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.374491763903783</v>
+        <v>-3.318937041350233</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.27839324716571</v>
+        <v>1.30061513618713</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.06432310015072</v>
+        <v>1.131254662655861</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.267140237131403</v>
+        <v>3.307299174634488</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284877</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.216200346364511</v>
+        <v>-3.160645623810961</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.392957579364459</v>
+        <v>1.415179468385879</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.06432310015072</v>
+        <v>1.131254662655861</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.318388002314443</v>
+        <v>3.358546939817527</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321022</v>
+        <v>3.865338681321021</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.008558342730035</v>
+        <v>-2.953003620176485</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.474455085412502</v>
+        <v>1.496676974433923</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.271965103785196</v>
+        <v>1.338896666290337</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.441413909089382</v>
+        <v>3.481572846592466</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.957526250007507</v>
+        <v>-2.901971527453957</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.489816150739784</v>
+        <v>1.512038039761204</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.322997196507724</v>
+        <v>1.389928759012865</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.466981392961169</v>
+        <v>3.507140330464253</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.892302068880301</v>
+        <v>-2.836747346326751</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.533093227283371</v>
+        <v>1.555315116304791</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.38822137763493</v>
+        <v>1.45515294014007</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.523303305730197</v>
+        <v>3.563462243233281</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882557</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.854875048809168</v>
+        <v>-2.799320326255617</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.544025007611105</v>
+        <v>1.566246896632525</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.393472915664112</v>
+        <v>1.460404478169252</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.522415200846986</v>
+        <v>3.562574138350071</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992662</v>
+        <v>3.845169808992661</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.874986704843876</v>
+        <v>-2.819431982290326</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.537237137528462</v>
+        <v>1.559459026549882</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.404500260661531</v>
+        <v>1.471431823166671</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.530288400176678</v>
+        <v>3.570447337679763</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636288</v>
+        <v>3.828661445636287</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.846573441743992</v>
+        <v>-2.791018719190442</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.709160213789626</v>
+        <v>1.731382102811046</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.345524697915102</v>
+        <v>1.412456260420243</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.655460833550031</v>
+        <v>3.695619771053116</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957627</v>
+        <v>3.813222820957626</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.77179118071898</v>
+        <v>-2.716236458165429</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.859186027417448</v>
+        <v>1.881407916438868</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.420306958940115</v>
+        <v>1.487238521445255</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.820443099382857</v>
+        <v>3.860602036885941</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.745707096455172</v>
+        <v>-2.690152373901622</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.86132763713683</v>
+        <v>1.88354952615825</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.420306958940115</v>
+        <v>1.487238521445255</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.812151075396716</v>
+        <v>3.8523100128998</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.657829183346051</v>
+        <v>-2.602274460792501</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.894671997964258</v>
+        <v>1.916893886985678</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.536232601363466</v>
+        <v>1.603164163868606</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.879899656434505</v>
+        <v>3.92005859393759</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.648936721952768</v>
+        <v>-2.593381999399218</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.915783388248363</v>
+        <v>1.938005277269783</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.536232601363466</v>
+        <v>1.603164163868606</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.897454062161297</v>
+        <v>3.937612999664381</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945365</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.817412838922646</v>
+        <v>-2.761858116369095</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.840247988864996</v>
+        <v>1.862469877886416</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.508284765646885</v>
+        <v>1.575216328152026</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.872540408135932</v>
+        <v>3.912699345639017</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782708</v>
+        <v>3.79557406678271</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.371156646293206</v>
+        <v>-2.315601923739655</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.000020163104633</v>
+        <v>2.022242052126054</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.413566095977252</v>
+        <v>1.480497658482393</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.796978903522015</v>
+        <v>3.837137841025099</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632636</v>
+        <v>3.784671345632638</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.348435542610053</v>
+        <v>-2.292880820056503</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.999772627074799</v>
+        <v>2.021994516096219</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.413566095977252</v>
+        <v>1.480497658482393</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.787642926018919</v>
+        <v>3.827801863522003</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777673</v>
+        <v>3.783205696777675</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.477637355904096</v>
+        <v>-2.422082633350545</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.106998027608351</v>
+        <v>2.129219916629771</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.28436428268321</v>
+        <v>1.351295845188351</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.869027963893663</v>
+        <v>3.909186901396747</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644414</v>
+        <v>3.779933725644415</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.503511754378121</v>
+        <v>-2.447957031824571</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.133726090712387</v>
+        <v>2.155947979733807</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.329275891394951</v>
+        <v>1.396207453900092</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.933052751614354</v>
+        <v>3.973211689117439</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799961</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.496457064162948</v>
+        <v>-2.440902341609398</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.133223322788002</v>
+        <v>2.155445211809422</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.336330581610125</v>
+        <v>1.403262144115266</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.933960921733004</v>
+        <v>3.974119859236088</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331115</v>
+        <v>3.766673496331117</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.46950583983646</v>
+        <v>-2.41395111728291</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.154009966163339</v>
+        <v>2.176231855184759</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.351210927637844</v>
+        <v>1.418142490142985</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.952895282994376</v>
+        <v>3.993054220497461</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784108</v>
+        <v>3.768052067784111</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.491050067667247</v>
+        <v>-2.435495345113697</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.329495407175984</v>
+        <v>2.351717296197404</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.351210927637844</v>
+        <v>1.418142490142985</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.136998415139336</v>
+        <v>4.17715735264242</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714422</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.513458185472119</v>
+        <v>-2.457903462918569</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.312648854957028</v>
+        <v>2.334870743978448</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.351210927637844</v>
+        <v>1.418142490142985</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.12911511004233</v>
+        <v>4.169274047545414</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155034</v>
+        <v>3.719118627155035</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.541682421049719</v>
+        <v>-2.486127698496169</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.303413160275625</v>
+        <v>2.325635049297045</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.369187680089153</v>
+        <v>1.436119242594293</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.141955161062752</v>
+        <v>4.182114098565837</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.72945228516198</v>
+        <v>3.729452285161981</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.551123346938249</v>
+        <v>-2.495568624384699</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.35589050764206</v>
+        <v>2.378112396663481</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.491614797632544</v>
+        <v>1.558546360137685</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.271665149310634</v>
+        <v>4.311824086813719</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321637</v>
+        <v>3.714941193321638</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.639999978106723</v>
+        <v>-2.584445255553173</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.323230949719972</v>
+        <v>2.345452838741392</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.40273816646407</v>
+        <v>1.469669728969211</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.22123026515485</v>
+        <v>4.261389202657935</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347706</v>
+        <v>3.727898186347708</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.716329955707629</v>
+        <v>-2.660775233154079</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.290810771573384</v>
+        <v>2.313032660594804</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.40273816646407</v>
+        <v>1.469669728969211</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.219342078048625</v>
+        <v>4.25950101555171</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887752</v>
+        <v>3.710654104887753</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.80999390038517</v>
+        <v>-2.75443917783162</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.24816542330523</v>
+        <v>2.27038731232665</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.309074221786529</v>
+        <v>1.37600578429167</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.157963940844963</v>
+        <v>4.198122878348047</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343069</v>
+        <v>3.712897612343071</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.971562325912426</v>
+        <v>-2.916007603358875</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.181972063304481</v>
+        <v>2.204193952325901</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.18229129798865</v>
+        <v>1.24922286049379</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.080328196776388</v>
+        <v>4.120487134279472</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389352</v>
+        <v>3.754596135389354</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.079862987782545</v>
+        <v>-3.024308265228995</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.151725205422351</v>
+        <v>2.173947094443771</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.18229129798865</v>
+        <v>1.24922286049379</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.093401603642307</v>
+        <v>4.133560541145391</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74988269137839</v>
+        <v>3.749882691378391</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.097666959503289</v>
+        <v>-3.042112236949739</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.136608813516994</v>
+        <v>2.158830702538414</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.111756675083448</v>
+        <v>1.178688237588589</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.043086026682126</v>
+        <v>4.08324496418521</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006973</v>
+        <v>3.715819895006975</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.125567746612762</v>
+        <v>-3.070013024059212</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.123972539800207</v>
+        <v>2.146194428821627</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.077159750940514</v>
+        <v>1.144091313445654</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.020851913323367</v>
+        <v>4.061010850826452</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787386</v>
+        <v>3.684895778787388</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.248093849315656</v>
+        <v>-3.192539126762106</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.071726542696248</v>
+        <v>2.093948431717668</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9546336482376199</v>
+        <v>1.02156521074276</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.94410069567883</v>
+        <v>3.984259633181914</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585936</v>
+        <v>3.619348081585938</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.478608345501245</v>
+        <v>-3.423053622947695</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.046226703812516</v>
+        <v>2.068448592833936</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7241191520520311</v>
+        <v>0.7910507145571717</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.87249795755798</v>
+        <v>3.912656895061065</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814665</v>
+        <v>3.640750087814666</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.827353430725688</v>
+        <v>-3.771798708172138</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.047040388724585</v>
+        <v>2.069262277746005</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6153711981331333</v>
+        <v>0.6823027606382739</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.947560904208489</v>
+        <v>3.987719841711573</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237095</v>
+        <v>3.668289004237097</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.953957559222451</v>
+        <v>-3.925785125948279</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.06537900647152</v>
+        <v>2.076647979781189</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6153711981331333</v>
+        <v>0.6823027606382739</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.016541173354129</v>
+        <v>4.056700110857212</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423388</v>
+        <v>3.619923016423391</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.903435655394785</v>
+        <v>-3.875263222120613</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.071638970122708</v>
+        <v>2.082907943432376</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6153711981331333</v>
+        <v>0.6823027606382739</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.002592375474249</v>
+        <v>4.042751312977333</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609754</v>
+        <v>3.656332733609759</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.15591080940251</v>
+        <v>-4.127738376128337</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.982519397575031</v>
+        <v>1.993788370884701</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6153711981331333</v>
+        <v>0.6823027606382739</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.014462864529663</v>
+        <v>4.054621802032747</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973159</v>
+        <v>3.674028535973163</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.448806565881922</v>
+        <v>-4.420634132607749</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.86657162950221</v>
+        <v>1.877840602811879</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6153711981331333</v>
+        <v>0.6823027606382739</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.015673399048607</v>
+        <v>4.055832336551691</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663509457251948</v>
+        <v>3.66350945725195</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.63547069401673</v>
+        <v>-4.607298260742557</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.796027720475609</v>
+        <v>1.807296693785278</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5886322273085735</v>
+        <v>0.655563789813714</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.003751758781192</v>
+        <v>4.043910696284277</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916204</v>
+        <v>3.652149152916206</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.781491380930692</v>
+        <v>-4.75331894765652</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.732697298446213</v>
+        <v>1.743966271755882</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.5795491355147164</v>
+        <v>0.646480698019857</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.993379756441067</v>
+        <v>4.033538693944152</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830331</v>
+        <v>3.667962306830333</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.873205390040278</v>
+        <v>-4.845032956766104</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.858215751501423</v>
+        <v>1.869484724811092</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.5795491355147164</v>
+        <v>0.646480698019857</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.155583813140112</v>
+        <v>4.195742750643196</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071554</v>
+        <v>3.696539468071555</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.904857049100247</v>
+        <v>-4.876684615826074</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.840401725841249</v>
+        <v>1.851670699150919</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5743806782702763</v>
+        <v>0.6413122407754168</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.147329376757262</v>
+        <v>4.187488314260346</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868149</v>
+        <v>3.750044015868151</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.98679186736913</v>
+        <v>-4.958619434094957</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.817857216102187</v>
+        <v>1.829126189411857</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5644459326831961</v>
+        <v>0.6313774951883366</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.151597946973505</v>
+        <v>4.191756884476589</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332694</v>
+        <v>3.783632867332695</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.088767989617538</v>
+        <v>-5.060595556343364</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.785992405658727</v>
+        <v>1.797261378968396</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4624698104347885</v>
+        <v>0.5294013729399291</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.099337912080363</v>
+        <v>4.139496849583447</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231811</v>
+        <v>3.798296784231812</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.978761706140316</v>
+        <v>-4.950589272866143</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.822147806293791</v>
+        <v>1.83341677960346</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4856743823520637</v>
+        <v>0.5526059448572043</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.105413542474903</v>
+        <v>4.145572479977988</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818519</v>
+        <v>3.785563924818521</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.83570213039939</v>
+        <v>-4.807529697125217</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.883621647312135</v>
+        <v>1.894890620621805</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.493687808942043</v>
+        <v>0.5606193714471835</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.114471609150865</v>
+        <v>4.154630546653949</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051786</v>
+        <v>3.777237412051788</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.534255404927553</v>
+        <v>-4.506082971653379</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.011461220383406</v>
+        <v>2.022730193693076</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7951345344138803</v>
+        <v>0.8620660969190208</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.302600527316503</v>
+        <v>4.342759464819587</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679623</v>
+        <v>3.812635940679626</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.558845649162737</v>
+        <v>-4.530673215888563</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.002596300442043</v>
+        <v>2.013865273751713</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.7951345344138803</v>
+        <v>0.8620660969190208</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.303571705069213</v>
+        <v>4.343730642572298</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474159</v>
+        <v>3.821184182474163</v>
       </c>
       <c r="C2031" t="n">
         <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.507807273156216</v>
+        <v>-4.479634839882043</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.023854555224407</v>
+        <v>2.035123528534077</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.7951345344138803</v>
+        <v>0.8620660969190208</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.304414609448969</v>
+        <v>4.344573546952054</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969544</v>
+        <v>3.831734516969547</v>
       </c>
       <c r="C2032" t="n">
         <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.466667978289586</v>
+        <v>-4.438495545015412</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.059348372045205</v>
+        <v>2.070617345354874</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8362738292805111</v>
+        <v>0.9032053917856516</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.348136285243093</v>
+        <v>4.388295222746177</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.82575293270048</v>
+        <v>3.825752932700483</v>
       </c>
       <c r="C2033" t="n">
         <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.370033066270945</v>
+        <v>-4.341860632996772</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.914186332976596</v>
+        <v>1.925455306286265</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.932908741299151</v>
+        <v>0.9998403038042916</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.222301228578212</v>
+        <v>4.262460166081296</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077641</v>
+        <v>3.804688961077644</v>
       </c>
       <c r="C2034" t="n">
         <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.500613800801788</v>
+        <v>-4.472441367527614</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.865456083238223</v>
+        <v>1.876725056547892</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8023280067683085</v>
+        <v>0.8692595692734491</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.14745483193367</v>
+        <v>4.187613769436755</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833459</v>
+        <v>3.775028860833462</v>
       </c>
       <c r="C2035" t="n">
         <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.336117466610826</v>
+        <v>-4.307945033336653</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.91568143599069</v>
+        <v>1.92695040930036</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9668243409592704</v>
+        <v>1.033755903464411</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.23057945152433</v>
+        <v>4.270738389027414</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077626</v>
+        <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
         <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.259018865068954</v>
+        <v>-4.23084643179478</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.945708587043868</v>
+        <v>1.956977560353538</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9668243409592704</v>
+        <v>1.033755903464411</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.22976716196076</v>
+        <v>4.269926099463844</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.83230702414791</v>
+        <v>3.832307024147914</v>
       </c>
       <c r="C2037" t="n">
         <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.269404059958843</v>
+        <v>-4.241231626684669</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.951423288212985</v>
+        <v>1.962692261522655</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9564391460693811</v>
+        <v>1.023370708574522</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.233404824151899</v>
+        <v>4.273563761654983</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735283</v>
+        <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
         <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.287992218681068</v>
+        <v>-4.259819785406894</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.01482503050052</v>
+        <v>2.02609400381019</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9378509873471557</v>
+        <v>1.004782549852296</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.293088934694989</v>
+        <v>4.333247872198073</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496553</v>
+        <v>3.855120535496558</v>
       </c>
       <c r="C2039" t="n">
         <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.288290765377104</v>
+        <v>-4.26011833210293</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.011574622640405</v>
+        <v>2.022843595950074</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9375524406511198</v>
+        <v>1.00448400315626</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.289778817495666</v>
+        <v>4.32993775499875</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108858</v>
+        <v>3.815643212108861</v>
       </c>
       <c r="C2040" t="n">
         <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.187467631686676</v>
+        <v>-4.159295198412503</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.056434771055967</v>
+        <v>2.067703744365637</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.9500166561354736</v>
+        <v>1.016948218640614</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.301788241725669</v>
+        <v>4.341947179228754</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121469</v>
+        <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
         <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.996686270934269</v>
+        <v>-3.968513837660095</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.132876568835473</v>
+        <v>2.144145542145143</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.140798016887881</v>
+        <v>1.207729579393022</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.416386311655657</v>
+        <v>4.456545249158742</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906082</v>
+        <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
         <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.889722913084847</v>
+        <v>-3.861550479810673</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.155498757712839</v>
+        <v>2.166767731022508</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.199262624847683</v>
+        <v>1.266194187352823</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.431301922169134</v>
+        <v>4.471460859672219</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912987</v>
+        <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
         <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.834392325183085</v>
+        <v>-3.806219891908911</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.212597929485602</v>
+        <v>2.223866902795272</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.254593212749445</v>
+        <v>1.321524775254585</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.49946721152225</v>
+        <v>4.539626149025334</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539896</v>
+        <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
         <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.822338198270122</v>
+        <v>-3.794165764995948</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.211106148152225</v>
+        <v>2.222375121461894</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.266647339662407</v>
+        <v>1.333578902167548</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.500386255571465</v>
+        <v>4.54054519307455</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811012</v>
+        <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
         <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.863493317838343</v>
+        <v>-3.835320884564169</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.196524730509072</v>
+        <v>2.207793703818742</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.225492220094186</v>
+        <v>1.292423782599327</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.477573814014669</v>
+        <v>4.517732751517753</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382922</v>
+        <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
         <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.795444755146813</v>
+        <v>-3.767272321872639</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.236595181463567</v>
+        <v>2.247864154773236</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.293540782785716</v>
+        <v>1.360472345290857</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.531253977507469</v>
+        <v>4.571412915010553</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.64525678001343</v>
+        <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
         <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.027045148316314</v>
+        <v>-3.998872715042141</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.164157694369361</v>
+        <v>2.17542666767903</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.293540782785716</v>
+        <v>1.360472345290857</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.551456647681063</v>
+        <v>4.591615585184147</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.666747201498968</v>
+        <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
         <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.077096693845533</v>
+        <v>-4.04892426057136</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.127743312224555</v>
+        <v>2.139012285534224</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.293540782785716</v>
+        <v>1.360472345290857</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.535062883747946</v>
+        <v>4.57522182125103</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800097</v>
+        <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
         <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.252203526421978</v>
+        <v>-4.224031093147804</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.017952492787444</v>
+        <v>2.029221466097113</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.293540782785716</v>
+        <v>1.360472345290857</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.495314797341412</v>
+        <v>4.535473734844496</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660849</v>
+        <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
         <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.056103372991455</v>
+        <v>-4.027930939717281</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.103415173156593</v>
+        <v>2.114684146466262</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.489640936216239</v>
+        <v>1.55657249872138</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.619997508396666</v>
+        <v>4.66015644589975</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395086</v>
+        <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
         <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.903077980878171</v>
+        <v>-3.874905547603997</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.263796329574811</v>
+        <v>2.27506530288448</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.642666328329523</v>
+        <v>1.709597890834664</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.810983743237541</v>
+        <v>4.851142680740625</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791148</v>
+        <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
         <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.931385294751441</v>
+        <v>-3.903212861477267</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.439939628933796</v>
+        <v>2.451208602243465</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.642666328329523</v>
+        <v>1.709597890834664</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.998449968145833</v>
+        <v>5.038608905648918</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620434</v>
+        <v>3.699115615620437</v>
       </c>
       <c r="C2053" t="n">
         <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.097978519864963</v>
+        <v>-3.927740596783989</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.342705290242469</v>
+        <v>2.410800459474858</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.476073103216001</v>
+        <v>1.685070155527942</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.867896984431802</v>
+        <v>4.993295215818967</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285646</v>
+        <v>3.708182519285652</v>
       </c>
       <c r="C2054" t="n">
         <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.074942726503397</v>
+        <v>-3.904704803422423</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.355596010248813</v>
+        <v>2.423691179481202</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.476073103216001</v>
+        <v>1.685070155527942</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.87157338709352</v>
+        <v>4.996971618480685</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399469</v>
+        <v>3.740581401399474</v>
       </c>
       <c r="C2055" t="n">
         <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.0456967460477</v>
+        <v>-3.875458822966727</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.364912457554587</v>
+        <v>2.433007626786976</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.476073103216001</v>
+        <v>1.685070155527942</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.869191442217015</v>
+        <v>4.99458967360418</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256372</v>
+        <v>3.699404642256376</v>
       </c>
       <c r="C2056" t="n">
         <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.152622293925551</v>
+        <v>-3.982384370844579</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.319435477561082</v>
+        <v>2.38753064679347</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.36914755533815</v>
+        <v>1.578144607650091</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.80232935264794</v>
+        <v>4.927727584035104</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701003</v>
+        <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
         <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.2976408524328</v>
+        <v>-4.127402929351828</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.262856856301416</v>
+        <v>2.330952025533805</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.224128996830901</v>
+        <v>1.433126049142842</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.716747019686824</v>
+        <v>4.842145251073989</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687015</v>
+        <v>3.711852429687018</v>
       </c>
       <c r="C2058" t="n">
         <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.415982618217518</v>
+        <v>-4.245744695136545</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.315451389245282</v>
+        <v>2.383546558477671</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.234815035393791</v>
+        <v>1.443812087705732</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.823089882082312</v>
+        <v>4.948488113469476</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790805</v>
+        <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
         <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.467393040538226</v>
+        <v>-4.297155117457253</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.292672917442938</v>
+        <v>2.360768086675327</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.234815035393791</v>
+        <v>1.443812087705732</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.82087557920825</v>
+        <v>4.946273810595414</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437333</v>
+        <v>3.704757949437336</v>
       </c>
       <c r="C2060" t="n">
         <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.546812491745977</v>
+        <v>-4.376574568665005</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.260808265034127</v>
+        <v>2.328903434266516</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.234815035393791</v>
+        <v>1.443812087705732</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.82077870728254</v>
+        <v>4.946176938669704</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.7368049522984</v>
+        <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
         <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.642275489663195</v>
+        <v>-4.472037566582222</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.222616959425283</v>
+        <v>2.290712128657672</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.234815035393791</v>
+        <v>1.443812087705732</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.820772600840583</v>
+        <v>4.946170832227748</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218003</v>
+        <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
         <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.57789957881248</v>
+        <v>-4.407661655731507</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.24646372032818</v>
+        <v>2.314558889560569</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.299190946244506</v>
+        <v>1.508187998556447</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.857494543913623</v>
+        <v>4.982892775300788</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353539</v>
+        <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
         <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.633268740944674</v>
+        <v>-4.463030817863701</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.230049873223029</v>
+        <v>2.298145042455418</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.299190946244506</v>
+        <v>1.508187998556447</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.863228361661349</v>
+        <v>4.988626593048514</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113282</v>
+        <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
         <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.678706520775501</v>
+        <v>-4.508468597694528</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.21141312463363</v>
+        <v>2.279508293866019</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.256345955566347</v>
+        <v>1.465343007878288</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.837059730597386</v>
+        <v>4.96245796198455</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113691</v>
+        <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
         <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.590499686627923</v>
+        <v>-4.42026176354695</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.26657025114298</v>
+        <v>2.334665420375369</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.256345955566347</v>
+        <v>1.465343007878288</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.856934123447705</v>
+        <v>4.982332354834869</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016438</v>
+        <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
         <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.484464691422613</v>
+        <v>-4.314226768341641</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.292684949749832</v>
+        <v>2.360780118982221</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.256345955566347</v>
+        <v>1.465343007878288</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.840634823972433</v>
+        <v>4.966033055359597</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.79470509330767</v>
+        <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
         <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.301253028289518</v>
+        <v>-4.131015105208546</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.368400564467115</v>
+        <v>2.436495733699505</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.256345955566347</v>
+        <v>1.465343007878288</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.843065773436479</v>
+        <v>4.968464004823643</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863551</v>
+        <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
         <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.229531581275667</v>
+        <v>-4.059293658194695</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.362880329120545</v>
+        <v>2.430975498352934</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.328067402580198</v>
+        <v>1.537064454892139</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.851889827492678</v>
+        <v>4.977288058879843</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394114</v>
+        <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
         <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.207158555667961</v>
+        <v>-4.036920632586988</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.318745285284799</v>
+        <v>2.386840454517189</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.339323153693099</v>
+        <v>1.54832020600504</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.805559024081591</v>
+        <v>4.930957255468755</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456732</v>
+        <v>3.715607446456734</v>
       </c>
       <c r="C2070" t="n">
         <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.240174851578706</v>
+        <v>-4.069936928497733</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.490736971805857</v>
+        <v>2.558832141038246</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.269885777026347</v>
+        <v>1.478882829338289</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.949094802966895</v>
+        <v>5.07449303435406</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883679</v>
+        <v>3.713762536883681</v>
       </c>
       <c r="C2071" t="n">
         <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.228647215929097</v>
+        <v>-4.058409292848125</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.48726925189395</v>
+        <v>2.555364421126338</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.32888643522771</v>
+        <v>1.537883487539651</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.976416423715961</v>
+        <v>5.101814655103126</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236301</v>
+        <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
         <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.325988717271466</v>
+        <v>-4.155750794190493</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.45200076387879</v>
+        <v>2.52009593311118</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.284466253062222</v>
+        <v>1.493463305374163</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.953432426938457</v>
+        <v>5.078830658325622</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427687</v>
+        <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
         <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.411844746611433</v>
+        <v>-4.24160682353046</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.418909434335642</v>
+        <v>2.487004603568031</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.242090183836086</v>
+        <v>1.451087236148028</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.929257867595615</v>
+        <v>5.054656098982779</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610381</v>
+        <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
         <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.420681544027552</v>
+        <v>-4.250443620946579</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.397793917189696</v>
+        <v>2.465889086422085</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.234648011194736</v>
+        <v>1.443645063506677</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.907211765831306</v>
+        <v>5.03260999721847</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.715544411667458</v>
+        <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
         <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.51206410659301</v>
+        <v>-4.341826183512038</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.371405403208562</v>
+        <v>2.439500572440951</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.143265448629277</v>
+        <v>1.352262500941219</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.86254673933708</v>
+        <v>4.987944970724245</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889194</v>
+        <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
         <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.500357388606004</v>
+        <v>-4.330119465525032</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.478216348227633</v>
+        <v>2.546311517460022</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.154972166616284</v>
+        <v>1.363969218928225</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.971699027953552</v>
+        <v>5.097097259340717</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.68247609940957</v>
+        <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
         <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.400693884522342</v>
+        <v>-4.230455961441369</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.521114088592503</v>
+        <v>2.589209257824892</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.21815924981997</v>
+        <v>1.427156302131911</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.012643616607169</v>
+        <v>5.138041847994334</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452573</v>
+        <v>3.672895177452576</v>
       </c>
       <c r="C2078" t="n">
         <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.411009982688694</v>
+        <v>-4.240772059607721</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.72989248260402</v>
+        <v>2.797987651836409</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.21815924981997</v>
+        <v>1.427156302131911</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.225548449885227</v>
+        <v>5.350946681272392</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762291</v>
+        <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
         <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.410916014671321</v>
+        <v>-4.240678091590349</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.729108736723059</v>
+        <v>2.797203905955448</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.224949033605707</v>
+        <v>5.350347264992872</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988022</v>
+        <v>3.633213467988024</v>
       </c>
       <c r="C2080" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.418134838871166</v>
+        <v>-4.247896915790193</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.720453192987475</v>
+        <v>2.788548362219863</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.219181019550061</v>
+        <v>5.344579250937226</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740921</v>
+        <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
         <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.417186415753127</v>
+        <v>-4.246948492672154</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.72083256223469</v>
+        <v>2.788927731467079</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.219181019550061</v>
+        <v>5.344579250937226</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663623</v>
+        <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
         <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.574254874008751</v>
+        <v>-4.404016950927778</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.670732786913533</v>
+        <v>2.738827956145922</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.231908627531153</v>
+        <v>5.357306858918318</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424767</v>
+        <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
         <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.56826262721994</v>
+        <v>-4.398024704138966</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.675075684053445</v>
+        <v>2.743170853285834</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.233854625955541</v>
+        <v>5.359252857342706</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149216</v>
+        <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
         <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.479704666089172</v>
+        <v>-4.309466743008199</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.704153004523521</v>
+        <v>2.77224817375591</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.22750876197331</v>
+        <v>5.352906993360475</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383089</v>
+        <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
         <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.461945588586098</v>
+        <v>-4.291707665505125</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.710565312963746</v>
+        <v>2.778660482196135</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.226817439412305</v>
+        <v>5.35221567079947</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.788503044725581</v>
+        <v>3.887671577987278</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.540426601521109</v>
+        <v>4.689707370519057</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.461945588586098</v>
+        <v>-4.291707665505125</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.710565312963746</v>
+        <v>2.778660482196135</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.218529111167288</v>
+        <v>1.427526163479229</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.533490398507476</v>
+        <v>4.682771167505424</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>67.5%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.66</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>67.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,12 +666,12 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.3%</t>
+          <t>-16.1%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.6%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.7%</t>
+          <t>14.4%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>108.2%</t>
+          <t>102.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.0%</t>
+          <t>42.8%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.6%</t>
+          <t>41.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>43.9%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>89.6%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.1%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>157.3%</t>
+          <t>142.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-75.4%</t>
+          <t>-76.3%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>107.7%</t>
+          <t>108.0%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.70</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.1%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -982,7 +982,7 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-36.3%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>22.4%</t>
+          <t>21.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-45.7%</t>
+          <t>-47.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-70.8%</t>
+          <t>-72.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>422.9%</t>
+          <t>420.3%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-6.0%</t>
+          <t>-5.7%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-590.7%</t>
+          <t>-610.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>37.8%</t>
+          <t>35.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>57.0%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.1%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>53.0%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-6.6%</t>
+          <t>-9.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-2.9%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.5%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>34.1%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.6%</t>
+          <t>49.1%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.3%</t>
+          <t>-21.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>13.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-98.4%</t>
+          <t>-101.7%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.04</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>62.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.7%</t>
+          <t>73.6%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.7%</t>
+          <t>10.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>8.3%</t>
+          <t>3.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>55.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-25.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-322.8%</t>
+          <t>-320.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-81.2%</t>
+          <t>-99.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>114.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>72.6%</t>
+          <t>59.9%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>52.7%</t>
+          <t>54.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-3.7%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-0.9%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.3%</t>
+          <t>-22.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>76.3%</t>
+          <t>109.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>47.1%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>22.3%</t>
+          <t>82.8%</t>
         </is>
       </c>
     </row>
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.96220920424247</v>
+        <v>-9.163482897525986</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4064959158959582</v>
+        <v>-0.487005393209365</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.524190319047838</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.28897990274651</v>
+        <v>2.264229998686075</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812103</v>
+        <v>3.684843823812104</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.837630547904878</v>
+        <v>-9.038904241188394</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3555253088048627</v>
+        <v>-0.4360347861182694</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.482940478947112</v>
+        <v>-1.524190319047838</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.290119047302569</v>
+        <v>2.265369143242133</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.812593866336368</v>
+        <v>-9.013867559619884</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3428768620153511</v>
+        <v>-0.4233863393287578</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.498861231497102</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.307950273995118</v>
+        <v>2.283200369934682</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.740460691048487</v>
+        <v>-8.941734384332003</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3082898876615623</v>
+        <v>-0.3887993649749686</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.457611391396377</v>
+        <v>-1.498861231497102</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.313683978233754</v>
+        <v>2.288934074173319</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.669094298438839</v>
+        <v>-8.870367991722356</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.2894805930115685</v>
+        <v>-0.3699900703249748</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.427494838887454</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.346766551405678</v>
+        <v>2.322016647345242</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.575635264453615</v>
+        <v>-8.776908957737131</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2619804607303862</v>
+        <v>-0.3424899380437929</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.427494838887454</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.33688307009277</v>
+        <v>2.312133166032335</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.564982082900183</v>
+        <v>-8.7662557761837</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2595537486083872</v>
+        <v>-0.3400632259217939</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.386244998786729</v>
+        <v>-1.427494838887454</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.335048509593396</v>
+        <v>2.310298605532961</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.467075044223693</v>
+        <v>-8.668348737507209</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.220691248111252</v>
+        <v>-0.3012007254246583</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.318259248926172</v>
+        <v>-1.359509089026898</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.37553964453627</v>
+        <v>2.350789740475834</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.443121503247735</v>
+        <v>-8.644395196531251</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.210441325575375</v>
+        <v>-0.2909508028887817</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.294305707950215</v>
+        <v>-1.33555554805094</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.390580275267338</v>
+        <v>2.365830371206902</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.179061564924938</v>
+        <v>-8.380335258208454</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1180776664080083</v>
+        <v>-0.1985871437214151</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.071495609728144</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.535755922099263</v>
+        <v>2.511006018038828</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.4719819414201</v>
+        <v>-7.673255634703616</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1619671493336261</v>
+        <v>0.08145767202021936</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.030245769627419</v>
+        <v>-1.071495609728144</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.532968888438962</v>
+        <v>2.508218984378527</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.431797643053909</v>
+        <v>-7.633071336337426</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1783844925679436</v>
+        <v>0.0978750152545369</v>
       </c>
       <c r="F1901" t="n">
-        <v>-0.9900614712612278</v>
+        <v>-1.031311311361953</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.557423091346518</v>
+        <v>2.532673187286083</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.268397772114547</v>
+        <v>-7.469671465398063</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.2431112621644456</v>
+        <v>0.1626017848510388</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8266616003218653</v>
+        <v>-0.8679114404225907</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.654829835130893</v>
+        <v>2.630079931070457</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.034916549884948</v>
+        <v>-7.236190243168465</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.3444281798941371</v>
+        <v>0.2639187025807308</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.5931803780922668</v>
+        <v>-0.6344302181929922</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.802842997306504</v>
+        <v>2.778093093246069</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.885250158877433</v>
+        <v>-7.086523852160949</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4014025259841842</v>
+        <v>0.3208930486707775</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5002768868497308</v>
+        <v>-0.5415267269504562</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.855692881739067</v>
+        <v>2.830942977678631</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.752974685246547</v>
+        <v>-6.954248378530063</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.3555735014436934</v>
+        <v>0.2750640241302866</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.3680014132188442</v>
+        <v>-0.4092512533195696</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.836318951924753</v>
+        <v>2.811569047864318</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.581113469681644</v>
+        <v>-6.78238716296516</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.427133048357291</v>
+        <v>0.3466235710438843</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.1961401976539413</v>
+        <v>-0.2373900377546667</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.942250741951332</v>
+        <v>2.917500837890896</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.496148802952325</v>
+        <v>-6.697422496235841</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.4740252562726774</v>
+        <v>0.3935157789592707</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1111755309246217</v>
+        <v>-0.1524253710253471</v>
       </c>
       <c r="G1907" t="n">
-        <v>3.006135883212582</v>
+        <v>2.981385979152147</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.601738792725429</v>
+        <v>-6.803012486008946</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.3038133307642168</v>
+        <v>0.2233038534508105</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2167655206977261</v>
+        <v>-0.2580153607984515</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.814805959749501</v>
+        <v>2.790056055689066</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.533504208100002</v>
+        <v>-6.734777901383518</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.3796515064914745</v>
+        <v>0.2991420291780678</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.1983501978251901</v>
+        <v>-0.2396000379259155</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.874399495350109</v>
+        <v>2.849649591289674</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.385564166692403</v>
+        <v>-6.586837859975919</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3222067144161072</v>
+        <v>0.2416972371027004</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.1780292819166325</v>
+        <v>-0.2192791220173579</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.769971236256836</v>
+        <v>2.745221332196401</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.332594644438414</v>
+        <v>-6.53386833772193</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.3346805370642243</v>
+        <v>0.2541710597508176</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1663095997633691</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.793038963355751</v>
+        <v>2.768289059295316</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.166806448478123</v>
+        <v>-6.36808014176164</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.3940352033532473</v>
+        <v>0.313525726039841</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1663095997633691</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.786078351260658</v>
+        <v>2.761328447200223</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.133443241999355</v>
+        <v>-6.334716935282871</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.421842840325898</v>
+        <v>0.3413333630124913</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1663095997633691</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.800540705641801</v>
+        <v>2.775790801581366</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.025184104876833</v>
+        <v>-6.226457798160349</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.4596786156341017</v>
+        <v>0.379169138320695</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1250597596626437</v>
+        <v>-0.1663095997633691</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.795072826100996</v>
+        <v>2.770322922040561</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.901892970059702</v>
+        <v>-6.103166663343218</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.5064931635715308</v>
+        <v>0.4259836862581241</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.001768624845513156</v>
+        <v>-0.04301846494623857</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.866545601001851</v>
+        <v>2.841795696941416</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.849196102928411</v>
+        <v>-6.050469796211927</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.5352728886613725</v>
+        <v>0.4547634113479662</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.009678402185052615</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.905864699517951</v>
+        <v>2.881114795457516</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.605430660944966</v>
+        <v>-5.806704354228483</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.6285597738018009</v>
+        <v>0.5480502964883947</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.05092824228577802</v>
+        <v>0.009678402185052615</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.901645407865002</v>
+        <v>2.876895503804567</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.515654988568494</v>
+        <v>-5.716928681852011</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.6665943566724057</v>
+        <v>0.5860848793589994</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.112527687200088</v>
+        <v>0.07127784709936263</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.940729388733604</v>
+        <v>2.915979484673169</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.26580459461942</v>
+        <v>-5.467078287902936</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.7592765892357378</v>
+        <v>0.6787671119223315</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.112527687200088</v>
+        <v>0.07127784709936263</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.933471463717306</v>
+        <v>2.908721559656871</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.089912502151988</v>
+        <v>-5.291186195435504</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.8332325497433595</v>
+        <v>0.7527230724299527</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.112527687200088</v>
+        <v>0.07127784709936263</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.937070587237955</v>
+        <v>2.91232068317752</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.918466039129524</v>
+        <v>-5.11973973241304</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.9151386410068985</v>
+        <v>0.8346291636934922</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2839741502225512</v>
+        <v>0.2427243101218258</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.053265971105986</v>
+        <v>3.028516067045551</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.838443752020403</v>
+        <v>-5.03971744530392</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.9461680334668439</v>
+        <v>0.8656585561534373</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3639964373316721</v>
+        <v>0.3227465972309467</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.100299820987756</v>
+        <v>3.075549916927321</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.774808009786469</v>
+        <v>-4.976081703069985</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.976317131414735</v>
+        <v>0.8958076541013285</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.3863823394648813</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.143176067382434</v>
+        <v>3.118426163321999</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.681110691570074</v>
+        <v>-4.88238438485359</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9949903174850887</v>
+        <v>0.9144808401716822</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.4276321795656067</v>
+        <v>0.3863823394648813</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.124370326166229</v>
+        <v>3.099620422105795</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.691613314635362</v>
+        <v>-4.892887007918879</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9925323448838506</v>
+        <v>0.9120228675704438</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.3758797163995924</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.119811828951934</v>
+        <v>3.095061924891498</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.579127053966488</v>
+        <v>-4.780400747250004</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.04145616298622</v>
+        <v>0.9609466856728139</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.4171295565003178</v>
+        <v>0.3758797163995924</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.123741142786754</v>
+        <v>3.098991238726319</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.561413367088623</v>
+        <v>-4.762687060372139</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.049220221654707</v>
+        <v>0.9687107443413001</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.3790610452965092</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.126328524042244</v>
+        <v>3.101578619981809</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.437939095775604</v>
+        <v>-4.639212789059121</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.095608001399907</v>
+        <v>1.015098524086501</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.4203108853972346</v>
+        <v>0.3790610452965092</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.123326595262237</v>
+        <v>3.098576691201802</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.217918297738594</v>
+        <v>-4.41919199102211</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.185195357625326</v>
+        <v>1.104685880311919</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5202808903644894</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.20963753931364</v>
+        <v>3.184887635253205</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.085050608675316</v>
+        <v>-4.286324301958833</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.25423661605246</v>
+        <v>1.173727138739054</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5615307304652148</v>
+        <v>0.5202808903644894</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.225531722115463</v>
+        <v>3.200781818055028</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.964877525310817</v>
+        <v>-4.166151218594334</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.303451693838561</v>
+        <v>1.222942216525155</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6817038138297138</v>
+        <v>0.6404539737289884</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.298781416574464</v>
+        <v>3.274031512514029</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.82962416398084</v>
+        <v>-4.030897857264357</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.367641140931992</v>
+        <v>1.287131663618586</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.8169571751596909</v>
+        <v>0.7757073350589655</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.390021535933891</v>
+        <v>3.365271631873455</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.889498991338533</v>
+        <v>-4.090772684622049</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.329728701390341</v>
+        <v>1.249219224076934</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7158325077012734</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.340134130920701</v>
+        <v>3.315384226860266</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.769678760427695</v>
+        <v>-3.970952453711212</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.392945962988885</v>
+        <v>1.312436485675478</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7570823478019988</v>
+        <v>0.7158325077012734</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.355423300154909</v>
+        <v>3.330673396094474</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.772148466889501</v>
+        <v>-3.973422160173018</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.299602279726604</v>
+        <v>1.219092802413197</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7546126413401926</v>
+        <v>0.7133628012394673</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.261585675600267</v>
+        <v>3.236835771539832</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.840518653213511</v>
+        <v>-4.041792346497028</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.191516066682301</v>
+        <v>1.111006589368895</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7226385002756822</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.186412956507298</v>
+        <v>3.161663052446863</v>
       </c>
     </row>
     <row r="1937">
@@ -46102,16 +46102,16 @@
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.952390932839662</v>
+        <v>-4.153664626123178</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.137203863463732</v>
+        <v>1.056694386150326</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7226385002756822</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.176849665139189</v>
+        <v>3.152099761078754</v>
       </c>
     </row>
     <row r="1938">
@@ -46125,16 +46125,16 @@
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.007911008732251</v>
+        <v>-4.209184702015768</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.252026669798899</v>
+        <v>1.171517192485492</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7226385002756822</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.313880501831391</v>
+        <v>3.289130597770956</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.832436748939782</v>
+        <v>-4.033710442223299</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.326783605707674</v>
+        <v>1.246274128394268</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7226385002756822</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.318447733823179</v>
+        <v>3.293697829762744</v>
       </c>
     </row>
     <row r="1940">
@@ -46171,16 +46171,16 @@
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.824512374354868</v>
+        <v>-4.025786067638385</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.305695384302847</v>
+        <v>1.22518590698944</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7638883403764075</v>
+        <v>0.7226385002756822</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.294189762584386</v>
+        <v>3.269439858523951</v>
       </c>
     </row>
     <row r="1941">
@@ -46194,16 +46194,16 @@
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.818234171785019</v>
+        <v>-4.019507865068536</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.236744978732236</v>
+        <v>1.15623550141883</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7289167028455312</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.226494997527745</v>
+        <v>3.20174509346731</v>
       </c>
     </row>
     <row r="1942">
@@ -46217,16 +46217,16 @@
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.758381552581296</v>
+        <v>-3.959655245864813</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.270858412845858</v>
+        <v>1.190348935532451</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7289167028455312</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.236667383959878</v>
+        <v>3.211917479899443</v>
       </c>
     </row>
     <row r="1943">
@@ -46240,16 +46240,16 @@
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.672138089554918</v>
+        <v>-3.873411782838435</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.300302068630269</v>
+        <v>1.219792591316863</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7701665429462565</v>
+        <v>0.7289167028455312</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.231613654533738</v>
+        <v>3.206863750473303</v>
       </c>
     </row>
     <row r="1944">
@@ -46263,16 +46263,16 @@
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.717444908953898</v>
+        <v>-3.918718602237415</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.273955116315203</v>
+        <v>1.193445639001796</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.6881065398363004</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.198903332172725</v>
+        <v>3.17415342811229</v>
       </c>
     </row>
     <row r="1945">
@@ -46286,16 +46286,16 @@
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.7464780136562</v>
+        <v>-3.947751706939716</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.262893747467384</v>
+        <v>1.182384270153977</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.7293563799370257</v>
+        <v>0.6881065398363004</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.199455205205827</v>
+        <v>3.174705301145392</v>
       </c>
     </row>
     <row r="1946">
@@ -46309,16 +46309,16 @@
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.653667532205341</v>
+        <v>-3.854941225488857</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.229290631939093</v>
+        <v>1.148781154625687</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.8221668613878851</v>
+        <v>0.7809170212871598</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.184414185967708</v>
+        <v>3.159664281907273</v>
       </c>
     </row>
     <row r="1947">
@@ -46332,16 +46332,16 @@
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.698057001534768</v>
+        <v>-3.899330694818285</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.213408320131923</v>
+        <v>1.132898842818516</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7777773920584574</v>
+        <v>0.7365275519577321</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.159653980294652</v>
+        <v>3.134904076234217</v>
       </c>
     </row>
     <row r="1948">
@@ -46355,16 +46355,16 @@
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.677553307649271</v>
+        <v>-3.878827000932787</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.216685506197845</v>
+        <v>1.136176028884438</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.7570312458432295</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.167031905137673</v>
+        <v>3.142282001077239</v>
       </c>
     </row>
     <row r="1949">
@@ -46378,16 +46378,16 @@
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.717477402231843</v>
+        <v>-3.918751095515359</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.206207164195483</v>
+        <v>1.125697686882077</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7982810859439547</v>
+        <v>0.7570312458432295</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.172523200968341</v>
+        <v>3.147773296907906</v>
       </c>
     </row>
     <row r="1950">
@@ -46401,16 +46401,16 @@
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.745257800133196</v>
+        <v>-3.946531493416713</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.206592206803481</v>
+        <v>1.126082729490074</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7705006880426017</v>
+        <v>0.7292508479418764</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.167352163996068</v>
+        <v>3.142602259935633</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.782416487291561</v>
+        <v>-3.979267314095062</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.030084451940788</v>
+        <v>0.9513441212193881</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7798857394768036</v>
+        <v>0.7370637871075351</v>
       </c>
       <c r="G1951" t="n">
-        <v>3.011338914857243</v>
+        <v>2.985645743435681</v>
       </c>
     </row>
     <row r="1952">
@@ -46447,16 +46447,16 @@
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.891030565734892</v>
+        <v>-4.087881392538392</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.106788481282661</v>
+        <v>1.028048150561262</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7798857394768036</v>
+        <v>0.7370637871075351</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.131488575576448</v>
+        <v>3.105795404154887</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.85562152748675</v>
+        <v>-4.052472354290249</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.135465122684242</v>
+        <v>1.056724791962842</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7798857394768036</v>
+        <v>0.7370637871075351</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.146001601678771</v>
+        <v>3.12030843025721</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.817237864928599</v>
+        <v>-4.014088691732098</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.148238029049871</v>
+        <v>1.069497698328471</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.8182694020349548</v>
+        <v>0.7754474496656862</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.166451240556031</v>
+        <v>3.140758069134469</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.640121534893432</v>
+        <v>-3.836972361696932</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.215813589909239</v>
+        <v>1.137073259187839</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.8182694020349548</v>
+        <v>0.7754474496656862</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.163180269401332</v>
+        <v>3.137487097979771</v>
       </c>
     </row>
     <row r="1956">
@@ -46539,16 +46539,16 @@
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.685213779726978</v>
+        <v>-3.882064606530478</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.198460083737734</v>
+        <v>1.119719753016334</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.756373358865565</v>
+        <v>0.7135514064962964</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.126726035261612</v>
+        <v>3.101032863840051</v>
       </c>
     </row>
     <row r="1957">
@@ -46562,16 +46562,16 @@
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.50583835848821</v>
+        <v>-3.70268918529171</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.263997227539655</v>
+        <v>1.185256896818255</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.9131501170362837</v>
+        <v>0.8703281646670151</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.214579065470457</v>
+        <v>3.188885894048896</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.550852572008817</v>
+        <v>-3.747703398812317</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.226798997463002</v>
+        <v>1.148058666741603</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8828012217216791</v>
+        <v>0.8399792693524105</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.177177183613284</v>
+        <v>3.151484012191723</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.817857082281252</v>
+        <v>-4.014707909084752</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.125688755692974</v>
+        <v>1.046948424971574</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6884381836787306</v>
+        <v>0.645616231309462</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.066250923126461</v>
+        <v>3.0405577517049</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.919054863718425</v>
+        <v>-4.115905690521925</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.084413565014607</v>
+        <v>1.005673234293206</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.6200293701334114</v>
+        <v>0.5772074177641429</v>
       </c>
       <c r="G1960" t="n">
-        <v>3.024409556895771</v>
+        <v>2.99871638547421</v>
       </c>
     </row>
     <row r="1961">
@@ -46654,16 +46654,16 @@
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.912543897104112</v>
+        <v>-4.109394723907612</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.084617913214648</v>
+        <v>1.005877582493248</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.6200293701334114</v>
+        <v>0.5772074177641429</v>
       </c>
       <c r="G1961" t="n">
-        <v>3.022009518450087</v>
+        <v>2.996316347028527</v>
       </c>
     </row>
     <row r="1962">
@@ -46677,16 +46677,16 @@
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.893505769396815</v>
+        <v>-4.090356596200315</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.088757883505812</v>
+        <v>1.010017552784412</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5618457588022169</v>
+        <v>0.5190238064329483</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.983624070859616</v>
+        <v>2.957930899438054</v>
       </c>
     </row>
     <row r="1963">
@@ -46700,16 +46700,16 @@
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.946021571671635</v>
+        <v>-4.142872398475135</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.187045964230074</v>
+        <v>1.108305633508674</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5618457588022169</v>
+        <v>0.5190238064329483</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.102918472493806</v>
+        <v>3.077225301072245</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.949429883106215</v>
+        <v>-4.146280709909715</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.186515968642376</v>
+        <v>1.107775637920976</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5943623278115943</v>
+        <v>0.5515403754423257</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.123261742885566</v>
+        <v>3.097568571464005</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.90894689118387</v>
+        <v>-4.10579771798737</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.20871769580824</v>
+        <v>1.12997736508684</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5943623278115943</v>
+        <v>0.5515403754423257</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.129270273282492</v>
+        <v>3.103577101860931</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.761203920948868</v>
+        <v>-3.958054747752368</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.16576510517944</v>
+        <v>1.08702477445804</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7621696850464774</v>
+        <v>0.7193477326772089</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.127904908900621</v>
+        <v>3.10221173747906</v>
       </c>
     </row>
     <row r="1967">
@@ -46792,16 +46792,16 @@
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.845025142223566</v>
+        <v>-4.041875969027066</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.135030238201042</v>
+        <v>1.056289907479642</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7621696850464774</v>
+        <v>0.7193477326772089</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.130698530432102</v>
+        <v>3.105005359010541</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.838872436170782</v>
+        <v>-4.035723262974281</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.138153669013814</v>
+        <v>1.059413338292414</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7683223910992617</v>
+        <v>0.7255004387299931</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.135052502455431</v>
+        <v>3.10935933103387</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.855681734321283</v>
+        <v>-4.052532561124783</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.130510426493724</v>
+        <v>1.051770095772324</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.7515130929487601</v>
+        <v>0.7086911405794916</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.124047400305241</v>
+        <v>3.09835422888368</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.793383735545161</v>
+        <v>-3.990234562348661</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.221765179800993</v>
+        <v>1.143024849079593</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7968073572232022</v>
+        <v>0.7539854048539336</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.217559512666726</v>
+        <v>3.191866341245166</v>
       </c>
     </row>
     <row r="1971">
@@ -46884,16 +46884,16 @@
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.591593537880003</v>
+        <v>-3.788444364683504</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.104773260581184</v>
+        <v>1.026032929859783</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.9948255493923566</v>
+        <v>0.952003597023088</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.138662429682346</v>
+        <v>3.112969258260785</v>
       </c>
     </row>
     <row r="1972">
@@ -46907,16 +46907,16 @@
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.642480250566198</v>
+        <v>-3.839331077369698</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.154708807828881</v>
+        <v>1.075968477107481</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9439388367061621</v>
+        <v>0.9011168843368935</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.178420634392805</v>
+        <v>3.152727462971244</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.555869507916391</v>
+        <v>-3.752720334719891</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.203980841004848</v>
+        <v>1.125240510283447</v>
       </c>
       <c r="F1973" t="n">
-        <v>1.02256456791132</v>
+        <v>0.9797426155420518</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.240223809231944</v>
+        <v>3.214530637810382</v>
       </c>
     </row>
     <row r="1974">
@@ -46953,16 +46953,16 @@
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.616078805921675</v>
+        <v>-3.812929632725175</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.178433102627405</v>
+        <v>1.099692771906005</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9623552699060357</v>
+        <v>0.9195333175367673</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.202634211253444</v>
+        <v>3.176941039831883</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.566892157237324</v>
+        <v>-3.763742984040824</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.196599380141075</v>
+        <v>1.117859049419674</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9623552699060357</v>
+        <v>0.9195333175367673</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.201125829293373</v>
+        <v>3.175432657871812</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.522519025598755</v>
+        <v>-3.719369852402255</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.214211500231938</v>
+        <v>1.135471169510538</v>
       </c>
       <c r="F1976" t="n">
-        <v>1.006728401544604</v>
+        <v>0.9639064491753359</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.22761257571195</v>
+        <v>3.201919404290389</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.54499937645764</v>
+        <v>-3.74185020326114</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.199613154026975</v>
+        <v>1.120872823305575</v>
       </c>
       <c r="F1977" t="n">
-        <v>1.006728401544604</v>
+        <v>0.9639064491753359</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.222006369850541</v>
+        <v>3.19631319842898</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.497343645896584</v>
+        <v>-3.694194472700085</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.225057203279202</v>
+        <v>1.146316872557801</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.05438413210566</v>
+        <v>1.011562179736392</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.256981565214979</v>
+        <v>3.231288393793418</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.396825487397829</v>
+        <v>-3.59367631420133</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.270156840053428</v>
+        <v>1.191416509332028</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.154902290604415</v>
+        <v>1.112080338235146</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.322184833688957</v>
+        <v>3.296491662267395</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.380920157965477</v>
+        <v>-3.577770984768978</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.263273644302242</v>
+        <v>1.184533313580841</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.075789629895176</v>
+        <v>1.032967677525907</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.261471909739285</v>
+        <v>3.235778738317724</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.336081756357079</v>
+        <v>-3.53293258316058</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.285306707556229</v>
+        <v>1.206566376834829</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.080333062840045</v>
+        <v>1.037511110470777</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.268295672116836</v>
+        <v>3.242602500695274</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.355580212599087</v>
+        <v>-3.552431039402588</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.281668264690504</v>
+        <v>1.202927933969104</v>
       </c>
       <c r="F1982" t="n">
-        <v>1.032248421560141</v>
+        <v>0.9894264691908725</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.243605826979971</v>
+        <v>3.21791265555841</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.311377375513187</v>
+        <v>-3.508228202316687</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.305229002052702</v>
+        <v>1.226488671331301</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.076451258646041</v>
+        <v>1.033629306276773</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.276007131759348</v>
+        <v>3.250313960337787</v>
       </c>
     </row>
     <row r="1984">
@@ -47183,16 +47183,16 @@
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.318937041350233</v>
+        <v>-3.515787868153734</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.30061513618713</v>
+        <v>1.22187480546573</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.131254662655861</v>
+        <v>1.088432710286592</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.307299174634488</v>
+        <v>3.281606003212926</v>
       </c>
     </row>
     <row r="1985">
@@ -47206,16 +47206,16 @@
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.160645623810961</v>
+        <v>-3.357496450614462</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.415179468385879</v>
+        <v>1.336439137664478</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.131254662655861</v>
+        <v>1.088432710286592</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.358546939817527</v>
+        <v>3.332853768395966</v>
       </c>
     </row>
     <row r="1986">
@@ -47229,16 +47229,16 @@
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.953003620176485</v>
+        <v>-3.149854446979986</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.496676974433923</v>
+        <v>1.417936643712522</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.338896666290337</v>
+        <v>1.296074713921068</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.481572846592466</v>
+        <v>3.455879675170905</v>
       </c>
     </row>
     <row r="1987">
@@ -47252,16 +47252,16 @@
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.901971527453957</v>
+        <v>-3.098822354257458</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.512038039761204</v>
+        <v>1.433297709039803</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.389928759012865</v>
+        <v>1.347106806643596</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.507140330464253</v>
+        <v>3.481447159042692</v>
       </c>
     </row>
     <row r="1988">
@@ -47275,16 +47275,16 @@
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.836747346326751</v>
+        <v>-3.033598173130252</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.555315116304791</v>
+        <v>1.476574785583391</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.45515294014007</v>
+        <v>1.412330987770802</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.563462243233281</v>
+        <v>3.53776907181172</v>
       </c>
     </row>
     <row r="1989">
@@ -47298,16 +47298,16 @@
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.799320326255617</v>
+        <v>-2.996171153059118</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.566246896632525</v>
+        <v>1.487506565911125</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.460404478169252</v>
+        <v>1.417582525799984</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.562574138350071</v>
+        <v>3.53688096692851</v>
       </c>
     </row>
     <row r="1990">
@@ -47321,16 +47321,16 @@
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.819431982290326</v>
+        <v>-3.016282809093827</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.559459026549882</v>
+        <v>1.480718695828481</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.471431823166671</v>
+        <v>1.428609870797403</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.570447337679763</v>
+        <v>3.544754166258202</v>
       </c>
     </row>
     <row r="1991">
@@ -47344,16 +47344,16 @@
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.791018719190442</v>
+        <v>-2.987869545993943</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.731382102811046</v>
+        <v>1.652641772089646</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.412456260420243</v>
+        <v>1.369634308050974</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.695619771053116</v>
+        <v>3.669926599631555</v>
       </c>
     </row>
     <row r="1992">
@@ -47367,16 +47367,16 @@
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.716236458165429</v>
+        <v>-2.91308728496893</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.881407916438868</v>
+        <v>1.802667585717468</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.487238521445255</v>
+        <v>1.444416569075987</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.860602036885941</v>
+        <v>3.83490886546438</v>
       </c>
     </row>
     <row r="1993">
@@ -47390,16 +47390,16 @@
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.690152373901622</v>
+        <v>-2.887003200705122</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.88354952615825</v>
+        <v>1.80480919543685</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.487238521445255</v>
+        <v>1.444416569075987</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.8523100128998</v>
+        <v>3.826616841478239</v>
       </c>
     </row>
     <row r="1994">
@@ -47413,16 +47413,16 @@
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.602274460792501</v>
+        <v>-2.799125287596002</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.916893886985678</v>
+        <v>1.838153556264278</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.603164163868606</v>
+        <v>1.560342211499338</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.92005859393759</v>
+        <v>3.894365422516029</v>
       </c>
     </row>
     <row r="1995">
@@ -47436,16 +47436,16 @@
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.593381999399218</v>
+        <v>-2.790232826202718</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.938005277269783</v>
+        <v>1.859264946548383</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.603164163868606</v>
+        <v>1.560342211499338</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.937612999664381</v>
+        <v>3.91191982824282</v>
       </c>
     </row>
     <row r="1996">
@@ -47459,16 +47459,16 @@
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.761858116369095</v>
+        <v>-2.958708943172596</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.862469877886416</v>
+        <v>1.783729547165015</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.575216328152026</v>
+        <v>1.532394375782757</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.912699345639017</v>
+        <v>3.887006174217456</v>
       </c>
     </row>
     <row r="1997">
@@ -47482,16 +47482,16 @@
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.315601923739655</v>
+        <v>-2.512452750543156</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.022242052126054</v>
+        <v>1.943501721404653</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.480497658482393</v>
+        <v>1.437675706113124</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.837137841025099</v>
+        <v>3.811444669603538</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.292880820056503</v>
+        <v>-2.489731646860004</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.021994516096219</v>
+        <v>1.943254185374819</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.480497658482393</v>
+        <v>1.437675706113124</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.827801863522003</v>
+        <v>3.802108692100442</v>
       </c>
     </row>
     <row r="1999">
@@ -47528,16 +47528,16 @@
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.422082633350545</v>
+        <v>-2.618933460154046</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.129219916629771</v>
+        <v>2.050479585908371</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.351295845188351</v>
+        <v>1.308473892819082</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.909186901396747</v>
+        <v>3.883493729975186</v>
       </c>
     </row>
     <row r="2000">
@@ -47551,16 +47551,16 @@
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.447957031824571</v>
+        <v>-2.644807858628072</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.155947979733807</v>
+        <v>2.077207649012407</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.396207453900092</v>
+        <v>1.353385501530823</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.973211689117439</v>
+        <v>3.947518517695878</v>
       </c>
     </row>
     <row r="2001">
@@ -47574,16 +47574,16 @@
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.440902341609398</v>
+        <v>-2.637753168412898</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.155445211809422</v>
+        <v>2.076704881088022</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.403262144115266</v>
+        <v>1.360440191745997</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.974119859236088</v>
+        <v>3.948426687814527</v>
       </c>
     </row>
     <row r="2002">
@@ -47597,16 +47597,16 @@
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.41395111728291</v>
+        <v>-2.61080194408641</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.176231855184759</v>
+        <v>2.097491524463359</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.418142490142985</v>
+        <v>1.375320537773716</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.993054220497461</v>
+        <v>3.9673610490759</v>
       </c>
     </row>
     <row r="2003">
@@ -47620,16 +47620,16 @@
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.435495345113697</v>
+        <v>-2.632346171917197</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.351717296197404</v>
+        <v>2.272976965476003</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.418142490142985</v>
+        <v>1.375320537773716</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.17715735264242</v>
+        <v>4.151464181220859</v>
       </c>
     </row>
     <row r="2004">
@@ -47643,16 +47643,16 @@
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.457903462918569</v>
+        <v>-2.65475428972207</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.334870743978448</v>
+        <v>2.256130413257048</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.418142490142985</v>
+        <v>1.375320537773716</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.169274047545414</v>
+        <v>4.143580876123853</v>
       </c>
     </row>
     <row r="2005">
@@ -47666,16 +47666,16 @@
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.486127698496169</v>
+        <v>-2.68297852529967</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.325635049297045</v>
+        <v>2.246894718575645</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.436119242594293</v>
+        <v>1.393297290225025</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.182114098565837</v>
+        <v>4.156420927144275</v>
       </c>
     </row>
     <row r="2006">
@@ -47689,16 +47689,16 @@
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.495568624384699</v>
+        <v>-2.6924194511882</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.378112396663481</v>
+        <v>2.29937206594208</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.558546360137685</v>
+        <v>1.515724407768416</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.311824086813719</v>
+        <v>4.286130915392158</v>
       </c>
     </row>
     <row r="2007">
@@ -47712,16 +47712,16 @@
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.584445255553173</v>
+        <v>-2.781296082356674</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.345452838741392</v>
+        <v>2.266712508019991</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.469669728969211</v>
+        <v>1.426847776599943</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.261389202657935</v>
+        <v>4.235696031236374</v>
       </c>
     </row>
     <row r="2008">
@@ -47735,16 +47735,16 @@
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.660775233154079</v>
+        <v>-2.85762605995758</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.313032660594804</v>
+        <v>2.234292329873404</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.469669728969211</v>
+        <v>1.426847776599943</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.25950101555171</v>
+        <v>4.233807844130149</v>
       </c>
     </row>
     <row r="2009">
@@ -47758,16 +47758,16 @@
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.75443917783162</v>
+        <v>-2.951290004635121</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.27038731232665</v>
+        <v>2.19164698160525</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.37600578429167</v>
+        <v>1.333183831922401</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.198122878348047</v>
+        <v>4.172429706926486</v>
       </c>
     </row>
     <row r="2010">
@@ -47781,16 +47781,16 @@
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.916007603358875</v>
+        <v>-3.112858430162376</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.204193952325901</v>
+        <v>2.1254536216045</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.24922286049379</v>
+        <v>1.206400908124522</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.120487134279472</v>
+        <v>4.094793962857911</v>
       </c>
     </row>
     <row r="2011">
@@ -47804,16 +47804,16 @@
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.024308265228995</v>
+        <v>-3.221159092032496</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.173947094443771</v>
+        <v>2.095206763722371</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.24922286049379</v>
+        <v>1.206400908124522</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.133560541145391</v>
+        <v>4.10786736972383</v>
       </c>
     </row>
     <row r="2012">
@@ -47827,16 +47827,16 @@
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.042112236949739</v>
+        <v>-3.23896306375324</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.158830702538414</v>
+        <v>2.080090371817013</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.178688237588589</v>
+        <v>1.135866285219321</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.08324496418521</v>
+        <v>4.05755179276365</v>
       </c>
     </row>
     <row r="2013">
@@ -47850,16 +47850,16 @@
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.070013024059212</v>
+        <v>-3.266863850862713</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.146194428821627</v>
+        <v>2.067454098100226</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.144091313445654</v>
+        <v>1.101269361076386</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.061010850826452</v>
+        <v>4.035317679404891</v>
       </c>
     </row>
     <row r="2014">
@@ -47873,16 +47873,16 @@
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.192539126762106</v>
+        <v>-3.389389953565606</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.093948431717668</v>
+        <v>2.015208100996268</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.02156521074276</v>
+        <v>0.9787432583734921</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.984259633181914</v>
+        <v>3.958566461760353</v>
       </c>
     </row>
     <row r="2015">
@@ -47896,16 +47896,16 @@
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.423053622947695</v>
+        <v>-3.619904449751195</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.068448592833936</v>
+        <v>1.989708262112535</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7910507145571717</v>
+        <v>0.7482287621879034</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.912656895061065</v>
+        <v>3.886963723639503</v>
       </c>
     </row>
     <row r="2016">
@@ -47919,16 +47919,16 @@
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.771798708172138</v>
+        <v>-3.968649534975639</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.069262277746005</v>
+        <v>1.990521947024605</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6823027606382739</v>
+        <v>0.6394808082690056</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.987719841711573</v>
+        <v>3.962026670290012</v>
       </c>
     </row>
     <row r="2017">
@@ -47942,16 +47942,16 @@
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.925785125948279</v>
+        <v>-4.12263595275178</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.076647979781189</v>
+        <v>1.997907649059789</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6823027606382739</v>
+        <v>0.6394808082690056</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.056700110857212</v>
+        <v>4.031006939435652</v>
       </c>
     </row>
     <row r="2018">
@@ -47965,16 +47965,16 @@
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.875263222120613</v>
+        <v>-4.072114048924114</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.082907943432376</v>
+        <v>2.004167612710976</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6823027606382739</v>
+        <v>0.6394808082690056</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.042751312977333</v>
+        <v>4.017058141555772</v>
       </c>
     </row>
     <row r="2019">
@@ -47988,16 +47988,16 @@
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.127738376128337</v>
+        <v>-4.324589202931838</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.993788370884701</v>
+        <v>1.9150480401633</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6823027606382739</v>
+        <v>0.6394808082690056</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.054621802032747</v>
+        <v>4.028928630611186</v>
       </c>
     </row>
     <row r="2020">
@@ -48011,16 +48011,16 @@
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.420634132607749</v>
+        <v>-4.61748495941125</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.877840602811879</v>
+        <v>1.799100272090479</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6823027606382739</v>
+        <v>0.6394808082690056</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.055832336551691</v>
+        <v>4.03013916513013</v>
       </c>
     </row>
     <row r="2021">
@@ -48034,16 +48034,16 @@
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.607298260742557</v>
+        <v>-4.804149087546058</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.807296693785278</v>
+        <v>1.728556363063877</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.655563789813714</v>
+        <v>0.6127418374444457</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.043910696284277</v>
+        <v>4.018217524862716</v>
       </c>
     </row>
     <row r="2022">
@@ -48057,16 +48057,16 @@
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.75331894765652</v>
+        <v>-4.95016977446002</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.743966271755882</v>
+        <v>1.665225941034482</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.646480698019857</v>
+        <v>0.6036587456505886</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.033538693944152</v>
+        <v>4.007845522522591</v>
       </c>
     </row>
     <row r="2023">
@@ -48080,16 +48080,16 @@
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-4.845032956766104</v>
+        <v>-5.041883783569606</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.869484724811092</v>
+        <v>1.790744394089692</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.646480698019857</v>
+        <v>0.6036587456505886</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.195742750643196</v>
+        <v>4.170049579221635</v>
       </c>
     </row>
     <row r="2024">
@@ -48103,16 +48103,16 @@
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.876684615826074</v>
+        <v>-5.073535442629575</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.851670699150919</v>
+        <v>1.772930368429518</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.6413122407754168</v>
+        <v>0.5984902884061485</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.187488314260346</v>
+        <v>4.161795142838785</v>
       </c>
     </row>
     <row r="2025">
@@ -48126,16 +48126,16 @@
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.958619434094957</v>
+        <v>-5.155470260898459</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.829126189411857</v>
+        <v>1.750385858690456</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6313774951883366</v>
+        <v>0.5885555428190683</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.191756884476589</v>
+        <v>4.166063713055028</v>
       </c>
     </row>
     <row r="2026">
@@ -48149,16 +48149,16 @@
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.060595556343364</v>
+        <v>-5.257446383146866</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.797261378968396</v>
+        <v>1.718521048246995</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.5294013729399291</v>
+        <v>0.4865794205706607</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.139496849583447</v>
+        <v>4.113803678161886</v>
       </c>
     </row>
     <row r="2027">
@@ -48172,16 +48172,16 @@
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-4.950589272866143</v>
+        <v>-5.147440099669645</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.83341677960346</v>
+        <v>1.754676448882059</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5526059448572043</v>
+        <v>0.5097839924879359</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.145572479977988</v>
+        <v>4.119879308556427</v>
       </c>
     </row>
     <row r="2028">
@@ -48195,16 +48195,16 @@
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-4.807529697125217</v>
+        <v>-5.004380523928718</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.894890620621805</v>
+        <v>1.816150289900404</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5606193714471835</v>
+        <v>0.5177974190779152</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.154630546653949</v>
+        <v>4.128937375232388</v>
       </c>
     </row>
     <row r="2029">
@@ -48218,16 +48218,16 @@
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.506082971653379</v>
+        <v>-4.702933798456881</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.022730193693076</v>
+        <v>1.943989862971675</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8620660969190208</v>
+        <v>0.8192441445497525</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.342759464819587</v>
+        <v>4.317066293398026</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679626</v>
+        <v>3.812635940679625</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.530673215888563</v>
+        <v>-4.727524042692065</v>
       </c>
       <c r="E2030" t="n">
-        <v>2.013865273751713</v>
+        <v>1.935124943030312</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8620660969190208</v>
+        <v>0.8192441445497525</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.343730642572298</v>
+        <v>4.318037471150737</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474163</v>
+        <v>3.821184182474162</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.827333888800641</v>
+        <v>3.652071838888125</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.479634839882043</v>
+        <v>-4.676485666685545</v>
       </c>
       <c r="E2031" t="n">
-        <v>2.035123528534077</v>
+        <v>1.781121147900159</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8620660969190208</v>
+        <v>0.8192441445497525</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.344573546952054</v>
+        <v>4.143618325617976</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969547</v>
+        <v>3.831734516969546</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.846371987674786</v>
+        <v>3.67110993776227</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.438495545015412</v>
+        <v>-4.635346371818914</v>
       </c>
       <c r="E2032" t="n">
-        <v>2.070617345354874</v>
+        <v>1.816614964720957</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.9032053917856516</v>
+        <v>0.8603834394163833</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.388295222746177</v>
+        <v>4.1873400014121</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700483</v>
+        <v>3.825752932700482</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.662555983798721</v>
+        <v>3.487293933886205</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.341860632996772</v>
+        <v>-4.538711459800274</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.925455306286265</v>
+        <v>1.671452925652348</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9998403038042916</v>
+        <v>0.9570183514350232</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.262460166081296</v>
+        <v>4.061504944747218</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077644</v>
+        <v>3.804688961077643</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.666058027872685</v>
+        <v>3.490795977960168</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.472441367527614</v>
+        <v>-4.669292194331116</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.876725056547892</v>
+        <v>1.622722675913975</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8692595692734491</v>
+        <v>0.8264376169041807</v>
       </c>
       <c r="G2034" t="n">
-        <v>4.187613769436755</v>
+        <v>3.986658548102677</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833462</v>
+        <v>3.775028860833461</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.650484846948768</v>
+        <v>3.475222797036251</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.307945033336653</v>
+        <v>-4.504795860140154</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.92695040930036</v>
+        <v>1.672948028666442</v>
       </c>
       <c r="F2035" t="n">
-        <v>1.033755903464411</v>
+        <v>0.9909339510951427</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.270738389027414</v>
+        <v>4.069783167693337</v>
       </c>
     </row>
     <row r="2036">
@@ -48376,19 +48376,19 @@
         <v>3.821030660077628</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.649672557385197</v>
+        <v>3.474410507472681</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.23084643179478</v>
+        <v>-4.427697258598282</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.956977560353538</v>
+        <v>1.702975179719621</v>
       </c>
       <c r="F2036" t="n">
-        <v>1.033755903464411</v>
+        <v>0.9909339510951427</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.269926099463844</v>
+        <v>4.068970878129766</v>
       </c>
     </row>
     <row r="2037">
@@ -48399,19 +48399,19 @@
         <v>3.832307024147914</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.65954133651027</v>
+        <v>3.484279286597753</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.241231626684669</v>
+        <v>-4.438082453488171</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.962692261522655</v>
+        <v>1.708689880888737</v>
       </c>
       <c r="F2037" t="n">
-        <v>1.023370708574522</v>
+        <v>0.9805487562052534</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.273563761654983</v>
+        <v>4.072608540320905</v>
       </c>
     </row>
     <row r="2038">
@@ -48422,19 +48422,19 @@
         <v>3.834415493735285</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.730378342286695</v>
+        <v>3.555116292374178</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.259819785406894</v>
+        <v>-4.456670612210396</v>
       </c>
       <c r="E2038" t="n">
-        <v>2.02609400381019</v>
+        <v>1.772091623176272</v>
       </c>
       <c r="F2038" t="n">
-        <v>1.004782549852296</v>
+        <v>0.9619605974830281</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.333247872198073</v>
+        <v>4.132292650863995</v>
       </c>
     </row>
     <row r="2039">
@@ -48445,19 +48445,19 @@
         <v>3.855120535496558</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.727247353104993</v>
+        <v>3.551985303192477</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.26011833210293</v>
+        <v>-4.456969158906432</v>
       </c>
       <c r="E2039" t="n">
-        <v>2.022843595950074</v>
+        <v>1.768841215316157</v>
       </c>
       <c r="F2039" t="n">
-        <v>1.00448400315626</v>
+        <v>0.9616620507869922</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.32993775499875</v>
+        <v>4.128982533664672</v>
       </c>
     </row>
     <row r="2040">
@@ -48468,19 +48468,19 @@
         <v>3.815643212108861</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.731778248044385</v>
+        <v>3.556516198131868</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.159295198412503</v>
+        <v>-4.356146025216004</v>
       </c>
       <c r="E2040" t="n">
-        <v>2.067703744365637</v>
+        <v>1.813701363731719</v>
       </c>
       <c r="F2040" t="n">
-        <v>1.016948218640614</v>
+        <v>0.974126266271346</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.341947179228754</v>
+        <v>4.140991957894676</v>
       </c>
     </row>
     <row r="2041">
@@ -48491,19 +48491,19 @@
         <v>3.807356168121472</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.731907501522928</v>
+        <v>3.556645451610411</v>
       </c>
       <c r="D2041" t="n">
-        <v>-3.968513837660095</v>
+        <v>-4.165364664463597</v>
       </c>
       <c r="E2041" t="n">
-        <v>2.144145542145143</v>
+        <v>1.890143161511225</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.207729579393022</v>
+        <v>1.164907627023753</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.456545249158742</v>
+        <v>4.255590027824663</v>
       </c>
     </row>
     <row r="2042">
@@ -48514,19 +48514,19 @@
         <v>3.775233033906085</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.711744347260525</v>
+        <v>3.536482297348008</v>
       </c>
       <c r="D2042" t="n">
-        <v>-3.861550479810673</v>
+        <v>-4.058401306614176</v>
       </c>
       <c r="E2042" t="n">
-        <v>2.166767731022508</v>
+        <v>1.91276535038859</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.266194187352823</v>
+        <v>1.223372234983555</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.471460859672219</v>
+        <v>4.270505638338141</v>
       </c>
     </row>
     <row r="2043">
@@ -48537,19 +48537,19 @@
         <v>3.785761685912989</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.746711283872583</v>
+        <v>3.571449233960066</v>
       </c>
       <c r="D2043" t="n">
-        <v>-3.806219891908911</v>
+        <v>-4.003070718712413</v>
       </c>
       <c r="E2043" t="n">
-        <v>2.223866902795272</v>
+        <v>1.969864522161354</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.321524775254585</v>
+        <v>1.278702822885317</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.539626149025334</v>
+        <v>4.338670927691257</v>
       </c>
     </row>
     <row r="2044">
@@ -48560,19 +48560,19 @@
         <v>3.743767956539899</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.740397851774021</v>
+        <v>3.565135801861504</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.794165764995948</v>
+        <v>-3.99101659179945</v>
       </c>
       <c r="E2044" t="n">
-        <v>2.222375121461894</v>
+        <v>1.968372740827976</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.333578902167548</v>
+        <v>1.29075694979828</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.54054519307455</v>
+        <v>4.339589971740472</v>
       </c>
     </row>
     <row r="2045">
@@ -48583,19 +48583,19 @@
         <v>3.725010844811014</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.742278481958157</v>
+        <v>3.56701643204564</v>
       </c>
       <c r="D2045" t="n">
-        <v>-3.835320884564169</v>
+        <v>-4.032171711367672</v>
       </c>
       <c r="E2045" t="n">
-        <v>2.207793703818742</v>
+        <v>1.953791323184824</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.292423782599327</v>
+        <v>1.249601830230059</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.517732751517753</v>
+        <v>4.316777530183676</v>
       </c>
     </row>
     <row r="2046">
@@ -48606,19 +48606,19 @@
         <v>3.612322444382925</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.755129507836039</v>
+        <v>3.579867457923522</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.767272321872639</v>
+        <v>-3.964123148676142</v>
       </c>
       <c r="E2046" t="n">
-        <v>2.247864154773236</v>
+        <v>1.993861774139318</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.360472345290857</v>
+        <v>1.317650392921589</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.571412915010553</v>
+        <v>4.370457693676475</v>
       </c>
     </row>
     <row r="2047">
@@ -48629,19 +48629,19 @@
         <v>3.645256780013432</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.775332178009633</v>
+        <v>3.600070128097117</v>
       </c>
       <c r="D2047" t="n">
-        <v>-3.998872715042141</v>
+        <v>-4.195723541845643</v>
       </c>
       <c r="E2047" t="n">
-        <v>2.17542666767903</v>
+        <v>1.921424287045112</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.360472345290857</v>
+        <v>1.317650392921589</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.591615585184147</v>
+        <v>4.39066036385007</v>
       </c>
     </row>
     <row r="2048">
@@ -48652,19 +48652,19 @@
         <v>3.66674720149897</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.758938414076515</v>
+        <v>3.583676364163999</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.04892426057136</v>
+        <v>-4.245775087374863</v>
       </c>
       <c r="E2048" t="n">
-        <v>2.139012285534224</v>
+        <v>1.885009904900306</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.360472345290857</v>
+        <v>1.317650392921589</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.57522182125103</v>
+        <v>4.374266599916952</v>
       </c>
     </row>
     <row r="2049">
@@ -48675,19 +48675,19 @@
         <v>3.670048702800099</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.719190327669982</v>
+        <v>3.543928277757465</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.224031093147804</v>
+        <v>-4.420881919951308</v>
       </c>
       <c r="E2049" t="n">
-        <v>2.029221466097113</v>
+        <v>1.775219085463195</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.360472345290857</v>
+        <v>1.317650392921589</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.535473734844496</v>
+        <v>4.334518513510418</v>
       </c>
     </row>
     <row r="2050">
@@ -48698,19 +48698,19 @@
         <v>3.745573148660852</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.726212946666922</v>
+        <v>3.550950896754405</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.027930939717281</v>
+        <v>-4.224781766520785</v>
       </c>
       <c r="E2050" t="n">
-        <v>2.114684146466262</v>
+        <v>1.860681765832344</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.55657249872138</v>
+        <v>1.513750546352111</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.66015644589975</v>
+        <v>4.459201224565672</v>
       </c>
     </row>
     <row r="2051">
@@ -48721,19 +48721,19 @@
         <v>3.730570473395089</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.825383946239826</v>
+        <v>3.65012189632731</v>
       </c>
       <c r="D2051" t="n">
-        <v>-3.874905547603997</v>
+        <v>-4.0717563744075</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.27506530288448</v>
+        <v>2.021062922250562</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.709597890834664</v>
+        <v>1.666775938465396</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.851142680740625</v>
+        <v>4.650187459406547</v>
       </c>
     </row>
     <row r="2052">
@@ -48744,19 +48744,19 @@
         <v>3.741278332791151</v>
       </c>
       <c r="C2052" t="n">
-        <v>4.012850171148119</v>
+        <v>3.837588121235602</v>
       </c>
       <c r="D2052" t="n">
-        <v>-3.903212861477267</v>
+        <v>-4.100063688280771</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.451208602243465</v>
+        <v>2.197206221609547</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.709597890834664</v>
+        <v>1.666775938465396</v>
       </c>
       <c r="G2052" t="n">
-        <v>5.038608905648918</v>
+        <v>4.83765368431484</v>
       </c>
     </row>
     <row r="2053">
@@ -48767,19 +48767,19 @@
         <v>3.699115615620437</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.982253122502201</v>
+        <v>3.806991072589685</v>
       </c>
       <c r="D2053" t="n">
-        <v>-3.927740596783989</v>
+        <v>-4.266656913394293</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.410800459474858</v>
+        <v>2.09997188291822</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.685070155527942</v>
+        <v>1.500182713351873</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.993295215818967</v>
+        <v>4.707100700600809</v>
       </c>
     </row>
     <row r="2054">
@@ -48790,19 +48790,19 @@
         <v>3.708182519285652</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.985929525163919</v>
+        <v>3.810667475251403</v>
       </c>
       <c r="D2054" t="n">
-        <v>-3.904704803422423</v>
+        <v>-4.243621120032727</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.423691179481202</v>
+        <v>2.112862602924565</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.685070155527942</v>
+        <v>1.500182713351873</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.996971618480685</v>
+        <v>4.710777103262527</v>
       </c>
     </row>
     <row r="2055">
@@ -48813,19 +48813,19 @@
         <v>3.740581401399474</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.983547580287414</v>
+        <v>3.808285530374898</v>
       </c>
       <c r="D2055" t="n">
-        <v>-3.875458822966727</v>
+        <v>-4.21437513957703</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.433007626786976</v>
+        <v>2.122179050230339</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.685070155527942</v>
+        <v>1.500182713351873</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.99458967360418</v>
+        <v>4.708395158386022</v>
       </c>
     </row>
     <row r="2056">
@@ -48836,19 +48836,19 @@
         <v>3.699404642256376</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.980840819445049</v>
+        <v>3.805578769532533</v>
       </c>
       <c r="D2056" t="n">
-        <v>-3.982384370844579</v>
+        <v>-4.321300687454881</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.38753064679347</v>
+        <v>2.076702070236833</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.578144607650091</v>
+        <v>1.393257165474022</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.927727584035104</v>
+        <v>4.641533068816946</v>
       </c>
     </row>
     <row r="2057">
@@ -48859,19 +48859,19 @@
         <v>3.689942600701007</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.982269621588284</v>
+        <v>3.807007571675767</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.127402929351828</v>
+        <v>-4.46631924596213</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.330952025533805</v>
+        <v>2.020123448977168</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.433126049142842</v>
+        <v>1.248238606966773</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.842145251073989</v>
+        <v>4.555950735855832</v>
       </c>
     </row>
     <row r="2058">
@@ -48882,19 +48882,19 @@
         <v>3.711852429687018</v>
       </c>
       <c r="C2058" t="n">
-        <v>4.082200860846037</v>
+        <v>3.90693881093352</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.245744695136545</v>
+        <v>-4.584661011746848</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.383546558477671</v>
+        <v>2.072717981921034</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.443812087705732</v>
+        <v>1.258924645529663</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.948488113469476</v>
+        <v>4.662293598251319</v>
       </c>
     </row>
     <row r="2059">
@@ -48905,19 +48905,19 @@
         <v>3.714879051790808</v>
       </c>
       <c r="C2059" t="n">
-        <v>4.079986557971975</v>
+        <v>3.904724508059459</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.297155117457253</v>
+        <v>-4.636071434067556</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.360768086675327</v>
+        <v>2.04993951011869</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.443812087705732</v>
+        <v>1.258924645529663</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.946273810595414</v>
+        <v>4.660079295377257</v>
       </c>
     </row>
     <row r="2060">
@@ -48928,19 +48928,19 @@
         <v>3.704757949437336</v>
       </c>
       <c r="C2060" t="n">
-        <v>4.079889686046265</v>
+        <v>3.904627636133748</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.376574568665005</v>
+        <v>-4.715490885275307</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.328903434266516</v>
+        <v>2.018074857709878</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.443812087705732</v>
+        <v>1.258924645529663</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.946176938669704</v>
+        <v>4.659982423451547</v>
       </c>
     </row>
     <row r="2061">
@@ -48951,19 +48951,19 @@
         <v>3.736804952298403</v>
       </c>
       <c r="C2061" t="n">
-        <v>4.079883579604308</v>
+        <v>3.904621529691791</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.472037566582222</v>
+        <v>-4.810953883192525</v>
       </c>
       <c r="E2061" t="n">
-        <v>2.290712128657672</v>
+        <v>1.979883552101034</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.443812087705732</v>
+        <v>1.258924645529663</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.946170832227748</v>
+        <v>4.65997631700959</v>
       </c>
     </row>
     <row r="2062">
@@ -48974,19 +48974,19 @@
         <v>3.715372960218006</v>
       </c>
       <c r="C2062" t="n">
-        <v>4.077979976166919</v>
+        <v>3.902717926254402</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.407661655731507</v>
+        <v>-4.74657797234181</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.314558889560569</v>
+        <v>2.003730313003931</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.508187998556447</v>
+        <v>1.323300556380379</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.982892775300788</v>
+        <v>4.69669826008263</v>
       </c>
     </row>
     <row r="2063">
@@ -48997,19 +48997,19 @@
         <v>3.736089413353541</v>
       </c>
       <c r="C2063" t="n">
-        <v>4.083713793914646</v>
+        <v>3.908451744002129</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.463030817863701</v>
+        <v>-4.801947134474004</v>
       </c>
       <c r="E2063" t="n">
-        <v>2.298145042455418</v>
+        <v>1.98731646589878</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.508187998556447</v>
+        <v>1.323300556380379</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.988626593048514</v>
+        <v>4.702432077830356</v>
       </c>
     </row>
     <row r="2064">
@@ -49020,19 +49020,19 @@
         <v>3.736822870113285</v>
       </c>
       <c r="C2064" t="n">
-        <v>4.083252157257578</v>
+        <v>3.907990107345061</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.508468597694528</v>
+        <v>-4.847384914304831</v>
       </c>
       <c r="E2064" t="n">
-        <v>2.279508293866019</v>
+        <v>1.968679717309382</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.465343007878288</v>
+        <v>1.280455565702219</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.96245796198455</v>
+        <v>4.676263446766392</v>
       </c>
     </row>
     <row r="2065">
@@ -49043,19 +49043,19 @@
         <v>3.790272500113693</v>
       </c>
       <c r="C2065" t="n">
-        <v>4.103126550107897</v>
+        <v>3.92786450019538</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.42026176354695</v>
+        <v>-4.759178080157253</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.334665420375369</v>
+        <v>2.023836843818732</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.465343007878288</v>
+        <v>1.280455565702219</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.982332354834869</v>
+        <v>4.696137839616711</v>
       </c>
     </row>
     <row r="2066">
@@ -49066,19 +49066,19 @@
         <v>3.794486844016441</v>
       </c>
       <c r="C2066" t="n">
-        <v>4.086827250632624</v>
+        <v>3.911565200720108</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.314226768341641</v>
+        <v>-4.653143084951943</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.360780118982221</v>
+        <v>2.049951542425583</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.465343007878288</v>
+        <v>1.280455565702219</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.966033055359597</v>
+        <v>4.679838540141439</v>
       </c>
     </row>
     <row r="2067">
@@ -49089,19 +49089,19 @@
         <v>3.794705093307672</v>
       </c>
       <c r="C2067" t="n">
-        <v>4.08925820009667</v>
+        <v>3.913996150184154</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.131015105208546</v>
+        <v>-4.469931421818848</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.436495733699505</v>
+        <v>2.125667157142867</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.465343007878288</v>
+        <v>1.280455565702219</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.968464004823643</v>
+        <v>4.682269489605485</v>
       </c>
     </row>
     <row r="2068">
@@ -49112,19 +49112,19 @@
         <v>3.776846557863553</v>
       </c>
       <c r="C2068" t="n">
-        <v>4.055049385944559</v>
+        <v>3.879787336032043</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.059293658194695</v>
+        <v>-4.398209974804997</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.430975498352934</v>
+        <v>2.120146921796297</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.537064454892139</v>
+        <v>1.35217701271607</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.977288058879843</v>
+        <v>4.691093543661686</v>
       </c>
     </row>
     <row r="2069">
@@ -49135,19 +49135,19 @@
         <v>3.723789705394116</v>
       </c>
       <c r="C2069" t="n">
-        <v>4.001965131865731</v>
+        <v>3.826703081953215</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.036920632586988</v>
+        <v>-4.375836949197291</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.386840454517189</v>
+        <v>2.076011877960552</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.54832020600504</v>
+        <v>1.363432763828971</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.930957255468755</v>
+        <v>4.644762740250598</v>
       </c>
     </row>
     <row r="2070">
@@ -49158,19 +49158,19 @@
         <v>3.715607446456734</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.187163336751087</v>
+        <v>4.011901286838571</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.069936928497733</v>
+        <v>-4.408853245108036</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.558832141038246</v>
+        <v>2.248003564481609</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.478882829338289</v>
+        <v>1.29399538716222</v>
       </c>
       <c r="G2070" t="n">
-        <v>5.07449303435406</v>
+        <v>4.788298519135902</v>
       </c>
     </row>
     <row r="2071">
@@ -49181,19 +49181,19 @@
         <v>3.713762536883681</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.179084562579336</v>
+        <v>4.00382251266682</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.058409292848125</v>
+        <v>-4.397325609458427</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.555364421126338</v>
+        <v>2.244535844569701</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.537883487539651</v>
+        <v>1.352996045363582</v>
       </c>
       <c r="G2071" t="n">
-        <v>5.101814655103126</v>
+        <v>4.815620139884969</v>
       </c>
     </row>
     <row r="2072">
@@ -49204,19 +49204,19 @@
         <v>3.717150699236303</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.182752675101124</v>
+        <v>4.007490625188608</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.155750794190493</v>
+        <v>-4.494667110800796</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.52009593311118</v>
+        <v>2.209267356554543</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.493463305374163</v>
+        <v>1.308575863198094</v>
       </c>
       <c r="G2072" t="n">
-        <v>5.078830658325622</v>
+        <v>4.792636143107464</v>
       </c>
     </row>
     <row r="2073">
@@ -49227,19 +49227,19 @@
         <v>3.705201079427689</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.184003757293962</v>
+        <v>4.008741707381446</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.24160682353046</v>
+        <v>-4.580523140140762</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.487004603568031</v>
+        <v>2.176176027011394</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.451087236148028</v>
+        <v>1.266199793971959</v>
       </c>
       <c r="G2073" t="n">
-        <v>5.054656098982779</v>
+        <v>4.768461583764622</v>
       </c>
     </row>
     <row r="2074">
@@ -49250,19 +49250,19 @@
         <v>3.691835499610383</v>
       </c>
       <c r="C2074" t="n">
-        <v>4.166422959114464</v>
+        <v>3.991160909201948</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.250443620946579</v>
+        <v>-4.589359937556882</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.465889086422085</v>
+        <v>2.155060509865448</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.443645063506677</v>
+        <v>1.258757621330608</v>
       </c>
       <c r="G2074" t="n">
-        <v>5.03260999721847</v>
+        <v>4.746415482000313</v>
       </c>
     </row>
     <row r="2075">
@@ -49273,19 +49273,19 @@
         <v>3.71554441166746</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.176587470159514</v>
+        <v>4.001325420246998</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.341826183512038</v>
+        <v>-4.68074250012234</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.439500572440951</v>
+        <v>2.128671995884314</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.352262500941219</v>
+        <v>1.16737505876515</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.987944970724245</v>
+        <v>4.701750455506088</v>
       </c>
     </row>
     <row r="2076">
@@ -49296,19 +49296,19 @@
         <v>3.673978374889196</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.278715727983782</v>
+        <v>4.103453678071265</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.330119465525032</v>
+        <v>-4.669035782135334</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.546311517460022</v>
+        <v>2.235482940903384</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.363969218928225</v>
+        <v>1.179081776752156</v>
       </c>
       <c r="G2076" t="n">
-        <v>5.097097259340717</v>
+        <v>4.810902744122559</v>
       </c>
     </row>
     <row r="2077">
@@ -49319,19 +49319,19 @@
         <v>3.682476099409572</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.281748066715187</v>
+        <v>4.10648601680267</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.230455961441369</v>
+        <v>-4.569372278051672</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.589209257824892</v>
+        <v>2.278380681268254</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.427156302131911</v>
+        <v>1.242268859955842</v>
       </c>
       <c r="G2077" t="n">
-        <v>5.138041847994334</v>
+        <v>4.851847332776176</v>
       </c>
     </row>
     <row r="2078">
@@ -49342,19 +49342,19 @@
         <v>3.672895177452576</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.494652899993245</v>
+        <v>4.319390850080728</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.240772059607721</v>
+        <v>-4.579688376218024</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.797987651836409</v>
+        <v>2.487159075279771</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.427156302131911</v>
+        <v>1.242268859955842</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.350946681272392</v>
+        <v>5.064752166054234</v>
       </c>
     </row>
     <row r="2079">
@@ -49365,19 +49365,19 @@
         <v>3.623960959762293</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.493831566905334</v>
+        <v>4.318569516992818</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.240678091590349</v>
+        <v>-4.579594408200651</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.797203905955448</v>
+        <v>2.48637532939881</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.350347264992872</v>
+        <v>5.064152749774714</v>
       </c>
     </row>
     <row r="2080">
@@ -49388,19 +49388,19 @@
         <v>3.633213467988024</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.488063552849688</v>
+        <v>4.312801502937171</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.247896915790193</v>
+        <v>-4.586813232400496</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.788548362219863</v>
+        <v>2.477719785663226</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.344579250937226</v>
+        <v>5.058384735719068</v>
       </c>
     </row>
     <row r="2081">
@@ -49411,19 +49411,19 @@
         <v>3.647907242740922</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.488063552849688</v>
+        <v>4.312801502937171</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.246948492672154</v>
+        <v>-4.585864809282457</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.788927731467079</v>
+        <v>2.478099154910441</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.344579250937226</v>
+        <v>5.058384735719068</v>
       </c>
     </row>
     <row r="2082">
@@ -49434,19 +49434,19 @@
         <v>3.881065366663625</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.50079116083078</v>
+        <v>4.325529110918263</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.404016950927778</v>
+        <v>-4.742933267538081</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.738827956145922</v>
+        <v>2.427999379589283</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.357306858918318</v>
+        <v>5.07111234370016</v>
       </c>
     </row>
     <row r="2083">
@@ -49457,19 +49457,19 @@
         <v>3.717071158424769</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.502737159255168</v>
+        <v>4.327475109342651</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.398024704138966</v>
+        <v>-4.73694102074927</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.743170853285834</v>
+        <v>2.432342276729196</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.359252857342706</v>
+        <v>5.073058342124548</v>
       </c>
     </row>
     <row r="2084">
@@ -49480,19 +49480,19 @@
         <v>3.741942347149218</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.496391295272937</v>
+        <v>4.32112924536042</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.309466743008199</v>
+        <v>-4.648383059618502</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.77224817375591</v>
+        <v>2.461419597199272</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.352906993360475</v>
+        <v>5.066712478142317</v>
       </c>
     </row>
     <row r="2085">
@@ -49503,19 +49503,19 @@
         <v>3.735300721383092</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.495699972711932</v>
+        <v>4.320437922799416</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.291707665505125</v>
+        <v>-4.710414428845689</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.778660482196135</v>
+        <v>2.435915726947393</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.35221567079947</v>
+        <v>5.066021155581312</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.887671577987278</v>
+        <v>3.425021889512868</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.689707370519057</v>
+        <v>4.542568320241119</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.291707665505125</v>
+        <v>-4.492859487133471</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.778660482196135</v>
+        <v>2.745068101073983</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.427526163479229</v>
+        <v>1.24263872130316</v>
       </c>
       <c r="G2086" t="n">
-        <v>4.682771167505424</v>
+        <v>5.288151553023016</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240913.xlsx
+++ b/tame_output/ON/bt/strategyON_20240913.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>53.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.5%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.66</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.7%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-16.1%</t>
+          <t>-15.3%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.6%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>44.5%</t>
         </is>
       </c>
     </row>
@@ -758,22 +758,22 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>102.1%</t>
+          <t>103.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>42.8%</t>
+          <t>41.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="F3" t="n">
@@ -791,12 +791,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>41.2%</t>
+          <t>39.6%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>42.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>87.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>33.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-8.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.4%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>142.6%</t>
+          <t>143.2%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-76.3%</t>
+          <t>-77.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>108.0%</t>
+          <t>107.7%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-0.72</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>123.5%</t>
+          <t>123.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.5%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.6%</t>
+          <t>-46.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-72.1%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1022,17 +1022,17 @@
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>420.3%</t>
+          <t>422.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-5.7%</t>
+          <t>-5.6%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-610.9%</t>
+          <t>-630.2%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>35.8%</t>
+          <t>35.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>57.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.2%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>52.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.6%</t>
+          <t>-6.6%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.5%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>31.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>49.1%</t>
+          <t>47.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-21.5%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.4%</t>
+          <t>13.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-101.7%</t>
+          <t>-108.9%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>62.3%</t>
+          <t>62.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>73.6%</t>
+          <t>73.7%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.3%</t>
+          <t>10.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-25.7%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>55.3%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-25.9%</t>
+          <t>-21.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-320.7%</t>
+          <t>-319.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-99.7%</t>
+          <t>-96.8%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>114.4%</t>
+          <t>116.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>55.5%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.03</t>
+          <t>2.09</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>58.9%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>59.9%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>54.0%</t>
+          <t>52.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>144</v>
+        <v>138</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>109.1%</t>
+          <t>106.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.1%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.0%</t>
+          <t>36.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>82.8%</t>
+          <t>85.1%</t>
         </is>
       </c>
     </row>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.2781997024955</v>
+        <v>3.278199702495499</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178244</v>
+        <v>3.315884374178243</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207814</v>
+        <v>3.305316798207812</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310981</v>
+        <v>3.28461951331098</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006535</v>
+        <v>3.305849539006533</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330525</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191737</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108639</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097821</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297747</v>
+        <v>3.458100091297748</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317617</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737171</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539463</v>
+        <v>3.501052558539465</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937499</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141702</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496851904729889</v>
+        <v>3.496851904729891</v>
       </c>
       <c r="C1879" t="n">
         <v>3.144802646739683</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608601</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410272</v>
+        <v>3.485878594410273</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480692492764396</v>
+        <v>3.480692492764398</v>
       </c>
       <c r="C1883" t="n">
         <v>3.160838213305049</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390587</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297396</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322543</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158921</v>
+        <v>3.600038265158923</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940718</v>
+        <v>3.691571733940719</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676841549770579</v>
+        <v>3.67684154977058</v>
       </c>
       <c r="C1889" t="n">
         <v>3.169165117078568</v>
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685161381615283</v>
+        <v>3.685161381615284</v>
       </c>
       <c r="C1890" t="n">
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.163482897525986</v>
+        <v>-9.143402144257667</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.487005393209365</v>
+        <v>-0.4789730919020374</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.524190319047838</v>
+        <v>-1.517801720485393</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.264229998686075</v>
+        <v>2.268063157823542</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.038904241188394</v>
+        <v>-9.018823487920075</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4360347861182694</v>
+        <v>-0.4280024848109418</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.524190319047838</v>
+        <v>-1.517801720485393</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.265369143242133</v>
+        <v>2.2692023023796</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.013867559619884</v>
+        <v>-8.993786806351565</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.4233863393287578</v>
+        <v>-0.4153540380214302</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.498861231497102</v>
+        <v>-1.492472632934657</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.283200369934682</v>
+        <v>2.28703352907215</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611571</v>
+        <v>3.76895167461157</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.941734384332003</v>
+        <v>-8.921653631063684</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3887993649749686</v>
+        <v>-0.380767063667641</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.498861231497102</v>
+        <v>-1.492472632934657</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.288934074173319</v>
+        <v>2.292767233310786</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.72857792995533</v>
+        <v>3.728577929955329</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.870367991722356</v>
+        <v>-8.850287238454037</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3699900703249748</v>
+        <v>-0.3619577690176472</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.427494838887454</v>
+        <v>-1.421106240325009</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.322016647345242</v>
+        <v>2.32584980648271</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232417</v>
+        <v>3.747702660232415</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.776908957737131</v>
+        <v>-8.756828204468812</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3424899380437929</v>
+        <v>-0.3344576367364653</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.427494838887454</v>
+        <v>-1.421106240325009</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.312133166032335</v>
+        <v>2.315966325169802</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436233</v>
+        <v>3.766317079436231</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.7662557761837</v>
+        <v>-8.746175022915381</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.3400632259217939</v>
+        <v>-0.3320309246144664</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.427494838887454</v>
+        <v>-1.421106240325009</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.310298605532961</v>
+        <v>2.314131764670428</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311952</v>
+        <v>3.78468452131195</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.668348737507209</v>
+        <v>-8.64826798423889</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.3012007254246583</v>
+        <v>-0.2931684241173307</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.359509089026898</v>
+        <v>-1.353120490464453</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.350789740475834</v>
+        <v>2.354622899613301</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097247</v>
+        <v>3.800829354097245</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.644395196531251</v>
+        <v>-8.624314443262932</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2909508028887817</v>
+        <v>-0.2829185015814542</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.33555554805094</v>
+        <v>-1.329166949488495</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.365830371206902</v>
+        <v>2.369663530344369</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017773</v>
+        <v>3.789311112017772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.380335258208454</v>
+        <v>-8.360254504940135</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1985871437214151</v>
+        <v>-0.1905548424140875</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.071495609728144</v>
+        <v>-1.065107011165699</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.511006018038828</v>
+        <v>2.514839177176295</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.673255634703616</v>
+        <v>-7.653174881435297</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.08145767202021936</v>
+        <v>0.08948997332754693</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.071495609728144</v>
+        <v>-1.065107011165699</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.508218984378527</v>
+        <v>2.512052143515994</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.633071336337426</v>
+        <v>-7.612990583069107</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.0978750152545369</v>
+        <v>0.1059073165618645</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.031311311361953</v>
+        <v>-1.024922712799508</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.532673187286083</v>
+        <v>2.53650634642355</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.469671465398063</v>
+        <v>-7.449590712129744</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.1626017848510388</v>
+        <v>0.1706340861583664</v>
       </c>
       <c r="F1902" t="n">
-        <v>-0.8679114404225907</v>
+        <v>-0.8615228418601455</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.630079931070457</v>
+        <v>2.633913090207924</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.236190243168465</v>
+        <v>-7.216109489900146</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.2639187025807308</v>
+        <v>0.2719510038880584</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.6344302181929922</v>
+        <v>-0.6280416196305469</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.778093093246069</v>
+        <v>2.781926252383536</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-7.086523852160949</v>
+        <v>-7.066443098892631</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3208930486707775</v>
+        <v>0.3289253499781051</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.5415267269504562</v>
+        <v>-0.535138128388011</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.830942977678631</v>
+        <v>2.834776136816098</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.057119799856059</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.954248378530063</v>
+        <v>-6.934167625261744</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.2750640241302866</v>
+        <v>0.2830963254376142</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.4092512533195696</v>
+        <v>-0.4028626547571243</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.811569047864318</v>
+        <v>2.815402207001785</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.059934860543696</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.78238716296516</v>
+        <v>-6.762306409696841</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.3466235710438843</v>
+        <v>0.3546558723512119</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.2373900377546667</v>
+        <v>-0.2310014391922215</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.917500837890896</v>
+        <v>2.921333997028364</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.072841201767355</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.697422496235841</v>
+        <v>-6.677341742967522</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.3935157789592707</v>
+        <v>0.4015480802665983</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.1524253710253471</v>
+        <v>-0.1460367724629019</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.981385979152147</v>
+        <v>2.985219138289614</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>2.944865272168136</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.803012486008946</v>
+        <v>-6.782931732740627</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.2233038534508105</v>
+        <v>0.2313361547581381</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.2580153607984515</v>
+        <v>-0.2516267622360063</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.790056055689066</v>
+        <v>2.793889214826533</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>2.993409614045222</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.734777901383518</v>
+        <v>-6.714697148115199</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.2991420291780678</v>
+        <v>0.3071743304853953</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.2396000379259155</v>
+        <v>-0.2332114393634703</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.849649591289674</v>
+        <v>2.853482750427141</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.876788805406815</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.586837859975919</v>
+        <v>-6.5667571067076</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.2416972371027004</v>
+        <v>0.249729538410028</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.2192791220173579</v>
+        <v>-0.2128905234549127</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.745221332196401</v>
+        <v>2.749054491333868</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
         <v>2.868074819153337</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.53386833772193</v>
+        <v>-6.513787584453612</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.2541710597508176</v>
+        <v>0.2622033610581451</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.1663095997633691</v>
+        <v>-0.1599210012009238</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.768289059295316</v>
+        <v>2.772122218432783</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
         <v>2.861114207058244</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.36808014176164</v>
+        <v>-6.347999388493321</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.313525726039841</v>
+        <v>0.3215580273471685</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.1663095997633691</v>
+        <v>-0.1599210012009238</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.761328447200223</v>
+        <v>2.76516160633769</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
         <v>2.875576561439387</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.334716935282871</v>
+        <v>-6.314636182014552</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.3413333630124913</v>
+        <v>0.3493656643198189</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.1663095997633691</v>
+        <v>-0.1599210012009238</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.775790801581366</v>
+        <v>2.779623960718833</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722819</v>
       </c>
       <c r="C1914" t="n">
         <v>2.870108681898582</v>
       </c>
       <c r="D1914" t="n">
-        <v>-6.226457798160349</v>
+        <v>-6.20637704489203</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.379169138320695</v>
+        <v>0.3872014396280226</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.1663095997633691</v>
+        <v>-0.1599210012009238</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.770322922040561</v>
+        <v>2.774156081178028</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792047</v>
       </c>
       <c r="C1915" t="n">
         <v>2.867606775909159</v>
       </c>
       <c r="D1915" t="n">
-        <v>-6.103166663343218</v>
+        <v>-6.0830859100749</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.4259836862581241</v>
+        <v>0.4340159875654517</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.04301846494623857</v>
+        <v>-0.03662986638379334</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.841795696941416</v>
+        <v>2.845628856078883</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.875307754146484</v>
       </c>
       <c r="D1916" t="n">
-        <v>-6.050469796211927</v>
+        <v>-6.030389042943608</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.4547634113479662</v>
+        <v>0.4627957126552937</v>
       </c>
       <c r="F1916" t="n">
-        <v>0.009678402185052615</v>
+        <v>0.01606700074749784</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.881114795457516</v>
+        <v>2.884947954594983</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.871088462493535</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.806704354228483</v>
+        <v>-5.786623600960164</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.5480502964883947</v>
+        <v>0.5560825977957222</v>
       </c>
       <c r="F1917" t="n">
-        <v>0.009678402185052615</v>
+        <v>0.01606700074749784</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.876895503804567</v>
+        <v>2.880728662942034</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.873212776413551</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.716928681852011</v>
+        <v>-5.696847928583692</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.5860848793589994</v>
+        <v>0.594117180666327</v>
       </c>
       <c r="F1918" t="n">
-        <v>0.07127784709936263</v>
+        <v>0.07766644566180786</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.915979484673169</v>
+        <v>2.919812643810636</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.865954851397253</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.467078287902936</v>
+        <v>-5.446997534634617</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.6787671119223315</v>
+        <v>0.6867994132296591</v>
       </c>
       <c r="F1919" t="n">
-        <v>0.07127784709936263</v>
+        <v>0.07766644566180786</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.908721559656871</v>
+        <v>2.912554718794338</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.869553974917902</v>
       </c>
       <c r="D1920" t="n">
-        <v>-5.291186195435504</v>
+        <v>-5.271105442167185</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.7527230724299527</v>
+        <v>0.7607553737372803</v>
       </c>
       <c r="F1920" t="n">
-        <v>0.07127784709936263</v>
+        <v>0.07766644566180786</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.91232068317752</v>
+        <v>2.916153842314987</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.882881480972455</v>
       </c>
       <c r="D1921" t="n">
-        <v>-5.11973973241304</v>
+        <v>-5.099658979144722</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.8346291636934922</v>
+        <v>0.8426614650008197</v>
       </c>
       <c r="F1921" t="n">
-        <v>0.2427243101218258</v>
+        <v>0.249112908684271</v>
       </c>
       <c r="G1921" t="n">
-        <v>3.028516067045551</v>
+        <v>3.032349226183018</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632782</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
         <v>2.881901958588752</v>
       </c>
       <c r="D1922" t="n">
-        <v>-5.03971744530392</v>
+        <v>-5.019636692035601</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.8656585561534373</v>
+        <v>0.8736908574607649</v>
       </c>
       <c r="F1922" t="n">
-        <v>0.3227465972309467</v>
+        <v>0.329135195793392</v>
       </c>
       <c r="G1922" t="n">
-        <v>3.075549916927321</v>
+        <v>3.079383076064788</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883074</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
         <v>2.88659675964307</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.976081703069985</v>
+        <v>-4.956000949801666</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.8958076541013285</v>
+        <v>0.903839955408656</v>
       </c>
       <c r="F1923" t="n">
-        <v>0.3863823394648813</v>
+        <v>0.3927709380273265</v>
       </c>
       <c r="G1923" t="n">
-        <v>3.118426163321999</v>
+        <v>3.122259322459466</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074785</v>
+        <v>3.798814771074783</v>
       </c>
       <c r="C1924" t="n">
         <v>2.867791018426865</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.88238438485359</v>
+        <v>-4.862303631585271</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.9144808401716822</v>
+        <v>0.9225131414790098</v>
       </c>
       <c r="F1924" t="n">
-        <v>0.3863823394648813</v>
+        <v>0.3927709380273265</v>
       </c>
       <c r="G1924" t="n">
-        <v>3.099620422105795</v>
+        <v>3.103453581243262</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242295</v>
+        <v>3.797694884242294</v>
       </c>
       <c r="C1925" t="n">
         <v>2.869534095051743</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.892887007918879</v>
+        <v>-4.87280625465056</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9120228675704438</v>
+        <v>0.9200551688777714</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.3758797163995924</v>
+        <v>0.3822683149620376</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.095061924891498</v>
+        <v>3.098895084028966</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.873463408886563</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.780400747250004</v>
+        <v>-4.760319993981685</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9609466856728139</v>
+        <v>0.9689789869801415</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.3758797163995924</v>
+        <v>0.3822683149620376</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.098991238726319</v>
+        <v>3.102824397863786</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879966</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
         <v>2.874141992803903</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.762687060372139</v>
+        <v>-4.74260630710382</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9687107443413001</v>
+        <v>0.9767430456486277</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.3790610452965092</v>
+        <v>0.3854496438589544</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.101578619981809</v>
+        <v>3.105411779119276</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.871140064023896</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.639212789059121</v>
+        <v>-4.619132035790802</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.015098524086501</v>
+        <v>1.023130825393828</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.3790610452965092</v>
+        <v>0.3854496438589544</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.098576691201802</v>
+        <v>3.102409850339269</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.872719101034511</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.41919199102211</v>
+        <v>-4.399111237753791</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.104685880311919</v>
+        <v>1.112718181619247</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.5202808903644894</v>
+        <v>0.5266694889269347</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.184887635253205</v>
+        <v>3.188720794390671</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.888613283836334</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.286324301958833</v>
+        <v>-4.266243548690514</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.173727138739054</v>
+        <v>1.181759440046381</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.5202808903644894</v>
+        <v>0.5266694889269347</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.200781818055028</v>
+        <v>3.204614977192495</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>2.889759128276636</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.166151218594334</v>
+        <v>-4.146070465326015</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.222942216525155</v>
+        <v>1.230974517832482</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.6404539737289884</v>
+        <v>0.6468425722914336</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.274031512514029</v>
+        <v>3.277864671651496</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>2.899847230838076</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.030897857264357</v>
+        <v>-4.010817103996038</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.287131663618586</v>
+        <v>1.295163964925913</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.7757073350589655</v>
+        <v>0.7820959336214107</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.365271631873455</v>
+        <v>3.369104791010922</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>2.885884722239501</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.090772684622049</v>
+        <v>-4.07069193135373</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.249219224076934</v>
+        <v>1.257251525384262</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.7158325077012734</v>
+        <v>0.7222211062637186</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.315384226860266</v>
+        <v>3.319217385997733</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>2.90117389147371</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.970952453711212</v>
+        <v>-3.950871700442893</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.312436485675478</v>
+        <v>1.320468786982806</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.7158325077012734</v>
+        <v>0.7222211062637186</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.330673396094474</v>
+        <v>3.334506555231942</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>2.808818090796152</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.973422160173018</v>
+        <v>-3.953341406904699</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.219092802413197</v>
+        <v>1.227125103720525</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.7133628012394673</v>
+        <v>0.7197513998019125</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.236835771539832</v>
+        <v>3.240668930677299</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,16 +46079,16 @@
         <v>2.728079952281453</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.041792346497028</v>
+        <v>-4.021711593228709</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.111006589368895</v>
+        <v>1.119038890676222</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.7226385002756822</v>
+        <v>0.7290270988381274</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.161663052446863</v>
+        <v>3.16549621158433</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508368</v>
       </c>
       <c r="C1937" t="n">
         <v>2.718516660913344</v>
       </c>
       <c r="D1937" t="n">
-        <v>-4.153664626123178</v>
+        <v>-4.133583872854859</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.056694386150326</v>
+        <v>1.064726687457653</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.7226385002756822</v>
+        <v>0.7290270988381274</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.152099761078754</v>
+        <v>3.155932920216221</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417705</v>
+        <v>3.710906731417704</v>
       </c>
       <c r="C1938" t="n">
         <v>2.855547497605547</v>
       </c>
       <c r="D1938" t="n">
-        <v>-4.209184702015768</v>
+        <v>-4.189103948747449</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.171517192485492</v>
+        <v>1.17954949379282</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.7226385002756822</v>
+        <v>0.7290270988381274</v>
       </c>
       <c r="G1938" t="n">
-        <v>3.289130597770956</v>
+        <v>3.292963756908423</v>
       </c>
     </row>
     <row r="1939">
@@ -46148,16 +46148,16 @@
         <v>2.860114729597334</v>
       </c>
       <c r="D1939" t="n">
-        <v>-4.033710442223299</v>
+        <v>-4.01362968895498</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.246274128394268</v>
+        <v>1.254306429701595</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.7226385002756822</v>
+        <v>0.7290270988381274</v>
       </c>
       <c r="G1939" t="n">
-        <v>3.293697829762744</v>
+        <v>3.297530988900211</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225443</v>
       </c>
       <c r="C1940" t="n">
         <v>2.835856758358541</v>
       </c>
       <c r="D1940" t="n">
-        <v>-4.025786067638385</v>
+        <v>-4.005705314370066</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.22518590698944</v>
+        <v>1.233218208296768</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.7226385002756822</v>
+        <v>0.7290270988381274</v>
       </c>
       <c r="G1940" t="n">
-        <v>3.269439858523951</v>
+        <v>3.273273017661418</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111293</v>
       </c>
       <c r="C1941" t="n">
         <v>2.764395071759991</v>
       </c>
       <c r="D1941" t="n">
-        <v>-4.019507865068536</v>
+        <v>-3.999427111800217</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.15623550141883</v>
+        <v>1.164267802726157</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.7289167028455312</v>
+        <v>0.7353053014079765</v>
       </c>
       <c r="G1941" t="n">
-        <v>3.20174509346731</v>
+        <v>3.205578252604777</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
         <v>2.774567458192124</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.959655245864813</v>
+        <v>-3.939574492596494</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.190348935532451</v>
+        <v>1.198381236839779</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.7289167028455312</v>
+        <v>0.7353053014079765</v>
       </c>
       <c r="G1942" t="n">
-        <v>3.211917479899443</v>
+        <v>3.215750639036909</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742296</v>
+        <v>3.786949957742298</v>
       </c>
       <c r="C1943" t="n">
         <v>2.769513728765984</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.873411782838435</v>
+        <v>-3.853331029570116</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.219792591316863</v>
+        <v>1.22782489262419</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.7289167028455312</v>
+        <v>0.7353053014079765</v>
       </c>
       <c r="G1943" t="n">
-        <v>3.206863750473303</v>
+        <v>3.21069690961077</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
         <v>2.761289504210509</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.918718602237415</v>
+        <v>-3.898637848969096</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.193445639001796</v>
+        <v>1.201477940309124</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.6881065398363004</v>
+        <v>0.6944951383987457</v>
       </c>
       <c r="G1944" t="n">
-        <v>3.17415342811229</v>
+        <v>3.177986587249757</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
         <v>2.761841377243611</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.947751706939716</v>
+        <v>-3.927670953671397</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.182384270153977</v>
+        <v>1.190416571461305</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.6881065398363004</v>
+        <v>0.6944951383987457</v>
       </c>
       <c r="G1945" t="n">
-        <v>3.174705301145392</v>
+        <v>3.178538460282859</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.733390600809497</v>
       </c>
       <c r="C1946" t="n">
         <v>2.691114069134977</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.854941225488857</v>
+        <v>-3.834860472220538</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.148781154625687</v>
+        <v>1.156813455933014</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.7809170212871598</v>
+        <v>0.787305619849605</v>
       </c>
       <c r="G1946" t="n">
-        <v>3.159664281907273</v>
+        <v>3.16349744104474</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560424</v>
       </c>
       <c r="C1947" t="n">
         <v>2.692987545059577</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.899330694818285</v>
+        <v>-3.879249941549966</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.132898842818516</v>
+        <v>1.140931144125844</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.7365275519577321</v>
+        <v>0.7429161505201773</v>
       </c>
       <c r="G1947" t="n">
-        <v>3.134904076234217</v>
+        <v>3.138737235371684</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472732</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.6880632535713</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.878827000932787</v>
+        <v>-3.858746247664468</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.136176028884438</v>
+        <v>1.144208330191766</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7570312458432295</v>
+        <v>0.7634198444056747</v>
       </c>
       <c r="G1948" t="n">
-        <v>3.142282001077239</v>
+        <v>3.146115160214705</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798533</v>
+        <v>3.743047603798535</v>
       </c>
       <c r="C1949" t="n">
         <v>2.693554549401968</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.918751095515359</v>
+        <v>-3.898670342247041</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.125697686882077</v>
+        <v>1.133729988189404</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7570312458432295</v>
+        <v>0.7634198444056747</v>
       </c>
       <c r="G1949" t="n">
-        <v>3.147773296907906</v>
+        <v>3.151606456045373</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498862</v>
       </c>
       <c r="C1950" t="n">
         <v>2.705051751170507</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.946531493416713</v>
+        <v>-3.926450740148394</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.126082729490074</v>
+        <v>1.134115030797402</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7292508479418764</v>
+        <v>0.7356394465043217</v>
       </c>
       <c r="G1950" t="n">
-        <v>3.142602259935633</v>
+        <v>3.1464354190731</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705321</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
         <v>2.54340747117116</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.979267314095062</v>
+        <v>-4.044831412878532</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9513441212193881</v>
+        <v>0.9251184817060001</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.7370637871075351</v>
+        <v>0.6684215943533455</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.985645743435681</v>
+        <v>2.944460427783167</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
         <v>2.663557131890366</v>
       </c>
       <c r="D1952" t="n">
-        <v>-4.087881392538392</v>
+        <v>-4.153445491321863</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.028048150561262</v>
+        <v>1.001822511047873</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.7370637871075351</v>
+        <v>0.6684215943533455</v>
       </c>
       <c r="G1952" t="n">
-        <v>3.105795404154887</v>
+        <v>3.064610088502373</v>
       </c>
     </row>
     <row r="1953">
@@ -46470,16 +46470,16 @@
         <v>2.678070157992689</v>
       </c>
       <c r="D1953" t="n">
-        <v>-4.052472354290249</v>
+        <v>-4.11803645307372</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.056724791962842</v>
+        <v>1.030499152449453</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.7370637871075351</v>
+        <v>0.6684215943533455</v>
       </c>
       <c r="G1953" t="n">
-        <v>3.12030843025721</v>
+        <v>3.079123114604696</v>
       </c>
     </row>
     <row r="1954">
@@ -46493,16 +46493,16 @@
         <v>2.675489599335057</v>
       </c>
       <c r="D1954" t="n">
-        <v>-4.014088691732098</v>
+        <v>-4.079652790515569</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.069497698328471</v>
+        <v>1.043272058815083</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7754474496656862</v>
+        <v>0.7068052569114966</v>
       </c>
       <c r="G1954" t="n">
-        <v>3.140758069134469</v>
+        <v>3.099572753481956</v>
       </c>
     </row>
     <row r="1955">
@@ -46516,16 +46516,16 @@
         <v>2.672218628180359</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.836972361696932</v>
+        <v>-3.902536460480403</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.137073259187839</v>
+        <v>1.110847619674451</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7754474496656862</v>
+        <v>0.7068052569114966</v>
       </c>
       <c r="G1955" t="n">
-        <v>3.137487097979771</v>
+        <v>3.096301782327258</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793901</v>
+        <v>3.741328448793902</v>
       </c>
       <c r="C1956" t="n">
         <v>2.672902019942272</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.882064606530478</v>
+        <v>-3.947628705313948</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.119719753016334</v>
+        <v>1.093494113502946</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.7135514064962964</v>
+        <v>0.6449092137421069</v>
       </c>
       <c r="G1956" t="n">
-        <v>3.101032863840051</v>
+        <v>3.059847548187537</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011233</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
         <v>2.666688995248687</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.70268918529171</v>
+        <v>-3.768253284075181</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.185256896818255</v>
+        <v>1.159031257304867</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8703281646670151</v>
+        <v>0.8016859719128255</v>
       </c>
       <c r="G1957" t="n">
-        <v>3.188885894048896</v>
+        <v>3.147700578396382</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982227</v>
+        <v>3.716991718982228</v>
       </c>
       <c r="C1958" t="n">
         <v>2.647496450580276</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.747703398812317</v>
+        <v>-3.813267497595787</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.148058666741603</v>
+        <v>1.121833027228214</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8399792693524105</v>
+        <v>0.7713370765982209</v>
       </c>
       <c r="G1958" t="n">
-        <v>3.151484012191723</v>
+        <v>3.110298696539209</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509538</v>
       </c>
       <c r="C1959" t="n">
         <v>2.653188012919222</v>
       </c>
       <c r="D1959" t="n">
-        <v>-4.014707909084752</v>
+        <v>-4.080272007868222</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.046948424971574</v>
+        <v>1.020722785458186</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.645616231309462</v>
+        <v>0.5769740385552724</v>
       </c>
       <c r="G1959" t="n">
-        <v>3.0405577517049</v>
+        <v>2.999372436052386</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760807</v>
+        <v>3.702309454760809</v>
       </c>
       <c r="C1960" t="n">
         <v>2.652391934815724</v>
       </c>
       <c r="D1960" t="n">
-        <v>-4.115905690521925</v>
+        <v>-4.181469789305395</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.005673234293206</v>
+        <v>0.9794475947798182</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5772074177641429</v>
+        <v>0.5085652250099533</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.99871638547421</v>
+        <v>2.957531069821696</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815451</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
         <v>2.64999189637004</v>
       </c>
       <c r="D1961" t="n">
-        <v>-4.109394723907612</v>
+        <v>-4.174958822691083</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.005877582493248</v>
+        <v>0.97965194297986</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5772074177641429</v>
+        <v>0.5085652250099533</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.996316347028527</v>
+        <v>2.955131031376013</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378099</v>
       </c>
       <c r="C1962" t="n">
         <v>2.646516615578285</v>
       </c>
       <c r="D1962" t="n">
-        <v>-4.090356596200315</v>
+        <v>-4.155920694983785</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.010017552784412</v>
+        <v>0.983791913271024</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.5190238064329483</v>
+        <v>0.4503816136787587</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.957930899438054</v>
+        <v>2.916745583785541</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131244</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.765811017212476</v>
       </c>
       <c r="D1963" t="n">
-        <v>-4.142872398475135</v>
+        <v>-4.208436497258606</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.108305633508674</v>
+        <v>1.082079993995286</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.5190238064329483</v>
+        <v>0.4503816136787587</v>
       </c>
       <c r="G1963" t="n">
-        <v>3.077225301072245</v>
+        <v>3.036039985419731</v>
       </c>
     </row>
     <row r="1964">
@@ -46723,16 +46723,16 @@
         <v>2.766644346198609</v>
       </c>
       <c r="D1964" t="n">
-        <v>-4.146280709909715</v>
+        <v>-4.211844808693185</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.107775637920976</v>
+        <v>1.081549998407588</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.5515403754423257</v>
+        <v>0.4828981826881361</v>
       </c>
       <c r="G1964" t="n">
-        <v>3.097568571464005</v>
+        <v>3.056383255811491</v>
       </c>
     </row>
     <row r="1965">
@@ -46746,16 +46746,16 @@
         <v>2.772652876595535</v>
       </c>
       <c r="D1965" t="n">
-        <v>-4.10579771798737</v>
+        <v>-4.210612562600716</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.12997736508684</v>
+        <v>1.088051427241502</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.5515403754423257</v>
+        <v>0.5324503412278421</v>
       </c>
       <c r="G1965" t="n">
-        <v>3.103577101860931</v>
+        <v>3.09212308133224</v>
       </c>
     </row>
     <row r="1966">
@@ -46769,16 +46769,16 @@
         <v>2.670603097872735</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.958054747752368</v>
+        <v>-4.062869592365713</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.08702477445804</v>
+        <v>1.045098836612702</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.7193477326772089</v>
+        <v>0.7002576984627252</v>
       </c>
       <c r="G1966" t="n">
-        <v>3.10221173747906</v>
+        <v>3.09075771695037</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181168</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
         <v>2.673396719404216</v>
       </c>
       <c r="D1967" t="n">
-        <v>-4.041875969027066</v>
+        <v>-4.146690813640411</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.056289907479642</v>
+        <v>1.014363969634304</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.7193477326772089</v>
+        <v>0.7002576984627252</v>
       </c>
       <c r="G1967" t="n">
-        <v>3.105005359010541</v>
+        <v>3.093551338481851</v>
       </c>
     </row>
     <row r="1968">
@@ -46815,16 +46815,16 @@
         <v>2.674059067795874</v>
       </c>
       <c r="D1968" t="n">
-        <v>-4.035723262974281</v>
+        <v>-4.140538107587627</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.059413338292414</v>
+        <v>1.017487400447076</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.7255004387299931</v>
+        <v>0.7064104045155095</v>
       </c>
       <c r="G1968" t="n">
-        <v>3.10935933103387</v>
+        <v>3.09790531050518</v>
       </c>
     </row>
     <row r="1969">
@@ -46838,16 +46838,16 @@
         <v>2.673139544535984</v>
       </c>
       <c r="D1969" t="n">
-        <v>-4.052532561124783</v>
+        <v>-4.157347405738129</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.051770095772324</v>
+        <v>1.009844157926985</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.7086911405794916</v>
+        <v>0.6896011063650078</v>
       </c>
       <c r="G1969" t="n">
-        <v>3.09835422888368</v>
+        <v>3.086900208354989</v>
       </c>
     </row>
     <row r="1970">
@@ -46861,16 +46861,16 @@
         <v>2.739475098332805</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.990234562348661</v>
+        <v>-4.095049406962007</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.143024849079593</v>
+        <v>1.101098911234255</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.7539854048539336</v>
+        <v>0.7348953706394499</v>
       </c>
       <c r="G1970" t="n">
-        <v>3.191866341245166</v>
+        <v>3.180412320716475</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.84872913999219</v>
+        <v>3.848729139992189</v>
       </c>
       <c r="C1971" t="n">
         <v>2.541767100046932</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.788444364683504</v>
+        <v>-3.893259209296849</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.026032929859783</v>
+        <v>0.9841069920144454</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.952003597023088</v>
+        <v>0.9329135628086043</v>
       </c>
       <c r="G1971" t="n">
-        <v>3.112969258260785</v>
+        <v>3.101515237732095</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852419</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.612057332369107</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.839331077369698</v>
+        <v>-3.944145921983043</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.075968477107481</v>
+        <v>1.034042539262143</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9011168843368935</v>
+        <v>0.8820268501224098</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.152727462971244</v>
+        <v>3.141273442442554</v>
       </c>
     </row>
     <row r="1973">
@@ -46930,16 +46930,16 @@
         <v>2.626685068485151</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.752720334719891</v>
+        <v>-3.857535179333236</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.125240510283447</v>
+        <v>1.083314572438109</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9797426155420518</v>
+        <v>0.960652581327568</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.214530637810382</v>
+        <v>3.203076617281692</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489382</v>
+        <v>3.831819032489383</v>
       </c>
       <c r="C1974" t="n">
         <v>2.625221049309823</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.812929632725175</v>
+        <v>-3.917744477338521</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.099692771906005</v>
+        <v>1.057766834060667</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.9195333175367673</v>
+        <v>0.9004432833222835</v>
       </c>
       <c r="G1974" t="n">
-        <v>3.176941039831883</v>
+        <v>3.165487019303193</v>
       </c>
     </row>
     <row r="1975">
@@ -46976,16 +46976,16 @@
         <v>2.623712667349751</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.763742984040824</v>
+        <v>-3.868557828654169</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.117859049419674</v>
+        <v>1.075933111574336</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.9195333175367673</v>
+        <v>0.9004432833222835</v>
       </c>
       <c r="G1975" t="n">
-        <v>3.175432657871812</v>
+        <v>3.163978637343122</v>
       </c>
     </row>
     <row r="1976">
@@ -46999,16 +46999,16 @@
         <v>2.623575534785187</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.719369852402255</v>
+        <v>-3.824184697015601</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.135471169510538</v>
+        <v>1.0935452316652</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.9639064491753359</v>
+        <v>0.9448164149608521</v>
       </c>
       <c r="G1976" t="n">
-        <v>3.201919404290389</v>
+        <v>3.190465383761699</v>
       </c>
     </row>
     <row r="1977">
@@ -47022,16 +47022,16 @@
         <v>2.617969328923778</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.74185020326114</v>
+        <v>-3.846665047874485</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.120872823305575</v>
+        <v>1.078946885460236</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.9639064491753359</v>
+        <v>0.9448164149608521</v>
       </c>
       <c r="G1977" t="n">
-        <v>3.19631319842898</v>
+        <v>3.184859177900289</v>
       </c>
     </row>
     <row r="1978">
@@ -47045,16 +47045,16 @@
         <v>2.624351085951583</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.694194472700085</v>
+        <v>-3.79900931731343</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.146316872557801</v>
+        <v>1.104390934712463</v>
       </c>
       <c r="F1978" t="n">
-        <v>1.011562179736392</v>
+        <v>0.9924721455219077</v>
       </c>
       <c r="G1978" t="n">
-        <v>3.231288393793418</v>
+        <v>3.219834373264727</v>
       </c>
     </row>
     <row r="1979">
@@ -47068,16 +47068,16 @@
         <v>2.629243459326307</v>
       </c>
       <c r="D1979" t="n">
-        <v>-3.59367631420133</v>
+        <v>-3.698491158814675</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.191416509332028</v>
+        <v>1.14949057148669</v>
       </c>
       <c r="F1979" t="n">
-        <v>1.112080338235146</v>
+        <v>1.092990304020662</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.296491662267395</v>
+        <v>3.285037641738705</v>
       </c>
     </row>
     <row r="1980">
@@ -47091,16 +47091,16 @@
         <v>2.61599813180218</v>
       </c>
       <c r="D1980" t="n">
-        <v>-3.577770984768978</v>
+        <v>-3.682585829382322</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.184533313580841</v>
+        <v>1.142607375735504</v>
       </c>
       <c r="F1980" t="n">
-        <v>1.032967677525907</v>
+        <v>1.013877643311423</v>
       </c>
       <c r="G1980" t="n">
-        <v>3.235778738317724</v>
+        <v>3.224324717789034</v>
       </c>
     </row>
     <row r="1981">
@@ -47114,16 +47114,16 @@
         <v>2.620095834412808</v>
       </c>
       <c r="D1981" t="n">
-        <v>-3.53293258316058</v>
+        <v>-3.637747427773924</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.206566376834829</v>
+        <v>1.164640438989491</v>
       </c>
       <c r="F1981" t="n">
-        <v>1.037511110470777</v>
+        <v>1.018421076256293</v>
       </c>
       <c r="G1981" t="n">
-        <v>3.242602500695274</v>
+        <v>3.231148480166584</v>
       </c>
     </row>
     <row r="1982">
@@ -47137,16 +47137,16 @@
         <v>2.624256774043886</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.552431039402588</v>
+        <v>-3.657245884015933</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.202927933969104</v>
+        <v>1.161001996123766</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.9894264691908725</v>
+        <v>0.9703364349763886</v>
       </c>
       <c r="G1982" t="n">
-        <v>3.21791265555841</v>
+        <v>3.20645863502972</v>
       </c>
     </row>
     <row r="1983">
@@ -47160,16 +47160,16 @@
         <v>2.630136376571723</v>
       </c>
       <c r="D1983" t="n">
-        <v>-3.508228202316687</v>
+        <v>-3.613043046930032</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.226488671331301</v>
+        <v>1.184562733485963</v>
       </c>
       <c r="F1983" t="n">
-        <v>1.033629306276773</v>
+        <v>1.014539272062289</v>
       </c>
       <c r="G1983" t="n">
-        <v>3.250313960337787</v>
+        <v>3.238859939809097</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265642</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
         <v>2.628546377040971</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.515787868153734</v>
+        <v>-3.620602712767079</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.22187480546573</v>
+        <v>1.179948867620392</v>
       </c>
       <c r="F1984" t="n">
-        <v>1.088432710286592</v>
+        <v>1.069342676072108</v>
       </c>
       <c r="G1984" t="n">
-        <v>3.281606003212926</v>
+        <v>3.270151982684236</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284877</v>
+        <v>3.863895080284876</v>
       </c>
       <c r="C1985" t="n">
         <v>2.679794142224011</v>
       </c>
       <c r="D1985" t="n">
-        <v>-3.357496450614462</v>
+        <v>-3.462311295227807</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.336439137664478</v>
+        <v>1.294513199819141</v>
       </c>
       <c r="F1985" t="n">
-        <v>1.088432710286592</v>
+        <v>1.069342676072108</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.332853768395966</v>
+        <v>3.321399747867276</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321021</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
         <v>2.678234846818264</v>
       </c>
       <c r="D1986" t="n">
-        <v>-3.149854446979986</v>
+        <v>-3.254669291593331</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.417936643712522</v>
+        <v>1.376010705867184</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.296074713921068</v>
+        <v>1.276984679706584</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.455879675170905</v>
+        <v>3.444425654642215</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475139</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
         <v>2.673183075056534</v>
       </c>
       <c r="D1987" t="n">
-        <v>-3.098822354257458</v>
+        <v>-3.203637198870803</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.433297709039803</v>
+        <v>1.391371771194466</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.347106806643596</v>
+        <v>1.328016772429113</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.481447159042692</v>
+        <v>3.469993138514002</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404853</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
         <v>2.690370479149239</v>
       </c>
       <c r="D1988" t="n">
-        <v>-3.033598173130252</v>
+        <v>-3.138413017743597</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.476574785583391</v>
+        <v>1.434648847738053</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.412330987770802</v>
+        <v>1.393240953556318</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.53776907181172</v>
+        <v>3.52631505128303</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882554</v>
       </c>
       <c r="C1989" t="n">
         <v>2.686331451448519</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.996171153059118</v>
+        <v>-3.100985997672463</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.487506565911125</v>
+        <v>1.445580628065787</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.417582525799984</v>
+        <v>1.3984924915855</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.53688096692851</v>
+        <v>3.525426946399819</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992661</v>
+        <v>3.84516980899266</v>
       </c>
       <c r="C1990" t="n">
         <v>2.687588243779759</v>
       </c>
       <c r="D1990" t="n">
-        <v>-3.016282809093827</v>
+        <v>-3.121097653707171</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.480718695828481</v>
+        <v>1.438792757983144</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.428609870797403</v>
+        <v>1.409519836582919</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.544754166258202</v>
+        <v>3.533300145729511</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636287</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
         <v>2.84814601480097</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.987869545993943</v>
+        <v>-3.092684390607288</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.652641772089646</v>
+        <v>1.610715834244308</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.369634308050974</v>
+        <v>1.35054427383649</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.669926599631555</v>
+        <v>3.658472579102864</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957626</v>
+        <v>3.813222820957625</v>
       </c>
       <c r="C1992" t="n">
         <v>2.968258924018787</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.91308728496893</v>
+        <v>-3.017902129582275</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.802667585717468</v>
+        <v>1.76074164787213</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.444416569075987</v>
+        <v>1.425326534861503</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.83490886546438</v>
+        <v>3.823454844935689</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998751</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
         <v>2.959966900032646</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.887003200705122</v>
+        <v>-2.991818045318467</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.80480919543685</v>
+        <v>1.762883257591512</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.444416569075987</v>
+        <v>1.425326534861503</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.826616841478239</v>
+        <v>3.815162820949548</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896925</v>
       </c>
       <c r="C1994" t="n">
         <v>2.958160095616426</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.799125287596002</v>
+        <v>-2.903940132209347</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.838153556264278</v>
+        <v>1.79622761841894</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.560342211499338</v>
+        <v>1.541252177284854</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.894365422516029</v>
+        <v>3.882911401987339</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.796264143959854</v>
       </c>
       <c r="C1995" t="n">
         <v>2.975714501343217</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.790232826202718</v>
+        <v>-2.895047670816063</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.859264946548383</v>
+        <v>1.817339008703045</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.560342211499338</v>
+        <v>1.541252177284854</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.91191982824282</v>
+        <v>3.90046580771413</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.794424941945363</v>
       </c>
       <c r="C1996" t="n">
         <v>2.967569548747801</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.958708943172596</v>
+        <v>-3.063523787785941</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.783729547165015</v>
+        <v>1.741803609319677</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.532394375782757</v>
+        <v>1.513304341568273</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.887006174217456</v>
+        <v>3.875552153688765</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.79557406678271</v>
+        <v>3.795574066782706</v>
       </c>
       <c r="C1997" t="n">
         <v>2.948839245935663</v>
       </c>
       <c r="D1997" t="n">
-        <v>-2.512452750543156</v>
+        <v>-2.617267595156501</v>
       </c>
       <c r="E1997" t="n">
-        <v>1.943501721404653</v>
+        <v>1.901575783559315</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.437675706113124</v>
+        <v>1.41858567189864</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.811444669603538</v>
+        <v>3.799990649074847</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632638</v>
+        <v>3.784671345632634</v>
       </c>
       <c r="C1998" t="n">
         <v>2.939503268432567</v>
       </c>
       <c r="D1998" t="n">
-        <v>-2.489731646860004</v>
+        <v>-2.594546491473348</v>
       </c>
       <c r="E1998" t="n">
-        <v>1.943254185374819</v>
+        <v>1.901328247529481</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.437675706113124</v>
+        <v>1.41858567189864</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.802108692100442</v>
+        <v>3.790654671571752</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777675</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
         <v>3.098409394283737</v>
       </c>
       <c r="D1999" t="n">
-        <v>-2.618933460154046</v>
+        <v>-2.723748304767391</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.050479585908371</v>
+        <v>2.008553648063033</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.308473892819082</v>
+        <v>1.289383858604598</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.883493729975186</v>
+        <v>3.872039709446496</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644415</v>
+        <v>3.779933725644412</v>
       </c>
       <c r="C2000" t="n">
         <v>3.135487216777383</v>
       </c>
       <c r="D2000" t="n">
-        <v>-2.644807858628072</v>
+        <v>-2.749622703241417</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.077207649012407</v>
+        <v>2.035281711167069</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.353385501530823</v>
+        <v>1.334295467316339</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.947518517695878</v>
+        <v>3.936064497167187</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799959</v>
       </c>
       <c r="C2001" t="n">
         <v>3.132162572766928</v>
       </c>
       <c r="D2001" t="n">
-        <v>-2.637753168412898</v>
+        <v>-2.742568013026243</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.076704881088022</v>
+        <v>2.034778943242684</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.360440191745997</v>
+        <v>1.341350157531513</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.948426687814527</v>
+        <v>3.936972667285836</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331117</v>
+        <v>3.766673496331112</v>
       </c>
       <c r="C2002" t="n">
         <v>3.14216872641167</v>
       </c>
       <c r="D2002" t="n">
-        <v>-2.61080194408641</v>
+        <v>-2.715616788699755</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.097491524463359</v>
+        <v>2.05556558661802</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.375320537773716</v>
+        <v>1.356230503559232</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.9673610490759</v>
+        <v>3.95590702854721</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784111</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
         <v>3.32627185855663</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.632346171917197</v>
+        <v>-2.737161016530542</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.272976965476003</v>
+        <v>2.231051027630666</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.375320537773716</v>
+        <v>1.356230503559232</v>
       </c>
       <c r="G2003" t="n">
-        <v>4.151464181220859</v>
+        <v>4.140010160692169</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714421</v>
       </c>
       <c r="C2004" t="n">
         <v>3.318388553459623</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.65475428972207</v>
+        <v>-2.759569134335414</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.256130413257048</v>
+        <v>2.21420447541171</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.375320537773716</v>
+        <v>1.356230503559232</v>
       </c>
       <c r="G2004" t="n">
-        <v>4.143580876123853</v>
+        <v>4.132126855595162</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155035</v>
+        <v>3.719118627155032</v>
       </c>
       <c r="C2005" t="n">
         <v>3.32044255300926</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.68297852529967</v>
+        <v>-2.787793369913015</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.246894718575645</v>
+        <v>2.204968780730307</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.393297290225025</v>
+        <v>1.374207256010541</v>
       </c>
       <c r="G2005" t="n">
-        <v>4.156420927144275</v>
+        <v>4.144966906615585</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161981</v>
+        <v>3.729452285161978</v>
       </c>
       <c r="C2006" t="n">
         <v>3.376696270731107</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.6924194511882</v>
+        <v>-2.797234295801545</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.29937206594208</v>
+        <v>2.257446128096742</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.515724407768416</v>
+        <v>1.496634373553932</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.286130915392158</v>
+        <v>4.274676894863467</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321638</v>
+        <v>3.714941193321635</v>
       </c>
       <c r="C2007" t="n">
         <v>3.379587365276408</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.781296082356674</v>
+        <v>-2.886110926970018</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.266712508019991</v>
+        <v>2.224786570174653</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.426847776599943</v>
+        <v>1.407757742385459</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.235696031236374</v>
+        <v>4.224242010707684</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347708</v>
+        <v>3.727898186347704</v>
       </c>
       <c r="C2008" t="n">
         <v>3.377699178170183</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.85762605995758</v>
+        <v>-2.962440904570924</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.234292329873404</v>
+        <v>2.192366392028066</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.426847776599943</v>
+        <v>1.407757742385459</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.233807844130149</v>
+        <v>4.222353823601459</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887753</v>
+        <v>3.71065410488775</v>
       </c>
       <c r="C2009" t="n">
         <v>3.372519407773046</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.951290004635121</v>
+        <v>-3.056104849248466</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.19164698160525</v>
+        <v>2.149721043759912</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.333183831922401</v>
+        <v>1.314093797707917</v>
       </c>
       <c r="G2009" t="n">
-        <v>4.172429706926486</v>
+        <v>4.160975686397796</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343071</v>
+        <v>3.712897612343068</v>
       </c>
       <c r="C2010" t="n">
         <v>3.370953417983198</v>
       </c>
       <c r="D2010" t="n">
-        <v>-3.112858430162376</v>
+        <v>-3.217673274775721</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.1254536216045</v>
+        <v>2.083527683759162</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.206400908124522</v>
+        <v>1.187310873910038</v>
       </c>
       <c r="G2010" t="n">
-        <v>4.094793962857911</v>
+        <v>4.08333994232922</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754596135389354</v>
+        <v>3.754596135389351</v>
       </c>
       <c r="C2011" t="n">
         <v>3.384026824849117</v>
       </c>
       <c r="D2011" t="n">
-        <v>-3.221159092032496</v>
+        <v>-3.32597393664584</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.095206763722371</v>
+        <v>2.053280825877033</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.206400908124522</v>
+        <v>1.187310873910038</v>
       </c>
       <c r="G2011" t="n">
-        <v>4.10786736972383</v>
+        <v>4.09641334919514</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749882691378391</v>
+        <v>3.749882691378388</v>
       </c>
       <c r="C2012" t="n">
         <v>3.376032021632057</v>
       </c>
       <c r="D2012" t="n">
-        <v>-3.23896306375324</v>
+        <v>-3.343777908366584</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.080090371817013</v>
+        <v>2.038164433971676</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.135866285219321</v>
+        <v>1.116776251004837</v>
       </c>
       <c r="G2012" t="n">
-        <v>4.05755179276365</v>
+        <v>4.046097772234959</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715819895006975</v>
+        <v>3.715819895006971</v>
       </c>
       <c r="C2013" t="n">
         <v>3.374556062759059</v>
       </c>
       <c r="D2013" t="n">
-        <v>-3.266863850862713</v>
+        <v>-3.371678695476057</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.067454098100226</v>
+        <v>2.025528160254888</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.101269361076386</v>
+        <v>1.082179326861902</v>
       </c>
       <c r="G2013" t="n">
-        <v>4.035317679404891</v>
+        <v>4.0238636588762</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684895778787388</v>
+        <v>3.684895778787384</v>
       </c>
       <c r="C2014" t="n">
         <v>3.371320506736257</v>
       </c>
       <c r="D2014" t="n">
-        <v>-3.389389953565606</v>
+        <v>-3.494204798178951</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.015208100996268</v>
+        <v>1.973282163150929</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.9787432583734921</v>
+        <v>0.9596532241590081</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.958566461760353</v>
+        <v>3.947112441231662</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619348081585938</v>
+        <v>3.619348081585934</v>
       </c>
       <c r="C2015" t="n">
         <v>3.438026466326761</v>
       </c>
       <c r="D2015" t="n">
-        <v>-3.619904449751195</v>
+        <v>-3.72471929436454</v>
       </c>
       <c r="E2015" t="n">
-        <v>1.989708262112535</v>
+        <v>1.947782324267198</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7482287621879034</v>
+        <v>0.7291387279734194</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.886963723639503</v>
+        <v>3.875509703110813</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640750087814666</v>
+        <v>3.640750087814663</v>
       </c>
       <c r="C2016" t="n">
         <v>3.578338185328608</v>
       </c>
       <c r="D2016" t="n">
-        <v>-3.968649534975639</v>
+        <v>-4.073464379588984</v>
       </c>
       <c r="E2016" t="n">
-        <v>1.990521947024605</v>
+        <v>1.948596009179267</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.6394808082690056</v>
+        <v>0.6203907740545216</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.962026670290012</v>
+        <v>3.950572649761321</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668289004237097</v>
+        <v>3.668289004237093</v>
       </c>
       <c r="C2017" t="n">
         <v>3.647318454474248</v>
       </c>
       <c r="D2017" t="n">
-        <v>-4.12263595275178</v>
+        <v>-4.227450797365124</v>
       </c>
       <c r="E2017" t="n">
-        <v>1.997907649059789</v>
+        <v>1.955981711214451</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.6394808082690056</v>
+        <v>0.6203907740545216</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.031006939435652</v>
+        <v>4.019552918906961</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619923016423391</v>
+        <v>3.619923016423386</v>
       </c>
       <c r="C2018" t="n">
         <v>3.633369656594369</v>
       </c>
       <c r="D2018" t="n">
-        <v>-4.072114048924114</v>
+        <v>-4.176928893537458</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.004167612710976</v>
+        <v>1.962241674865638</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.6394808082690056</v>
+        <v>0.6203907740545216</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.017058141555772</v>
+        <v>4.005604121027082</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656332733609759</v>
+        <v>3.656332733609752</v>
       </c>
       <c r="C2019" t="n">
         <v>3.645240145649783</v>
       </c>
       <c r="D2019" t="n">
-        <v>-4.324589202931838</v>
+        <v>-4.429404047545183</v>
       </c>
       <c r="E2019" t="n">
-        <v>1.9150480401633</v>
+        <v>1.873122102317962</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.6394808082690056</v>
+        <v>0.6203907740545216</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.028928630611186</v>
+        <v>4.017474610082496</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674028535973163</v>
+        <v>3.674028535973157</v>
       </c>
       <c r="C2020" t="n">
         <v>3.646450680168726</v>
       </c>
       <c r="D2020" t="n">
-        <v>-4.61748495941125</v>
+        <v>-4.722299804024595</v>
       </c>
       <c r="E2020" t="n">
-        <v>1.799100272090479</v>
+        <v>1.757174334245141</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.6394808082690056</v>
+        <v>0.6203907740545216</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.03013916513013</v>
+        <v>4.01868514460144</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66350945725195</v>
+        <v>3.663509457251946</v>
       </c>
       <c r="C2021" t="n">
         <v>3.650572422396048</v>
       </c>
       <c r="D2021" t="n">
-        <v>-4.804149087546058</v>
+        <v>-4.908963932159403</v>
       </c>
       <c r="E2021" t="n">
-        <v>1.728556363063877</v>
+        <v>1.686630425218539</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.6127418374444457</v>
+        <v>0.5936518032299617</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.018217524862716</v>
+        <v>4.006763504334026</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652149152916206</v>
+        <v>3.652149152916202</v>
       </c>
       <c r="C2022" t="n">
         <v>3.645650275132237</v>
       </c>
       <c r="D2022" t="n">
-        <v>-4.95016977446002</v>
+        <v>-5.054984619073365</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.665225941034482</v>
+        <v>1.623300003189144</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.6036587456505886</v>
+        <v>0.5845687114361047</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.007845522522591</v>
+        <v>3.996391501993901</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667962306830333</v>
+        <v>3.667962306830329</v>
       </c>
       <c r="C2023" t="n">
         <v>3.807854331831281</v>
       </c>
       <c r="D2023" t="n">
-        <v>-5.041883783569606</v>
+        <v>-5.14669862818295</v>
       </c>
       <c r="E2023" t="n">
-        <v>1.790744394089692</v>
+        <v>1.748818456244354</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.6036587456505886</v>
+        <v>0.5845687114361047</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.170049579221635</v>
+        <v>4.158595558692944</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696539468071555</v>
+        <v>3.696539468071552</v>
       </c>
       <c r="C2024" t="n">
         <v>3.802700969795096</v>
       </c>
       <c r="D2024" t="n">
-        <v>-5.073535442629575</v>
+        <v>-5.178350287242919</v>
       </c>
       <c r="E2024" t="n">
-        <v>1.772930368429518</v>
+        <v>1.731004430584181</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.5984902884061485</v>
+        <v>0.5794002541916645</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.161795142838785</v>
+        <v>4.150341122310095</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750044015868151</v>
+        <v>3.750044015868148</v>
       </c>
       <c r="C2025" t="n">
         <v>3.812930387363587</v>
       </c>
       <c r="D2025" t="n">
-        <v>-5.155470260898459</v>
+        <v>-5.260285105511803</v>
       </c>
       <c r="E2025" t="n">
-        <v>1.750385858690456</v>
+        <v>1.708459920845118</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.5885555428190683</v>
+        <v>0.5694655086045843</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.166063713055028</v>
+        <v>4.154609692526337</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783632867332695</v>
+        <v>3.783632867332692</v>
       </c>
       <c r="C2026" t="n">
         <v>3.821856025819489</v>
       </c>
       <c r="D2026" t="n">
-        <v>-5.257446383146866</v>
+        <v>-5.36226122776021</v>
       </c>
       <c r="E2026" t="n">
-        <v>1.718521048246995</v>
+        <v>1.676595110401658</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4865794205706607</v>
+        <v>0.4674893863561768</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.113803678161886</v>
+        <v>4.102349657633195</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798296784231812</v>
+        <v>3.798296784231809</v>
       </c>
       <c r="C2027" t="n">
         <v>3.814008913063665</v>
       </c>
       <c r="D2027" t="n">
-        <v>-5.147440099669645</v>
+        <v>-5.252254944282988</v>
       </c>
       <c r="E2027" t="n">
-        <v>1.754676448882059</v>
+        <v>1.712750511036722</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.5097839924879359</v>
+        <v>0.490693958273452</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.119879308556427</v>
+        <v>4.108425288027736</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785563924818521</v>
+        <v>3.785563924818518</v>
       </c>
       <c r="C2028" t="n">
         <v>3.818258923785639</v>
       </c>
       <c r="D2028" t="n">
-        <v>-5.004380523928718</v>
+        <v>-5.109195368542062</v>
       </c>
       <c r="E2028" t="n">
-        <v>1.816150289900404</v>
+        <v>1.774224352055067</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.5177974190779152</v>
+        <v>0.4987073848634312</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.128937375232388</v>
+        <v>4.117483354703698</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.777237412051788</v>
+        <v>3.777237412051784</v>
       </c>
       <c r="C2029" t="n">
         <v>3.825519806668175</v>
       </c>
       <c r="D2029" t="n">
-        <v>-4.702933798456881</v>
+        <v>-4.807748643070225</v>
       </c>
       <c r="E2029" t="n">
-        <v>1.943989862971675</v>
+        <v>1.902063925126338</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8192441445497525</v>
+        <v>0.8001541103352685</v>
       </c>
       <c r="G2029" t="n">
-        <v>4.317066293398026</v>
+        <v>4.305612272869336</v>
       </c>
     </row>
     <row r="2030">
@@ -48235,22 +48235,22 @@
         <v>45492</v>
       </c>
       <c r="B2030" t="n">
-        <v>3.812635940679625</v>
+        <v>3.812635940679622</v>
       </c>
       <c r="C2030" t="n">
         <v>3.826490984420885</v>
       </c>
       <c r="D2030" t="n">
-        <v>-4.727524042692065</v>
+        <v>-4.832338887305409</v>
       </c>
       <c r="E2030" t="n">
-        <v>1.935124943030312</v>
+        <v>1.893199005184975</v>
       </c>
       <c r="F2030" t="n">
-        <v>0.8192441445497525</v>
+        <v>0.8001541103352685</v>
       </c>
       <c r="G2030" t="n">
-        <v>4.318037471150737</v>
+        <v>4.306583450622047</v>
       </c>
     </row>
     <row r="2031">
@@ -48258,22 +48258,22 @@
         <v>45493</v>
       </c>
       <c r="B2031" t="n">
-        <v>3.821184182474162</v>
+        <v>3.821184182474157</v>
       </c>
       <c r="C2031" t="n">
-        <v>3.652071838888125</v>
+        <v>3.827333888800641</v>
       </c>
       <c r="D2031" t="n">
-        <v>-4.676485666685545</v>
+        <v>-4.781300511298888</v>
       </c>
       <c r="E2031" t="n">
-        <v>1.781121147900159</v>
+        <v>1.914457259967338</v>
       </c>
       <c r="F2031" t="n">
-        <v>0.8192441445497525</v>
+        <v>0.8001541103352685</v>
       </c>
       <c r="G2031" t="n">
-        <v>4.143618325617976</v>
+        <v>4.307426355001803</v>
       </c>
     </row>
     <row r="2032">
@@ -48281,22 +48281,22 @@
         <v>45494</v>
       </c>
       <c r="B2032" t="n">
-        <v>3.831734516969546</v>
+        <v>3.831734516969542</v>
       </c>
       <c r="C2032" t="n">
-        <v>3.67110993776227</v>
+        <v>3.846371987674786</v>
       </c>
       <c r="D2032" t="n">
-        <v>-4.635346371818914</v>
+        <v>-4.740161216432258</v>
       </c>
       <c r="E2032" t="n">
-        <v>1.816614964720957</v>
+        <v>1.949951076788136</v>
       </c>
       <c r="F2032" t="n">
-        <v>0.8603834394163833</v>
+        <v>0.8412934052018993</v>
       </c>
       <c r="G2032" t="n">
-        <v>4.1873400014121</v>
+        <v>4.351148030795926</v>
       </c>
     </row>
     <row r="2033">
@@ -48304,22 +48304,22 @@
         <v>45495</v>
       </c>
       <c r="B2033" t="n">
-        <v>3.825752932700482</v>
+        <v>3.825752932700478</v>
       </c>
       <c r="C2033" t="n">
-        <v>3.487293933886205</v>
+        <v>3.662555983798721</v>
       </c>
       <c r="D2033" t="n">
-        <v>-4.538711459800274</v>
+        <v>-4.643526304413617</v>
       </c>
       <c r="E2033" t="n">
-        <v>1.671452925652348</v>
+        <v>1.804789037719527</v>
       </c>
       <c r="F2033" t="n">
-        <v>0.9570183514350232</v>
+        <v>0.9379283172205393</v>
       </c>
       <c r="G2033" t="n">
-        <v>4.061504944747218</v>
+        <v>4.225312974131045</v>
       </c>
     </row>
     <row r="2034">
@@ -48327,22 +48327,22 @@
         <v>45496</v>
       </c>
       <c r="B2034" t="n">
-        <v>3.804688961077643</v>
+        <v>3.804688961077639</v>
       </c>
       <c r="C2034" t="n">
-        <v>3.490795977960168</v>
+        <v>3.666058027872685</v>
       </c>
       <c r="D2034" t="n">
-        <v>-4.669292194331116</v>
+        <v>-4.77410703894446</v>
       </c>
       <c r="E2034" t="n">
-        <v>1.622722675913975</v>
+        <v>1.756058787981154</v>
       </c>
       <c r="F2034" t="n">
-        <v>0.8264376169041807</v>
+        <v>0.8073475826896968</v>
       </c>
       <c r="G2034" t="n">
-        <v>3.986658548102677</v>
+        <v>4.150466577486504</v>
       </c>
     </row>
     <row r="2035">
@@ -48350,22 +48350,22 @@
         <v>45497</v>
       </c>
       <c r="B2035" t="n">
-        <v>3.775028860833461</v>
+        <v>3.775028860833458</v>
       </c>
       <c r="C2035" t="n">
-        <v>3.475222797036251</v>
+        <v>3.650484846948768</v>
       </c>
       <c r="D2035" t="n">
-        <v>-4.504795860140154</v>
+        <v>-4.609610704753498</v>
       </c>
       <c r="E2035" t="n">
-        <v>1.672948028666442</v>
+        <v>1.806284140733621</v>
       </c>
       <c r="F2035" t="n">
-        <v>0.9909339510951427</v>
+        <v>0.9718439168806586</v>
       </c>
       <c r="G2035" t="n">
-        <v>4.069783167693337</v>
+        <v>4.233591197077163</v>
       </c>
     </row>
     <row r="2036">
@@ -48373,22 +48373,22 @@
         <v>45498</v>
       </c>
       <c r="B2036" t="n">
-        <v>3.821030660077628</v>
+        <v>3.821030660077624</v>
       </c>
       <c r="C2036" t="n">
-        <v>3.474410507472681</v>
+        <v>3.649672557385197</v>
       </c>
       <c r="D2036" t="n">
-        <v>-4.427697258598282</v>
+        <v>-4.532512103211626</v>
       </c>
       <c r="E2036" t="n">
-        <v>1.702975179719621</v>
+        <v>1.8363112917868</v>
       </c>
       <c r="F2036" t="n">
-        <v>0.9909339510951427</v>
+        <v>0.9718439168806586</v>
       </c>
       <c r="G2036" t="n">
-        <v>4.068970878129766</v>
+        <v>4.232778907513593</v>
       </c>
     </row>
     <row r="2037">
@@ -48396,22 +48396,22 @@
         <v>45499</v>
       </c>
       <c r="B2037" t="n">
-        <v>3.832307024147914</v>
+        <v>3.832307024147908</v>
       </c>
       <c r="C2037" t="n">
-        <v>3.484279286597753</v>
+        <v>3.65954133651027</v>
       </c>
       <c r="D2037" t="n">
-        <v>-4.438082453488171</v>
+        <v>-4.542897298101515</v>
       </c>
       <c r="E2037" t="n">
-        <v>1.708689880888737</v>
+        <v>1.842025992955917</v>
       </c>
       <c r="F2037" t="n">
-        <v>0.9805487562052534</v>
+        <v>0.9614587219907693</v>
       </c>
       <c r="G2037" t="n">
-        <v>4.072608540320905</v>
+        <v>4.236416569704732</v>
       </c>
     </row>
     <row r="2038">
@@ -48419,22 +48419,22 @@
         <v>45500</v>
       </c>
       <c r="B2038" t="n">
-        <v>3.834415493735285</v>
+        <v>3.834415493735281</v>
       </c>
       <c r="C2038" t="n">
-        <v>3.555116292374178</v>
+        <v>3.730378342286695</v>
       </c>
       <c r="D2038" t="n">
-        <v>-4.456670612210396</v>
+        <v>-4.56148545682374</v>
       </c>
       <c r="E2038" t="n">
-        <v>1.772091623176272</v>
+        <v>1.905427735243452</v>
       </c>
       <c r="F2038" t="n">
-        <v>0.9619605974830281</v>
+        <v>0.9428705632685439</v>
       </c>
       <c r="G2038" t="n">
-        <v>4.132292650863995</v>
+        <v>4.296100680247822</v>
       </c>
     </row>
     <row r="2039">
@@ -48442,22 +48442,22 @@
         <v>45501</v>
       </c>
       <c r="B2039" t="n">
-        <v>3.855120535496558</v>
+        <v>3.855120535496551</v>
       </c>
       <c r="C2039" t="n">
-        <v>3.551985303192477</v>
+        <v>3.727247353104993</v>
       </c>
       <c r="D2039" t="n">
-        <v>-4.456969158906432</v>
+        <v>-4.561784003519776</v>
       </c>
       <c r="E2039" t="n">
-        <v>1.768841215316157</v>
+        <v>1.902177327383336</v>
       </c>
       <c r="F2039" t="n">
-        <v>0.9616620507869922</v>
+        <v>0.942572016572508</v>
       </c>
       <c r="G2039" t="n">
-        <v>4.128982533664672</v>
+        <v>4.292790563048499</v>
       </c>
     </row>
     <row r="2040">
@@ -48465,22 +48465,22 @@
         <v>45502</v>
       </c>
       <c r="B2040" t="n">
-        <v>3.815643212108861</v>
+        <v>3.815643212108856</v>
       </c>
       <c r="C2040" t="n">
-        <v>3.556516198131868</v>
+        <v>3.731778248044385</v>
       </c>
       <c r="D2040" t="n">
-        <v>-4.356146025216004</v>
+        <v>-4.460960869829348</v>
       </c>
       <c r="E2040" t="n">
-        <v>1.813701363731719</v>
+        <v>1.947037475798898</v>
       </c>
       <c r="F2040" t="n">
-        <v>0.974126266271346</v>
+        <v>0.9550362320568618</v>
       </c>
       <c r="G2040" t="n">
-        <v>4.140991957894676</v>
+        <v>4.304799987278503</v>
       </c>
     </row>
     <row r="2041">
@@ -48488,22 +48488,22 @@
         <v>45503</v>
       </c>
       <c r="B2041" t="n">
-        <v>3.807356168121472</v>
+        <v>3.807356168121467</v>
       </c>
       <c r="C2041" t="n">
-        <v>3.556645451610411</v>
+        <v>3.731907501522928</v>
       </c>
       <c r="D2041" t="n">
-        <v>-4.165364664463597</v>
+        <v>-4.270179509076941</v>
       </c>
       <c r="E2041" t="n">
-        <v>1.890143161511225</v>
+        <v>2.023479273578404</v>
       </c>
       <c r="F2041" t="n">
-        <v>1.164907627023753</v>
+        <v>1.145817592809269</v>
       </c>
       <c r="G2041" t="n">
-        <v>4.255590027824663</v>
+        <v>4.41939805720849</v>
       </c>
     </row>
     <row r="2042">
@@ -48511,22 +48511,22 @@
         <v>45504</v>
       </c>
       <c r="B2042" t="n">
-        <v>3.775233033906085</v>
+        <v>3.775233033906081</v>
       </c>
       <c r="C2042" t="n">
-        <v>3.536482297348008</v>
+        <v>3.711744347260525</v>
       </c>
       <c r="D2042" t="n">
-        <v>-4.058401306614176</v>
+        <v>-4.16321615122752</v>
       </c>
       <c r="E2042" t="n">
-        <v>1.91276535038859</v>
+        <v>2.04610146245577</v>
       </c>
       <c r="F2042" t="n">
-        <v>1.223372234983555</v>
+        <v>1.204282200769071</v>
       </c>
       <c r="G2042" t="n">
-        <v>4.270505638338141</v>
+        <v>4.434313667721968</v>
       </c>
     </row>
     <row r="2043">
@@ -48534,22 +48534,22 @@
         <v>45505</v>
       </c>
       <c r="B2043" t="n">
-        <v>3.785761685912989</v>
+        <v>3.785761685912985</v>
       </c>
       <c r="C2043" t="n">
-        <v>3.571449233960066</v>
+        <v>3.746711283872583</v>
       </c>
       <c r="D2043" t="n">
-        <v>-4.003070718712413</v>
+        <v>-4.107885563325757</v>
       </c>
       <c r="E2043" t="n">
-        <v>1.969864522161354</v>
+        <v>2.103200634228533</v>
       </c>
       <c r="F2043" t="n">
-        <v>1.278702822885317</v>
+        <v>1.259612788670833</v>
       </c>
       <c r="G2043" t="n">
-        <v>4.338670927691257</v>
+        <v>4.502478957075083</v>
       </c>
     </row>
     <row r="2044">
@@ -48557,22 +48557,22 @@
         <v>45506</v>
       </c>
       <c r="B2044" t="n">
-        <v>3.743767956539899</v>
+        <v>3.743767956539894</v>
       </c>
       <c r="C2044" t="n">
-        <v>3.565135801861504</v>
+        <v>3.740397851774021</v>
       </c>
       <c r="D2044" t="n">
-        <v>-3.99101659179945</v>
+        <v>-4.095831436412794</v>
       </c>
       <c r="E2044" t="n">
-        <v>1.968372740827976</v>
+        <v>2.101708852895156</v>
       </c>
       <c r="F2044" t="n">
-        <v>1.29075694979828</v>
+        <v>1.271666915583796</v>
       </c>
       <c r="G2044" t="n">
-        <v>4.339589971740472</v>
+        <v>4.503398001124299</v>
       </c>
     </row>
     <row r="2045">
@@ -48580,22 +48580,22 @@
         <v>45507</v>
       </c>
       <c r="B2045" t="n">
-        <v>3.725010844811014</v>
+        <v>3.72501084481101</v>
       </c>
       <c r="C2045" t="n">
-        <v>3.56701643204564</v>
+        <v>3.742278481958157</v>
       </c>
       <c r="D2045" t="n">
-        <v>-4.032171711367672</v>
+        <v>-4.136986555981015</v>
       </c>
       <c r="E2045" t="n">
-        <v>1.953791323184824</v>
+        <v>2.087127435252003</v>
       </c>
       <c r="F2045" t="n">
-        <v>1.249601830230059</v>
+        <v>1.230511796015575</v>
       </c>
       <c r="G2045" t="n">
-        <v>4.316777530183676</v>
+        <v>4.480585559567502</v>
       </c>
     </row>
     <row r="2046">
@@ -48603,22 +48603,22 @@
         <v>45508</v>
       </c>
       <c r="B2046" t="n">
-        <v>3.612322444382925</v>
+        <v>3.61232244438292</v>
       </c>
       <c r="C2046" t="n">
-        <v>3.579867457923522</v>
+        <v>3.755129507836039</v>
       </c>
       <c r="D2046" t="n">
-        <v>-3.964123148676142</v>
+        <v>-4.068937993289485</v>
       </c>
       <c r="E2046" t="n">
-        <v>1.993861774139318</v>
+        <v>2.127197886206498</v>
       </c>
       <c r="F2046" t="n">
-        <v>1.317650392921589</v>
+        <v>1.298560358707105</v>
       </c>
       <c r="G2046" t="n">
-        <v>4.370457693676475</v>
+        <v>4.534265723060302</v>
       </c>
     </row>
     <row r="2047">
@@ -48626,22 +48626,22 @@
         <v>45509</v>
       </c>
       <c r="B2047" t="n">
-        <v>3.645256780013432</v>
+        <v>3.645256780013428</v>
       </c>
       <c r="C2047" t="n">
-        <v>3.600070128097117</v>
+        <v>3.775332178009633</v>
       </c>
       <c r="D2047" t="n">
-        <v>-4.195723541845643</v>
+        <v>-4.300538386458986</v>
       </c>
       <c r="E2047" t="n">
-        <v>1.921424287045112</v>
+        <v>2.054760399112292</v>
       </c>
       <c r="F2047" t="n">
-        <v>1.317650392921589</v>
+        <v>1.298560358707105</v>
       </c>
       <c r="G2047" t="n">
-        <v>4.39066036385007</v>
+        <v>4.554468393233896</v>
       </c>
     </row>
     <row r="2048">
@@ -48649,22 +48649,22 @@
         <v>45510</v>
       </c>
       <c r="B2048" t="n">
-        <v>3.66674720149897</v>
+        <v>3.666747201498966</v>
       </c>
       <c r="C2048" t="n">
-        <v>3.583676364163999</v>
+        <v>3.758938414076515</v>
       </c>
       <c r="D2048" t="n">
-        <v>-4.245775087374863</v>
+        <v>-4.350589931988205</v>
       </c>
       <c r="E2048" t="n">
-        <v>1.885009904900306</v>
+        <v>2.018346016967486</v>
       </c>
       <c r="F2048" t="n">
-        <v>1.317650392921589</v>
+        <v>1.298560358707105</v>
       </c>
       <c r="G2048" t="n">
-        <v>4.374266599916952</v>
+        <v>4.538074629300779</v>
       </c>
     </row>
     <row r="2049">
@@ -48672,22 +48672,22 @@
         <v>45511</v>
       </c>
       <c r="B2049" t="n">
-        <v>3.670048702800099</v>
+        <v>3.670048702800095</v>
       </c>
       <c r="C2049" t="n">
-        <v>3.543928277757465</v>
+        <v>3.719190327669982</v>
       </c>
       <c r="D2049" t="n">
-        <v>-4.420881919951308</v>
+        <v>-4.52569676456465</v>
       </c>
       <c r="E2049" t="n">
-        <v>1.775219085463195</v>
+        <v>1.908555197530375</v>
       </c>
       <c r="F2049" t="n">
-        <v>1.317650392921589</v>
+        <v>1.298560358707105</v>
       </c>
       <c r="G2049" t="n">
-        <v>4.334518513510418</v>
+        <v>4.498326542894245</v>
       </c>
     </row>
     <row r="2050">
@@ -48695,22 +48695,22 @@
         <v>45512</v>
       </c>
       <c r="B2050" t="n">
-        <v>3.745573148660852</v>
+        <v>3.745573148660847</v>
       </c>
       <c r="C2050" t="n">
-        <v>3.550950896754405</v>
+        <v>3.726212946666922</v>
       </c>
       <c r="D2050" t="n">
-        <v>-4.224781766520785</v>
+        <v>-4.329596611134127</v>
       </c>
       <c r="E2050" t="n">
-        <v>1.860681765832344</v>
+        <v>1.994017877899524</v>
       </c>
       <c r="F2050" t="n">
-        <v>1.513750546352111</v>
+        <v>1.494660512137628</v>
       </c>
       <c r="G2050" t="n">
-        <v>4.459201224565672</v>
+        <v>4.623009253949498</v>
       </c>
     </row>
     <row r="2051">
@@ -48718,22 +48718,22 @@
         <v>45513</v>
       </c>
       <c r="B2051" t="n">
-        <v>3.730570473395089</v>
+        <v>3.730570473395084</v>
       </c>
       <c r="C2051" t="n">
-        <v>3.65012189632731</v>
+        <v>3.825383946239826</v>
       </c>
       <c r="D2051" t="n">
-        <v>-4.0717563744075</v>
+        <v>-4.176571219020842</v>
       </c>
       <c r="E2051" t="n">
-        <v>2.021062922250562</v>
+        <v>2.154399034317742</v>
       </c>
       <c r="F2051" t="n">
-        <v>1.666775938465396</v>
+        <v>1.647685904250912</v>
       </c>
       <c r="G2051" t="n">
-        <v>4.650187459406547</v>
+        <v>4.813995488790374</v>
       </c>
     </row>
     <row r="2052">
@@ -48741,22 +48741,22 @@
         <v>45514</v>
       </c>
       <c r="B2052" t="n">
-        <v>3.741278332791151</v>
+        <v>3.741278332791146</v>
       </c>
       <c r="C2052" t="n">
-        <v>3.837588121235602</v>
+        <v>4.012850171148119</v>
       </c>
       <c r="D2052" t="n">
-        <v>-4.100063688280771</v>
+        <v>-4.204878532894113</v>
       </c>
       <c r="E2052" t="n">
-        <v>2.197206221609547</v>
+        <v>2.330542333676727</v>
       </c>
       <c r="F2052" t="n">
-        <v>1.666775938465396</v>
+        <v>1.647685904250912</v>
       </c>
       <c r="G2052" t="n">
-        <v>4.83765368431484</v>
+        <v>5.001461713698666</v>
       </c>
     </row>
     <row r="2053">
@@ -48764,22 +48764,22 @@
         <v>45515</v>
       </c>
       <c r="B2053" t="n">
-        <v>3.699115615620437</v>
+        <v>3.699115615620432</v>
       </c>
       <c r="C2053" t="n">
-        <v>3.806991072589685</v>
+        <v>3.982253122502201</v>
       </c>
       <c r="D2053" t="n">
-        <v>-4.266656913394293</v>
+        <v>-4.371471758007635</v>
       </c>
       <c r="E2053" t="n">
-        <v>2.09997188291822</v>
+        <v>2.2333079949854</v>
       </c>
       <c r="F2053" t="n">
-        <v>1.500182713351873</v>
+        <v>1.481092679137389</v>
       </c>
       <c r="G2053" t="n">
-        <v>4.707100700600809</v>
+        <v>4.870908729984635</v>
       </c>
     </row>
     <row r="2054">
@@ -48787,22 +48787,22 @@
         <v>45516</v>
       </c>
       <c r="B2054" t="n">
-        <v>3.708182519285652</v>
+        <v>3.708182519285645</v>
       </c>
       <c r="C2054" t="n">
-        <v>3.810667475251403</v>
+        <v>3.985929525163919</v>
       </c>
       <c r="D2054" t="n">
-        <v>-4.243621120032727</v>
+        <v>-4.348435964646069</v>
       </c>
       <c r="E2054" t="n">
-        <v>2.112862602924565</v>
+        <v>2.246198714991744</v>
       </c>
       <c r="F2054" t="n">
-        <v>1.500182713351873</v>
+        <v>1.481092679137389</v>
       </c>
       <c r="G2054" t="n">
-        <v>4.710777103262527</v>
+        <v>4.874585132646352</v>
       </c>
     </row>
     <row r="2055">
@@ -48810,22 +48810,22 @@
         <v>45517</v>
       </c>
       <c r="B2055" t="n">
-        <v>3.740581401399474</v>
+        <v>3.740581401399467</v>
       </c>
       <c r="C2055" t="n">
-        <v>3.808285530374898</v>
+        <v>3.983547580287414</v>
       </c>
       <c r="D2055" t="n">
-        <v>-4.21437513957703</v>
+        <v>-4.319189984190372</v>
       </c>
       <c r="E2055" t="n">
-        <v>2.122179050230339</v>
+        <v>2.255515162297518</v>
       </c>
       <c r="F2055" t="n">
-        <v>1.500182713351873</v>
+        <v>1.481092679137389</v>
       </c>
       <c r="G2055" t="n">
-        <v>4.708395158386022</v>
+        <v>4.872203187769848</v>
       </c>
     </row>
     <row r="2056">
@@ -48833,22 +48833,22 @@
         <v>45518</v>
       </c>
       <c r="B2056" t="n">
-        <v>3.699404642256376</v>
+        <v>3.69940464225637</v>
       </c>
       <c r="C2056" t="n">
-        <v>3.805578769532533</v>
+        <v>3.980840819445049</v>
       </c>
       <c r="D2056" t="n">
-        <v>-4.321300687454881</v>
+        <v>-4.426115532068224</v>
       </c>
       <c r="E2056" t="n">
-        <v>2.076702070236833</v>
+        <v>2.210038182304013</v>
       </c>
       <c r="F2056" t="n">
-        <v>1.393257165474022</v>
+        <v>1.374167131259538</v>
       </c>
       <c r="G2056" t="n">
-        <v>4.641533068816946</v>
+        <v>4.805341098200772</v>
       </c>
     </row>
     <row r="2057">
@@ -48856,22 +48856,22 @@
         <v>45519</v>
       </c>
       <c r="B2057" t="n">
-        <v>3.689942600701007</v>
+        <v>3.689942600701001</v>
       </c>
       <c r="C2057" t="n">
-        <v>3.807007571675767</v>
+        <v>3.982269621588284</v>
       </c>
       <c r="D2057" t="n">
-        <v>-4.46631924596213</v>
+        <v>-4.571134090575472</v>
       </c>
       <c r="E2057" t="n">
-        <v>2.020123448977168</v>
+        <v>2.153459561044348</v>
       </c>
       <c r="F2057" t="n">
-        <v>1.248238606966773</v>
+        <v>1.229148572752289</v>
       </c>
       <c r="G2057" t="n">
-        <v>4.555950735855832</v>
+        <v>4.719758765239657</v>
       </c>
     </row>
     <row r="2058">
@@ -48879,22 +48879,22 @@
         <v>45520</v>
       </c>
       <c r="B2058" t="n">
-        <v>3.711852429687018</v>
+        <v>3.711852429687013</v>
       </c>
       <c r="C2058" t="n">
-        <v>3.90693881093352</v>
+        <v>4.082200860846037</v>
       </c>
       <c r="D2058" t="n">
-        <v>-4.584661011746848</v>
+        <v>-4.68947585636019</v>
       </c>
       <c r="E2058" t="n">
-        <v>2.072717981921034</v>
+        <v>2.206054093988214</v>
       </c>
       <c r="F2058" t="n">
-        <v>1.258924645529663</v>
+        <v>1.239834611315179</v>
       </c>
       <c r="G2058" t="n">
-        <v>4.662293598251319</v>
+        <v>4.826101627635144</v>
       </c>
     </row>
     <row r="2059">
@@ -48902,22 +48902,22 @@
         <v>45521</v>
       </c>
       <c r="B2059" t="n">
-        <v>3.714879051790808</v>
+        <v>3.714879051790803</v>
       </c>
       <c r="C2059" t="n">
-        <v>3.904724508059459</v>
+        <v>4.079986557971975</v>
       </c>
       <c r="D2059" t="n">
-        <v>-4.636071434067556</v>
+        <v>-4.740886278680898</v>
       </c>
       <c r="E2059" t="n">
-        <v>2.04993951011869</v>
+        <v>2.183275622185869</v>
       </c>
       <c r="F2059" t="n">
-        <v>1.258924645529663</v>
+        <v>1.239834611315179</v>
       </c>
       <c r="G2059" t="n">
-        <v>4.660079295377257</v>
+        <v>4.823887324761083</v>
       </c>
     </row>
     <row r="2060">
@@ -48925,22 +48925,22 @@
         <v>45522</v>
       </c>
       <c r="B2060" t="n">
-        <v>3.704757949437336</v>
+        <v>3.704757949437331</v>
       </c>
       <c r="C2060" t="n">
-        <v>3.904627636133748</v>
+        <v>4.079889686046265</v>
       </c>
       <c r="D2060" t="n">
-        <v>-4.715490885275307</v>
+        <v>-4.820305729888649</v>
       </c>
       <c r="E2060" t="n">
-        <v>2.018074857709878</v>
+        <v>2.151410969777058</v>
       </c>
       <c r="F2060" t="n">
-        <v>1.258924645529663</v>
+        <v>1.239834611315179</v>
       </c>
       <c r="G2060" t="n">
-        <v>4.659982423451547</v>
+        <v>4.823790452835373</v>
       </c>
     </row>
     <row r="2061">
@@ -48948,22 +48948,22 @@
         <v>45523</v>
       </c>
       <c r="B2061" t="n">
-        <v>3.736804952298403</v>
+        <v>3.736804952298399</v>
       </c>
       <c r="C2061" t="n">
-        <v>3.904621529691791</v>
+        <v>4.079883579604308</v>
       </c>
       <c r="D2061" t="n">
-        <v>-4.810953883192525</v>
+        <v>-4.915768727805867</v>
       </c>
       <c r="E2061" t="n">
-        <v>1.979883552101034</v>
+        <v>2.113219664168214</v>
       </c>
       <c r="F2061" t="n">
-        <v>1.258924645529663</v>
+        <v>1.239834611315179</v>
       </c>
       <c r="G2061" t="n">
-        <v>4.65997631700959</v>
+        <v>4.823784346393416</v>
       </c>
     </row>
     <row r="2062">
@@ -48971,22 +48971,22 @@
         <v>45524</v>
       </c>
       <c r="B2062" t="n">
-        <v>3.715372960218006</v>
+        <v>3.715372960218001</v>
       </c>
       <c r="C2062" t="n">
-        <v>3.902717926254402</v>
+        <v>4.077979976166919</v>
       </c>
       <c r="D2062" t="n">
-        <v>-4.74657797234181</v>
+        <v>-4.851392816955152</v>
       </c>
       <c r="E2062" t="n">
-        <v>2.003730313003931</v>
+        <v>2.137066425071111</v>
       </c>
       <c r="F2062" t="n">
-        <v>1.323300556380379</v>
+        <v>1.304210522165895</v>
       </c>
       <c r="G2062" t="n">
-        <v>4.69669826008263</v>
+        <v>4.860506289466456</v>
       </c>
     </row>
     <row r="2063">
@@ -48994,22 +48994,22 @@
         <v>45525</v>
       </c>
       <c r="B2063" t="n">
-        <v>3.736089413353541</v>
+        <v>3.736089413353537</v>
       </c>
       <c r="C2063" t="n">
-        <v>3.908451744002129</v>
+        <v>4.083713793914646</v>
       </c>
       <c r="D2063" t="n">
-        <v>-4.801947134474004</v>
+        <v>-4.906761979087346</v>
       </c>
       <c r="E2063" t="n">
-        <v>1.98731646589878</v>
+        <v>2.12065257796596</v>
       </c>
       <c r="F2063" t="n">
-        <v>1.323300556380379</v>
+        <v>1.304210522165895</v>
       </c>
       <c r="G2063" t="n">
-        <v>4.702432077830356</v>
+        <v>4.866240107214183</v>
       </c>
     </row>
     <row r="2064">
@@ -49017,22 +49017,22 @@
         <v>45526</v>
       </c>
       <c r="B2064" t="n">
-        <v>3.736822870113285</v>
+        <v>3.73682287011328</v>
       </c>
       <c r="C2064" t="n">
-        <v>3.907990107345061</v>
+        <v>4.083252157257578</v>
       </c>
       <c r="D2064" t="n">
-        <v>-4.847384914304831</v>
+        <v>-4.952199758918173</v>
       </c>
       <c r="E2064" t="n">
-        <v>1.968679717309382</v>
+        <v>2.102015829376561</v>
       </c>
       <c r="F2064" t="n">
-        <v>1.280455565702219</v>
+        <v>1.261365531487735</v>
       </c>
       <c r="G2064" t="n">
-        <v>4.676263446766392</v>
+        <v>4.840071476150219</v>
       </c>
     </row>
     <row r="2065">
@@ -49040,22 +49040,22 @@
         <v>45527</v>
       </c>
       <c r="B2065" t="n">
-        <v>3.790272500113693</v>
+        <v>3.790272500113689</v>
       </c>
       <c r="C2065" t="n">
-        <v>3.92786450019538</v>
+        <v>4.103126550107897</v>
       </c>
       <c r="D2065" t="n">
-        <v>-4.759178080157253</v>
+        <v>-4.863992924770595</v>
       </c>
       <c r="E2065" t="n">
-        <v>2.023836843818732</v>
+        <v>2.157172955885911</v>
       </c>
       <c r="F2065" t="n">
-        <v>1.280455565702219</v>
+        <v>1.261365531487735</v>
       </c>
       <c r="G2065" t="n">
-        <v>4.696137839616711</v>
+        <v>4.859945869000538</v>
       </c>
     </row>
     <row r="2066">
@@ -49063,22 +49063,22 @@
         <v>45528</v>
       </c>
       <c r="B2066" t="n">
-        <v>3.794486844016441</v>
+        <v>3.794486844016436</v>
       </c>
       <c r="C2066" t="n">
-        <v>3.911565200720108</v>
+        <v>4.086827250632624</v>
       </c>
       <c r="D2066" t="n">
-        <v>-4.653143084951943</v>
+        <v>-4.757957929565285</v>
       </c>
       <c r="E2066" t="n">
-        <v>2.049951542425583</v>
+        <v>2.183287654492763</v>
       </c>
       <c r="F2066" t="n">
-        <v>1.280455565702219</v>
+        <v>1.261365531487735</v>
       </c>
       <c r="G2066" t="n">
-        <v>4.679838540141439</v>
+        <v>4.843646569525266</v>
       </c>
     </row>
     <row r="2067">
@@ -49086,22 +49086,22 @@
         <v>45529</v>
       </c>
       <c r="B2067" t="n">
-        <v>3.794705093307672</v>
+        <v>3.794705093307668</v>
       </c>
       <c r="C2067" t="n">
-        <v>3.913996150184154</v>
+        <v>4.08925820009667</v>
       </c>
       <c r="D2067" t="n">
-        <v>-4.469931421818848</v>
+        <v>-4.57474626643219</v>
       </c>
       <c r="E2067" t="n">
-        <v>2.125667157142867</v>
+        <v>2.259003269210047</v>
       </c>
       <c r="F2067" t="n">
-        <v>1.280455565702219</v>
+        <v>1.261365531487735</v>
       </c>
       <c r="G2067" t="n">
-        <v>4.682269489605485</v>
+        <v>4.846077518989311</v>
       </c>
     </row>
     <row r="2068">
@@ -49109,22 +49109,22 @@
         <v>45530</v>
       </c>
       <c r="B2068" t="n">
-        <v>3.776846557863553</v>
+        <v>3.776846557863549</v>
       </c>
       <c r="C2068" t="n">
-        <v>3.879787336032043</v>
+        <v>4.055049385944559</v>
       </c>
       <c r="D2068" t="n">
-        <v>-4.398209974804997</v>
+        <v>-4.503024819418339</v>
       </c>
       <c r="E2068" t="n">
-        <v>2.120146921796297</v>
+        <v>2.253483033863477</v>
       </c>
       <c r="F2068" t="n">
-        <v>1.35217701271607</v>
+        <v>1.333086978501586</v>
       </c>
       <c r="G2068" t="n">
-        <v>4.691093543661686</v>
+        <v>4.854901573045511</v>
       </c>
     </row>
     <row r="2069">
@@ -49132,22 +49132,22 @@
         <v>45531</v>
       </c>
       <c r="B2069" t="n">
-        <v>3.723789705394116</v>
+        <v>3.723789705394112</v>
       </c>
       <c r="C2069" t="n">
-        <v>3.826703081953215</v>
+        <v>4.001965131865731</v>
       </c>
       <c r="D2069" t="n">
-        <v>-4.375836949197291</v>
+        <v>-4.480651793810633</v>
       </c>
       <c r="E2069" t="n">
-        <v>2.076011877960552</v>
+        <v>2.20934799002773</v>
       </c>
       <c r="F2069" t="n">
-        <v>1.363432763828971</v>
+        <v>1.344342729614487</v>
       </c>
       <c r="G2069" t="n">
-        <v>4.644762740250598</v>
+        <v>4.808570769634423</v>
       </c>
     </row>
     <row r="2070">
@@ -49155,22 +49155,22 @@
         <v>45532</v>
       </c>
       <c r="B2070" t="n">
-        <v>3.715607446456734</v>
+        <v>3.715607446456731</v>
       </c>
       <c r="C2070" t="n">
-        <v>4.011901286838571</v>
+        <v>4.187163336751087</v>
       </c>
       <c r="D2070" t="n">
-        <v>-4.408853245108036</v>
+        <v>-4.513668089721378</v>
       </c>
       <c r="E2070" t="n">
-        <v>2.248003564481609</v>
+        <v>2.381339676548788</v>
       </c>
       <c r="F2070" t="n">
-        <v>1.29399538716222</v>
+        <v>1.274905352947736</v>
       </c>
       <c r="G2070" t="n">
-        <v>4.788298519135902</v>
+        <v>4.952106548519728</v>
       </c>
     </row>
     <row r="2071">
@@ -49178,22 +49178,22 @@
         <v>45533</v>
       </c>
       <c r="B2071" t="n">
-        <v>3.713762536883681</v>
+        <v>3.713762536883677</v>
       </c>
       <c r="C2071" t="n">
-        <v>4.00382251266682</v>
+        <v>4.179084562579336</v>
       </c>
       <c r="D2071" t="n">
-        <v>-4.397325609458427</v>
+        <v>-4.502140454071769</v>
       </c>
       <c r="E2071" t="n">
-        <v>2.244535844569701</v>
+        <v>2.377871956636881</v>
       </c>
       <c r="F2071" t="n">
-        <v>1.352996045363582</v>
+        <v>1.333906011149098</v>
       </c>
       <c r="G2071" t="n">
-        <v>4.815620139884969</v>
+        <v>4.979428169268795</v>
       </c>
     </row>
     <row r="2072">
@@ -49201,22 +49201,22 @@
         <v>45534</v>
       </c>
       <c r="B2072" t="n">
-        <v>3.717150699236303</v>
+        <v>3.717150699236299</v>
       </c>
       <c r="C2072" t="n">
-        <v>4.007490625188608</v>
+        <v>4.182752675101124</v>
       </c>
       <c r="D2072" t="n">
-        <v>-4.494667110800796</v>
+        <v>-4.599481955414138</v>
       </c>
       <c r="E2072" t="n">
-        <v>2.209267356554543</v>
+        <v>2.342603468621721</v>
       </c>
       <c r="F2072" t="n">
-        <v>1.308575863198094</v>
+        <v>1.28948582898361</v>
       </c>
       <c r="G2072" t="n">
-        <v>4.792636143107464</v>
+        <v>4.95644417249129</v>
       </c>
     </row>
     <row r="2073">
@@ -49224,22 +49224,22 @@
         <v>45535</v>
       </c>
       <c r="B2073" t="n">
-        <v>3.705201079427689</v>
+        <v>3.705201079427686</v>
       </c>
       <c r="C2073" t="n">
-        <v>4.008741707381446</v>
+        <v>4.184003757293962</v>
       </c>
       <c r="D2073" t="n">
-        <v>-4.580523140140762</v>
+        <v>-4.685337984754105</v>
       </c>
       <c r="E2073" t="n">
-        <v>2.176176027011394</v>
+        <v>2.309512139078573</v>
       </c>
       <c r="F2073" t="n">
-        <v>1.266199793971959</v>
+        <v>1.247109759757475</v>
       </c>
       <c r="G2073" t="n">
-        <v>4.768461583764622</v>
+        <v>4.932269613148447</v>
       </c>
     </row>
     <row r="2074">
@@ -49247,22 +49247,22 @@
         <v>45536</v>
       </c>
       <c r="B2074" t="n">
-        <v>3.691835499610383</v>
+        <v>3.691835499610379</v>
       </c>
       <c r="C2074" t="n">
-        <v>3.991160909201948</v>
+        <v>4.166422959114464</v>
       </c>
       <c r="D2074" t="n">
-        <v>-4.589359937556882</v>
+        <v>-4.694174782170224</v>
       </c>
       <c r="E2074" t="n">
-        <v>2.155060509865448</v>
+        <v>2.288396621932627</v>
       </c>
       <c r="F2074" t="n">
-        <v>1.258757621330608</v>
+        <v>1.239667587116124</v>
       </c>
       <c r="G2074" t="n">
-        <v>4.746415482000313</v>
+        <v>4.910223511384139</v>
       </c>
     </row>
     <row r="2075">
@@ -49270,22 +49270,22 @@
         <v>45537</v>
       </c>
       <c r="B2075" t="n">
-        <v>3.71554441166746</v>
+        <v>3.715544411667456</v>
       </c>
       <c r="C2075" t="n">
-        <v>4.001325420246998</v>
+        <v>4.176587470159514</v>
       </c>
       <c r="D2075" t="n">
-        <v>-4.68074250012234</v>
+        <v>-4.785557344735683</v>
       </c>
       <c r="E2075" t="n">
-        <v>2.128671995884314</v>
+        <v>2.262008107951493</v>
       </c>
       <c r="F2075" t="n">
-        <v>1.16737505876515</v>
+        <v>1.148285024550666</v>
       </c>
       <c r="G2075" t="n">
-        <v>4.701750455506088</v>
+        <v>4.865558484889913</v>
       </c>
     </row>
     <row r="2076">
@@ -49293,22 +49293,22 @@
         <v>45538</v>
       </c>
       <c r="B2076" t="n">
-        <v>3.673978374889196</v>
+        <v>3.673978374889193</v>
       </c>
       <c r="C2076" t="n">
-        <v>4.103453678071265</v>
+        <v>4.278715727983782</v>
       </c>
       <c r="D2076" t="n">
-        <v>-4.669035782135334</v>
+        <v>-4.773850626748676</v>
       </c>
       <c r="E2076" t="n">
-        <v>2.235482940903384</v>
+        <v>2.368819052970564</v>
       </c>
       <c r="F2076" t="n">
-        <v>1.179081776752156</v>
+        <v>1.159991742537672</v>
       </c>
       <c r="G2076" t="n">
-        <v>4.810902744122559</v>
+        <v>4.974710773506385</v>
       </c>
     </row>
     <row r="2077">
@@ -49316,22 +49316,22 @@
         <v>45539</v>
       </c>
       <c r="B2077" t="n">
-        <v>3.682476099409572</v>
+        <v>3.682476099409568</v>
       </c>
       <c r="C2077" t="n">
-        <v>4.10648601680267</v>
+        <v>4.281748066715187</v>
       </c>
       <c r="D2077" t="n">
-        <v>-4.569372278051672</v>
+        <v>-4.674187122665014</v>
       </c>
       <c r="E2077" t="n">
-        <v>2.278380681268254</v>
+        <v>2.411716793335434</v>
       </c>
       <c r="F2077" t="n">
-        <v>1.242268859955842</v>
+        <v>1.223178825741358</v>
       </c>
       <c r="G2077" t="n">
-        <v>4.851847332776176</v>
+        <v>5.015655362160002</v>
       </c>
     </row>
     <row r="2078">
@@ -49339,22 +49339,22 @@
         <v>45540</v>
       </c>
       <c r="B2078" t="n">
-        <v>3.672895177452576</v>
+        <v>3.672895177452571</v>
       </c>
       <c r="C2078" t="n">
-        <v>4.319390850080728</v>
+        <v>4.494652899993245</v>
       </c>
       <c r="D2078" t="n">
-        <v>-4.579688376218024</v>
+        <v>-4.684503220831366</v>
       </c>
       <c r="E2078" t="n">
-        <v>2.487159075279771</v>
+        <v>2.620495187346951</v>
       </c>
       <c r="F2078" t="n">
-        <v>1.242268859955842</v>
+        <v>1.223178825741358</v>
       </c>
       <c r="G2078" t="n">
-        <v>5.064752166054234</v>
+        <v>5.22856019543806</v>
       </c>
     </row>
     <row r="2079">
@@ -49362,22 +49362,22 @@
         <v>45541</v>
       </c>
       <c r="B2079" t="n">
-        <v>3.623960959762293</v>
+        <v>3.623960959762289</v>
       </c>
       <c r="C2079" t="n">
-        <v>4.318569516992818</v>
+        <v>4.493831566905334</v>
       </c>
       <c r="D2079" t="n">
-        <v>-4.579594408200651</v>
+        <v>-4.684409252813993</v>
       </c>
       <c r="E2079" t="n">
-        <v>2.48637532939881</v>
+        <v>2.61971144146599</v>
       </c>
       <c r="F2079" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2079" t="n">
-        <v>5.064152749774714</v>
+        <v>5.227960779158541</v>
       </c>
     </row>
     <row r="2080">
@@ -49385,22 +49385,22 @@
         <v>45542</v>
       </c>
       <c r="B2080" t="n">
-        <v>3.633213467988024</v>
+        <v>3.63321346798802</v>
       </c>
       <c r="C2080" t="n">
-        <v>4.312801502937171</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2080" t="n">
-        <v>-4.586813232400496</v>
+        <v>-4.691628077013838</v>
       </c>
       <c r="E2080" t="n">
-        <v>2.477719785663226</v>
+        <v>2.611055897730406</v>
       </c>
       <c r="F2080" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2080" t="n">
-        <v>5.058384735719068</v>
+        <v>5.222192765102895</v>
       </c>
     </row>
     <row r="2081">
@@ -49408,22 +49408,22 @@
         <v>45543</v>
       </c>
       <c r="B2081" t="n">
-        <v>3.647907242740922</v>
+        <v>3.647907242740919</v>
       </c>
       <c r="C2081" t="n">
-        <v>4.312801502937171</v>
+        <v>4.488063552849688</v>
       </c>
       <c r="D2081" t="n">
-        <v>-4.585864809282457</v>
+        <v>-4.690679653895799</v>
       </c>
       <c r="E2081" t="n">
-        <v>2.478099154910441</v>
+        <v>2.611435266977622</v>
       </c>
       <c r="F2081" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2081" t="n">
-        <v>5.058384735719068</v>
+        <v>5.222192765102895</v>
       </c>
     </row>
     <row r="2082">
@@ -49431,22 +49431,22 @@
         <v>45544</v>
       </c>
       <c r="B2082" t="n">
-        <v>3.881065366663625</v>
+        <v>3.881065366663622</v>
       </c>
       <c r="C2082" t="n">
-        <v>4.325529110918263</v>
+        <v>4.50079116083078</v>
       </c>
       <c r="D2082" t="n">
-        <v>-4.742933267538081</v>
+        <v>-4.847748112151423</v>
       </c>
       <c r="E2082" t="n">
-        <v>2.427999379589283</v>
+        <v>2.561335491656464</v>
       </c>
       <c r="F2082" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2082" t="n">
-        <v>5.07111234370016</v>
+        <v>5.234920373083987</v>
       </c>
     </row>
     <row r="2083">
@@ -49454,22 +49454,22 @@
         <v>45545</v>
       </c>
       <c r="B2083" t="n">
-        <v>3.717071158424769</v>
+        <v>3.717071158424766</v>
       </c>
       <c r="C2083" t="n">
-        <v>4.327475109342651</v>
+        <v>4.502737159255168</v>
       </c>
       <c r="D2083" t="n">
-        <v>-4.73694102074927</v>
+        <v>-4.841755865362612</v>
       </c>
       <c r="E2083" t="n">
-        <v>2.432342276729196</v>
+        <v>2.565678388796376</v>
       </c>
       <c r="F2083" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2083" t="n">
-        <v>5.073058342124548</v>
+        <v>5.236866371508374</v>
       </c>
     </row>
     <row r="2084">
@@ -49477,22 +49477,22 @@
         <v>45546</v>
       </c>
       <c r="B2084" t="n">
-        <v>3.741942347149218</v>
+        <v>3.741942347149214</v>
       </c>
       <c r="C2084" t="n">
-        <v>4.32112924536042</v>
+        <v>4.496391295272937</v>
       </c>
       <c r="D2084" t="n">
-        <v>-4.648383059618502</v>
+        <v>-4.753197904231844</v>
       </c>
       <c r="E2084" t="n">
-        <v>2.461419597199272</v>
+        <v>2.594755709266452</v>
       </c>
       <c r="F2084" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2084" t="n">
-        <v>5.066712478142317</v>
+        <v>5.230520507526143</v>
       </c>
     </row>
     <row r="2085">
@@ -49500,22 +49500,22 @@
         <v>45547</v>
       </c>
       <c r="B2085" t="n">
-        <v>3.735300721383092</v>
+        <v>3.735300721383088</v>
       </c>
       <c r="C2085" t="n">
-        <v>4.320437922799416</v>
+        <v>4.495699972711932</v>
       </c>
       <c r="D2085" t="n">
-        <v>-4.710414428845689</v>
+        <v>-4.73543882672877</v>
       </c>
       <c r="E2085" t="n">
-        <v>2.435915726947393</v>
+        <v>2.601168017706677</v>
       </c>
       <c r="F2085" t="n">
-        <v>1.24263872130316</v>
+        <v>1.223548687088676</v>
       </c>
       <c r="G2085" t="n">
-        <v>5.066021155581312</v>
+        <v>5.229829184965139</v>
       </c>
     </row>
     <row r="2086">
@@ -49523,22 +49523,22 @@
         <v>45548</v>
       </c>
       <c r="B2086" t="n">
-        <v>3.425021889512868</v>
+        <v>3.725892978717522</v>
       </c>
       <c r="C2086" t="n">
-        <v>4.542568320241119</v>
+        <v>4.547881931456991</v>
       </c>
       <c r="D2086" t="n">
-        <v>-4.492859487133471</v>
+        <v>-4.686747722018088</v>
       </c>
       <c r="E2086" t="n">
-        <v>2.745068101073983</v>
+        <v>2.672826418336009</v>
       </c>
       <c r="F2086" t="n">
-        <v>1.24263872130316</v>
+        <v>1.272239791799359</v>
       </c>
       <c r="G2086" t="n">
-        <v>5.288151553023016</v>
+        <v>5.311225806536607</v>
       </c>
     </row>
   </sheetData>
